--- a/output_transmittal_register.xlsx
+++ b/output_transmittal_register.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 13/06/2026 05:28</t>
+          <t>Generated: 13/06/2026 05:35</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,11 @@
           <t>Shop Drawing Submisison - Stretch-04.2 Viaduct Structure Foundation-Pier Shop Drawing &amp; BBS-PM-100, BBS-PM-101, BBS-PM-102 and Setting Out Pocket Track PM-100 to PM-102: MLCC-S0681-CIV-VBR-PIR-DRW-13000 to 13002 and 13015_Rev C01</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -883,7 +887,7 @@
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
       <c r="Y9" s="5" t="n">
-        <v>46186.22807304923</v>
+        <v>46186.23290197642</v>
       </c>
       <c r="Z9" s="4" t="inlineStr"/>
     </row>
@@ -951,7 +955,7 @@
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr"/>
       <c r="Y10" s="5" t="n">
-        <v>46186.22807304996</v>
+        <v>46186.23290197708</v>
       </c>
       <c r="Z10" s="4" t="inlineStr"/>
     </row>
@@ -1023,7 +1027,7 @@
       <c r="W11" s="8" t="inlineStr"/>
       <c r="X11" s="8" t="inlineStr"/>
       <c r="Y11" s="9" t="n">
-        <v>46186.22807305047</v>
+        <v>46186.23290197818</v>
       </c>
       <c r="Z11" s="8" t="inlineStr"/>
     </row>
@@ -1095,7 +1099,7 @@
       <c r="W12" s="8" t="inlineStr"/>
       <c r="X12" s="8" t="inlineStr"/>
       <c r="Y12" s="9" t="n">
-        <v>46186.22807305097</v>
+        <v>46186.23290197906</v>
       </c>
       <c r="Z12" s="8" t="inlineStr"/>
     </row>
@@ -1167,7 +1171,7 @@
       <c r="W13" s="8" t="inlineStr"/>
       <c r="X13" s="8" t="inlineStr"/>
       <c r="Y13" s="9" t="n">
-        <v>46186.22807305161</v>
+        <v>46186.23290197951</v>
       </c>
       <c r="Z13" s="8" t="inlineStr"/>
     </row>
@@ -1239,7 +1243,7 @@
       <c r="W14" s="8" t="inlineStr"/>
       <c r="X14" s="8" t="inlineStr"/>
       <c r="Y14" s="9" t="n">
-        <v>46186.22807305309</v>
+        <v>46186.23290198026</v>
       </c>
       <c r="Z14" s="8" t="inlineStr"/>
     </row>
@@ -1307,7 +1311,7 @@
       <c r="W15" s="8" t="inlineStr"/>
       <c r="X15" s="8" t="inlineStr"/>
       <c r="Y15" s="9" t="n">
-        <v>46186.22807305522</v>
+        <v>46186.23290198193</v>
       </c>
       <c r="Z15" s="8" t="inlineStr"/>
     </row>
@@ -1375,7 +1379,7 @@
       <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="5" t="n">
-        <v>46186.22807305573</v>
+        <v>46186.23290198237</v>
       </c>
       <c r="Z16" s="4" t="inlineStr"/>
     </row>
@@ -1443,7 +1447,7 @@
       <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="5" t="n">
-        <v>46186.22807305603</v>
+        <v>46186.23290198264</v>
       </c>
       <c r="Z17" s="4" t="inlineStr"/>
     </row>
@@ -1511,7 +1515,7 @@
       <c r="W18" s="4" t="inlineStr"/>
       <c r="X18" s="4" t="inlineStr"/>
       <c r="Y18" s="5" t="n">
-        <v>46186.22807305631</v>
+        <v>46186.2329019829</v>
       </c>
       <c r="Z18" s="4" t="inlineStr"/>
     </row>
@@ -1579,7 +1583,7 @@
       <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="5" t="n">
-        <v>46186.22807305692</v>
+        <v>46186.23290198314</v>
       </c>
       <c r="Z19" s="4" t="inlineStr"/>
     </row>
@@ -1647,7 +1651,7 @@
       <c r="W20" s="8" t="inlineStr"/>
       <c r="X20" s="8" t="inlineStr"/>
       <c r="Y20" s="9" t="n">
-        <v>46186.22807305728</v>
+        <v>46186.23290198341</v>
       </c>
       <c r="Z20" s="8" t="inlineStr"/>
     </row>
@@ -1715,7 +1719,7 @@
       <c r="W21" s="8" t="inlineStr"/>
       <c r="X21" s="8" t="inlineStr"/>
       <c r="Y21" s="9" t="n">
-        <v>46186.22807305778</v>
+        <v>46186.23290198439</v>
       </c>
       <c r="Z21" s="8" t="inlineStr"/>
     </row>
@@ -1767,7 +1771,7 @@
       <c r="W22" s="8" t="inlineStr"/>
       <c r="X22" s="8" t="inlineStr"/>
       <c r="Y22" s="9" t="n">
-        <v>46186.22807305807</v>
+        <v>46186.23290198476</v>
       </c>
       <c r="Z22" s="8" t="inlineStr"/>
     </row>
@@ -1835,7 +1839,7 @@
       <c r="W23" s="8" t="inlineStr"/>
       <c r="X23" s="8" t="inlineStr"/>
       <c r="Y23" s="9" t="n">
-        <v>46186.22807305838</v>
+        <v>46186.23290198508</v>
       </c>
       <c r="Z23" s="8" t="inlineStr"/>
     </row>
@@ -1903,7 +1907,7 @@
       <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="5" t="n">
-        <v>46186.22807305897</v>
+        <v>46186.23290198534</v>
       </c>
       <c r="Z24" s="4" t="inlineStr"/>
     </row>
@@ -1971,7 +1975,7 @@
       <c r="W25" s="8" t="inlineStr"/>
       <c r="X25" s="8" t="inlineStr"/>
       <c r="Y25" s="9" t="n">
-        <v>46186.22807305938</v>
+        <v>46186.23290198569</v>
       </c>
       <c r="Z25" s="8" t="inlineStr"/>
     </row>
@@ -2039,7 +2043,7 @@
       <c r="W26" s="8" t="inlineStr"/>
       <c r="X26" s="8" t="inlineStr"/>
       <c r="Y26" s="9" t="n">
-        <v>46186.22807305969</v>
+        <v>46186.23290198595</v>
       </c>
       <c r="Z26" s="8" t="inlineStr"/>
     </row>
@@ -2107,7 +2111,7 @@
       <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="5" t="n">
-        <v>46186.22807306043</v>
+        <v>46186.23290198619</v>
       </c>
       <c r="Z27" s="4" t="inlineStr"/>
     </row>
@@ -2175,7 +2179,7 @@
       <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="5" t="n">
-        <v>46186.22807306077</v>
+        <v>46186.23290198641</v>
       </c>
       <c r="Z28" s="4" t="inlineStr"/>
     </row>
@@ -2243,7 +2247,7 @@
       <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="5" t="n">
-        <v>46186.22807306109</v>
+        <v>46186.23290198665</v>
       </c>
       <c r="Z29" s="4" t="inlineStr"/>
     </row>
@@ -2311,7 +2315,7 @@
       <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="5" t="n">
-        <v>46186.22807306136</v>
+        <v>46186.2329019869</v>
       </c>
       <c r="Z30" s="4" t="inlineStr"/>
     </row>
@@ -2335,7 +2339,11 @@
           <t>Re: Shop Drawings Submission - CC01-Cut &amp; Cover Structure D-Wall Reinforcement Shop Drawings Type-D Primary Panel (P35) and (P25): MLCC-S0701-CIV-CCV-RFC-DRW-13003 to 13010_Rev C02</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -2375,7 +2383,7 @@
       <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="5" t="n">
-        <v>46186.22807306163</v>
+        <v>46186.23290198712</v>
       </c>
       <c r="Z31" s="4" t="inlineStr"/>
     </row>
@@ -2431,7 +2439,7 @@
       <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="5" t="n">
-        <v>46186.22807306185</v>
+        <v>46186.23290198731</v>
       </c>
       <c r="Z32" s="4" t="inlineStr"/>
     </row>
@@ -2499,7 +2507,7 @@
       <c r="W33" s="4" t="inlineStr"/>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="5" t="n">
-        <v>46186.22807306211</v>
+        <v>46186.23290198753</v>
       </c>
       <c r="Z33" s="4" t="inlineStr"/>
     </row>
@@ -2571,7 +2579,7 @@
       <c r="W34" s="4" t="inlineStr"/>
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="5" t="n">
-        <v>46186.22807306234</v>
+        <v>46186.23290198776</v>
       </c>
       <c r="Z34" s="4" t="inlineStr"/>
     </row>
@@ -2639,7 +2647,7 @@
       <c r="W35" s="4" t="inlineStr"/>
       <c r="X35" s="4" t="inlineStr"/>
       <c r="Y35" s="5" t="n">
-        <v>46186.22807306257</v>
+        <v>46186.23290198794</v>
       </c>
       <c r="Z35" s="4" t="inlineStr"/>
     </row>
@@ -2707,7 +2715,7 @@
       <c r="W36" s="8" t="inlineStr"/>
       <c r="X36" s="8" t="inlineStr"/>
       <c r="Y36" s="9" t="n">
-        <v>46186.22807306283</v>
+        <v>46186.23290198819</v>
       </c>
       <c r="Z36" s="8" t="inlineStr"/>
     </row>
@@ -2775,7 +2783,7 @@
       <c r="W37" s="8" t="inlineStr"/>
       <c r="X37" s="8" t="inlineStr"/>
       <c r="Y37" s="9" t="n">
-        <v>46186.22807306328</v>
+        <v>46186.23290198853</v>
       </c>
       <c r="Z37" s="8" t="inlineStr"/>
     </row>
@@ -2827,7 +2835,7 @@
       <c r="W38" s="4" t="inlineStr"/>
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="5" t="n">
-        <v>46186.22807306382</v>
+        <v>46186.23290198872</v>
       </c>
       <c r="Z38" s="4" t="inlineStr"/>
     </row>
@@ -2895,7 +2903,7 @@
       <c r="W39" s="8" t="inlineStr"/>
       <c r="X39" s="8" t="inlineStr"/>
       <c r="Y39" s="9" t="n">
-        <v>46186.22807306418</v>
+        <v>46186.23290198907</v>
       </c>
       <c r="Z39" s="8" t="inlineStr"/>
     </row>
@@ -2963,7 +2971,7 @@
       <c r="W40" s="8" t="inlineStr"/>
       <c r="X40" s="8" t="inlineStr"/>
       <c r="Y40" s="9" t="n">
-        <v>46186.22807306448</v>
+        <v>46186.23290198935</v>
       </c>
       <c r="Z40" s="8" t="inlineStr"/>
     </row>
@@ -3031,7 +3039,7 @@
       <c r="W41" s="8" t="inlineStr"/>
       <c r="X41" s="8" t="inlineStr"/>
       <c r="Y41" s="9" t="n">
-        <v>46186.22807306489</v>
+        <v>46186.2329019897</v>
       </c>
       <c r="Z41" s="8" t="inlineStr"/>
     </row>
@@ -3099,7 +3107,7 @@
       <c r="W42" s="8" t="inlineStr"/>
       <c r="X42" s="8" t="inlineStr"/>
       <c r="Y42" s="9" t="n">
-        <v>46186.22807306516</v>
+        <v>46186.23290198996</v>
       </c>
       <c r="Z42" s="8" t="inlineStr"/>
     </row>
@@ -3167,7 +3175,7 @@
       <c r="W43" s="8" t="inlineStr"/>
       <c r="X43" s="8" t="inlineStr"/>
       <c r="Y43" s="9" t="n">
-        <v>46186.22807306563</v>
+        <v>46186.23290199139</v>
       </c>
       <c r="Z43" s="8" t="inlineStr"/>
     </row>
@@ -3223,7 +3231,7 @@
       <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="8" t="inlineStr"/>
       <c r="Y44" s="9" t="n">
-        <v>46186.22807306597</v>
+        <v>46186.23290199217</v>
       </c>
       <c r="Z44" s="8" t="inlineStr"/>
     </row>
@@ -3291,7 +3299,7 @@
       <c r="W45" s="8" t="inlineStr"/>
       <c r="X45" s="8" t="inlineStr"/>
       <c r="Y45" s="9" t="n">
-        <v>46186.22807306634</v>
+        <v>46186.23290199258</v>
       </c>
       <c r="Z45" s="8" t="inlineStr"/>
     </row>
@@ -3347,7 +3355,7 @@
       <c r="W46" s="8" t="inlineStr"/>
       <c r="X46" s="8" t="inlineStr"/>
       <c r="Y46" s="9" t="n">
-        <v>46186.2280730666</v>
+        <v>46186.23290199284</v>
       </c>
       <c r="Z46" s="8" t="inlineStr"/>
     </row>
@@ -3403,7 +3411,7 @@
       <c r="W47" s="8" t="inlineStr"/>
       <c r="X47" s="8" t="inlineStr"/>
       <c r="Y47" s="9" t="n">
-        <v>46186.22807306684</v>
+        <v>46186.23290199309</v>
       </c>
       <c r="Z47" s="8" t="inlineStr"/>
     </row>
@@ -3427,7 +3435,11 @@
           <t>Re: Report Submission - Technical Note - MEP - LV Cable Colour Coding Project Wide (DE.GEN.GN00.MEP.M0.GN): MLCC-N0003-BES-NWW-ANO-RPT-70000_Rev C02</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr"/>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
       <c r="G48" s="8" t="inlineStr"/>
       <c r="H48" s="8" t="inlineStr">
         <is>
@@ -3467,7 +3479,7 @@
       <c r="W48" s="8" t="inlineStr"/>
       <c r="X48" s="8" t="inlineStr"/>
       <c r="Y48" s="9" t="n">
-        <v>46186.2280730672</v>
+        <v>46186.23290199345</v>
       </c>
       <c r="Z48" s="8" t="inlineStr"/>
     </row>
@@ -3523,7 +3535,7 @@
       <c r="W49" s="8" t="inlineStr"/>
       <c r="X49" s="8" t="inlineStr"/>
       <c r="Y49" s="9" t="n">
-        <v>46186.22807306743</v>
+        <v>46186.23290199368</v>
       </c>
       <c r="Z49" s="8" t="inlineStr"/>
     </row>
@@ -3595,7 +3607,7 @@
       <c r="W50" s="8" t="inlineStr"/>
       <c r="X50" s="8" t="inlineStr"/>
       <c r="Y50" s="9" t="n">
-        <v>46186.22807306778</v>
+        <v>46186.23290199401</v>
       </c>
       <c r="Z50" s="8" t="inlineStr"/>
     </row>
@@ -3667,7 +3679,7 @@
       <c r="W51" s="8" t="inlineStr"/>
       <c r="X51" s="8" t="inlineStr"/>
       <c r="Y51" s="9" t="n">
-        <v>46186.22807306837</v>
+        <v>46186.23290199429</v>
       </c>
       <c r="Z51" s="8" t="inlineStr"/>
     </row>
@@ -3723,7 +3735,7 @@
       <c r="W52" s="8" t="inlineStr"/>
       <c r="X52" s="8" t="inlineStr"/>
       <c r="Y52" s="9" t="n">
-        <v>46186.22807306871</v>
+        <v>46186.23290199455</v>
       </c>
       <c r="Z52" s="8" t="inlineStr"/>
     </row>
@@ -3775,7 +3787,7 @@
       <c r="W53" s="4" t="inlineStr"/>
       <c r="X53" s="4" t="inlineStr"/>
       <c r="Y53" s="5" t="n">
-        <v>46186.22807306896</v>
+        <v>46186.23290199476</v>
       </c>
       <c r="Z53" s="4" t="inlineStr"/>
     </row>
@@ -3843,7 +3855,7 @@
       <c r="W54" s="8" t="inlineStr"/>
       <c r="X54" s="8" t="inlineStr"/>
       <c r="Y54" s="9" t="n">
-        <v>46186.22807306926</v>
+        <v>46186.23290199503</v>
       </c>
       <c r="Z54" s="8" t="inlineStr"/>
     </row>
@@ -3911,7 +3923,7 @@
       <c r="W55" s="4" t="inlineStr"/>
       <c r="X55" s="4" t="inlineStr"/>
       <c r="Y55" s="5" t="n">
-        <v>46186.22807306949</v>
+        <v>46186.23290199525</v>
       </c>
       <c r="Z55" s="4" t="inlineStr"/>
     </row>
@@ -3967,7 +3979,7 @@
       <c r="W56" s="4" t="inlineStr"/>
       <c r="X56" s="4" t="inlineStr"/>
       <c r="Y56" s="5" t="n">
-        <v>46186.2280730697</v>
+        <v>46186.23290199544</v>
       </c>
       <c r="Z56" s="4" t="inlineStr"/>
     </row>
@@ -4035,7 +4047,7 @@
       <c r="W57" s="8" t="inlineStr"/>
       <c r="X57" s="8" t="inlineStr"/>
       <c r="Y57" s="9" t="n">
-        <v>46186.22807306996</v>
+        <v>46186.2329019957</v>
       </c>
       <c r="Z57" s="8" t="inlineStr"/>
     </row>
@@ -4091,7 +4103,7 @@
       <c r="W58" s="4" t="inlineStr"/>
       <c r="X58" s="4" t="inlineStr"/>
       <c r="Y58" s="5" t="n">
-        <v>46186.22807307016</v>
+        <v>46186.23290199589</v>
       </c>
       <c r="Z58" s="4" t="inlineStr"/>
     </row>
@@ -4147,7 +4159,7 @@
       <c r="W59" s="4" t="inlineStr"/>
       <c r="X59" s="4" t="inlineStr"/>
       <c r="Y59" s="5" t="n">
-        <v>46186.22807307035</v>
+        <v>46186.23290199607</v>
       </c>
       <c r="Z59" s="4" t="inlineStr"/>
     </row>
@@ -4215,7 +4227,7 @@
       <c r="W60" s="4" t="inlineStr"/>
       <c r="X60" s="4" t="inlineStr"/>
       <c r="Y60" s="5" t="n">
-        <v>46186.22807307059</v>
+        <v>46186.23290199631</v>
       </c>
       <c r="Z60" s="4" t="inlineStr"/>
     </row>
@@ -4283,7 +4295,7 @@
       <c r="W61" s="8" t="inlineStr"/>
       <c r="X61" s="8" t="inlineStr"/>
       <c r="Y61" s="9" t="n">
-        <v>46186.22807307095</v>
+        <v>46186.23290199666</v>
       </c>
       <c r="Z61" s="8" t="inlineStr"/>
     </row>
@@ -4351,7 +4363,7 @@
       <c r="W62" s="4" t="inlineStr"/>
       <c r="X62" s="4" t="inlineStr"/>
       <c r="Y62" s="5" t="n">
-        <v>46186.22807307119</v>
+        <v>46186.2329019969</v>
       </c>
       <c r="Z62" s="4" t="inlineStr"/>
     </row>
@@ -4419,7 +4431,7 @@
       <c r="W63" s="4" t="inlineStr"/>
       <c r="X63" s="4" t="inlineStr"/>
       <c r="Y63" s="5" t="n">
-        <v>46186.22807307139</v>
+        <v>46186.23290199709</v>
       </c>
       <c r="Z63" s="4" t="inlineStr"/>
     </row>
@@ -4475,7 +4487,7 @@
       <c r="W64" s="4" t="inlineStr"/>
       <c r="X64" s="4" t="inlineStr"/>
       <c r="Y64" s="5" t="n">
-        <v>46186.22807307157</v>
+        <v>46186.23290199728</v>
       </c>
       <c r="Z64" s="4" t="inlineStr"/>
     </row>
@@ -4543,7 +4555,7 @@
       <c r="W65" s="4" t="inlineStr"/>
       <c r="X65" s="4" t="inlineStr"/>
       <c r="Y65" s="5" t="n">
-        <v>46186.2280730718</v>
+        <v>46186.2329019975</v>
       </c>
       <c r="Z65" s="4" t="inlineStr"/>
     </row>
@@ -4611,7 +4623,7 @@
       <c r="W66" s="4" t="inlineStr"/>
       <c r="X66" s="4" t="inlineStr"/>
       <c r="Y66" s="5" t="n">
-        <v>46186.228073072</v>
+        <v>46186.23290199768</v>
       </c>
       <c r="Z66" s="4" t="inlineStr"/>
     </row>
@@ -4667,7 +4679,7 @@
       <c r="W67" s="4" t="inlineStr"/>
       <c r="X67" s="4" t="inlineStr"/>
       <c r="Y67" s="5" t="n">
-        <v>46186.22807307219</v>
+        <v>46186.23290199787</v>
       </c>
       <c r="Z67" s="4" t="inlineStr"/>
     </row>
@@ -4735,7 +4747,7 @@
       <c r="W68" s="4" t="inlineStr"/>
       <c r="X68" s="4" t="inlineStr"/>
       <c r="Y68" s="5" t="n">
-        <v>46186.22807307241</v>
+        <v>46186.23290199808</v>
       </c>
       <c r="Z68" s="4" t="inlineStr"/>
     </row>
@@ -4791,7 +4803,7 @@
       <c r="W69" s="4" t="inlineStr"/>
       <c r="X69" s="4" t="inlineStr"/>
       <c r="Y69" s="5" t="n">
-        <v>46186.22807307259</v>
+        <v>46186.23290199826</v>
       </c>
       <c r="Z69" s="4" t="inlineStr"/>
     </row>
@@ -4859,7 +4871,7 @@
       <c r="W70" s="4" t="inlineStr"/>
       <c r="X70" s="4" t="inlineStr"/>
       <c r="Y70" s="5" t="n">
-        <v>46186.2280730728</v>
+        <v>46186.23290199846</v>
       </c>
       <c r="Z70" s="4" t="inlineStr"/>
     </row>
@@ -4927,7 +4939,7 @@
       <c r="W71" s="4" t="inlineStr"/>
       <c r="X71" s="4" t="inlineStr"/>
       <c r="Y71" s="5" t="n">
-        <v>46186.22807307304</v>
+        <v>46186.23290199918</v>
       </c>
       <c r="Z71" s="4" t="inlineStr"/>
     </row>
@@ -4999,7 +5011,7 @@
       <c r="W72" s="4" t="inlineStr"/>
       <c r="X72" s="4" t="inlineStr"/>
       <c r="Y72" s="5" t="n">
-        <v>46186.22807307325</v>
+        <v>46186.23290199946</v>
       </c>
       <c r="Z72" s="4" t="inlineStr"/>
     </row>
@@ -5067,7 +5079,7 @@
       <c r="W73" s="4" t="inlineStr"/>
       <c r="X73" s="4" t="inlineStr"/>
       <c r="Y73" s="5" t="n">
-        <v>46186.22807307347</v>
+        <v>46186.23290199969</v>
       </c>
       <c r="Z73" s="4" t="inlineStr"/>
     </row>
@@ -5135,7 +5147,7 @@
       <c r="W74" s="4" t="inlineStr"/>
       <c r="X74" s="4" t="inlineStr"/>
       <c r="Y74" s="5" t="n">
-        <v>46186.22807307367</v>
+        <v>46186.23290199991</v>
       </c>
       <c r="Z74" s="4" t="inlineStr"/>
     </row>
@@ -5203,7 +5215,7 @@
       <c r="W75" s="4" t="inlineStr"/>
       <c r="X75" s="4" t="inlineStr"/>
       <c r="Y75" s="5" t="n">
-        <v>46186.22807307388</v>
+        <v>46186.23290200011</v>
       </c>
       <c r="Z75" s="4" t="inlineStr"/>
     </row>
@@ -5275,7 +5287,7 @@
       <c r="W76" s="4" t="inlineStr"/>
       <c r="X76" s="4" t="inlineStr"/>
       <c r="Y76" s="5" t="n">
-        <v>46186.22807307407</v>
+        <v>46186.23290200031</v>
       </c>
       <c r="Z76" s="4" t="inlineStr"/>
     </row>
@@ -5347,7 +5359,7 @@
       <c r="W77" s="8" t="inlineStr"/>
       <c r="X77" s="8" t="inlineStr"/>
       <c r="Y77" s="9" t="n">
-        <v>46186.2280730744</v>
+        <v>46186.2329020011</v>
       </c>
       <c r="Z77" s="8" t="inlineStr"/>
     </row>
@@ -5415,7 +5427,7 @@
       <c r="W78" s="8" t="inlineStr"/>
       <c r="X78" s="8" t="inlineStr"/>
       <c r="Y78" s="9" t="n">
-        <v>46186.22807307474</v>
+        <v>46186.23290200156</v>
       </c>
       <c r="Z78" s="8" t="inlineStr"/>
     </row>
@@ -5471,7 +5483,7 @@
       <c r="W79" s="8" t="inlineStr"/>
       <c r="X79" s="8" t="inlineStr"/>
       <c r="Y79" s="9" t="n">
-        <v>46186.22807307506</v>
+        <v>46186.23290200183</v>
       </c>
       <c r="Z79" s="8" t="inlineStr"/>
     </row>
@@ -5543,7 +5555,7 @@
       <c r="W80" s="8" t="inlineStr"/>
       <c r="X80" s="8" t="inlineStr"/>
       <c r="Y80" s="9" t="n">
-        <v>46186.22807307531</v>
+        <v>46186.23290200209</v>
       </c>
       <c r="Z80" s="8" t="inlineStr"/>
     </row>
@@ -5615,7 +5627,7 @@
       <c r="W81" s="8" t="inlineStr"/>
       <c r="X81" s="8" t="inlineStr"/>
       <c r="Y81" s="9" t="n">
-        <v>46186.22807307557</v>
+        <v>46186.23290200236</v>
       </c>
       <c r="Z81" s="8" t="inlineStr"/>
     </row>
@@ -5687,7 +5699,7 @@
       <c r="W82" s="8" t="inlineStr"/>
       <c r="X82" s="8" t="inlineStr"/>
       <c r="Y82" s="9" t="n">
-        <v>46186.22807307584</v>
+        <v>46186.23290200295</v>
       </c>
       <c r="Z82" s="8" t="inlineStr"/>
     </row>
@@ -5755,7 +5767,7 @@
       <c r="W83" s="4" t="inlineStr"/>
       <c r="X83" s="4" t="inlineStr"/>
       <c r="Y83" s="5" t="n">
-        <v>46186.22807307605</v>
+        <v>46186.23290200358</v>
       </c>
       <c r="Z83" s="4" t="inlineStr"/>
     </row>
@@ -5807,7 +5819,7 @@
       <c r="W84" s="8" t="inlineStr"/>
       <c r="X84" s="8" t="inlineStr"/>
       <c r="Y84" s="9" t="n">
-        <v>46186.22807307629</v>
+        <v>46186.23290200385</v>
       </c>
       <c r="Z84" s="8" t="inlineStr"/>
     </row>
@@ -5863,7 +5875,7 @@
       <c r="W85" s="4" t="inlineStr"/>
       <c r="X85" s="4" t="inlineStr"/>
       <c r="Y85" s="5" t="n">
-        <v>46186.22807307647</v>
+        <v>46186.23290200406</v>
       </c>
       <c r="Z85" s="4" t="inlineStr"/>
     </row>
@@ -5931,7 +5943,7 @@
       <c r="W86" s="8" t="inlineStr"/>
       <c r="X86" s="8" t="inlineStr"/>
       <c r="Y86" s="9" t="n">
-        <v>46186.22807307675</v>
+        <v>46186.23290200435</v>
       </c>
       <c r="Z86" s="8" t="inlineStr"/>
     </row>
@@ -5999,7 +6011,7 @@
       <c r="W87" s="8" t="inlineStr"/>
       <c r="X87" s="8" t="inlineStr"/>
       <c r="Y87" s="9" t="n">
-        <v>46186.22807307704</v>
+        <v>46186.23290200464</v>
       </c>
       <c r="Z87" s="8" t="inlineStr"/>
     </row>
@@ -6071,7 +6083,7 @@
       <c r="W88" s="8" t="inlineStr"/>
       <c r="X88" s="8" t="inlineStr"/>
       <c r="Y88" s="9" t="n">
-        <v>46186.22807307729</v>
+        <v>46186.23290200491</v>
       </c>
       <c r="Z88" s="8" t="inlineStr"/>
     </row>
@@ -6139,7 +6151,7 @@
       <c r="W89" s="4" t="inlineStr"/>
       <c r="X89" s="4" t="inlineStr"/>
       <c r="Y89" s="5" t="n">
-        <v>46186.22807307749</v>
+        <v>46186.2329020051</v>
       </c>
       <c r="Z89" s="4" t="inlineStr"/>
     </row>
@@ -6211,7 +6223,7 @@
       <c r="W90" s="8" t="inlineStr"/>
       <c r="X90" s="8" t="inlineStr"/>
       <c r="Y90" s="9" t="n">
-        <v>46186.22807307776</v>
+        <v>46186.23290200539</v>
       </c>
       <c r="Z90" s="8" t="inlineStr"/>
     </row>
@@ -6267,7 +6279,7 @@
       <c r="W91" s="8" t="inlineStr"/>
       <c r="X91" s="8" t="inlineStr"/>
       <c r="Y91" s="9" t="n">
-        <v>46186.2280730781</v>
+        <v>46186.23290200604</v>
       </c>
       <c r="Z91" s="8" t="inlineStr"/>
     </row>
@@ -6291,7 +6303,11 @@
           <t>Re: Report Submission - DCP2 - Station (BR10) - CFD Report for Fire Scenarios : DE.ELS.RE00.MEP.M4.D2 : MLCC-C0201-BES-VAC-SYW-RPT-70001-DCP2_Rev C01</t>
         </is>
       </c>
-      <c r="F92" s="8" t="inlineStr"/>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
       <c r="G92" s="8" t="inlineStr"/>
       <c r="H92" s="8" t="inlineStr">
         <is>
@@ -6335,7 +6351,7 @@
       <c r="W92" s="8" t="inlineStr"/>
       <c r="X92" s="8" t="inlineStr"/>
       <c r="Y92" s="9" t="n">
-        <v>46186.22807307838</v>
+        <v>46186.23290200644</v>
       </c>
       <c r="Z92" s="8" t="inlineStr"/>
     </row>
@@ -6403,7 +6419,7 @@
       <c r="W93" s="8" t="inlineStr"/>
       <c r="X93" s="8" t="inlineStr"/>
       <c r="Y93" s="9" t="n">
-        <v>46186.2280730791</v>
+        <v>46186.23290200681</v>
       </c>
       <c r="Z93" s="8" t="inlineStr"/>
     </row>
@@ -6471,7 +6487,7 @@
       <c r="W94" s="8" t="inlineStr"/>
       <c r="X94" s="8" t="inlineStr"/>
       <c r="Y94" s="9" t="n">
-        <v>46186.22807307943</v>
+        <v>46186.2329020071</v>
       </c>
       <c r="Z94" s="8" t="inlineStr"/>
     </row>
@@ -6527,7 +6543,7 @@
       <c r="W95" s="8" t="inlineStr"/>
       <c r="X95" s="8" t="inlineStr"/>
       <c r="Y95" s="9" t="n">
-        <v>46186.22807308003</v>
+        <v>46186.23290200735</v>
       </c>
       <c r="Z95" s="8" t="inlineStr"/>
     </row>
@@ -6583,7 +6599,7 @@
       <c r="W96" s="4" t="inlineStr"/>
       <c r="X96" s="4" t="inlineStr"/>
       <c r="Y96" s="5" t="n">
-        <v>46186.22807308031</v>
+        <v>46186.23290200756</v>
       </c>
       <c r="Z96" s="4" t="inlineStr"/>
     </row>
@@ -6639,7 +6655,7 @@
       <c r="W97" s="4" t="inlineStr"/>
       <c r="X97" s="4" t="inlineStr"/>
       <c r="Y97" s="5" t="n">
-        <v>46186.22807308052</v>
+        <v>46186.23290200774</v>
       </c>
       <c r="Z97" s="4" t="inlineStr"/>
     </row>
@@ -6711,7 +6727,7 @@
       <c r="W98" s="4" t="inlineStr"/>
       <c r="X98" s="4" t="inlineStr"/>
       <c r="Y98" s="5" t="n">
-        <v>46186.22807308079</v>
+        <v>46186.23290200796</v>
       </c>
       <c r="Z98" s="4" t="inlineStr"/>
     </row>
@@ -6767,7 +6783,7 @@
       <c r="W99" s="4" t="inlineStr"/>
       <c r="X99" s="4" t="inlineStr"/>
       <c r="Y99" s="5" t="n">
-        <v>46186.22807308099</v>
+        <v>46186.23290200816</v>
       </c>
       <c r="Z99" s="4" t="inlineStr"/>
     </row>
@@ -6823,7 +6839,7 @@
       <c r="W100" s="4" t="inlineStr"/>
       <c r="X100" s="4" t="inlineStr"/>
       <c r="Y100" s="5" t="n">
-        <v>46186.22807308118</v>
+        <v>46186.23290200834</v>
       </c>
       <c r="Z100" s="4" t="inlineStr"/>
     </row>
@@ -6891,7 +6907,7 @@
       <c r="W101" s="4" t="inlineStr"/>
       <c r="X101" s="4" t="inlineStr"/>
       <c r="Y101" s="5" t="n">
-        <v>46186.22807308142</v>
+        <v>46186.23290200859</v>
       </c>
       <c r="Z101" s="4" t="inlineStr"/>
     </row>
@@ -6963,7 +6979,7 @@
       <c r="W102" s="4" t="inlineStr"/>
       <c r="X102" s="4" t="inlineStr"/>
       <c r="Y102" s="5" t="n">
-        <v>46186.2280730817</v>
+        <v>46186.23290200884</v>
       </c>
       <c r="Z102" s="4" t="inlineStr"/>
     </row>
@@ -7031,7 +7047,7 @@
       <c r="W103" s="4" t="inlineStr"/>
       <c r="X103" s="4" t="inlineStr"/>
       <c r="Y103" s="5" t="n">
-        <v>46186.2280730819</v>
+        <v>46186.23290200904</v>
       </c>
       <c r="Z103" s="4" t="inlineStr"/>
     </row>
@@ -7099,7 +7115,7 @@
       <c r="W104" s="4" t="inlineStr"/>
       <c r="X104" s="4" t="inlineStr"/>
       <c r="Y104" s="5" t="n">
-        <v>46186.22807308211</v>
+        <v>46186.23290200924</v>
       </c>
       <c r="Z104" s="4" t="inlineStr"/>
     </row>
@@ -7167,7 +7183,7 @@
       <c r="W105" s="4" t="inlineStr"/>
       <c r="X105" s="4" t="inlineStr"/>
       <c r="Y105" s="5" t="n">
-        <v>46186.2280730823</v>
+        <v>46186.23290200943</v>
       </c>
       <c r="Z105" s="4" t="inlineStr"/>
     </row>
@@ -7239,7 +7255,7 @@
       <c r="W106" s="4" t="inlineStr"/>
       <c r="X106" s="4" t="inlineStr"/>
       <c r="Y106" s="5" t="n">
-        <v>46186.22807308249</v>
+        <v>46186.23290200961</v>
       </c>
       <c r="Z106" s="4" t="inlineStr"/>
     </row>
@@ -7307,7 +7323,7 @@
       <c r="W107" s="4" t="inlineStr"/>
       <c r="X107" s="4" t="inlineStr"/>
       <c r="Y107" s="5" t="n">
-        <v>46186.22807308272</v>
+        <v>46186.23290200981</v>
       </c>
       <c r="Z107" s="4" t="inlineStr"/>
     </row>
@@ -7375,7 +7391,7 @@
       <c r="W108" s="4" t="inlineStr"/>
       <c r="X108" s="4" t="inlineStr"/>
       <c r="Y108" s="5" t="n">
-        <v>46186.22807308295</v>
+        <v>46186.23290201004</v>
       </c>
       <c r="Z108" s="4" t="inlineStr"/>
     </row>
@@ -7443,7 +7459,7 @@
       <c r="W109" s="4" t="inlineStr"/>
       <c r="X109" s="4" t="inlineStr"/>
       <c r="Y109" s="5" t="n">
-        <v>46186.22807308315</v>
+        <v>46186.2329020102</v>
       </c>
       <c r="Z109" s="4" t="inlineStr"/>
     </row>
@@ -7511,7 +7527,7 @@
       <c r="W110" s="4" t="inlineStr"/>
       <c r="X110" s="4" t="inlineStr"/>
       <c r="Y110" s="5" t="n">
-        <v>46186.22807308337</v>
+        <v>46186.23290201041</v>
       </c>
       <c r="Z110" s="4" t="inlineStr"/>
     </row>
@@ -7575,7 +7591,7 @@
       <c r="W111" s="4" t="inlineStr"/>
       <c r="X111" s="4" t="inlineStr"/>
       <c r="Y111" s="5" t="n">
-        <v>46186.22807308356</v>
+        <v>46186.23290201061</v>
       </c>
       <c r="Z111" s="4" t="inlineStr"/>
     </row>
@@ -7627,7 +7643,7 @@
       <c r="W112" s="4" t="inlineStr"/>
       <c r="X112" s="4" t="inlineStr"/>
       <c r="Y112" s="5" t="n">
-        <v>46186.22807308379</v>
+        <v>46186.23290201081</v>
       </c>
       <c r="Z112" s="4" t="inlineStr"/>
     </row>
@@ -7651,7 +7667,11 @@
           <t>Shop Drawing Submisison - Stretch-02.2 - Viaduct Structure Foundation Pile Cap - BC-3SP-72-03 - PM55: MLCC-S0663-CIV-VBR-PAP-DRW-84070, MLCC-S0663-CIV-VBR-PAP-DRW-84071, MLCC-S0663-CIV-VBR-PAP-DRW-84072 &amp; MLCC-S0663-CIV-VBR-PAP-DRW-84073_Rev C01</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
       <c r="G113" s="4" t="inlineStr"/>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -7691,7 +7711,7 @@
       <c r="W113" s="4" t="inlineStr"/>
       <c r="X113" s="4" t="inlineStr"/>
       <c r="Y113" s="5" t="n">
-        <v>46186.22807308401</v>
+        <v>46186.23290201106</v>
       </c>
       <c r="Z113" s="4" t="inlineStr"/>
     </row>
@@ -7715,7 +7735,11 @@
           <t>Shop Drawing Submission - Stretch-02.2 - Viaduct Structure Foundation Pile Cap - BC-3SP-72-03 - PM51: MLCC-S0663-CIV-VBR-PAP-DRW-84040 to MLCC-S0663-CIV-VBR-PAP-DRW-84043_Rev C01</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
       <c r="G114" s="4" t="inlineStr"/>
       <c r="H114" s="4" t="inlineStr">
         <is>
@@ -7755,7 +7779,7 @@
       <c r="W114" s="4" t="inlineStr"/>
       <c r="X114" s="4" t="inlineStr"/>
       <c r="Y114" s="5" t="n">
-        <v>46186.22807308424</v>
+        <v>46186.23290201127</v>
       </c>
       <c r="Z114" s="4" t="inlineStr"/>
     </row>
@@ -7803,7 +7827,7 @@
       <c r="W115" s="4" t="inlineStr"/>
       <c r="X115" s="4" t="inlineStr"/>
       <c r="Y115" s="5" t="n">
-        <v>46186.22807308442</v>
+        <v>46186.23290201146</v>
       </c>
       <c r="Z115" s="4" t="inlineStr"/>
     </row>
@@ -7851,7 +7875,7 @@
       <c r="W116" s="4" t="inlineStr"/>
       <c r="X116" s="4" t="inlineStr"/>
       <c r="Y116" s="5" t="n">
-        <v>46186.2280730846</v>
+        <v>46186.23290201163</v>
       </c>
       <c r="Z116" s="4" t="inlineStr"/>
     </row>
@@ -7919,7 +7943,7 @@
       <c r="W117" s="4" t="inlineStr"/>
       <c r="X117" s="4" t="inlineStr"/>
       <c r="Y117" s="5" t="n">
-        <v>46186.2280730848</v>
+        <v>46186.23290201183</v>
       </c>
       <c r="Z117" s="4" t="inlineStr"/>
     </row>
@@ -7987,7 +8011,7 @@
       <c r="W118" s="8" t="inlineStr"/>
       <c r="X118" s="8" t="inlineStr"/>
       <c r="Y118" s="9" t="n">
-        <v>46186.22807308519</v>
+        <v>46186.23290201282</v>
       </c>
       <c r="Z118" s="8" t="inlineStr"/>
     </row>
@@ -8059,7 +8083,7 @@
       <c r="W119" s="4" t="inlineStr"/>
       <c r="X119" s="4" t="inlineStr"/>
       <c r="Y119" s="5" t="n">
-        <v>46186.2280730854</v>
+        <v>46186.23290201318</v>
       </c>
       <c r="Z119" s="4" t="inlineStr"/>
     </row>
@@ -8127,7 +8151,7 @@
       <c r="W120" s="8" t="inlineStr"/>
       <c r="X120" s="8" t="inlineStr"/>
       <c r="Y120" s="9" t="n">
-        <v>46186.22807308568</v>
+        <v>46186.23290201351</v>
       </c>
       <c r="Z120" s="8" t="inlineStr"/>
     </row>
@@ -8195,7 +8219,7 @@
       <c r="W121" s="8" t="inlineStr"/>
       <c r="X121" s="8" t="inlineStr"/>
       <c r="Y121" s="9" t="n">
-        <v>46186.22807308601</v>
+        <v>46186.23290201378</v>
       </c>
       <c r="Z121" s="8" t="inlineStr"/>
     </row>
@@ -8263,7 +8287,7 @@
       <c r="W122" s="8" t="inlineStr"/>
       <c r="X122" s="8" t="inlineStr"/>
       <c r="Y122" s="9" t="n">
-        <v>46186.22807308625</v>
+        <v>46186.23290201404</v>
       </c>
       <c r="Z122" s="8" t="inlineStr"/>
     </row>
@@ -8331,7 +8355,7 @@
       <c r="W123" s="4" t="inlineStr"/>
       <c r="X123" s="4" t="inlineStr"/>
       <c r="Y123" s="5" t="n">
-        <v>46186.22807308655</v>
+        <v>46186.23290201427</v>
       </c>
       <c r="Z123" s="4" t="inlineStr"/>
     </row>
@@ -8399,7 +8423,7 @@
       <c r="W124" s="4" t="inlineStr"/>
       <c r="X124" s="4" t="inlineStr"/>
       <c r="Y124" s="5" t="n">
-        <v>46186.22807308676</v>
+        <v>46186.23290201449</v>
       </c>
       <c r="Z124" s="4" t="inlineStr"/>
     </row>
@@ -8467,7 +8491,7 @@
       <c r="W125" s="4" t="inlineStr"/>
       <c r="X125" s="4" t="inlineStr"/>
       <c r="Y125" s="5" t="n">
-        <v>46186.22807308698</v>
+        <v>46186.23290201504</v>
       </c>
       <c r="Z125" s="4" t="inlineStr"/>
     </row>
@@ -8535,7 +8559,7 @@
       <c r="W126" s="4" t="inlineStr"/>
       <c r="X126" s="4" t="inlineStr"/>
       <c r="Y126" s="5" t="n">
-        <v>46186.22807308721</v>
+        <v>46186.23290201537</v>
       </c>
       <c r="Z126" s="4" t="inlineStr"/>
     </row>
@@ -8603,7 +8627,7 @@
       <c r="W127" s="4" t="inlineStr"/>
       <c r="X127" s="4" t="inlineStr"/>
       <c r="Y127" s="5" t="n">
-        <v>46186.2280730874</v>
+        <v>46186.23290201561</v>
       </c>
       <c r="Z127" s="4" t="inlineStr"/>
     </row>
@@ -8671,7 +8695,7 @@
       <c r="W128" s="4" t="inlineStr"/>
       <c r="X128" s="4" t="inlineStr"/>
       <c r="Y128" s="5" t="n">
-        <v>46186.22807308759</v>
+        <v>46186.23290201582</v>
       </c>
       <c r="Z128" s="4" t="inlineStr"/>
     </row>
@@ -8739,7 +8763,7 @@
       <c r="W129" s="4" t="inlineStr"/>
       <c r="X129" s="4" t="inlineStr"/>
       <c r="Y129" s="5" t="n">
-        <v>46186.22807308779</v>
+        <v>46186.23290201603</v>
       </c>
       <c r="Z129" s="4" t="inlineStr"/>
     </row>
@@ -8807,7 +8831,7 @@
       <c r="W130" s="4" t="inlineStr"/>
       <c r="X130" s="4" t="inlineStr"/>
       <c r="Y130" s="5" t="n">
-        <v>46186.228073088</v>
+        <v>46186.23290201624</v>
       </c>
       <c r="Z130" s="4" t="inlineStr"/>
     </row>
@@ -8875,7 +8899,7 @@
       <c r="W131" s="4" t="inlineStr"/>
       <c r="X131" s="4" t="inlineStr"/>
       <c r="Y131" s="5" t="n">
-        <v>46186.2280730882</v>
+        <v>46186.23290201646</v>
       </c>
       <c r="Z131" s="4" t="inlineStr"/>
     </row>
@@ -8931,7 +8955,7 @@
       <c r="W132" s="4" t="inlineStr"/>
       <c r="X132" s="4" t="inlineStr"/>
       <c r="Y132" s="5" t="n">
-        <v>46186.22807308838</v>
+        <v>46186.23290201664</v>
       </c>
       <c r="Z132" s="4" t="inlineStr"/>
     </row>
@@ -8999,7 +9023,7 @@
       <c r="W133" s="4" t="inlineStr"/>
       <c r="X133" s="4" t="inlineStr"/>
       <c r="Y133" s="5" t="n">
-        <v>46186.22807308859</v>
+        <v>46186.23290201685</v>
       </c>
       <c r="Z133" s="4" t="inlineStr"/>
     </row>
@@ -9067,7 +9091,7 @@
       <c r="W134" s="4" t="inlineStr"/>
       <c r="X134" s="4" t="inlineStr"/>
       <c r="Y134" s="5" t="n">
-        <v>46186.22807308882</v>
+        <v>46186.23290201708</v>
       </c>
       <c r="Z134" s="4" t="inlineStr"/>
     </row>
@@ -9135,7 +9159,7 @@
       <c r="W135" s="4" t="inlineStr"/>
       <c r="X135" s="4" t="inlineStr"/>
       <c r="Y135" s="5" t="n">
-        <v>46186.22807308903</v>
+        <v>46186.23290201733</v>
       </c>
       <c r="Z135" s="4" t="inlineStr"/>
     </row>
@@ -9191,7 +9215,7 @@
       <c r="W136" s="4" t="inlineStr"/>
       <c r="X136" s="4" t="inlineStr"/>
       <c r="Y136" s="5" t="n">
-        <v>46186.2280730892</v>
+        <v>46186.23290201751</v>
       </c>
       <c r="Z136" s="4" t="inlineStr"/>
     </row>
@@ -9247,7 +9271,7 @@
       <c r="W137" s="4" t="inlineStr"/>
       <c r="X137" s="4" t="inlineStr"/>
       <c r="Y137" s="5" t="n">
-        <v>46186.22807308938</v>
+        <v>46186.2329020177</v>
       </c>
       <c r="Z137" s="4" t="inlineStr"/>
     </row>
@@ -9315,7 +9339,7 @@
       <c r="W138" s="4" t="inlineStr"/>
       <c r="X138" s="4" t="inlineStr"/>
       <c r="Y138" s="5" t="n">
-        <v>46186.22807308962</v>
+        <v>46186.23290201792</v>
       </c>
       <c r="Z138" s="4" t="inlineStr"/>
     </row>
@@ -9383,7 +9407,7 @@
       <c r="W139" s="4" t="inlineStr"/>
       <c r="X139" s="4" t="inlineStr"/>
       <c r="Y139" s="5" t="n">
-        <v>46186.22807308983</v>
+        <v>46186.23290201813</v>
       </c>
       <c r="Z139" s="4" t="inlineStr"/>
     </row>
@@ -9451,7 +9475,7 @@
       <c r="W140" s="4" t="inlineStr"/>
       <c r="X140" s="4" t="inlineStr"/>
       <c r="Y140" s="5" t="n">
-        <v>46186.22807309005</v>
+        <v>46186.23290201833</v>
       </c>
       <c r="Z140" s="4" t="inlineStr"/>
     </row>
@@ -9519,7 +9543,7 @@
       <c r="W141" s="4" t="inlineStr"/>
       <c r="X141" s="4" t="inlineStr"/>
       <c r="Y141" s="5" t="n">
-        <v>46186.22807309024</v>
+        <v>46186.23290201854</v>
       </c>
       <c r="Z141" s="4" t="inlineStr"/>
     </row>
@@ -9587,7 +9611,7 @@
       <c r="W142" s="4" t="inlineStr"/>
       <c r="X142" s="4" t="inlineStr"/>
       <c r="Y142" s="5" t="n">
-        <v>46186.22807309044</v>
+        <v>46186.23290201875</v>
       </c>
       <c r="Z142" s="4" t="inlineStr"/>
     </row>
@@ -9655,7 +9679,7 @@
       <c r="W143" s="4" t="inlineStr"/>
       <c r="X143" s="4" t="inlineStr"/>
       <c r="Y143" s="5" t="n">
-        <v>46186.22807309066</v>
+        <v>46186.23290201898</v>
       </c>
       <c r="Z143" s="4" t="inlineStr"/>
     </row>
@@ -9723,7 +9747,7 @@
       <c r="W144" s="4" t="inlineStr"/>
       <c r="X144" s="4" t="inlineStr"/>
       <c r="Y144" s="5" t="n">
-        <v>46186.22807309087</v>
+        <v>46186.2329020192</v>
       </c>
       <c r="Z144" s="4" t="inlineStr"/>
     </row>
@@ -9791,7 +9815,7 @@
       <c r="W145" s="4" t="inlineStr"/>
       <c r="X145" s="4" t="inlineStr"/>
       <c r="Y145" s="5" t="n">
-        <v>46186.22807309136</v>
+        <v>46186.23290201942</v>
       </c>
       <c r="Z145" s="4" t="inlineStr"/>
     </row>
@@ -9859,7 +9883,7 @@
       <c r="W146" s="4" t="inlineStr"/>
       <c r="X146" s="4" t="inlineStr"/>
       <c r="Y146" s="5" t="n">
-        <v>46186.22807309186</v>
+        <v>46186.23290201962</v>
       </c>
       <c r="Z146" s="4" t="inlineStr"/>
     </row>
@@ -9927,7 +9951,7 @@
       <c r="W147" s="8" t="inlineStr"/>
       <c r="X147" s="8" t="inlineStr"/>
       <c r="Y147" s="9" t="n">
-        <v>46186.22807309224</v>
+        <v>46186.23290201993</v>
       </c>
       <c r="Z147" s="8" t="inlineStr"/>
     </row>
@@ -9995,7 +10019,7 @@
       <c r="W148" s="8" t="inlineStr"/>
       <c r="X148" s="8" t="inlineStr"/>
       <c r="Y148" s="9" t="n">
-        <v>46186.22807309263</v>
+        <v>46186.23290202021</v>
       </c>
       <c r="Z148" s="8" t="inlineStr"/>
     </row>
@@ -10063,7 +10087,7 @@
       <c r="W149" s="8" t="inlineStr"/>
       <c r="X149" s="8" t="inlineStr"/>
       <c r="Y149" s="9" t="n">
-        <v>46186.22807309308</v>
+        <v>46186.23290202087</v>
       </c>
       <c r="Z149" s="8" t="inlineStr"/>
     </row>
@@ -10131,7 +10155,7 @@
       <c r="W150" s="8" t="inlineStr"/>
       <c r="X150" s="8" t="inlineStr"/>
       <c r="Y150" s="9" t="n">
-        <v>46186.22807309341</v>
+        <v>46186.23290202131</v>
       </c>
       <c r="Z150" s="8" t="inlineStr"/>
     </row>
@@ -10199,7 +10223,7 @@
       <c r="W151" s="4" t="inlineStr"/>
       <c r="X151" s="4" t="inlineStr"/>
       <c r="Y151" s="5" t="n">
-        <v>46186.22807309363</v>
+        <v>46186.23290202158</v>
       </c>
       <c r="Z151" s="4" t="inlineStr"/>
     </row>
@@ -10267,7 +10291,7 @@
       <c r="W152" s="8" t="inlineStr"/>
       <c r="X152" s="8" t="inlineStr"/>
       <c r="Y152" s="9" t="n">
-        <v>46186.22807309389</v>
+        <v>46186.23290202185</v>
       </c>
       <c r="Z152" s="8" t="inlineStr"/>
     </row>
@@ -10319,7 +10343,7 @@
       <c r="W153" s="8" t="inlineStr"/>
       <c r="X153" s="8" t="inlineStr"/>
       <c r="Y153" s="9" t="n">
-        <v>46186.22807309419</v>
+        <v>46186.23290202217</v>
       </c>
       <c r="Z153" s="8" t="inlineStr"/>
     </row>
@@ -10387,7 +10411,7 @@
       <c r="W154" s="8" t="inlineStr"/>
       <c r="X154" s="8" t="inlineStr"/>
       <c r="Y154" s="9" t="n">
-        <v>46186.22807309448</v>
+        <v>46186.23290202246</v>
       </c>
       <c r="Z154" s="8" t="inlineStr"/>
     </row>
@@ -10459,7 +10483,7 @@
       <c r="W155" s="8" t="inlineStr"/>
       <c r="X155" s="8" t="inlineStr"/>
       <c r="Y155" s="9" t="n">
-        <v>46186.22807309475</v>
+        <v>46186.23290202272</v>
       </c>
       <c r="Z155" s="8" t="inlineStr"/>
     </row>
@@ -10515,7 +10539,7 @@
       <c r="W156" s="4" t="inlineStr"/>
       <c r="X156" s="4" t="inlineStr"/>
       <c r="Y156" s="5" t="n">
-        <v>46186.22807309496</v>
+        <v>46186.23290202293</v>
       </c>
       <c r="Z156" s="4" t="inlineStr"/>
     </row>
@@ -10571,7 +10595,7 @@
       <c r="W157" s="4" t="inlineStr"/>
       <c r="X157" s="4" t="inlineStr"/>
       <c r="Y157" s="5" t="n">
-        <v>46186.22807309514</v>
+        <v>46186.23290202311</v>
       </c>
       <c r="Z157" s="4" t="inlineStr"/>
     </row>
@@ -10627,7 +10651,7 @@
       <c r="W158" s="4" t="inlineStr"/>
       <c r="X158" s="4" t="inlineStr"/>
       <c r="Y158" s="5" t="n">
-        <v>46186.22807309531</v>
+        <v>46186.23290202329</v>
       </c>
       <c r="Z158" s="4" t="inlineStr"/>
     </row>
@@ -10695,7 +10719,7 @@
       <c r="W159" s="8" t="inlineStr"/>
       <c r="X159" s="8" t="inlineStr"/>
       <c r="Y159" s="9" t="n">
-        <v>46186.22807309561</v>
+        <v>46186.23290202364</v>
       </c>
       <c r="Z159" s="8" t="inlineStr"/>
     </row>
@@ -10751,7 +10775,7 @@
       <c r="W160" s="8" t="inlineStr"/>
       <c r="X160" s="8" t="inlineStr"/>
       <c r="Y160" s="9" t="n">
-        <v>46186.22807309589</v>
+        <v>46186.23290202391</v>
       </c>
       <c r="Z160" s="8" t="inlineStr"/>
     </row>
@@ -10807,7 +10831,7 @@
       <c r="W161" s="8" t="inlineStr"/>
       <c r="X161" s="8" t="inlineStr"/>
       <c r="Y161" s="9" t="n">
-        <v>46186.2280730961</v>
+        <v>46186.23290202411</v>
       </c>
       <c r="Z161" s="8" t="inlineStr"/>
     </row>
@@ -10863,7 +10887,7 @@
       <c r="W162" s="8" t="inlineStr"/>
       <c r="X162" s="8" t="inlineStr"/>
       <c r="Y162" s="9" t="n">
-        <v>46186.22807309631</v>
+        <v>46186.23290202431</v>
       </c>
       <c r="Z162" s="8" t="inlineStr"/>
     </row>
@@ -10919,7 +10943,7 @@
       <c r="W163" s="8" t="inlineStr"/>
       <c r="X163" s="8" t="inlineStr"/>
       <c r="Y163" s="9" t="n">
-        <v>46186.22807309655</v>
+        <v>46186.23290202452</v>
       </c>
       <c r="Z163" s="8" t="inlineStr"/>
     </row>
@@ -10987,7 +11011,7 @@
       <c r="W164" s="8" t="inlineStr"/>
       <c r="X164" s="8" t="inlineStr"/>
       <c r="Y164" s="9" t="n">
-        <v>46186.22807309689</v>
+        <v>46186.23290202481</v>
       </c>
       <c r="Z164" s="8" t="inlineStr"/>
     </row>
@@ -11055,7 +11079,7 @@
       <c r="W165" s="8" t="inlineStr"/>
       <c r="X165" s="8" t="inlineStr"/>
       <c r="Y165" s="9" t="n">
-        <v>46186.22807309715</v>
+        <v>46186.23290202507</v>
       </c>
       <c r="Z165" s="8" t="inlineStr"/>
     </row>
@@ -11127,7 +11151,7 @@
       <c r="W166" s="8" t="inlineStr"/>
       <c r="X166" s="8" t="inlineStr"/>
       <c r="Y166" s="9" t="n">
-        <v>46186.22807309739</v>
+        <v>46186.23290202531</v>
       </c>
       <c r="Z166" s="8" t="inlineStr"/>
     </row>
@@ -11199,7 +11223,7 @@
       <c r="W167" s="8" t="inlineStr"/>
       <c r="X167" s="8" t="inlineStr"/>
       <c r="Y167" s="9" t="n">
-        <v>46186.22807309767</v>
+        <v>46186.23290202559</v>
       </c>
       <c r="Z167" s="8" t="inlineStr"/>
     </row>
@@ -11271,7 +11295,7 @@
       <c r="W168" s="8" t="inlineStr"/>
       <c r="X168" s="8" t="inlineStr"/>
       <c r="Y168" s="9" t="n">
-        <v>46186.22807309802</v>
+        <v>46186.23290202585</v>
       </c>
       <c r="Z168" s="8" t="inlineStr"/>
     </row>
@@ -11327,7 +11351,7 @@
       <c r="W169" s="8" t="inlineStr"/>
       <c r="X169" s="8" t="inlineStr"/>
       <c r="Y169" s="9" t="n">
-        <v>46186.22807309827</v>
+        <v>46186.23290202607</v>
       </c>
       <c r="Z169" s="8" t="inlineStr"/>
     </row>
@@ -11383,7 +11407,7 @@
       <c r="W170" s="8" t="inlineStr"/>
       <c r="X170" s="8" t="inlineStr"/>
       <c r="Y170" s="9" t="n">
-        <v>46186.22807309852</v>
+        <v>46186.23290202674</v>
       </c>
       <c r="Z170" s="8" t="inlineStr"/>
     </row>
@@ -11451,7 +11475,7 @@
       <c r="W171" s="8" t="inlineStr"/>
       <c r="X171" s="8" t="inlineStr"/>
       <c r="Y171" s="9" t="n">
-        <v>46186.22807309932</v>
+        <v>46186.23290202718</v>
       </c>
       <c r="Z171" s="8" t="inlineStr"/>
     </row>
@@ -11519,7 +11543,7 @@
       <c r="W172" s="8" t="inlineStr"/>
       <c r="X172" s="8" t="inlineStr"/>
       <c r="Y172" s="9" t="n">
-        <v>46186.22807309977</v>
+        <v>46186.23290202751</v>
       </c>
       <c r="Z172" s="8" t="inlineStr"/>
     </row>
@@ -11587,7 +11611,7 @@
       <c r="W173" s="8" t="inlineStr"/>
       <c r="X173" s="8" t="inlineStr"/>
       <c r="Y173" s="9" t="n">
-        <v>46186.22807310021</v>
+        <v>46186.23290202777</v>
       </c>
       <c r="Z173" s="8" t="inlineStr"/>
     </row>
@@ -11655,7 +11679,7 @@
       <c r="W174" s="8" t="inlineStr"/>
       <c r="X174" s="8" t="inlineStr"/>
       <c r="Y174" s="9" t="n">
-        <v>46186.22807310057</v>
+        <v>46186.23290202807</v>
       </c>
       <c r="Z174" s="8" t="inlineStr"/>
     </row>
@@ -11723,7 +11747,7 @@
       <c r="W175" s="8" t="inlineStr"/>
       <c r="X175" s="8" t="inlineStr"/>
       <c r="Y175" s="9" t="n">
-        <v>46186.22807310117</v>
+        <v>46186.23290202837</v>
       </c>
       <c r="Z175" s="8" t="inlineStr"/>
     </row>
@@ -11791,7 +11815,7 @@
       <c r="W176" s="8" t="inlineStr"/>
       <c r="X176" s="8" t="inlineStr"/>
       <c r="Y176" s="9" t="n">
-        <v>46186.22807310182</v>
+        <v>46186.23290202862</v>
       </c>
       <c r="Z176" s="8" t="inlineStr"/>
     </row>
@@ -11859,7 +11883,7 @@
       <c r="W177" s="8" t="inlineStr"/>
       <c r="X177" s="8" t="inlineStr"/>
       <c r="Y177" s="9" t="n">
-        <v>46186.22807310221</v>
+        <v>46186.23290202887</v>
       </c>
       <c r="Z177" s="8" t="inlineStr"/>
     </row>
@@ -11927,7 +11951,7 @@
       <c r="W178" s="8" t="inlineStr"/>
       <c r="X178" s="8" t="inlineStr"/>
       <c r="Y178" s="9" t="n">
-        <v>46186.2280731025</v>
+        <v>46186.23290202911</v>
       </c>
       <c r="Z178" s="8" t="inlineStr"/>
     </row>
@@ -11995,7 +12019,7 @@
       <c r="W179" s="8" t="inlineStr"/>
       <c r="X179" s="8" t="inlineStr"/>
       <c r="Y179" s="9" t="n">
-        <v>46186.22807310325</v>
+        <v>46186.23290202933</v>
       </c>
       <c r="Z179" s="8" t="inlineStr"/>
     </row>
@@ -12051,7 +12075,7 @@
       <c r="W180" s="4" t="inlineStr"/>
       <c r="X180" s="4" t="inlineStr"/>
       <c r="Y180" s="5" t="n">
-        <v>46186.22807310364</v>
+        <v>46186.23290202952</v>
       </c>
       <c r="Z180" s="4" t="inlineStr"/>
     </row>
@@ -12103,7 +12127,7 @@
       <c r="W181" s="8" t="inlineStr"/>
       <c r="X181" s="8" t="inlineStr"/>
       <c r="Y181" s="9" t="n">
-        <v>46186.22807310405</v>
+        <v>46186.23290202978</v>
       </c>
       <c r="Z181" s="8" t="inlineStr"/>
     </row>
@@ -12171,7 +12195,7 @@
       <c r="W182" s="8" t="inlineStr"/>
       <c r="X182" s="8" t="inlineStr"/>
       <c r="Y182" s="9" t="n">
-        <v>46186.22807310439</v>
+        <v>46186.23290203007</v>
       </c>
       <c r="Z182" s="8" t="inlineStr"/>
     </row>
@@ -12239,7 +12263,7 @@
       <c r="W183" s="8" t="inlineStr"/>
       <c r="X183" s="8" t="inlineStr"/>
       <c r="Y183" s="9" t="n">
-        <v>46186.22807310474</v>
+        <v>46186.23290203038</v>
       </c>
       <c r="Z183" s="8" t="inlineStr"/>
     </row>
@@ -12311,7 +12335,7 @@
       <c r="W184" s="4" t="inlineStr"/>
       <c r="X184" s="4" t="inlineStr"/>
       <c r="Y184" s="5" t="n">
-        <v>46186.22807310527</v>
+        <v>46186.23290203095</v>
       </c>
       <c r="Z184" s="4" t="inlineStr"/>
     </row>
@@ -12383,7 +12407,7 @@
       <c r="W185" s="4" t="inlineStr"/>
       <c r="X185" s="4" t="inlineStr"/>
       <c r="Y185" s="5" t="n">
-        <v>46186.22807310562</v>
+        <v>46186.23290203128</v>
       </c>
       <c r="Z185" s="4" t="inlineStr"/>
     </row>
@@ -12455,7 +12479,7 @@
       <c r="W186" s="4" t="inlineStr"/>
       <c r="X186" s="4" t="inlineStr"/>
       <c r="Y186" s="5" t="n">
-        <v>46186.22807310584</v>
+        <v>46186.2329020315</v>
       </c>
       <c r="Z186" s="4" t="inlineStr"/>
     </row>
@@ -12511,7 +12535,7 @@
       <c r="W187" s="4" t="inlineStr"/>
       <c r="X187" s="4" t="inlineStr"/>
       <c r="Y187" s="5" t="n">
-        <v>46186.22807310604</v>
+        <v>46186.2329020317</v>
       </c>
       <c r="Z187" s="4" t="inlineStr"/>
     </row>
@@ -12583,7 +12607,7 @@
       <c r="W188" s="4" t="inlineStr"/>
       <c r="X188" s="4" t="inlineStr"/>
       <c r="Y188" s="5" t="n">
-        <v>46186.22807310624</v>
+        <v>46186.23290203189</v>
       </c>
       <c r="Z188" s="4" t="inlineStr"/>
     </row>
@@ -12655,7 +12679,7 @@
       <c r="W189" s="4" t="inlineStr"/>
       <c r="X189" s="4" t="inlineStr"/>
       <c r="Y189" s="5" t="n">
-        <v>46186.22807310642</v>
+        <v>46186.23290203207</v>
       </c>
       <c r="Z189" s="4" t="inlineStr"/>
     </row>
@@ -12727,7 +12751,7 @@
       <c r="W190" s="4" t="inlineStr"/>
       <c r="X190" s="4" t="inlineStr"/>
       <c r="Y190" s="5" t="n">
-        <v>46186.2280731066</v>
+        <v>46186.23290203224</v>
       </c>
       <c r="Z190" s="4" t="inlineStr"/>
     </row>
@@ -12799,7 +12823,7 @@
       <c r="W191" s="4" t="inlineStr"/>
       <c r="X191" s="4" t="inlineStr"/>
       <c r="Y191" s="5" t="n">
-        <v>46186.22807310677</v>
+        <v>46186.23290203242</v>
       </c>
       <c r="Z191" s="4" t="inlineStr"/>
     </row>
@@ -12871,7 +12895,7 @@
       <c r="W192" s="4" t="inlineStr"/>
       <c r="X192" s="4" t="inlineStr"/>
       <c r="Y192" s="5" t="n">
-        <v>46186.22807310693</v>
+        <v>46186.23290203258</v>
       </c>
       <c r="Z192" s="4" t="inlineStr"/>
     </row>
@@ -12939,7 +12963,7 @@
       <c r="W193" s="8" t="inlineStr"/>
       <c r="X193" s="8" t="inlineStr"/>
       <c r="Y193" s="9" t="n">
-        <v>46186.22807310719</v>
+        <v>46186.23290203283</v>
       </c>
       <c r="Z193" s="8" t="inlineStr"/>
     </row>
@@ -13011,7 +13035,7 @@
       <c r="W194" s="8" t="inlineStr"/>
       <c r="X194" s="8" t="inlineStr"/>
       <c r="Y194" s="9" t="n">
-        <v>46186.2280731076</v>
+        <v>46186.23290203354</v>
       </c>
       <c r="Z194" s="8" t="inlineStr"/>
     </row>
@@ -13079,7 +13103,7 @@
       <c r="W195" s="8" t="inlineStr"/>
       <c r="X195" s="8" t="inlineStr"/>
       <c r="Y195" s="9" t="n">
-        <v>46186.22807310789</v>
+        <v>46186.23290203394</v>
       </c>
       <c r="Z195" s="8" t="inlineStr"/>
     </row>
@@ -13135,7 +13159,7 @@
       <c r="W196" s="8" t="inlineStr"/>
       <c r="X196" s="8" t="inlineStr"/>
       <c r="Y196" s="9" t="n">
-        <v>46186.22807310819</v>
+        <v>46186.2329020342</v>
       </c>
       <c r="Z196" s="8" t="inlineStr"/>
     </row>
@@ -13155,7 +13179,11 @@
           <t>Re: Package Submission - DCP3 - Geotechnical - Technical Note-Working Pile Load Test at BG34 (GLE03) (SOP-65 and SOP-154): DE.ELS.GE03.GEO.G1.D3_Rev C04</t>
         </is>
       </c>
-      <c r="F197" s="8" t="inlineStr"/>
+      <c r="F197" s="8" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
       <c r="G197" s="8" t="inlineStr"/>
       <c r="H197" s="8" t="inlineStr"/>
       <c r="I197" s="8" t="inlineStr"/>
@@ -13187,7 +13215,7 @@
       <c r="W197" s="8" t="inlineStr"/>
       <c r="X197" s="8" t="inlineStr"/>
       <c r="Y197" s="9" t="n">
-        <v>46186.22807310856</v>
+        <v>46186.23290203446</v>
       </c>
       <c r="Z197" s="8" t="inlineStr"/>
     </row>
@@ -13239,7 +13267,7 @@
       <c r="W198" s="8" t="inlineStr"/>
       <c r="X198" s="8" t="inlineStr"/>
       <c r="Y198" s="9" t="n">
-        <v>46186.22807310878</v>
+        <v>46186.23290203467</v>
       </c>
       <c r="Z198" s="8" t="inlineStr"/>
     </row>
@@ -13307,7 +13335,7 @@
       <c r="W199" s="8" t="inlineStr"/>
       <c r="X199" s="8" t="inlineStr"/>
       <c r="Y199" s="9" t="n">
-        <v>46186.22807310907</v>
+        <v>46186.23290203494</v>
       </c>
       <c r="Z199" s="8" t="inlineStr"/>
     </row>
@@ -13363,7 +13391,7 @@
       <c r="W200" s="8" t="inlineStr"/>
       <c r="X200" s="8" t="inlineStr"/>
       <c r="Y200" s="9" t="n">
-        <v>46186.22807310931</v>
+        <v>46186.23290203526</v>
       </c>
       <c r="Z200" s="8" t="inlineStr"/>
     </row>
@@ -13419,7 +13447,7 @@
       <c r="W201" s="8" t="inlineStr"/>
       <c r="X201" s="8" t="inlineStr"/>
       <c r="Y201" s="9" t="n">
-        <v>46186.2280731096</v>
+        <v>46186.2329020355</v>
       </c>
       <c r="Z201" s="8" t="inlineStr"/>
     </row>
@@ -13487,7 +13515,7 @@
       <c r="W202" s="4" t="inlineStr"/>
       <c r="X202" s="4" t="inlineStr"/>
       <c r="Y202" s="5" t="n">
-        <v>46186.22807310987</v>
+        <v>46186.23290203574</v>
       </c>
       <c r="Z202" s="4" t="inlineStr"/>
     </row>
@@ -13543,7 +13571,7 @@
       <c r="W203" s="4" t="inlineStr"/>
       <c r="X203" s="4" t="inlineStr"/>
       <c r="Y203" s="5" t="n">
-        <v>46186.22807311007</v>
+        <v>46186.23290203592</v>
       </c>
       <c r="Z203" s="4" t="inlineStr"/>
     </row>
@@ -13611,7 +13639,7 @@
       <c r="W204" s="4" t="inlineStr"/>
       <c r="X204" s="4" t="inlineStr"/>
       <c r="Y204" s="5" t="n">
-        <v>46186.22807311031</v>
+        <v>46186.23290203614</v>
       </c>
       <c r="Z204" s="4" t="inlineStr"/>
     </row>
@@ -13679,7 +13707,7 @@
       <c r="W205" s="4" t="inlineStr"/>
       <c r="X205" s="4" t="inlineStr"/>
       <c r="Y205" s="5" t="n">
-        <v>46186.22807311058</v>
+        <v>46186.23290203649</v>
       </c>
       <c r="Z205" s="4" t="inlineStr"/>
     </row>
@@ -13747,7 +13775,7 @@
       <c r="W206" s="4" t="inlineStr"/>
       <c r="X206" s="4" t="inlineStr"/>
       <c r="Y206" s="5" t="n">
-        <v>46186.22807311083</v>
+        <v>46186.23290203685</v>
       </c>
       <c r="Z206" s="4" t="inlineStr"/>
     </row>
@@ -13803,7 +13831,7 @@
       <c r="W207" s="4" t="inlineStr"/>
       <c r="X207" s="4" t="inlineStr"/>
       <c r="Y207" s="5" t="n">
-        <v>46186.22807311105</v>
+        <v>46186.23290203721</v>
       </c>
       <c r="Z207" s="4" t="inlineStr"/>
     </row>
@@ -13859,7 +13887,7 @@
       <c r="W208" s="4" t="inlineStr"/>
       <c r="X208" s="4" t="inlineStr"/>
       <c r="Y208" s="5" t="n">
-        <v>46186.22807311125</v>
+        <v>46186.23290203772</v>
       </c>
       <c r="Z208" s="4" t="inlineStr"/>
     </row>
@@ -13915,7 +13943,7 @@
       <c r="W209" s="4" t="inlineStr"/>
       <c r="X209" s="4" t="inlineStr"/>
       <c r="Y209" s="5" t="n">
-        <v>46186.22807311144</v>
+        <v>46186.23290203849</v>
       </c>
       <c r="Z209" s="4" t="inlineStr"/>
     </row>
@@ -13983,7 +14011,7 @@
       <c r="W210" s="4" t="inlineStr"/>
       <c r="X210" s="4" t="inlineStr"/>
       <c r="Y210" s="5" t="n">
-        <v>46186.22807311167</v>
+        <v>46186.23290203877</v>
       </c>
       <c r="Z210" s="4" t="inlineStr"/>
     </row>
@@ -14051,7 +14079,7 @@
       <c r="W211" s="4" t="inlineStr"/>
       <c r="X211" s="4" t="inlineStr"/>
       <c r="Y211" s="5" t="n">
-        <v>46186.2280731119</v>
+        <v>46186.23290203902</v>
       </c>
       <c r="Z211" s="4" t="inlineStr"/>
     </row>
@@ -14119,7 +14147,7 @@
       <c r="W212" s="4" t="inlineStr"/>
       <c r="X212" s="4" t="inlineStr"/>
       <c r="Y212" s="5" t="n">
-        <v>46186.22807311211</v>
+        <v>46186.23290203924</v>
       </c>
       <c r="Z212" s="4" t="inlineStr"/>
     </row>
@@ -14187,7 +14215,7 @@
       <c r="W213" s="4" t="inlineStr"/>
       <c r="X213" s="4" t="inlineStr"/>
       <c r="Y213" s="5" t="n">
-        <v>46186.22807311234</v>
+        <v>46186.23290203947</v>
       </c>
       <c r="Z213" s="4" t="inlineStr"/>
     </row>
@@ -14255,7 +14283,7 @@
       <c r="W214" s="4" t="inlineStr"/>
       <c r="X214" s="4" t="inlineStr"/>
       <c r="Y214" s="5" t="n">
-        <v>46186.22807311256</v>
+        <v>46186.23290203968</v>
       </c>
       <c r="Z214" s="4" t="inlineStr"/>
     </row>
@@ -14323,7 +14351,7 @@
       <c r="W215" s="4" t="inlineStr"/>
       <c r="X215" s="4" t="inlineStr"/>
       <c r="Y215" s="5" t="n">
-        <v>46186.22807311279</v>
+        <v>46186.23290203992</v>
       </c>
       <c r="Z215" s="4" t="inlineStr"/>
     </row>
@@ -14379,7 +14407,7 @@
       <c r="W216" s="4" t="inlineStr"/>
       <c r="X216" s="4" t="inlineStr"/>
       <c r="Y216" s="5" t="n">
-        <v>46186.22807311297</v>
+        <v>46186.23290204012</v>
       </c>
       <c r="Z216" s="4" t="inlineStr"/>
     </row>
@@ -14435,7 +14463,7 @@
       <c r="W217" s="4" t="inlineStr"/>
       <c r="X217" s="4" t="inlineStr"/>
       <c r="Y217" s="5" t="n">
-        <v>46186.22807311316</v>
+        <v>46186.2329020403</v>
       </c>
       <c r="Z217" s="4" t="inlineStr"/>
     </row>
@@ -14491,7 +14519,7 @@
       <c r="W218" s="4" t="inlineStr"/>
       <c r="X218" s="4" t="inlineStr"/>
       <c r="Y218" s="5" t="n">
-        <v>46186.22807311334</v>
+        <v>46186.23290204046</v>
       </c>
       <c r="Z218" s="4" t="inlineStr"/>
     </row>
@@ -14547,7 +14575,7 @@
       <c r="W219" s="4" t="inlineStr"/>
       <c r="X219" s="4" t="inlineStr"/>
       <c r="Y219" s="5" t="n">
-        <v>46186.2280731135</v>
+        <v>46186.23290204061</v>
       </c>
       <c r="Z219" s="4" t="inlineStr"/>
     </row>
@@ -14615,7 +14643,7 @@
       <c r="W220" s="4" t="inlineStr"/>
       <c r="X220" s="4" t="inlineStr"/>
       <c r="Y220" s="5" t="n">
-        <v>46186.22807311373</v>
+        <v>46186.23290204082</v>
       </c>
       <c r="Z220" s="4" t="inlineStr"/>
     </row>
@@ -14683,7 +14711,7 @@
       <c r="W221" s="4" t="inlineStr"/>
       <c r="X221" s="4" t="inlineStr"/>
       <c r="Y221" s="5" t="n">
-        <v>46186.22807311393</v>
+        <v>46186.23290204106</v>
       </c>
       <c r="Z221" s="4" t="inlineStr"/>
     </row>
@@ -14751,7 +14779,7 @@
       <c r="W222" s="4" t="inlineStr"/>
       <c r="X222" s="4" t="inlineStr"/>
       <c r="Y222" s="5" t="n">
-        <v>46186.22807311414</v>
+        <v>46186.23290204129</v>
       </c>
       <c r="Z222" s="4" t="inlineStr"/>
     </row>
@@ -14819,7 +14847,7 @@
       <c r="W223" s="4" t="inlineStr"/>
       <c r="X223" s="4" t="inlineStr"/>
       <c r="Y223" s="5" t="n">
-        <v>46186.22807311475</v>
+        <v>46186.23290204151</v>
       </c>
       <c r="Z223" s="4" t="inlineStr"/>
     </row>
@@ -14887,7 +14915,7 @@
       <c r="W224" s="4" t="inlineStr"/>
       <c r="X224" s="4" t="inlineStr"/>
       <c r="Y224" s="5" t="n">
-        <v>46186.22807311507</v>
+        <v>46186.23290204172</v>
       </c>
       <c r="Z224" s="4" t="inlineStr"/>
     </row>
@@ -14955,7 +14983,7 @@
       <c r="W225" s="4" t="inlineStr"/>
       <c r="X225" s="4" t="inlineStr"/>
       <c r="Y225" s="5" t="n">
-        <v>46186.22807311534</v>
+        <v>46186.23290204192</v>
       </c>
       <c r="Z225" s="4" t="inlineStr"/>
     </row>
@@ -15023,7 +15051,7 @@
       <c r="W226" s="4" t="inlineStr"/>
       <c r="X226" s="4" t="inlineStr"/>
       <c r="Y226" s="5" t="n">
-        <v>46186.22807311554</v>
+        <v>46186.23290204212</v>
       </c>
       <c r="Z226" s="4" t="inlineStr"/>
     </row>
@@ -15091,7 +15119,7 @@
       <c r="W227" s="4" t="inlineStr"/>
       <c r="X227" s="4" t="inlineStr"/>
       <c r="Y227" s="5" t="n">
-        <v>46186.22807311575</v>
+        <v>46186.23290204229</v>
       </c>
       <c r="Z227" s="4" t="inlineStr"/>
     </row>
@@ -15159,7 +15187,7 @@
       <c r="W228" s="4" t="inlineStr"/>
       <c r="X228" s="4" t="inlineStr"/>
       <c r="Y228" s="5" t="n">
-        <v>46186.22807311598</v>
+        <v>46186.2329020425</v>
       </c>
       <c r="Z228" s="4" t="inlineStr"/>
     </row>
@@ -15211,7 +15239,7 @@
       <c r="W229" s="4" t="inlineStr"/>
       <c r="X229" s="4" t="inlineStr"/>
       <c r="Y229" s="5" t="n">
-        <v>46186.22807311622</v>
+        <v>46186.23290204272</v>
       </c>
       <c r="Z229" s="4" t="inlineStr"/>
     </row>
@@ -15279,7 +15307,7 @@
       <c r="W230" s="4" t="inlineStr"/>
       <c r="X230" s="4" t="inlineStr"/>
       <c r="Y230" s="5" t="n">
-        <v>46186.22807311645</v>
+        <v>46186.23290204294</v>
       </c>
       <c r="Z230" s="4" t="inlineStr"/>
     </row>
@@ -15351,7 +15379,7 @@
       <c r="W231" s="4" t="inlineStr"/>
       <c r="X231" s="4" t="inlineStr"/>
       <c r="Y231" s="5" t="n">
-        <v>46186.22807311667</v>
+        <v>46186.23290204319</v>
       </c>
       <c r="Z231" s="4" t="inlineStr"/>
     </row>
@@ -15419,7 +15447,7 @@
       <c r="W232" s="4" t="inlineStr"/>
       <c r="X232" s="4" t="inlineStr"/>
       <c r="Y232" s="5" t="n">
-        <v>46186.22807311686</v>
+        <v>46186.23290204338</v>
       </c>
       <c r="Z232" s="4" t="inlineStr"/>
     </row>
@@ -15475,7 +15503,7 @@
       <c r="W233" s="4" t="inlineStr"/>
       <c r="X233" s="4" t="inlineStr"/>
       <c r="Y233" s="5" t="n">
-        <v>46186.22807311705</v>
+        <v>46186.23290204356</v>
       </c>
       <c r="Z233" s="4" t="inlineStr"/>
     </row>
@@ -15543,7 +15571,7 @@
       <c r="W234" s="4" t="inlineStr"/>
       <c r="X234" s="4" t="inlineStr"/>
       <c r="Y234" s="5" t="n">
-        <v>46186.22807311752</v>
+        <v>46186.23290204392</v>
       </c>
       <c r="Z234" s="4" t="inlineStr"/>
     </row>
@@ -15611,7 +15639,7 @@
       <c r="W235" s="4" t="inlineStr"/>
       <c r="X235" s="4" t="inlineStr"/>
       <c r="Y235" s="5" t="n">
-        <v>46186.22807311793</v>
+        <v>46186.23290204419</v>
       </c>
       <c r="Z235" s="4" t="inlineStr"/>
     </row>
@@ -15679,7 +15707,7 @@
       <c r="W236" s="4" t="inlineStr"/>
       <c r="X236" s="4" t="inlineStr"/>
       <c r="Y236" s="5" t="n">
-        <v>46186.22807311828</v>
+        <v>46186.23290204446</v>
       </c>
       <c r="Z236" s="4" t="inlineStr"/>
     </row>
@@ -15747,7 +15775,7 @@
       <c r="W237" s="4" t="inlineStr"/>
       <c r="X237" s="4" t="inlineStr"/>
       <c r="Y237" s="5" t="n">
-        <v>46186.22807311855</v>
+        <v>46186.23290204468</v>
       </c>
       <c r="Z237" s="4" t="inlineStr"/>
     </row>
@@ -15815,7 +15843,7 @@
       <c r="W238" s="4" t="inlineStr"/>
       <c r="X238" s="4" t="inlineStr"/>
       <c r="Y238" s="5" t="n">
-        <v>46186.22807311881</v>
+        <v>46186.23290204495</v>
       </c>
       <c r="Z238" s="4" t="inlineStr"/>
     </row>
@@ -15883,7 +15911,7 @@
       <c r="W239" s="4" t="inlineStr"/>
       <c r="X239" s="4" t="inlineStr"/>
       <c r="Y239" s="5" t="n">
-        <v>46186.22807311904</v>
+        <v>46186.23290204531</v>
       </c>
       <c r="Z239" s="4" t="inlineStr"/>
     </row>
@@ -15951,7 +15979,7 @@
       <c r="W240" s="4" t="inlineStr"/>
       <c r="X240" s="4" t="inlineStr"/>
       <c r="Y240" s="5" t="n">
-        <v>46186.2280731193</v>
+        <v>46186.23290204574</v>
       </c>
       <c r="Z240" s="4" t="inlineStr"/>
     </row>
@@ -16019,7 +16047,7 @@
       <c r="W241" s="4" t="inlineStr"/>
       <c r="X241" s="4" t="inlineStr"/>
       <c r="Y241" s="5" t="n">
-        <v>46186.22807311953</v>
+        <v>46186.23290204618</v>
       </c>
       <c r="Z241" s="4" t="inlineStr"/>
     </row>
@@ -16087,7 +16115,7 @@
       <c r="W242" s="8" t="inlineStr"/>
       <c r="X242" s="8" t="inlineStr"/>
       <c r="Y242" s="9" t="n">
-        <v>46186.22807311998</v>
+        <v>46186.23290204794</v>
       </c>
       <c r="Z242" s="8" t="inlineStr"/>
     </row>
@@ -16111,7 +16139,11 @@
           <t>Re: Specification Submission - DCP2 - Depot Equipment (DEP) - AD01, Bogie Lifting Equipment Preliminary Technical Specification (RLS.1.1.6.6.2.2) : MLCC-C0199-DEP-LHE-BGH-SPC-51063_Rev C03</t>
         </is>
       </c>
-      <c r="F243" s="8" t="inlineStr"/>
+      <c r="F243" s="8" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
       <c r="G243" s="8" t="inlineStr"/>
       <c r="H243" s="8" t="inlineStr">
         <is>
@@ -16155,7 +16187,7 @@
       <c r="W243" s="8" t="inlineStr"/>
       <c r="X243" s="8" t="inlineStr"/>
       <c r="Y243" s="9" t="n">
-        <v>46186.22807312026</v>
+        <v>46186.23290204839</v>
       </c>
       <c r="Z243" s="8" t="inlineStr"/>
     </row>
@@ -16227,7 +16259,7 @@
       <c r="W244" s="8" t="inlineStr"/>
       <c r="X244" s="8" t="inlineStr"/>
       <c r="Y244" s="9" t="n">
-        <v>46186.22807312053</v>
+        <v>46186.23290204869</v>
       </c>
       <c r="Z244" s="8" t="inlineStr"/>
     </row>
@@ -16295,7 +16327,7 @@
       <c r="W245" s="4" t="inlineStr"/>
       <c r="X245" s="4" t="inlineStr"/>
       <c r="Y245" s="5" t="n">
-        <v>46186.22807312076</v>
+        <v>46186.23290204893</v>
       </c>
       <c r="Z245" s="4" t="inlineStr"/>
     </row>
@@ -16363,7 +16395,7 @@
       <c r="W246" s="8" t="inlineStr"/>
       <c r="X246" s="8" t="inlineStr"/>
       <c r="Y246" s="9" t="n">
-        <v>46186.22807312106</v>
+        <v>46186.23290204923</v>
       </c>
       <c r="Z246" s="8" t="inlineStr"/>
     </row>
@@ -16431,7 +16463,7 @@
       <c r="W247" s="4" t="inlineStr"/>
       <c r="X247" s="4" t="inlineStr"/>
       <c r="Y247" s="5" t="n">
-        <v>46186.22807312132</v>
+        <v>46186.23290204992</v>
       </c>
       <c r="Z247" s="4" t="inlineStr"/>
     </row>
@@ -16487,7 +16519,7 @@
       <c r="W248" s="8" t="inlineStr"/>
       <c r="X248" s="8" t="inlineStr"/>
       <c r="Y248" s="9" t="n">
-        <v>46186.22807312157</v>
+        <v>46186.23290205027</v>
       </c>
       <c r="Z248" s="8" t="inlineStr"/>
     </row>
@@ -16555,7 +16587,7 @@
       <c r="W249" s="8" t="inlineStr"/>
       <c r="X249" s="8" t="inlineStr"/>
       <c r="Y249" s="9" t="n">
-        <v>46186.22807312184</v>
+        <v>46186.23290205056</v>
       </c>
       <c r="Z249" s="8" t="inlineStr"/>
     </row>
@@ -16611,7 +16643,7 @@
       <c r="W250" s="8" t="inlineStr"/>
       <c r="X250" s="8" t="inlineStr"/>
       <c r="Y250" s="9" t="n">
-        <v>46186.2280731221</v>
+        <v>46186.23290205081</v>
       </c>
       <c r="Z250" s="8" t="inlineStr"/>
     </row>
@@ -16683,7 +16715,7 @@
       <c r="W251" s="8" t="inlineStr"/>
       <c r="X251" s="8" t="inlineStr"/>
       <c r="Y251" s="9" t="n">
-        <v>46186.22807312233</v>
+        <v>46186.23290205105</v>
       </c>
       <c r="Z251" s="8" t="inlineStr"/>
     </row>
@@ -16751,7 +16783,7 @@
       <c r="W252" s="4" t="inlineStr"/>
       <c r="X252" s="4" t="inlineStr"/>
       <c r="Y252" s="5" t="n">
-        <v>46186.22807312257</v>
+        <v>46186.23290205132</v>
       </c>
       <c r="Z252" s="4" t="inlineStr"/>
     </row>
@@ -16819,7 +16851,7 @@
       <c r="W253" s="8" t="inlineStr"/>
       <c r="X253" s="8" t="inlineStr"/>
       <c r="Y253" s="9" t="n">
-        <v>46186.2280731229</v>
+        <v>46186.23290205164</v>
       </c>
       <c r="Z253" s="8" t="inlineStr"/>
     </row>
@@ -16887,7 +16919,7 @@
       <c r="W254" s="4" t="inlineStr"/>
       <c r="X254" s="4" t="inlineStr"/>
       <c r="Y254" s="5" t="n">
-        <v>46186.2280731231</v>
+        <v>46186.23290205185</v>
       </c>
       <c r="Z254" s="4" t="inlineStr"/>
     </row>
@@ -16959,7 +16991,7 @@
       <c r="W255" s="8" t="inlineStr"/>
       <c r="X255" s="8" t="inlineStr"/>
       <c r="Y255" s="9" t="n">
-        <v>46186.22807312337</v>
+        <v>46186.23290205212</v>
       </c>
       <c r="Z255" s="8" t="inlineStr"/>
     </row>
@@ -17027,7 +17059,7 @@
       <c r="W256" s="8" t="inlineStr"/>
       <c r="X256" s="8" t="inlineStr"/>
       <c r="Y256" s="9" t="n">
-        <v>46186.22807312363</v>
+        <v>46186.23290205238</v>
       </c>
       <c r="Z256" s="8" t="inlineStr"/>
     </row>
@@ -17099,7 +17131,7 @@
       <c r="W257" s="4" t="inlineStr"/>
       <c r="X257" s="4" t="inlineStr"/>
       <c r="Y257" s="5" t="n">
-        <v>46186.22807312383</v>
+        <v>46186.23290205257</v>
       </c>
       <c r="Z257" s="4" t="inlineStr"/>
     </row>
@@ -17155,7 +17187,7 @@
       <c r="W258" s="8" t="inlineStr"/>
       <c r="X258" s="8" t="inlineStr"/>
       <c r="Y258" s="9" t="n">
-        <v>46186.22807312406</v>
+        <v>46186.23290205283</v>
       </c>
       <c r="Z258" s="8" t="inlineStr"/>
     </row>
@@ -17223,7 +17255,7 @@
       <c r="W259" s="8" t="inlineStr"/>
       <c r="X259" s="8" t="inlineStr"/>
       <c r="Y259" s="9" t="n">
-        <v>46186.22807312434</v>
+        <v>46186.23290205309</v>
       </c>
       <c r="Z259" s="8" t="inlineStr"/>
     </row>
@@ -17295,7 +17327,7 @@
       <c r="W260" s="8" t="inlineStr"/>
       <c r="X260" s="8" t="inlineStr"/>
       <c r="Y260" s="9" t="n">
-        <v>46186.22807312459</v>
+        <v>46186.23290205334</v>
       </c>
       <c r="Z260" s="8" t="inlineStr"/>
     </row>
@@ -17351,7 +17383,7 @@
       <c r="W261" s="8" t="inlineStr"/>
       <c r="X261" s="8" t="inlineStr"/>
       <c r="Y261" s="9" t="n">
-        <v>46186.22807312482</v>
+        <v>46186.2329020536</v>
       </c>
       <c r="Z261" s="8" t="inlineStr"/>
     </row>
@@ -17423,7 +17455,7 @@
       <c r="W262" s="8" t="inlineStr"/>
       <c r="X262" s="8" t="inlineStr"/>
       <c r="Y262" s="9" t="n">
-        <v>46186.22807312507</v>
+        <v>46186.23290205385</v>
       </c>
       <c r="Z262" s="8" t="inlineStr"/>
     </row>
@@ -17479,7 +17511,7 @@
       <c r="W263" s="8" t="inlineStr"/>
       <c r="X263" s="8" t="inlineStr"/>
       <c r="Y263" s="9" t="n">
-        <v>46186.22807312531</v>
+        <v>46186.23290205409</v>
       </c>
       <c r="Z263" s="8" t="inlineStr"/>
     </row>
@@ -17535,7 +17567,7 @@
       <c r="W264" s="8" t="inlineStr"/>
       <c r="X264" s="8" t="inlineStr"/>
       <c r="Y264" s="9" t="n">
-        <v>46186.22807312553</v>
+        <v>46186.23290205432</v>
       </c>
       <c r="Z264" s="8" t="inlineStr"/>
     </row>
@@ -17603,7 +17635,7 @@
       <c r="W265" s="8" t="inlineStr"/>
       <c r="X265" s="8" t="inlineStr"/>
       <c r="Y265" s="9" t="n">
-        <v>46186.22807312576</v>
+        <v>46186.23290205455</v>
       </c>
       <c r="Z265" s="8" t="inlineStr"/>
     </row>
@@ -17671,7 +17703,7 @@
       <c r="W266" s="8" t="inlineStr"/>
       <c r="X266" s="8" t="inlineStr"/>
       <c r="Y266" s="9" t="n">
-        <v>46186.22807312648</v>
+        <v>46186.23290205479</v>
       </c>
       <c r="Z266" s="8" t="inlineStr"/>
     </row>
@@ -17739,7 +17771,7 @@
       <c r="W267" s="8" t="inlineStr"/>
       <c r="X267" s="8" t="inlineStr"/>
       <c r="Y267" s="9" t="n">
-        <v>46186.22807312677</v>
+        <v>46186.23290205502</v>
       </c>
       <c r="Z267" s="8" t="inlineStr"/>
     </row>
@@ -17807,7 +17839,7 @@
       <c r="W268" s="8" t="inlineStr"/>
       <c r="X268" s="8" t="inlineStr"/>
       <c r="Y268" s="9" t="n">
-        <v>46186.22807312707</v>
+        <v>46186.23290205526</v>
       </c>
       <c r="Z268" s="8" t="inlineStr"/>
     </row>
@@ -17875,7 +17907,7 @@
       <c r="W269" s="4" t="inlineStr"/>
       <c r="X269" s="4" t="inlineStr"/>
       <c r="Y269" s="5" t="n">
-        <v>46186.22807312736</v>
+        <v>46186.23290205582</v>
       </c>
       <c r="Z269" s="4" t="inlineStr"/>
     </row>
@@ -17943,7 +17975,7 @@
       <c r="W270" s="4" t="inlineStr"/>
       <c r="X270" s="4" t="inlineStr"/>
       <c r="Y270" s="5" t="n">
-        <v>46186.2280731276</v>
+        <v>46186.2329020562</v>
       </c>
       <c r="Z270" s="4" t="inlineStr"/>
     </row>
@@ -18011,7 +18043,7 @@
       <c r="W271" s="4" t="inlineStr"/>
       <c r="X271" s="4" t="inlineStr"/>
       <c r="Y271" s="5" t="n">
-        <v>46186.22807312784</v>
+        <v>46186.23290205644</v>
       </c>
       <c r="Z271" s="4" t="inlineStr"/>
     </row>
@@ -18079,7 +18111,7 @@
       <c r="W272" s="8" t="inlineStr"/>
       <c r="X272" s="8" t="inlineStr"/>
       <c r="Y272" s="9" t="n">
-        <v>46186.22807312811</v>
+        <v>46186.23290205671</v>
       </c>
       <c r="Z272" s="8" t="inlineStr"/>
     </row>
@@ -18135,7 +18167,7 @@
       <c r="W273" s="8" t="inlineStr"/>
       <c r="X273" s="8" t="inlineStr"/>
       <c r="Y273" s="9" t="n">
-        <v>46186.22807312844</v>
+        <v>46186.23290205703</v>
       </c>
       <c r="Z273" s="8" t="inlineStr"/>
     </row>
@@ -18207,7 +18239,7 @@
       <c r="W274" s="4" t="inlineStr"/>
       <c r="X274" s="4" t="inlineStr"/>
       <c r="Y274" s="5" t="n">
-        <v>46186.22807312868</v>
+        <v>46186.23290205727</v>
       </c>
       <c r="Z274" s="4" t="inlineStr"/>
     </row>
@@ -18275,7 +18307,7 @@
       <c r="W275" s="4" t="inlineStr"/>
       <c r="X275" s="4" t="inlineStr"/>
       <c r="Y275" s="5" t="n">
-        <v>46186.22807312889</v>
+        <v>46186.23290205748</v>
       </c>
       <c r="Z275" s="4" t="inlineStr"/>
     </row>
@@ -18343,7 +18375,7 @@
       <c r="W276" s="4" t="inlineStr"/>
       <c r="X276" s="4" t="inlineStr"/>
       <c r="Y276" s="5" t="n">
-        <v>46186.22807312909</v>
+        <v>46186.23290205767</v>
       </c>
       <c r="Z276" s="4" t="inlineStr"/>
     </row>
@@ -18399,7 +18431,7 @@
       <c r="W277" s="4" t="inlineStr"/>
       <c r="X277" s="4" t="inlineStr"/>
       <c r="Y277" s="5" t="n">
-        <v>46186.22807312926</v>
+        <v>46186.23290205785</v>
       </c>
       <c r="Z277" s="4" t="inlineStr"/>
     </row>
@@ -18467,7 +18499,7 @@
       <c r="W278" s="4" t="inlineStr"/>
       <c r="X278" s="4" t="inlineStr"/>
       <c r="Y278" s="5" t="n">
-        <v>46186.22807312946</v>
+        <v>46186.23290205806</v>
       </c>
       <c r="Z278" s="4" t="inlineStr"/>
     </row>
@@ -18539,7 +18571,7 @@
       <c r="W279" s="4" t="inlineStr"/>
       <c r="X279" s="4" t="inlineStr"/>
       <c r="Y279" s="5" t="n">
-        <v>46186.22807312966</v>
+        <v>46186.23290205834</v>
       </c>
       <c r="Z279" s="4" t="inlineStr"/>
     </row>
@@ -18611,7 +18643,7 @@
       <c r="W280" s="4" t="inlineStr"/>
       <c r="X280" s="4" t="inlineStr"/>
       <c r="Y280" s="5" t="n">
-        <v>46186.22807312986</v>
+        <v>46186.23290205854</v>
       </c>
       <c r="Z280" s="4" t="inlineStr"/>
     </row>
@@ -18679,7 +18711,7 @@
       <c r="W281" s="4" t="inlineStr"/>
       <c r="X281" s="4" t="inlineStr"/>
       <c r="Y281" s="5" t="n">
-        <v>46186.22807313006</v>
+        <v>46186.23290205873</v>
       </c>
       <c r="Z281" s="4" t="inlineStr"/>
     </row>
@@ -18735,7 +18767,7 @@
       <c r="W282" s="4" t="inlineStr"/>
       <c r="X282" s="4" t="inlineStr"/>
       <c r="Y282" s="5" t="n">
-        <v>46186.22807313023</v>
+        <v>46186.23290205891</v>
       </c>
       <c r="Z282" s="4" t="inlineStr"/>
     </row>
@@ -18791,7 +18823,7 @@
       <c r="W283" s="4" t="inlineStr"/>
       <c r="X283" s="4" t="inlineStr"/>
       <c r="Y283" s="5" t="n">
-        <v>46186.22807313042</v>
+        <v>46186.2329020591</v>
       </c>
       <c r="Z283" s="4" t="inlineStr"/>
     </row>
@@ -18859,7 +18891,7 @@
       <c r="W284" s="4" t="inlineStr"/>
       <c r="X284" s="4" t="inlineStr"/>
       <c r="Y284" s="5" t="n">
-        <v>46186.22807313064</v>
+        <v>46186.23290205932</v>
       </c>
       <c r="Z284" s="4" t="inlineStr"/>
     </row>
@@ -18927,7 +18959,7 @@
       <c r="W285" s="4" t="inlineStr"/>
       <c r="X285" s="4" t="inlineStr"/>
       <c r="Y285" s="5" t="n">
-        <v>46186.22807313083</v>
+        <v>46186.23290205953</v>
       </c>
       <c r="Z285" s="4" t="inlineStr"/>
     </row>
@@ -18999,7 +19031,7 @@
       <c r="W286" s="4" t="inlineStr"/>
       <c r="X286" s="4" t="inlineStr"/>
       <c r="Y286" s="5" t="n">
-        <v>46186.22807313103</v>
+        <v>46186.23290205973</v>
       </c>
       <c r="Z286" s="4" t="inlineStr"/>
     </row>
@@ -19071,7 +19103,7 @@
       <c r="W287" s="4" t="inlineStr"/>
       <c r="X287" s="4" t="inlineStr"/>
       <c r="Y287" s="5" t="n">
-        <v>46186.22807313127</v>
+        <v>46186.23290205998</v>
       </c>
       <c r="Z287" s="4" t="inlineStr"/>
     </row>
@@ -19139,7 +19171,7 @@
       <c r="W288" s="4" t="inlineStr"/>
       <c r="X288" s="4" t="inlineStr"/>
       <c r="Y288" s="5" t="n">
-        <v>46186.2280731315</v>
+        <v>46186.23290206018</v>
       </c>
       <c r="Z288" s="4" t="inlineStr"/>
     </row>
@@ -19207,7 +19239,7 @@
       <c r="W289" s="8" t="inlineStr"/>
       <c r="X289" s="8" t="inlineStr"/>
       <c r="Y289" s="9" t="n">
-        <v>46186.22807313193</v>
+        <v>46186.23290206041</v>
       </c>
       <c r="Z289" s="8" t="inlineStr"/>
     </row>
@@ -19275,7 +19307,7 @@
       <c r="W290" s="8" t="inlineStr"/>
       <c r="X290" s="8" t="inlineStr"/>
       <c r="Y290" s="9" t="n">
-        <v>46186.22807313225</v>
+        <v>46186.23290206069</v>
       </c>
       <c r="Z290" s="8" t="inlineStr"/>
     </row>
@@ -19343,7 +19375,7 @@
       <c r="W291" s="8" t="inlineStr"/>
       <c r="X291" s="8" t="inlineStr"/>
       <c r="Y291" s="9" t="n">
-        <v>46186.2280731325</v>
+        <v>46186.23290206125</v>
       </c>
       <c r="Z291" s="8" t="inlineStr"/>
     </row>
@@ -19399,7 +19431,7 @@
       <c r="W292" s="8" t="inlineStr"/>
       <c r="X292" s="8" t="inlineStr"/>
       <c r="Y292" s="9" t="n">
-        <v>46186.22807313279</v>
+        <v>46186.23290206159</v>
       </c>
       <c r="Z292" s="8" t="inlineStr"/>
     </row>
@@ -19451,7 +19483,7 @@
       <c r="W293" s="8" t="inlineStr"/>
       <c r="X293" s="8" t="inlineStr"/>
       <c r="Y293" s="9" t="n">
-        <v>46186.22807313301</v>
+        <v>46186.23290206184</v>
       </c>
       <c r="Z293" s="8" t="inlineStr"/>
     </row>
@@ -19507,7 +19539,7 @@
       <c r="W294" s="8" t="inlineStr"/>
       <c r="X294" s="8" t="inlineStr"/>
       <c r="Y294" s="9" t="n">
-        <v>46186.22807313326</v>
+        <v>46186.2329020621</v>
       </c>
       <c r="Z294" s="8" t="inlineStr"/>
     </row>
@@ -19563,7 +19595,7 @@
       <c r="W295" s="8" t="inlineStr"/>
       <c r="X295" s="8" t="inlineStr"/>
       <c r="Y295" s="9" t="n">
-        <v>46186.22807313348</v>
+        <v>46186.23290206231</v>
       </c>
       <c r="Z295" s="8" t="inlineStr"/>
     </row>
@@ -19619,7 +19651,7 @@
       <c r="W296" s="8" t="inlineStr"/>
       <c r="X296" s="8" t="inlineStr"/>
       <c r="Y296" s="9" t="n">
-        <v>46186.22807313372</v>
+        <v>46186.23290206255</v>
       </c>
       <c r="Z296" s="8" t="inlineStr"/>
     </row>
@@ -19687,7 +19719,7 @@
       <c r="W297" s="8" t="inlineStr"/>
       <c r="X297" s="8" t="inlineStr"/>
       <c r="Y297" s="9" t="n">
-        <v>46186.22807313401</v>
+        <v>46186.23290206285</v>
       </c>
       <c r="Z297" s="8" t="inlineStr"/>
     </row>
@@ -19755,7 +19787,7 @@
       <c r="W298" s="8" t="inlineStr"/>
       <c r="X298" s="8" t="inlineStr"/>
       <c r="Y298" s="9" t="n">
-        <v>46186.22807313429</v>
+        <v>46186.23290206357</v>
       </c>
       <c r="Z298" s="8" t="inlineStr"/>
     </row>
@@ -19823,7 +19855,7 @@
       <c r="W299" s="8" t="inlineStr"/>
       <c r="X299" s="8" t="inlineStr"/>
       <c r="Y299" s="9" t="n">
-        <v>46186.22807313457</v>
+        <v>46186.2329020639</v>
       </c>
       <c r="Z299" s="8" t="inlineStr"/>
     </row>
@@ -19891,7 +19923,7 @@
       <c r="W300" s="8" t="inlineStr"/>
       <c r="X300" s="8" t="inlineStr"/>
       <c r="Y300" s="9" t="n">
-        <v>46186.22807313485</v>
+        <v>46186.23290206419</v>
       </c>
       <c r="Z300" s="8" t="inlineStr"/>
     </row>
@@ -19911,7 +19943,11 @@
           <t>Re: Package Submission - DCP3 - Station BG31 - Structural - BL Technical Level (Precast M-Girder) - DE.ELS.GE00.STR.S1.D3_Rev C01</t>
         </is>
       </c>
-      <c r="F301" s="8" t="inlineStr"/>
+      <c r="F301" s="8" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
       <c r="G301" s="8" t="inlineStr"/>
       <c r="H301" s="8" t="inlineStr"/>
       <c r="I301" s="8" t="inlineStr"/>
@@ -19943,7 +19979,7 @@
       <c r="W301" s="8" t="inlineStr"/>
       <c r="X301" s="8" t="inlineStr"/>
       <c r="Y301" s="9" t="n">
-        <v>46186.22807313505</v>
+        <v>46186.23290206443</v>
       </c>
       <c r="Z301" s="8" t="inlineStr"/>
     </row>
@@ -19999,7 +20035,7 @@
       <c r="W302" s="8" t="inlineStr"/>
       <c r="X302" s="8" t="inlineStr"/>
       <c r="Y302" s="9" t="n">
-        <v>46186.22807313528</v>
+        <v>46186.23290206466</v>
       </c>
       <c r="Z302" s="8" t="inlineStr"/>
     </row>
@@ -20055,7 +20091,7 @@
       <c r="W303" s="8" t="inlineStr"/>
       <c r="X303" s="8" t="inlineStr"/>
       <c r="Y303" s="9" t="n">
-        <v>46186.22807313551</v>
+        <v>46186.2329020649</v>
       </c>
       <c r="Z303" s="8" t="inlineStr"/>
     </row>
@@ -20127,7 +20163,7 @@
       <c r="W304" s="8" t="inlineStr"/>
       <c r="X304" s="8" t="inlineStr"/>
       <c r="Y304" s="9" t="n">
-        <v>46186.2280731358</v>
+        <v>46186.23290206557</v>
       </c>
       <c r="Z304" s="8" t="inlineStr"/>
     </row>
@@ -20199,7 +20235,7 @@
       <c r="W305" s="8" t="inlineStr"/>
       <c r="X305" s="8" t="inlineStr"/>
       <c r="Y305" s="9" t="n">
-        <v>46186.22807313609</v>
+        <v>46186.23290206596</v>
       </c>
       <c r="Z305" s="8" t="inlineStr"/>
     </row>
@@ -20271,7 +20307,7 @@
       <c r="W306" s="8" t="inlineStr"/>
       <c r="X306" s="8" t="inlineStr"/>
       <c r="Y306" s="9" t="n">
-        <v>46186.22807313634</v>
+        <v>46186.23290206625</v>
       </c>
       <c r="Z306" s="8" t="inlineStr"/>
     </row>
@@ -20343,7 +20379,7 @@
       <c r="W307" s="8" t="inlineStr"/>
       <c r="X307" s="8" t="inlineStr"/>
       <c r="Y307" s="9" t="n">
-        <v>46186.22807313658</v>
+        <v>46186.23290206651</v>
       </c>
       <c r="Z307" s="8" t="inlineStr"/>
     </row>
@@ -20415,7 +20451,7 @@
       <c r="W308" s="8" t="inlineStr"/>
       <c r="X308" s="8" t="inlineStr"/>
       <c r="Y308" s="9" t="n">
-        <v>46186.22807313684</v>
+        <v>46186.23290206677</v>
       </c>
       <c r="Z308" s="8" t="inlineStr"/>
     </row>
@@ -20483,7 +20519,7 @@
       <c r="W309" s="8" t="inlineStr"/>
       <c r="X309" s="8" t="inlineStr"/>
       <c r="Y309" s="9" t="n">
-        <v>46186.22807313711</v>
+        <v>46186.23290206705</v>
       </c>
       <c r="Z309" s="8" t="inlineStr"/>
     </row>
@@ -20539,7 +20575,7 @@
       <c r="W310" s="8" t="inlineStr"/>
       <c r="X310" s="8" t="inlineStr"/>
       <c r="Y310" s="9" t="n">
-        <v>46186.2280731376</v>
+        <v>46186.23290206729</v>
       </c>
       <c r="Z310" s="8" t="inlineStr"/>
     </row>
@@ -20595,7 +20631,7 @@
       <c r="W311" s="8" t="inlineStr"/>
       <c r="X311" s="8" t="inlineStr"/>
       <c r="Y311" s="9" t="n">
-        <v>46186.2280731381</v>
+        <v>46186.23290206794</v>
       </c>
       <c r="Z311" s="8" t="inlineStr"/>
     </row>
@@ -20663,7 +20699,7 @@
       <c r="W312" s="4" t="inlineStr"/>
       <c r="X312" s="4" t="inlineStr"/>
       <c r="Y312" s="5" t="n">
-        <v>46186.2280731384</v>
+        <v>46186.2329020683</v>
       </c>
       <c r="Z312" s="4" t="inlineStr"/>
     </row>
@@ -20731,7 +20767,7 @@
       <c r="W313" s="4" t="inlineStr"/>
       <c r="X313" s="4" t="inlineStr"/>
       <c r="Y313" s="5" t="n">
-        <v>46186.22807313875</v>
+        <v>46186.23290206862</v>
       </c>
       <c r="Z313" s="4" t="inlineStr"/>
     </row>
@@ -20787,7 +20823,7 @@
       <c r="W314" s="4" t="inlineStr"/>
       <c r="X314" s="4" t="inlineStr"/>
       <c r="Y314" s="5" t="n">
-        <v>46186.22807313896</v>
+        <v>46186.23290206882</v>
       </c>
       <c r="Z314" s="4" t="inlineStr"/>
     </row>
@@ -20859,7 +20895,7 @@
       <c r="W315" s="8" t="inlineStr"/>
       <c r="X315" s="8" t="inlineStr"/>
       <c r="Y315" s="9" t="n">
-        <v>46186.2280731392</v>
+        <v>46186.23290206905</v>
       </c>
       <c r="Z315" s="8" t="inlineStr"/>
     </row>
@@ -20927,7 +20963,7 @@
       <c r="W316" s="12" t="inlineStr"/>
       <c r="X316" s="12" t="inlineStr"/>
       <c r="Y316" s="13" t="n">
-        <v>46186.22807313948</v>
+        <v>46186.23290206933</v>
       </c>
       <c r="Z316" s="12" t="inlineStr">
         <is>
@@ -20999,7 +21035,7 @@
       <c r="W317" s="8" t="inlineStr"/>
       <c r="X317" s="8" t="inlineStr"/>
       <c r="Y317" s="9" t="n">
-        <v>46186.22807313977</v>
+        <v>46186.23290206958</v>
       </c>
       <c r="Z317" s="8" t="inlineStr"/>
     </row>
@@ -21067,7 +21103,7 @@
       <c r="W318" s="4" t="inlineStr"/>
       <c r="X318" s="4" t="inlineStr"/>
       <c r="Y318" s="5" t="n">
-        <v>46186.22807314003</v>
+        <v>46186.2329020699</v>
       </c>
       <c r="Z318" s="4" t="inlineStr"/>
     </row>
@@ -21135,7 +21171,7 @@
       <c r="W319" s="4" t="inlineStr"/>
       <c r="X319" s="4" t="inlineStr"/>
       <c r="Y319" s="5" t="n">
-        <v>46186.22807314028</v>
+        <v>46186.23290207014</v>
       </c>
       <c r="Z319" s="4" t="inlineStr"/>
     </row>
@@ -21207,7 +21243,7 @@
       <c r="W320" s="4" t="inlineStr"/>
       <c r="X320" s="4" t="inlineStr"/>
       <c r="Y320" s="5" t="n">
-        <v>46186.22807314061</v>
+        <v>46186.23290207044</v>
       </c>
       <c r="Z320" s="4" t="inlineStr"/>
     </row>
@@ -21275,7 +21311,7 @@
       <c r="W321" s="4" t="inlineStr"/>
       <c r="X321" s="4" t="inlineStr"/>
       <c r="Y321" s="5" t="n">
-        <v>46186.22807314089</v>
+        <v>46186.23290207074</v>
       </c>
       <c r="Z321" s="4" t="inlineStr"/>
     </row>
@@ -21347,7 +21383,7 @@
       <c r="W322" s="4" t="inlineStr"/>
       <c r="X322" s="4" t="inlineStr"/>
       <c r="Y322" s="5" t="n">
-        <v>46186.22807314114</v>
+        <v>46186.23290207099</v>
       </c>
       <c r="Z322" s="4" t="inlineStr"/>
     </row>
@@ -21415,7 +21451,7 @@
       <c r="W323" s="4" t="inlineStr"/>
       <c r="X323" s="4" t="inlineStr"/>
       <c r="Y323" s="5" t="n">
-        <v>46186.22807314144</v>
+        <v>46186.23290207129</v>
       </c>
       <c r="Z323" s="4" t="inlineStr"/>
     </row>
@@ -21483,7 +21519,7 @@
       <c r="W324" s="4" t="inlineStr"/>
       <c r="X324" s="4" t="inlineStr"/>
       <c r="Y324" s="5" t="n">
-        <v>46186.22807314169</v>
+        <v>46186.23290207155</v>
       </c>
       <c r="Z324" s="4" t="inlineStr"/>
     </row>
@@ -21551,7 +21587,7 @@
       <c r="W325" s="4" t="inlineStr"/>
       <c r="X325" s="4" t="inlineStr"/>
       <c r="Y325" s="5" t="n">
-        <v>46186.22807314193</v>
+        <v>46186.2329020718</v>
       </c>
       <c r="Z325" s="4" t="inlineStr"/>
     </row>
@@ -21607,7 +21643,7 @@
       <c r="W326" s="4" t="inlineStr"/>
       <c r="X326" s="4" t="inlineStr"/>
       <c r="Y326" s="5" t="n">
-        <v>46186.22807314232</v>
+        <v>46186.23290207244</v>
       </c>
       <c r="Z326" s="4" t="inlineStr"/>
     </row>
@@ -21675,7 +21711,7 @@
       <c r="W327" s="8" t="inlineStr"/>
       <c r="X327" s="8" t="inlineStr"/>
       <c r="Y327" s="9" t="n">
-        <v>46186.22807314264</v>
+        <v>46186.23290207342</v>
       </c>
       <c r="Z327" s="8" t="inlineStr"/>
     </row>
@@ -21747,7 +21783,7 @@
       <c r="W328" s="8" t="inlineStr"/>
       <c r="X328" s="8" t="inlineStr"/>
       <c r="Y328" s="9" t="n">
-        <v>46186.22807314289</v>
+        <v>46186.2329020738</v>
       </c>
       <c r="Z328" s="8" t="inlineStr"/>
     </row>
@@ -21819,7 +21855,7 @@
       <c r="W329" s="8" t="inlineStr"/>
       <c r="X329" s="8" t="inlineStr"/>
       <c r="Y329" s="9" t="n">
-        <v>46186.22807314314</v>
+        <v>46186.23290207409</v>
       </c>
       <c r="Z329" s="8" t="inlineStr"/>
     </row>
@@ -21887,7 +21923,7 @@
       <c r="W330" s="8" t="inlineStr"/>
       <c r="X330" s="8" t="inlineStr"/>
       <c r="Y330" s="9" t="n">
-        <v>46186.2280731434</v>
+        <v>46186.23290207438</v>
       </c>
       <c r="Z330" s="8" t="inlineStr"/>
     </row>
@@ -21955,7 +21991,7 @@
       <c r="W331" s="8" t="inlineStr"/>
       <c r="X331" s="8" t="inlineStr"/>
       <c r="Y331" s="9" t="n">
-        <v>46186.22807314365</v>
+        <v>46186.23290207463</v>
       </c>
       <c r="Z331" s="8" t="inlineStr"/>
     </row>
@@ -22023,7 +22059,7 @@
       <c r="W332" s="8" t="inlineStr"/>
       <c r="X332" s="8" t="inlineStr"/>
       <c r="Y332" s="9" t="n">
-        <v>46186.2280731439</v>
+        <v>46186.23290207489</v>
       </c>
       <c r="Z332" s="8" t="inlineStr"/>
     </row>
@@ -22091,7 +22127,7 @@
       <c r="W333" s="8" t="inlineStr"/>
       <c r="X333" s="8" t="inlineStr"/>
       <c r="Y333" s="9" t="n">
-        <v>46186.22807314416</v>
+        <v>46186.23290207516</v>
       </c>
       <c r="Z333" s="8" t="inlineStr"/>
     </row>
@@ -22159,7 +22195,7 @@
       <c r="W334" s="8" t="inlineStr"/>
       <c r="X334" s="8" t="inlineStr"/>
       <c r="Y334" s="9" t="n">
-        <v>46186.22807314448</v>
+        <v>46186.23290207542</v>
       </c>
       <c r="Z334" s="8" t="inlineStr"/>
     </row>
@@ -22227,7 +22263,7 @@
       <c r="W335" s="4" t="inlineStr"/>
       <c r="X335" s="4" t="inlineStr"/>
       <c r="Y335" s="5" t="n">
-        <v>46186.22807314473</v>
+        <v>46186.23290207567</v>
       </c>
       <c r="Z335" s="4" t="inlineStr"/>
     </row>
@@ -22295,7 +22331,7 @@
       <c r="W336" s="8" t="inlineStr"/>
       <c r="X336" s="8" t="inlineStr"/>
       <c r="Y336" s="9" t="n">
-        <v>46186.22807314555</v>
+        <v>46186.23290207639</v>
       </c>
       <c r="Z336" s="8" t="inlineStr"/>
     </row>
@@ -22319,7 +22355,11 @@
           <t>Re: Report Submission - Technical Note - MEP - LV Cable Colour Coding Project Wide (DE.GEN.GN00.MEP.M0.GN): MLCC-N0003-BES-NWW-ANO-RPT-70000_Rev C02</t>
         </is>
       </c>
-      <c r="F337" s="4" t="inlineStr"/>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
       <c r="G337" s="4" t="inlineStr"/>
       <c r="H337" s="4" t="inlineStr">
         <is>
@@ -22359,7 +22399,7 @@
       <c r="W337" s="4" t="inlineStr"/>
       <c r="X337" s="4" t="inlineStr"/>
       <c r="Y337" s="5" t="n">
-        <v>46186.22807314606</v>
+        <v>46186.2329020774</v>
       </c>
       <c r="Z337" s="4" t="inlineStr"/>
     </row>
@@ -22427,7 +22467,7 @@
       <c r="W338" s="8" t="inlineStr"/>
       <c r="X338" s="8" t="inlineStr"/>
       <c r="Y338" s="9" t="n">
-        <v>46186.22807314633</v>
+        <v>46186.2329020778</v>
       </c>
       <c r="Z338" s="8" t="inlineStr"/>
     </row>
@@ -22495,7 +22535,7 @@
       <c r="W339" s="8" t="inlineStr"/>
       <c r="X339" s="8" t="inlineStr"/>
       <c r="Y339" s="9" t="n">
-        <v>46186.22807314661</v>
+        <v>46186.23290207811</v>
       </c>
       <c r="Z339" s="8" t="inlineStr"/>
     </row>
@@ -22563,7 +22603,7 @@
       <c r="W340" s="4" t="inlineStr"/>
       <c r="X340" s="4" t="inlineStr"/>
       <c r="Y340" s="5" t="n">
-        <v>46186.22807314694</v>
+        <v>46186.23290207846</v>
       </c>
       <c r="Z340" s="4" t="inlineStr"/>
     </row>
@@ -22631,7 +22671,7 @@
       <c r="W341" s="4" t="inlineStr"/>
       <c r="X341" s="4" t="inlineStr"/>
       <c r="Y341" s="5" t="n">
-        <v>46186.22807314723</v>
+        <v>46186.23290207876</v>
       </c>
       <c r="Z341" s="4" t="inlineStr"/>
     </row>
@@ -22687,7 +22727,7 @@
       <c r="W342" s="4" t="inlineStr"/>
       <c r="X342" s="4" t="inlineStr"/>
       <c r="Y342" s="5" t="n">
-        <v>46186.22807314753</v>
+        <v>46186.23290207906</v>
       </c>
       <c r="Z342" s="4" t="inlineStr"/>
     </row>
@@ -22755,7 +22795,7 @@
       <c r="W343" s="8" t="inlineStr"/>
       <c r="X343" s="8" t="inlineStr"/>
       <c r="Y343" s="9" t="n">
-        <v>46186.22807314781</v>
+        <v>46186.23290207934</v>
       </c>
       <c r="Z343" s="8" t="inlineStr"/>
     </row>
@@ -22827,7 +22867,7 @@
       <c r="W344" s="4" t="inlineStr"/>
       <c r="X344" s="4" t="inlineStr"/>
       <c r="Y344" s="5" t="n">
-        <v>46186.22807314804</v>
+        <v>46186.23290207958</v>
       </c>
       <c r="Z344" s="4" t="inlineStr"/>
     </row>
@@ -22883,7 +22923,7 @@
       <c r="W345" s="4" t="inlineStr"/>
       <c r="X345" s="4" t="inlineStr"/>
       <c r="Y345" s="5" t="n">
-        <v>46186.22807314828</v>
+        <v>46186.23290207981</v>
       </c>
       <c r="Z345" s="4" t="inlineStr"/>
     </row>
@@ -22955,7 +22995,7 @@
       <c r="W346" s="4" t="inlineStr"/>
       <c r="X346" s="4" t="inlineStr"/>
       <c r="Y346" s="5" t="n">
-        <v>46186.22807314853</v>
+        <v>46186.23290208006</v>
       </c>
       <c r="Z346" s="4" t="inlineStr"/>
     </row>
@@ -23027,7 +23067,7 @@
       <c r="W347" s="8" t="inlineStr"/>
       <c r="X347" s="8" t="inlineStr"/>
       <c r="Y347" s="9" t="n">
-        <v>46186.22807314892</v>
+        <v>46186.23290208072</v>
       </c>
       <c r="Z347" s="8" t="inlineStr"/>
     </row>
@@ -23095,7 +23135,7 @@
       <c r="W348" s="4" t="inlineStr"/>
       <c r="X348" s="4" t="inlineStr"/>
       <c r="Y348" s="5" t="n">
-        <v>46186.22807314959</v>
+        <v>46186.23290208114</v>
       </c>
       <c r="Z348" s="4" t="inlineStr"/>
     </row>
@@ -23163,7 +23203,7 @@
       <c r="W349" s="4" t="inlineStr"/>
       <c r="X349" s="4" t="inlineStr"/>
       <c r="Y349" s="5" t="n">
-        <v>46186.2280731499</v>
+        <v>46186.23290208147</v>
       </c>
       <c r="Z349" s="4" t="inlineStr"/>
     </row>
@@ -23219,7 +23259,7 @@
       <c r="W350" s="4" t="inlineStr"/>
       <c r="X350" s="4" t="inlineStr"/>
       <c r="Y350" s="5" t="n">
-        <v>46186.22807315021</v>
+        <v>46186.23290208173</v>
       </c>
       <c r="Z350" s="4" t="inlineStr"/>
     </row>
@@ -23275,7 +23315,7 @@
       <c r="W351" s="8" t="inlineStr"/>
       <c r="X351" s="8" t="inlineStr"/>
       <c r="Y351" s="9" t="n">
-        <v>46186.22807315045</v>
+        <v>46186.23290208197</v>
       </c>
       <c r="Z351" s="8" t="inlineStr"/>
     </row>
@@ -23331,7 +23371,7 @@
       <c r="W352" s="4" t="inlineStr"/>
       <c r="X352" s="4" t="inlineStr"/>
       <c r="Y352" s="5" t="n">
-        <v>46186.2280731507</v>
+        <v>46186.2329020822</v>
       </c>
       <c r="Z352" s="4" t="inlineStr"/>
     </row>
@@ -23399,7 +23439,7 @@
       <c r="W353" s="4" t="inlineStr"/>
       <c r="X353" s="4" t="inlineStr"/>
       <c r="Y353" s="5" t="n">
-        <v>46186.228073151</v>
+        <v>46186.2329020825</v>
       </c>
       <c r="Z353" s="4" t="inlineStr"/>
     </row>
@@ -23455,7 +23495,7 @@
       <c r="W354" s="4" t="inlineStr"/>
       <c r="X354" s="4" t="inlineStr"/>
       <c r="Y354" s="5" t="n">
-        <v>46186.22807315121</v>
+        <v>46186.23290208271</v>
       </c>
       <c r="Z354" s="4" t="inlineStr"/>
     </row>
@@ -23511,7 +23551,7 @@
       <c r="W355" s="8" t="inlineStr"/>
       <c r="X355" s="8" t="inlineStr"/>
       <c r="Y355" s="9" t="n">
-        <v>46186.22807315143</v>
+        <v>46186.23290208293</v>
       </c>
       <c r="Z355" s="8" t="inlineStr"/>
     </row>
@@ -23579,7 +23619,7 @@
       <c r="W356" s="4" t="inlineStr"/>
       <c r="X356" s="4" t="inlineStr"/>
       <c r="Y356" s="5" t="n">
-        <v>46186.22807315171</v>
+        <v>46186.2329020832</v>
       </c>
       <c r="Z356" s="4" t="inlineStr"/>
     </row>
@@ -23635,7 +23675,7 @@
       <c r="W357" s="8" t="inlineStr"/>
       <c r="X357" s="8" t="inlineStr"/>
       <c r="Y357" s="9" t="n">
-        <v>46186.22807315193</v>
+        <v>46186.23290208341</v>
       </c>
       <c r="Z357" s="8" t="inlineStr"/>
     </row>
@@ -23703,7 +23743,7 @@
       <c r="W358" s="8" t="inlineStr"/>
       <c r="X358" s="8" t="inlineStr"/>
       <c r="Y358" s="9" t="n">
-        <v>46186.2280731522</v>
+        <v>46186.23290208368</v>
       </c>
       <c r="Z358" s="8" t="inlineStr"/>
     </row>
@@ -23759,7 +23799,7 @@
       <c r="W359" s="8" t="inlineStr"/>
       <c r="X359" s="8" t="inlineStr"/>
       <c r="Y359" s="9" t="n">
-        <v>46186.22807315241</v>
+        <v>46186.23290208389</v>
       </c>
       <c r="Z359" s="8" t="inlineStr"/>
     </row>
@@ -23815,7 +23855,7 @@
       <c r="W360" s="8" t="inlineStr"/>
       <c r="X360" s="8" t="inlineStr"/>
       <c r="Y360" s="9" t="n">
-        <v>46186.22807315262</v>
+        <v>46186.23290208436</v>
       </c>
       <c r="Z360" s="8" t="inlineStr"/>
     </row>
@@ -23871,7 +23911,7 @@
       <c r="W361" s="8" t="inlineStr"/>
       <c r="X361" s="8" t="inlineStr"/>
       <c r="Y361" s="9" t="n">
-        <v>46186.22807315282</v>
+        <v>46186.23290208469</v>
       </c>
       <c r="Z361" s="8" t="inlineStr"/>
     </row>
@@ -23939,7 +23979,7 @@
       <c r="W362" s="8" t="inlineStr"/>
       <c r="X362" s="8" t="inlineStr"/>
       <c r="Y362" s="9" t="n">
-        <v>46186.22807315308</v>
+        <v>46186.23290208498</v>
       </c>
       <c r="Z362" s="8" t="inlineStr"/>
     </row>
@@ -23995,7 +24035,7 @@
       <c r="W363" s="8" t="inlineStr"/>
       <c r="X363" s="8" t="inlineStr"/>
       <c r="Y363" s="9" t="n">
-        <v>46186.22807315331</v>
+        <v>46186.23290208522</v>
       </c>
       <c r="Z363" s="8" t="inlineStr"/>
     </row>
@@ -24051,7 +24091,7 @@
       <c r="W364" s="8" t="inlineStr"/>
       <c r="X364" s="8" t="inlineStr"/>
       <c r="Y364" s="9" t="n">
-        <v>46186.22807315355</v>
+        <v>46186.23290208546</v>
       </c>
       <c r="Z364" s="8" t="inlineStr"/>
     </row>
@@ -24119,7 +24159,7 @@
       <c r="W365" s="8" t="inlineStr"/>
       <c r="X365" s="8" t="inlineStr"/>
       <c r="Y365" s="9" t="n">
-        <v>46186.22807315382</v>
+        <v>46186.23290208574</v>
       </c>
       <c r="Z365" s="8" t="inlineStr"/>
     </row>
@@ -24187,7 +24227,7 @@
       <c r="W366" s="8" t="inlineStr"/>
       <c r="X366" s="8" t="inlineStr"/>
       <c r="Y366" s="9" t="n">
-        <v>46186.22807315407</v>
+        <v>46186.23290208602</v>
       </c>
       <c r="Z366" s="8" t="inlineStr"/>
     </row>
@@ -24255,7 +24295,7 @@
       <c r="W367" s="4" t="inlineStr"/>
       <c r="X367" s="4" t="inlineStr"/>
       <c r="Y367" s="5" t="n">
-        <v>46186.22807315439</v>
+        <v>46186.23290208634</v>
       </c>
       <c r="Z367" s="4" t="inlineStr"/>
     </row>
@@ -24323,7 +24363,7 @@
       <c r="W368" s="4" t="inlineStr"/>
       <c r="X368" s="4" t="inlineStr"/>
       <c r="Y368" s="5" t="n">
-        <v>46186.22807315468</v>
+        <v>46186.23290208663</v>
       </c>
       <c r="Z368" s="4" t="inlineStr"/>
     </row>
@@ -24391,7 +24431,7 @@
       <c r="W369" s="8" t="inlineStr"/>
       <c r="X369" s="8" t="inlineStr"/>
       <c r="Y369" s="9" t="n">
-        <v>46186.22807315492</v>
+        <v>46186.23290208688</v>
       </c>
       <c r="Z369" s="8" t="inlineStr"/>
     </row>
@@ -24459,7 +24499,7 @@
       <c r="W370" s="4" t="inlineStr"/>
       <c r="X370" s="4" t="inlineStr"/>
       <c r="Y370" s="5" t="n">
-        <v>46186.22807315517</v>
+        <v>46186.23290208712</v>
       </c>
       <c r="Z370" s="4" t="inlineStr"/>
     </row>
@@ -24531,7 +24571,7 @@
       <c r="W371" s="8" t="inlineStr"/>
       <c r="X371" s="8" t="inlineStr"/>
       <c r="Y371" s="9" t="n">
-        <v>46186.22807315546</v>
+        <v>46186.23290208737</v>
       </c>
       <c r="Z371" s="8" t="inlineStr"/>
     </row>
@@ -24599,7 +24639,7 @@
       <c r="W372" s="8" t="inlineStr"/>
       <c r="X372" s="8" t="inlineStr"/>
       <c r="Y372" s="9" t="n">
-        <v>46186.22807315578</v>
+        <v>46186.23290208767</v>
       </c>
       <c r="Z372" s="8" t="inlineStr"/>
     </row>
@@ -24667,7 +24707,7 @@
       <c r="W373" s="4" t="inlineStr"/>
       <c r="X373" s="4" t="inlineStr"/>
       <c r="Y373" s="5" t="n">
-        <v>46186.22807315618</v>
+        <v>46186.23290208798</v>
       </c>
       <c r="Z373" s="4" t="inlineStr"/>
     </row>
@@ -24735,7 +24775,7 @@
       <c r="W374" s="4" t="inlineStr"/>
       <c r="X374" s="4" t="inlineStr"/>
       <c r="Y374" s="5" t="n">
-        <v>46186.22807315645</v>
+        <v>46186.23290208823</v>
       </c>
       <c r="Z374" s="4" t="inlineStr"/>
     </row>
@@ -24803,7 +24843,7 @@
       <c r="W375" s="4" t="inlineStr"/>
       <c r="X375" s="4" t="inlineStr"/>
       <c r="Y375" s="5" t="n">
-        <v>46186.22807315674</v>
+        <v>46186.23290208851</v>
       </c>
       <c r="Z375" s="4" t="inlineStr"/>
     </row>
@@ -24871,7 +24911,7 @@
       <c r="W376" s="4" t="inlineStr"/>
       <c r="X376" s="4" t="inlineStr"/>
       <c r="Y376" s="5" t="n">
-        <v>46186.22807315699</v>
+        <v>46186.23290208874</v>
       </c>
       <c r="Z376" s="4" t="inlineStr"/>
     </row>
@@ -24939,7 +24979,7 @@
       <c r="W377" s="4" t="inlineStr"/>
       <c r="X377" s="4" t="inlineStr"/>
       <c r="Y377" s="5" t="n">
-        <v>46186.22807315725</v>
+        <v>46186.232902089</v>
       </c>
       <c r="Z377" s="4" t="inlineStr"/>
     </row>
@@ -25007,7 +25047,7 @@
       <c r="W378" s="4" t="inlineStr"/>
       <c r="X378" s="4" t="inlineStr"/>
       <c r="Y378" s="5" t="n">
-        <v>46186.22807315754</v>
+        <v>46186.23290208927</v>
       </c>
       <c r="Z378" s="4" t="inlineStr"/>
     </row>
@@ -25075,7 +25115,7 @@
       <c r="W379" s="4" t="inlineStr"/>
       <c r="X379" s="4" t="inlineStr"/>
       <c r="Y379" s="5" t="n">
-        <v>46186.22807315776</v>
+        <v>46186.2329020895</v>
       </c>
       <c r="Z379" s="4" t="inlineStr"/>
     </row>
@@ -25147,7 +25187,7 @@
       <c r="W380" s="4" t="inlineStr"/>
       <c r="X380" s="4" t="inlineStr"/>
       <c r="Y380" s="5" t="n">
-        <v>46186.22807315805</v>
+        <v>46186.23290208973</v>
       </c>
       <c r="Z380" s="4" t="inlineStr"/>
     </row>
@@ -25219,7 +25259,7 @@
       <c r="W381" s="4" t="inlineStr"/>
       <c r="X381" s="4" t="inlineStr"/>
       <c r="Y381" s="5" t="n">
-        <v>46186.22807315831</v>
+        <v>46186.23290208999</v>
       </c>
       <c r="Z381" s="4" t="inlineStr"/>
     </row>
@@ -25287,7 +25327,7 @@
       <c r="W382" s="4" t="inlineStr"/>
       <c r="X382" s="4" t="inlineStr"/>
       <c r="Y382" s="5" t="n">
-        <v>46186.22807315858</v>
+        <v>46186.23290209023</v>
       </c>
       <c r="Z382" s="4" t="inlineStr"/>
     </row>
@@ -25343,7 +25383,7 @@
       <c r="W383" s="4" t="inlineStr"/>
       <c r="X383" s="4" t="inlineStr"/>
       <c r="Y383" s="5" t="n">
-        <v>46186.22807315884</v>
+        <v>46186.23290209092</v>
       </c>
       <c r="Z383" s="4" t="inlineStr"/>
     </row>
@@ -25399,7 +25439,7 @@
       <c r="W384" s="4" t="inlineStr"/>
       <c r="X384" s="4" t="inlineStr"/>
       <c r="Y384" s="5" t="n">
-        <v>46186.22807315912</v>
+        <v>46186.23290209124</v>
       </c>
       <c r="Z384" s="4" t="inlineStr"/>
     </row>
@@ -25455,7 +25495,7 @@
       <c r="W385" s="4" t="inlineStr"/>
       <c r="X385" s="4" t="inlineStr"/>
       <c r="Y385" s="5" t="n">
-        <v>46186.22807315938</v>
+        <v>46186.23290209153</v>
       </c>
       <c r="Z385" s="4" t="inlineStr"/>
     </row>
@@ -25527,7 +25567,7 @@
       <c r="W386" s="4" t="inlineStr"/>
       <c r="X386" s="4" t="inlineStr"/>
       <c r="Y386" s="5" t="n">
-        <v>46186.22807315957</v>
+        <v>46186.23290209174</v>
       </c>
       <c r="Z386" s="4" t="inlineStr"/>
     </row>
@@ -25599,7 +25639,7 @@
       <c r="W387" s="4" t="inlineStr"/>
       <c r="X387" s="4" t="inlineStr"/>
       <c r="Y387" s="5" t="n">
-        <v>46186.22807315976</v>
+        <v>46186.23290209194</v>
       </c>
       <c r="Z387" s="4" t="inlineStr"/>
     </row>
@@ -25671,7 +25711,7 @@
       <c r="W388" s="4" t="inlineStr"/>
       <c r="X388" s="4" t="inlineStr"/>
       <c r="Y388" s="5" t="n">
-        <v>46186.22807315993</v>
+        <v>46186.23290209211</v>
       </c>
       <c r="Z388" s="4" t="inlineStr"/>
     </row>
@@ -25743,7 +25783,7 @@
       <c r="W389" s="4" t="inlineStr"/>
       <c r="X389" s="4" t="inlineStr"/>
       <c r="Y389" s="5" t="n">
-        <v>46186.22807316011</v>
+        <v>46186.23290209227</v>
       </c>
       <c r="Z389" s="4" t="inlineStr"/>
     </row>
@@ -25815,7 +25855,7 @@
       <c r="W390" s="4" t="inlineStr"/>
       <c r="X390" s="4" t="inlineStr"/>
       <c r="Y390" s="5" t="n">
-        <v>46186.22807316025</v>
+        <v>46186.23290209243</v>
       </c>
       <c r="Z390" s="4" t="inlineStr"/>
     </row>
@@ -25887,7 +25927,7 @@
       <c r="W391" s="4" t="inlineStr"/>
       <c r="X391" s="4" t="inlineStr"/>
       <c r="Y391" s="5" t="n">
-        <v>46186.2280731604</v>
+        <v>46186.23290209259</v>
       </c>
       <c r="Z391" s="4" t="inlineStr"/>
     </row>
@@ -25959,7 +25999,7 @@
       <c r="W392" s="4" t="inlineStr"/>
       <c r="X392" s="4" t="inlineStr"/>
       <c r="Y392" s="5" t="n">
-        <v>46186.22807316089</v>
+        <v>46186.23290209276</v>
       </c>
       <c r="Z392" s="4" t="inlineStr"/>
     </row>
@@ -26031,7 +26071,7 @@
       <c r="W393" s="4" t="inlineStr"/>
       <c r="X393" s="4" t="inlineStr"/>
       <c r="Y393" s="5" t="n">
-        <v>46186.22807316117</v>
+        <v>46186.23290209292</v>
       </c>
       <c r="Z393" s="4" t="inlineStr"/>
     </row>
@@ -26103,7 +26143,7 @@
       <c r="W394" s="8" t="inlineStr"/>
       <c r="X394" s="8" t="inlineStr"/>
       <c r="Y394" s="9" t="n">
-        <v>46186.22807316147</v>
+        <v>46186.23290209364</v>
       </c>
       <c r="Z394" s="8" t="inlineStr"/>
     </row>
@@ -26155,7 +26195,7 @@
       <c r="W395" s="4" t="inlineStr"/>
       <c r="X395" s="4" t="inlineStr"/>
       <c r="Y395" s="5" t="n">
-        <v>46186.22807316187</v>
+        <v>46186.23290209403</v>
       </c>
       <c r="Z395" s="4" t="inlineStr"/>
     </row>
@@ -26227,7 +26267,7 @@
       <c r="W396" s="8" t="inlineStr"/>
       <c r="X396" s="8" t="inlineStr"/>
       <c r="Y396" s="9" t="n">
-        <v>46186.22807316223</v>
+        <v>46186.23290209434</v>
       </c>
       <c r="Z396" s="8" t="inlineStr"/>
     </row>
@@ -26299,7 +26339,7 @@
       <c r="W397" s="8" t="inlineStr"/>
       <c r="X397" s="8" t="inlineStr"/>
       <c r="Y397" s="9" t="n">
-        <v>46186.22807316251</v>
+        <v>46186.23290209462</v>
       </c>
       <c r="Z397" s="8" t="inlineStr"/>
     </row>
@@ -26355,7 +26395,7 @@
       <c r="W398" s="8" t="inlineStr"/>
       <c r="X398" s="8" t="inlineStr"/>
       <c r="Y398" s="9" t="n">
-        <v>46186.22807316277</v>
+        <v>46186.23290209488</v>
       </c>
       <c r="Z398" s="8" t="inlineStr"/>
     </row>
@@ -26423,7 +26463,7 @@
       <c r="W399" s="4" t="inlineStr"/>
       <c r="X399" s="4" t="inlineStr"/>
       <c r="Y399" s="5" t="n">
-        <v>46186.22807316311</v>
+        <v>46186.23290209514</v>
       </c>
       <c r="Z399" s="4" t="inlineStr"/>
     </row>
@@ -26495,7 +26535,7 @@
       <c r="W400" s="8" t="inlineStr"/>
       <c r="X400" s="8" t="inlineStr"/>
       <c r="Y400" s="9" t="n">
-        <v>46186.22807316337</v>
+        <v>46186.23290209537</v>
       </c>
       <c r="Z400" s="8" t="inlineStr"/>
     </row>
@@ -26551,7 +26591,7 @@
       <c r="W401" s="8" t="inlineStr"/>
       <c r="X401" s="8" t="inlineStr"/>
       <c r="Y401" s="9" t="n">
-        <v>46186.22807316362</v>
+        <v>46186.23290209589</v>
       </c>
       <c r="Z401" s="8" t="inlineStr"/>
     </row>
@@ -26623,7 +26663,7 @@
       <c r="W402" s="8" t="inlineStr"/>
       <c r="X402" s="8" t="inlineStr"/>
       <c r="Y402" s="9" t="n">
-        <v>46186.2280731639</v>
+        <v>46186.23290209629</v>
       </c>
       <c r="Z402" s="8" t="inlineStr"/>
     </row>
@@ -26691,7 +26731,7 @@
       <c r="W403" s="8" t="inlineStr"/>
       <c r="X403" s="8" t="inlineStr"/>
       <c r="Y403" s="9" t="n">
-        <v>46186.22807316422</v>
+        <v>46186.23290209664</v>
       </c>
       <c r="Z403" s="8" t="inlineStr"/>
     </row>
@@ -26759,7 +26799,7 @@
       <c r="W404" s="8" t="inlineStr"/>
       <c r="X404" s="8" t="inlineStr"/>
       <c r="Y404" s="9" t="n">
-        <v>46186.22807316449</v>
+        <v>46186.2329020969</v>
       </c>
       <c r="Z404" s="8" t="inlineStr"/>
     </row>
@@ -26811,7 +26851,7 @@
       <c r="W405" s="8" t="inlineStr"/>
       <c r="X405" s="8" t="inlineStr"/>
       <c r="Y405" s="9" t="n">
-        <v>46186.22807316478</v>
+        <v>46186.2329020972</v>
       </c>
       <c r="Z405" s="8" t="inlineStr"/>
     </row>
@@ -26863,7 +26903,7 @@
       <c r="W406" s="8" t="inlineStr"/>
       <c r="X406" s="8" t="inlineStr"/>
       <c r="Y406" s="9" t="n">
-        <v>46186.228073165</v>
+        <v>46186.23290209741</v>
       </c>
       <c r="Z406" s="8" t="inlineStr"/>
     </row>
@@ -26919,7 +26959,7 @@
       <c r="W407" s="8" t="inlineStr"/>
       <c r="X407" s="8" t="inlineStr"/>
       <c r="Y407" s="9" t="n">
-        <v>46186.22807316526</v>
+        <v>46186.23290209768</v>
       </c>
       <c r="Z407" s="8" t="inlineStr"/>
     </row>
@@ -26975,7 +27015,7 @@
       <c r="W408" s="8" t="inlineStr"/>
       <c r="X408" s="8" t="inlineStr"/>
       <c r="Y408" s="9" t="n">
-        <v>46186.22807316553</v>
+        <v>46186.23290209795</v>
       </c>
       <c r="Z408" s="8" t="inlineStr"/>
     </row>
@@ -27031,7 +27071,7 @@
       <c r="W409" s="8" t="inlineStr"/>
       <c r="X409" s="8" t="inlineStr"/>
       <c r="Y409" s="9" t="n">
-        <v>46186.2280731658</v>
+        <v>46186.23290209821</v>
       </c>
       <c r="Z409" s="8" t="inlineStr"/>
     </row>
@@ -27099,7 +27139,7 @@
       <c r="W410" s="8" t="inlineStr"/>
       <c r="X410" s="8" t="inlineStr"/>
       <c r="Y410" s="9" t="n">
-        <v>46186.22807316612</v>
+        <v>46186.23290209853</v>
       </c>
       <c r="Z410" s="8" t="inlineStr"/>
     </row>
@@ -27167,7 +27207,7 @@
       <c r="W411" s="8" t="inlineStr"/>
       <c r="X411" s="8" t="inlineStr"/>
       <c r="Y411" s="9" t="n">
-        <v>46186.2280731665</v>
+        <v>46186.23290209928</v>
       </c>
       <c r="Z411" s="8" t="inlineStr"/>
     </row>
@@ -27239,7 +27279,7 @@
       <c r="W412" s="8" t="inlineStr"/>
       <c r="X412" s="8" t="inlineStr"/>
       <c r="Y412" s="9" t="n">
-        <v>46186.22807316676</v>
+        <v>46186.2329020996</v>
       </c>
       <c r="Z412" s="8" t="inlineStr"/>
     </row>
@@ -27307,7 +27347,7 @@
       <c r="W413" s="4" t="inlineStr"/>
       <c r="X413" s="4" t="inlineStr"/>
       <c r="Y413" s="5" t="n">
-        <v>46186.2280731671</v>
+        <v>46186.23290209995</v>
       </c>
       <c r="Z413" s="4" t="inlineStr"/>
     </row>
@@ -27363,7 +27403,7 @@
       <c r="W414" s="8" t="inlineStr"/>
       <c r="X414" s="8" t="inlineStr"/>
       <c r="Y414" s="9" t="n">
-        <v>46186.22807316734</v>
+        <v>46186.23290210023</v>
       </c>
       <c r="Z414" s="8" t="inlineStr"/>
     </row>
@@ -27431,7 +27471,7 @@
       <c r="W415" s="8" t="inlineStr"/>
       <c r="X415" s="8" t="inlineStr"/>
       <c r="Y415" s="9" t="n">
-        <v>46186.22807316771</v>
+        <v>46186.23290210054</v>
       </c>
       <c r="Z415" s="8" t="inlineStr"/>
     </row>
@@ -27499,7 +27539,7 @@
       <c r="W416" s="8" t="inlineStr"/>
       <c r="X416" s="8" t="inlineStr"/>
       <c r="Y416" s="9" t="n">
-        <v>46186.22807316803</v>
+        <v>46186.23290210088</v>
       </c>
       <c r="Z416" s="8" t="inlineStr"/>
     </row>
@@ -27555,7 +27595,7 @@
       <c r="W417" s="8" t="inlineStr"/>
       <c r="X417" s="8" t="inlineStr"/>
       <c r="Y417" s="9" t="n">
-        <v>46186.22807316824</v>
+        <v>46186.23290210111</v>
       </c>
       <c r="Z417" s="8" t="inlineStr"/>
     </row>
@@ -27623,7 +27663,7 @@
       <c r="W418" s="4" t="inlineStr"/>
       <c r="X418" s="4" t="inlineStr"/>
       <c r="Y418" s="5" t="n">
-        <v>46186.22807316848</v>
+        <v>46186.23290210136</v>
       </c>
       <c r="Z418" s="4" t="inlineStr"/>
     </row>
@@ -27691,7 +27731,7 @@
       <c r="W419" s="4" t="inlineStr"/>
       <c r="X419" s="4" t="inlineStr"/>
       <c r="Y419" s="5" t="n">
-        <v>46186.22807316875</v>
+        <v>46186.23290210163</v>
       </c>
       <c r="Z419" s="4" t="inlineStr"/>
     </row>
@@ -27759,7 +27799,7 @@
       <c r="W420" s="4" t="inlineStr"/>
       <c r="X420" s="4" t="inlineStr"/>
       <c r="Y420" s="5" t="n">
-        <v>46186.22807316897</v>
+        <v>46186.23290210185</v>
       </c>
       <c r="Z420" s="4" t="inlineStr"/>
     </row>
@@ -27827,7 +27867,7 @@
       <c r="W421" s="4" t="inlineStr"/>
       <c r="X421" s="4" t="inlineStr"/>
       <c r="Y421" s="5" t="n">
-        <v>46186.22807316918</v>
+        <v>46186.23290210206</v>
       </c>
       <c r="Z421" s="4" t="inlineStr"/>
     </row>
@@ -27895,7 +27935,7 @@
       <c r="W422" s="4" t="inlineStr"/>
       <c r="X422" s="4" t="inlineStr"/>
       <c r="Y422" s="5" t="n">
-        <v>46186.22807316946</v>
+        <v>46186.23290210234</v>
       </c>
       <c r="Z422" s="4" t="inlineStr"/>
     </row>
@@ -27951,7 +27991,7 @@
       <c r="W423" s="4" t="inlineStr"/>
       <c r="X423" s="4" t="inlineStr"/>
       <c r="Y423" s="5" t="n">
-        <v>46186.22807316975</v>
+        <v>46186.23290210264</v>
       </c>
       <c r="Z423" s="4" t="inlineStr"/>
     </row>
@@ -28003,7 +28043,7 @@
       <c r="W424" s="4" t="inlineStr"/>
       <c r="X424" s="4" t="inlineStr"/>
       <c r="Y424" s="5" t="n">
-        <v>46186.22807317002</v>
+        <v>46186.23290210291</v>
       </c>
       <c r="Z424" s="4" t="inlineStr"/>
     </row>
@@ -28067,7 +28107,7 @@
       <c r="W425" s="8" t="inlineStr"/>
       <c r="X425" s="8" t="inlineStr"/>
       <c r="Y425" s="9" t="n">
-        <v>46186.22807317044</v>
+        <v>46186.23290210389</v>
       </c>
       <c r="Z425" s="8" t="inlineStr"/>
     </row>
@@ -28139,7 +28179,7 @@
       <c r="W426" s="8" t="inlineStr"/>
       <c r="X426" s="8" t="inlineStr"/>
       <c r="Y426" s="9" t="n">
-        <v>46186.22807317069</v>
+        <v>46186.23290210432</v>
       </c>
       <c r="Z426" s="8" t="inlineStr"/>
     </row>
@@ -28207,7 +28247,7 @@
       <c r="W427" s="8" t="inlineStr"/>
       <c r="X427" s="8" t="inlineStr"/>
       <c r="Y427" s="9" t="n">
-        <v>46186.22807317096</v>
+        <v>46186.23290210471</v>
       </c>
       <c r="Z427" s="8" t="inlineStr"/>
     </row>
@@ -28271,7 +28311,7 @@
       <c r="W428" s="8" t="inlineStr"/>
       <c r="X428" s="8" t="inlineStr"/>
       <c r="Y428" s="9" t="n">
-        <v>46186.2280731713</v>
+        <v>46186.23290210502</v>
       </c>
       <c r="Z428" s="8" t="inlineStr"/>
     </row>
@@ -28339,7 +28379,7 @@
       <c r="W429" s="8" t="inlineStr"/>
       <c r="X429" s="8" t="inlineStr"/>
       <c r="Y429" s="9" t="n">
-        <v>46186.22807317163</v>
+        <v>46186.23290210532</v>
       </c>
       <c r="Z429" s="8" t="inlineStr"/>
     </row>
@@ -28407,7 +28447,7 @@
       <c r="W430" s="8" t="inlineStr"/>
       <c r="X430" s="8" t="inlineStr"/>
       <c r="Y430" s="9" t="n">
-        <v>46186.22807317194</v>
+        <v>46186.23290210563</v>
       </c>
       <c r="Z430" s="8" t="inlineStr"/>
     </row>
@@ -28475,7 +28515,7 @@
       <c r="W431" s="8" t="inlineStr"/>
       <c r="X431" s="8" t="inlineStr"/>
       <c r="Y431" s="9" t="n">
-        <v>46186.22807317256</v>
+        <v>46186.23290210589</v>
       </c>
       <c r="Z431" s="8" t="inlineStr"/>
     </row>
@@ -28531,7 +28571,7 @@
       <c r="W432" s="8" t="inlineStr"/>
       <c r="X432" s="8" t="inlineStr"/>
       <c r="Y432" s="9" t="n">
-        <v>46186.22807317292</v>
+        <v>46186.23290210614</v>
       </c>
       <c r="Z432" s="8" t="inlineStr"/>
     </row>
@@ -28599,7 +28639,7 @@
       <c r="W433" s="8" t="inlineStr"/>
       <c r="X433" s="8" t="inlineStr"/>
       <c r="Y433" s="9" t="n">
-        <v>46186.22807317328</v>
+        <v>46186.23290210639</v>
       </c>
       <c r="Z433" s="8" t="inlineStr"/>
     </row>
@@ -28623,7 +28663,11 @@
           <t>Re: Calculation Submission - Extension Calculation for ISO-32 PT-CU2 : MLCC-N0003-CIV-VBR-GAR-CAL-00001_Rev C01</t>
         </is>
       </c>
-      <c r="F434" s="8" t="inlineStr"/>
+      <c r="F434" s="8" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
       <c r="G434" s="8" t="inlineStr"/>
       <c r="H434" s="8" t="inlineStr">
         <is>
@@ -28663,7 +28707,7 @@
       <c r="W434" s="8" t="inlineStr"/>
       <c r="X434" s="8" t="inlineStr"/>
       <c r="Y434" s="9" t="n">
-        <v>46186.22807317355</v>
+        <v>46186.23290210663</v>
       </c>
       <c r="Z434" s="8" t="inlineStr"/>
     </row>
@@ -28719,7 +28763,7 @@
       <c r="W435" s="8" t="inlineStr"/>
       <c r="X435" s="8" t="inlineStr"/>
       <c r="Y435" s="9" t="n">
-        <v>46186.2280731738</v>
+        <v>46186.23290210687</v>
       </c>
       <c r="Z435" s="8" t="inlineStr"/>
     </row>
@@ -28791,7 +28835,7 @@
       <c r="W436" s="8" t="inlineStr"/>
       <c r="X436" s="8" t="inlineStr"/>
       <c r="Y436" s="9" t="n">
-        <v>46186.22807317402</v>
+        <v>46186.23290210708</v>
       </c>
       <c r="Z436" s="8" t="inlineStr"/>
     </row>
@@ -28863,7 +28907,7 @@
       <c r="W437" s="8" t="inlineStr"/>
       <c r="X437" s="8" t="inlineStr"/>
       <c r="Y437" s="9" t="n">
-        <v>46186.22807317428</v>
+        <v>46186.23290210763</v>
       </c>
       <c r="Z437" s="8" t="inlineStr"/>
     </row>
@@ -28935,7 +28979,7 @@
       <c r="W438" s="8" t="inlineStr"/>
       <c r="X438" s="8" t="inlineStr"/>
       <c r="Y438" s="9" t="n">
-        <v>46186.22807317453</v>
+        <v>46186.23290210795</v>
       </c>
       <c r="Z438" s="8" t="inlineStr"/>
     </row>
@@ -29007,7 +29051,7 @@
       <c r="W439" s="8" t="inlineStr"/>
       <c r="X439" s="8" t="inlineStr"/>
       <c r="Y439" s="9" t="n">
-        <v>46186.22807317477</v>
+        <v>46186.2329021082</v>
       </c>
       <c r="Z439" s="8" t="inlineStr"/>
     </row>
@@ -29075,7 +29119,7 @@
       <c r="W440" s="4" t="inlineStr"/>
       <c r="X440" s="4" t="inlineStr"/>
       <c r="Y440" s="5" t="n">
-        <v>46186.22807317531</v>
+        <v>46186.2329021085</v>
       </c>
       <c r="Z440" s="4" t="inlineStr"/>
     </row>
@@ -29143,7 +29187,7 @@
       <c r="W441" s="4" t="inlineStr"/>
       <c r="X441" s="4" t="inlineStr"/>
       <c r="Y441" s="5" t="n">
-        <v>46186.22807317605</v>
+        <v>46186.23290210914</v>
       </c>
       <c r="Z441" s="4" t="inlineStr"/>
     </row>
@@ -29211,7 +29255,7 @@
       <c r="W442" s="4" t="inlineStr"/>
       <c r="X442" s="4" t="inlineStr"/>
       <c r="Y442" s="5" t="n">
-        <v>46186.22807317643</v>
+        <v>46186.23290210957</v>
       </c>
       <c r="Z442" s="4" t="inlineStr"/>
     </row>
@@ -29279,7 +29323,7 @@
       <c r="W443" s="4" t="inlineStr"/>
       <c r="X443" s="4" t="inlineStr"/>
       <c r="Y443" s="5" t="n">
-        <v>46186.22807317675</v>
+        <v>46186.23290210988</v>
       </c>
       <c r="Z443" s="4" t="inlineStr"/>
     </row>
@@ -29347,7 +29391,7 @@
       <c r="W444" s="4" t="inlineStr"/>
       <c r="X444" s="4" t="inlineStr"/>
       <c r="Y444" s="5" t="n">
-        <v>46186.22807317705</v>
+        <v>46186.23290211018</v>
       </c>
       <c r="Z444" s="4" t="inlineStr"/>
     </row>
@@ -29415,7 +29459,7 @@
       <c r="W445" s="4" t="inlineStr"/>
       <c r="X445" s="4" t="inlineStr"/>
       <c r="Y445" s="5" t="n">
-        <v>46186.22807317737</v>
+        <v>46186.23290211051</v>
       </c>
       <c r="Z445" s="4" t="inlineStr"/>
     </row>
@@ -29483,7 +29527,7 @@
       <c r="W446" s="4" t="inlineStr"/>
       <c r="X446" s="4" t="inlineStr"/>
       <c r="Y446" s="5" t="n">
-        <v>46186.22807317767</v>
+        <v>46186.2329021108</v>
       </c>
       <c r="Z446" s="4" t="inlineStr"/>
     </row>
@@ -29551,7 +29595,7 @@
       <c r="W447" s="4" t="inlineStr"/>
       <c r="X447" s="4" t="inlineStr"/>
       <c r="Y447" s="5" t="n">
-        <v>46186.2280731779</v>
+        <v>46186.23290211102</v>
       </c>
       <c r="Z447" s="4" t="inlineStr"/>
     </row>
@@ -29619,7 +29663,7 @@
       <c r="W448" s="4" t="inlineStr"/>
       <c r="X448" s="4" t="inlineStr"/>
       <c r="Y448" s="5" t="n">
-        <v>46186.22807317822</v>
+        <v>46186.23290211133</v>
       </c>
       <c r="Z448" s="4" t="inlineStr"/>
     </row>
@@ -29687,7 +29731,7 @@
       <c r="W449" s="4" t="inlineStr"/>
       <c r="X449" s="4" t="inlineStr"/>
       <c r="Y449" s="5" t="n">
-        <v>46186.22807317848</v>
+        <v>46186.23290211161</v>
       </c>
       <c r="Z449" s="4" t="inlineStr"/>
     </row>
@@ -29755,7 +29799,7 @@
       <c r="W450" s="8" t="inlineStr"/>
       <c r="X450" s="8" t="inlineStr"/>
       <c r="Y450" s="9" t="n">
-        <v>46186.22807317889</v>
+        <v>46186.23290211256</v>
       </c>
       <c r="Z450" s="8" t="inlineStr"/>
     </row>
@@ -29823,7 +29867,7 @@
       <c r="W451" s="8" t="inlineStr"/>
       <c r="X451" s="8" t="inlineStr"/>
       <c r="Y451" s="9" t="n">
-        <v>46186.22807317923</v>
+        <v>46186.23290211296</v>
       </c>
       <c r="Z451" s="8" t="inlineStr"/>
     </row>
@@ -29891,7 +29935,7 @@
       <c r="W452" s="8" t="inlineStr"/>
       <c r="X452" s="8" t="inlineStr"/>
       <c r="Y452" s="9" t="n">
-        <v>46186.22807317951</v>
+        <v>46186.23290211329</v>
       </c>
       <c r="Z452" s="8" t="inlineStr"/>
     </row>
@@ -29959,7 +30003,7 @@
       <c r="W453" s="8" t="inlineStr"/>
       <c r="X453" s="8" t="inlineStr"/>
       <c r="Y453" s="9" t="n">
-        <v>46186.22807317978</v>
+        <v>46186.23290211357</v>
       </c>
       <c r="Z453" s="8" t="inlineStr"/>
     </row>
@@ -30027,7 +30071,7 @@
       <c r="W454" s="8" t="inlineStr"/>
       <c r="X454" s="8" t="inlineStr"/>
       <c r="Y454" s="9" t="n">
-        <v>46186.22807318001</v>
+        <v>46186.23290211382</v>
       </c>
       <c r="Z454" s="8" t="inlineStr"/>
     </row>
@@ -30095,7 +30139,7 @@
       <c r="W455" s="8" t="inlineStr"/>
       <c r="X455" s="8" t="inlineStr"/>
       <c r="Y455" s="9" t="n">
-        <v>46186.22807318025</v>
+        <v>46186.23290211405</v>
       </c>
       <c r="Z455" s="8" t="inlineStr"/>
     </row>
@@ -30163,7 +30207,7 @@
       <c r="W456" s="8" t="inlineStr"/>
       <c r="X456" s="8" t="inlineStr"/>
       <c r="Y456" s="9" t="n">
-        <v>46186.2280731805</v>
+        <v>46186.23290211429</v>
       </c>
       <c r="Z456" s="8" t="inlineStr"/>
     </row>
@@ -30231,7 +30275,7 @@
       <c r="W457" s="8" t="inlineStr"/>
       <c r="X457" s="8" t="inlineStr"/>
       <c r="Y457" s="9" t="n">
-        <v>46186.22807318103</v>
+        <v>46186.23290211457</v>
       </c>
       <c r="Z457" s="8" t="inlineStr"/>
     </row>
@@ -30299,7 +30343,7 @@
       <c r="W458" s="8" t="inlineStr"/>
       <c r="X458" s="8" t="inlineStr"/>
       <c r="Y458" s="9" t="n">
-        <v>46186.22807318162</v>
+        <v>46186.23290211482</v>
       </c>
       <c r="Z458" s="8" t="inlineStr"/>
     </row>
@@ -30371,7 +30415,7 @@
       <c r="W459" s="8" t="inlineStr"/>
       <c r="X459" s="8" t="inlineStr"/>
       <c r="Y459" s="9" t="n">
-        <v>46186.22807318193</v>
+        <v>46186.23290211506</v>
       </c>
       <c r="Z459" s="8" t="inlineStr"/>
     </row>
@@ -30395,7 +30439,11 @@
           <t>Re: Specification Submission - DCP2 - Traction System Design Specification and System Architecture (RLS.1.1.2.2.2): MLCC-N0003-PDS-MPD-TRP-SPC-51000_Rev C04</t>
         </is>
       </c>
-      <c r="F460" s="8" t="inlineStr"/>
+      <c r="F460" s="8" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
       <c r="G460" s="8" t="inlineStr"/>
       <c r="H460" s="8" t="inlineStr">
         <is>
@@ -30439,7 +30487,7 @@
       <c r="W460" s="8" t="inlineStr"/>
       <c r="X460" s="8" t="inlineStr"/>
       <c r="Y460" s="9" t="n">
-        <v>46186.22807318221</v>
+        <v>46186.23290211533</v>
       </c>
       <c r="Z460" s="8" t="inlineStr"/>
     </row>
@@ -30511,7 +30559,7 @@
       <c r="W461" s="8" t="inlineStr"/>
       <c r="X461" s="8" t="inlineStr"/>
       <c r="Y461" s="9" t="n">
-        <v>46186.22807318249</v>
+        <v>46186.23290211557</v>
       </c>
       <c r="Z461" s="8" t="inlineStr"/>
     </row>
@@ -30567,7 +30615,7 @@
       <c r="W462" s="8" t="inlineStr"/>
       <c r="X462" s="8" t="inlineStr"/>
       <c r="Y462" s="9" t="n">
-        <v>46186.22807318273</v>
+        <v>46186.23290211579</v>
       </c>
       <c r="Z462" s="8" t="inlineStr"/>
     </row>
@@ -30635,7 +30683,7 @@
       <c r="W463" s="8" t="inlineStr"/>
       <c r="X463" s="8" t="inlineStr"/>
       <c r="Y463" s="9" t="n">
-        <v>46186.228073183</v>
+        <v>46186.23290211603</v>
       </c>
       <c r="Z463" s="8" t="inlineStr"/>
     </row>
@@ -30703,7 +30751,7 @@
       <c r="W464" s="8" t="inlineStr"/>
       <c r="X464" s="8" t="inlineStr"/>
       <c r="Y464" s="9" t="n">
-        <v>46186.22807318321</v>
+        <v>46186.23290211631</v>
       </c>
       <c r="Z464" s="8" t="inlineStr"/>
     </row>
@@ -30771,7 +30819,7 @@
       <c r="W465" s="8" t="inlineStr"/>
       <c r="X465" s="8" t="inlineStr"/>
       <c r="Y465" s="9" t="n">
-        <v>46186.2280731835</v>
+        <v>46186.2329021166</v>
       </c>
       <c r="Z465" s="8" t="inlineStr"/>
     </row>
@@ -30839,7 +30887,7 @@
       <c r="W466" s="8" t="inlineStr"/>
       <c r="X466" s="8" t="inlineStr"/>
       <c r="Y466" s="9" t="n">
-        <v>46186.22807318405</v>
+        <v>46186.23290211688</v>
       </c>
       <c r="Z466" s="8" t="inlineStr"/>
     </row>
@@ -30907,7 +30955,7 @@
       <c r="W467" s="8" t="inlineStr"/>
       <c r="X467" s="8" t="inlineStr"/>
       <c r="Y467" s="9" t="n">
-        <v>46186.2280731844</v>
+        <v>46186.23290211711</v>
       </c>
       <c r="Z467" s="8" t="inlineStr"/>
     </row>
@@ -30975,7 +31023,7 @@
       <c r="W468" s="8" t="inlineStr"/>
       <c r="X468" s="8" t="inlineStr"/>
       <c r="Y468" s="9" t="n">
-        <v>46186.22807318471</v>
+        <v>46186.23290211736</v>
       </c>
       <c r="Z468" s="8" t="inlineStr"/>
     </row>
@@ -31043,7 +31091,7 @@
       <c r="W469" s="8" t="inlineStr"/>
       <c r="X469" s="8" t="inlineStr"/>
       <c r="Y469" s="9" t="n">
-        <v>46186.22807318501</v>
+        <v>46186.23290211762</v>
       </c>
       <c r="Z469" s="8" t="inlineStr"/>
     </row>
@@ -31111,7 +31159,7 @@
       <c r="W470" s="8" t="inlineStr"/>
       <c r="X470" s="8" t="inlineStr"/>
       <c r="Y470" s="9" t="n">
-        <v>46186.22807318536</v>
+        <v>46186.23290211792</v>
       </c>
       <c r="Z470" s="8" t="inlineStr"/>
     </row>
@@ -31179,7 +31227,7 @@
       <c r="W471" s="8" t="inlineStr"/>
       <c r="X471" s="8" t="inlineStr"/>
       <c r="Y471" s="9" t="n">
-        <v>46186.22807318562</v>
+        <v>46186.23290211816</v>
       </c>
       <c r="Z471" s="8" t="inlineStr"/>
     </row>
@@ -31247,7 +31295,7 @@
       <c r="W472" s="8" t="inlineStr"/>
       <c r="X472" s="8" t="inlineStr"/>
       <c r="Y472" s="9" t="n">
-        <v>46186.22807318588</v>
+        <v>46186.23290211839</v>
       </c>
       <c r="Z472" s="8" t="inlineStr"/>
     </row>
@@ -31315,7 +31363,7 @@
       <c r="W473" s="8" t="inlineStr"/>
       <c r="X473" s="8" t="inlineStr"/>
       <c r="Y473" s="9" t="n">
-        <v>46186.22807318615</v>
+        <v>46186.23290211866</v>
       </c>
       <c r="Z473" s="8" t="inlineStr"/>
     </row>
@@ -31383,7 +31431,7 @@
       <c r="W474" s="8" t="inlineStr"/>
       <c r="X474" s="8" t="inlineStr"/>
       <c r="Y474" s="9" t="n">
-        <v>46186.22807318642</v>
+        <v>46186.23290211927</v>
       </c>
       <c r="Z474" s="8" t="inlineStr"/>
     </row>
@@ -31451,7 +31499,7 @@
       <c r="W475" s="8" t="inlineStr"/>
       <c r="X475" s="8" t="inlineStr"/>
       <c r="Y475" s="9" t="n">
-        <v>46186.22807318678</v>
+        <v>46186.23290211974</v>
       </c>
       <c r="Z475" s="8" t="inlineStr"/>
     </row>
@@ -31519,7 +31567,7 @@
       <c r="W476" s="8" t="inlineStr"/>
       <c r="X476" s="8" t="inlineStr"/>
       <c r="Y476" s="9" t="n">
-        <v>46186.22807318706</v>
+        <v>46186.23290212005</v>
       </c>
       <c r="Z476" s="8" t="inlineStr"/>
     </row>
@@ -31571,7 +31619,7 @@
       <c r="W477" s="8" t="inlineStr"/>
       <c r="X477" s="8" t="inlineStr"/>
       <c r="Y477" s="9" t="n">
-        <v>46186.2280731873</v>
+        <v>46186.2329021203</v>
       </c>
       <c r="Z477" s="8" t="inlineStr"/>
     </row>
@@ -31639,7 +31687,7 @@
       <c r="W478" s="8" t="inlineStr"/>
       <c r="X478" s="8" t="inlineStr"/>
       <c r="Y478" s="9" t="n">
-        <v>46186.22807318762</v>
+        <v>46186.23290212062</v>
       </c>
       <c r="Z478" s="8" t="inlineStr"/>
     </row>
@@ -31707,7 +31755,7 @@
       <c r="W479" s="8" t="inlineStr"/>
       <c r="X479" s="8" t="inlineStr"/>
       <c r="Y479" s="9" t="n">
-        <v>46186.22807318787</v>
+        <v>46186.23290212089</v>
       </c>
       <c r="Z479" s="8" t="inlineStr"/>
     </row>
@@ -31775,7 +31823,7 @@
       <c r="W480" s="8" t="inlineStr"/>
       <c r="X480" s="8" t="inlineStr"/>
       <c r="Y480" s="9" t="n">
-        <v>46186.2280731881</v>
+        <v>46186.23290212113</v>
       </c>
       <c r="Z480" s="8" t="inlineStr"/>
     </row>
@@ -31847,7 +31895,7 @@
       <c r="W481" s="8" t="inlineStr"/>
       <c r="X481" s="8" t="inlineStr"/>
       <c r="Y481" s="9" t="n">
-        <v>46186.22807318839</v>
+        <v>46186.2329021214</v>
       </c>
       <c r="Z481" s="8" t="inlineStr"/>
     </row>
@@ -31915,7 +31963,7 @@
       <c r="W482" s="4" t="inlineStr"/>
       <c r="X482" s="4" t="inlineStr"/>
       <c r="Y482" s="5" t="n">
-        <v>46186.22807318867</v>
+        <v>46186.23290212166</v>
       </c>
       <c r="Z482" s="4" t="inlineStr"/>
     </row>
@@ -31971,7 +32019,7 @@
       <c r="W483" s="8" t="inlineStr"/>
       <c r="X483" s="8" t="inlineStr"/>
       <c r="Y483" s="9" t="n">
-        <v>46186.22807318893</v>
+        <v>46186.23290212192</v>
       </c>
       <c r="Z483" s="8" t="inlineStr"/>
     </row>
@@ -32027,7 +32075,7 @@
       <c r="W484" s="4" t="inlineStr"/>
       <c r="X484" s="4" t="inlineStr"/>
       <c r="Y484" s="5" t="n">
-        <v>46186.22807318914</v>
+        <v>46186.23290212214</v>
       </c>
       <c r="Z484" s="4" t="inlineStr"/>
     </row>
@@ -32099,7 +32147,7 @@
       <c r="W485" s="8" t="inlineStr"/>
       <c r="X485" s="8" t="inlineStr"/>
       <c r="Y485" s="9" t="n">
-        <v>46186.2280731894</v>
+        <v>46186.23290212239</v>
       </c>
       <c r="Z485" s="8" t="inlineStr"/>
     </row>
@@ -32167,7 +32215,7 @@
       <c r="W486" s="8" t="inlineStr"/>
       <c r="X486" s="8" t="inlineStr"/>
       <c r="Y486" s="9" t="n">
-        <v>46186.22807318971</v>
+        <v>46186.2329021227</v>
       </c>
       <c r="Z486" s="8" t="inlineStr"/>
     </row>
@@ -32235,7 +32283,7 @@
       <c r="W487" s="8" t="inlineStr"/>
       <c r="X487" s="8" t="inlineStr"/>
       <c r="Y487" s="9" t="n">
-        <v>46186.22807318997</v>
+        <v>46186.23290212296</v>
       </c>
       <c r="Z487" s="8" t="inlineStr"/>
     </row>
@@ -32303,7 +32351,7 @@
       <c r="W488" s="4" t="inlineStr"/>
       <c r="X488" s="4" t="inlineStr"/>
       <c r="Y488" s="5" t="n">
-        <v>46186.22807319028</v>
+        <v>46186.23290212327</v>
       </c>
       <c r="Z488" s="4" t="inlineStr"/>
     </row>
@@ -32371,7 +32419,7 @@
       <c r="W489" s="4" t="inlineStr"/>
       <c r="X489" s="4" t="inlineStr"/>
       <c r="Y489" s="5" t="n">
-        <v>46186.22807319058</v>
+        <v>46186.23290212351</v>
       </c>
       <c r="Z489" s="4" t="inlineStr"/>
     </row>
@@ -32439,7 +32487,7 @@
       <c r="W490" s="4" t="inlineStr"/>
       <c r="X490" s="4" t="inlineStr"/>
       <c r="Y490" s="5" t="n">
-        <v>46186.22807319085</v>
+        <v>46186.23290212376</v>
       </c>
       <c r="Z490" s="4" t="inlineStr"/>
     </row>
@@ -32507,7 +32555,7 @@
       <c r="W491" s="4" t="inlineStr"/>
       <c r="X491" s="4" t="inlineStr"/>
       <c r="Y491" s="5" t="n">
-        <v>46186.22807319111</v>
+        <v>46186.23290212401</v>
       </c>
       <c r="Z491" s="4" t="inlineStr"/>
     </row>
@@ -32563,7 +32611,7 @@
       <c r="W492" s="8" t="inlineStr"/>
       <c r="X492" s="8" t="inlineStr"/>
       <c r="Y492" s="9" t="n">
-        <v>46186.22807319176</v>
+        <v>46186.23290212425</v>
       </c>
       <c r="Z492" s="8" t="inlineStr"/>
     </row>
@@ -32631,7 +32679,7 @@
       <c r="W493" s="4" t="inlineStr"/>
       <c r="X493" s="4" t="inlineStr"/>
       <c r="Y493" s="5" t="n">
-        <v>46186.22807319219</v>
+        <v>46186.23290212455</v>
       </c>
       <c r="Z493" s="4" t="inlineStr"/>
     </row>
@@ -32699,7 +32747,7 @@
       <c r="W494" s="4" t="inlineStr"/>
       <c r="X494" s="4" t="inlineStr"/>
       <c r="Y494" s="5" t="n">
-        <v>46186.22807319246</v>
+        <v>46186.23290212478</v>
       </c>
       <c r="Z494" s="4" t="inlineStr"/>
     </row>
@@ -32755,7 +32803,7 @@
       <c r="W495" s="8" t="inlineStr"/>
       <c r="X495" s="8" t="inlineStr"/>
       <c r="Y495" s="9" t="n">
-        <v>46186.22807319272</v>
+        <v>46186.232902125</v>
       </c>
       <c r="Z495" s="8" t="inlineStr"/>
     </row>
@@ -32823,7 +32871,7 @@
       <c r="W496" s="4" t="inlineStr"/>
       <c r="X496" s="4" t="inlineStr"/>
       <c r="Y496" s="5" t="n">
-        <v>46186.228073193</v>
+        <v>46186.23290212525</v>
       </c>
       <c r="Z496" s="4" t="inlineStr"/>
     </row>
@@ -32895,7 +32943,7 @@
       <c r="W497" s="8" t="inlineStr"/>
       <c r="X497" s="8" t="inlineStr"/>
       <c r="Y497" s="9" t="n">
-        <v>46186.22807319326</v>
+        <v>46186.23290212552</v>
       </c>
       <c r="Z497" s="8" t="inlineStr"/>
     </row>
@@ -32967,7 +33015,7 @@
       <c r="W498" s="8" t="inlineStr"/>
       <c r="X498" s="8" t="inlineStr"/>
       <c r="Y498" s="9" t="n">
-        <v>46186.22807319355</v>
+        <v>46186.2329021258</v>
       </c>
       <c r="Z498" s="8" t="inlineStr"/>
     </row>
@@ -32987,7 +33035,11 @@
           <t>Re: Package Submission - DCP3 - Station BB05 - Earthing and Bonding Below Base Slab Design: DE.UGS.GE09.STR.S1.D3_Rev C02</t>
         </is>
       </c>
-      <c r="F499" s="8" t="inlineStr"/>
+      <c r="F499" s="8" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
       <c r="G499" s="8" t="inlineStr"/>
       <c r="H499" s="8" t="inlineStr"/>
       <c r="I499" s="8" t="inlineStr"/>
@@ -33019,7 +33071,7 @@
       <c r="W499" s="8" t="inlineStr"/>
       <c r="X499" s="8" t="inlineStr"/>
       <c r="Y499" s="9" t="n">
-        <v>46186.22807319379</v>
+        <v>46186.23290212604</v>
       </c>
       <c r="Z499" s="8" t="inlineStr"/>
     </row>
@@ -33075,7 +33127,7 @@
       <c r="W500" s="4" t="inlineStr"/>
       <c r="X500" s="4" t="inlineStr"/>
       <c r="Y500" s="5" t="n">
-        <v>46186.22807319403</v>
+        <v>46186.23290212628</v>
       </c>
       <c r="Z500" s="4" t="inlineStr"/>
     </row>
@@ -33131,7 +33183,7 @@
       <c r="W501" s="4" t="inlineStr"/>
       <c r="X501" s="4" t="inlineStr"/>
       <c r="Y501" s="5" t="n">
-        <v>46186.22807319422</v>
+        <v>46186.23290212648</v>
       </c>
       <c r="Z501" s="4" t="inlineStr"/>
     </row>
@@ -33199,7 +33251,7 @@
       <c r="W502" s="8" t="inlineStr"/>
       <c r="X502" s="8" t="inlineStr"/>
       <c r="Y502" s="9" t="n">
-        <v>46186.22807319449</v>
+        <v>46186.23290212675</v>
       </c>
       <c r="Z502" s="8" t="inlineStr"/>
     </row>
@@ -33267,7 +33319,7 @@
       <c r="W503" s="8" t="inlineStr"/>
       <c r="X503" s="8" t="inlineStr"/>
       <c r="Y503" s="9" t="n">
-        <v>46186.2280731948</v>
+        <v>46186.23290212705</v>
       </c>
       <c r="Z503" s="8" t="inlineStr"/>
     </row>
@@ -33335,7 +33387,7 @@
       <c r="W504" s="8" t="inlineStr"/>
       <c r="X504" s="8" t="inlineStr"/>
       <c r="Y504" s="9" t="n">
-        <v>46186.2280731952</v>
+        <v>46186.23290212735</v>
       </c>
       <c r="Z504" s="8" t="inlineStr"/>
     </row>
@@ -33391,7 +33443,7 @@
       <c r="W505" s="4" t="inlineStr"/>
       <c r="X505" s="4" t="inlineStr"/>
       <c r="Y505" s="5" t="n">
-        <v>46186.22807319602</v>
+        <v>46186.23290212759</v>
       </c>
       <c r="Z505" s="4" t="inlineStr"/>
     </row>
@@ -33459,7 +33511,7 @@
       <c r="W506" s="4" t="inlineStr"/>
       <c r="X506" s="4" t="inlineStr"/>
       <c r="Y506" s="5" t="n">
-        <v>46186.22807319655</v>
+        <v>46186.23290212791</v>
       </c>
       <c r="Z506" s="4" t="inlineStr"/>
     </row>
@@ -33515,7 +33567,7 @@
       <c r="W507" s="4" t="inlineStr"/>
       <c r="X507" s="4" t="inlineStr"/>
       <c r="Y507" s="5" t="n">
-        <v>46186.2280731971</v>
+        <v>46186.23290212818</v>
       </c>
       <c r="Z507" s="4" t="inlineStr"/>
     </row>
@@ -33583,7 +33635,7 @@
       <c r="W508" s="4" t="inlineStr"/>
       <c r="X508" s="4" t="inlineStr"/>
       <c r="Y508" s="5" t="n">
-        <v>46186.22807319759</v>
+        <v>46186.23290212852</v>
       </c>
       <c r="Z508" s="4" t="inlineStr"/>
     </row>
@@ -33651,7 +33703,7 @@
       <c r="W509" s="4" t="inlineStr"/>
       <c r="X509" s="4" t="inlineStr"/>
       <c r="Y509" s="5" t="n">
-        <v>46186.22807319814</v>
+        <v>46186.23290212883</v>
       </c>
       <c r="Z509" s="4" t="inlineStr"/>
     </row>
@@ -33703,7 +33755,7 @@
       <c r="W510" s="4" t="inlineStr"/>
       <c r="X510" s="4" t="inlineStr"/>
       <c r="Y510" s="5" t="n">
-        <v>46186.22807319861</v>
+        <v>46186.23290212911</v>
       </c>
       <c r="Z510" s="4" t="inlineStr"/>
     </row>
@@ -33759,7 +33811,7 @@
       <c r="W511" s="4" t="inlineStr"/>
       <c r="X511" s="4" t="inlineStr"/>
       <c r="Y511" s="5" t="n">
-        <v>46186.228073199</v>
+        <v>46186.23290212944</v>
       </c>
       <c r="Z511" s="4" t="inlineStr"/>
     </row>
@@ -33827,7 +33879,7 @@
       <c r="W512" s="4" t="inlineStr"/>
       <c r="X512" s="4" t="inlineStr"/>
       <c r="Y512" s="5" t="n">
-        <v>46186.22807319943</v>
+        <v>46186.23290212989</v>
       </c>
       <c r="Z512" s="4" t="inlineStr"/>
     </row>
@@ -33895,7 +33947,7 @@
       <c r="W513" s="4" t="inlineStr"/>
       <c r="X513" s="4" t="inlineStr"/>
       <c r="Y513" s="5" t="n">
-        <v>46186.22807319994</v>
+        <v>46186.23290213077</v>
       </c>
       <c r="Z513" s="4" t="inlineStr"/>
     </row>
@@ -33963,7 +34015,7 @@
       <c r="W514" s="4" t="inlineStr"/>
       <c r="X514" s="4" t="inlineStr"/>
       <c r="Y514" s="5" t="n">
-        <v>46186.22807320045</v>
+        <v>46186.23290213117</v>
       </c>
       <c r="Z514" s="4" t="inlineStr"/>
     </row>
@@ -34031,7 +34083,7 @@
       <c r="W515" s="4" t="inlineStr"/>
       <c r="X515" s="4" t="inlineStr"/>
       <c r="Y515" s="5" t="n">
-        <v>46186.22807320089</v>
+        <v>46186.23290213144</v>
       </c>
       <c r="Z515" s="4" t="inlineStr"/>
     </row>
@@ -34099,7 +34151,7 @@
       <c r="W516" s="4" t="inlineStr"/>
       <c r="X516" s="4" t="inlineStr"/>
       <c r="Y516" s="5" t="n">
-        <v>46186.22807320138</v>
+        <v>46186.23290213171</v>
       </c>
       <c r="Z516" s="4" t="inlineStr"/>
     </row>
@@ -34171,7 +34223,7 @@
       <c r="W517" s="4" t="inlineStr"/>
       <c r="X517" s="4" t="inlineStr"/>
       <c r="Y517" s="5" t="n">
-        <v>46186.22807320218</v>
+        <v>46186.23290213249</v>
       </c>
       <c r="Z517" s="4" t="inlineStr"/>
     </row>
@@ -34243,7 +34295,7 @@
       <c r="W518" s="4" t="inlineStr"/>
       <c r="X518" s="4" t="inlineStr"/>
       <c r="Y518" s="5" t="n">
-        <v>46186.22807320258</v>
+        <v>46186.23290213293</v>
       </c>
       <c r="Z518" s="4" t="inlineStr"/>
     </row>
@@ -34315,7 +34367,7 @@
       <c r="W519" s="4" t="inlineStr"/>
       <c r="X519" s="4" t="inlineStr"/>
       <c r="Y519" s="5" t="n">
-        <v>46186.22807320287</v>
+        <v>46186.23290213326</v>
       </c>
       <c r="Z519" s="4" t="inlineStr"/>
     </row>
@@ -34387,7 +34439,7 @@
       <c r="W520" s="4" t="inlineStr"/>
       <c r="X520" s="4" t="inlineStr"/>
       <c r="Y520" s="5" t="n">
-        <v>46186.22807320314</v>
+        <v>46186.23290213352</v>
       </c>
       <c r="Z520" s="4" t="inlineStr"/>
     </row>
@@ -34459,7 +34511,7 @@
       <c r="W521" s="4" t="inlineStr"/>
       <c r="X521" s="4" t="inlineStr"/>
       <c r="Y521" s="5" t="n">
-        <v>46186.22807320338</v>
+        <v>46186.23290213376</v>
       </c>
       <c r="Z521" s="4" t="inlineStr"/>
     </row>
@@ -34527,7 +34579,7 @@
       <c r="W522" s="4" t="inlineStr"/>
       <c r="X522" s="4" t="inlineStr"/>
       <c r="Y522" s="5" t="n">
-        <v>46186.22807320362</v>
+        <v>46186.232902134</v>
       </c>
       <c r="Z522" s="4" t="inlineStr"/>
     </row>
@@ -34583,7 +34635,7 @@
       <c r="W523" s="4" t="inlineStr"/>
       <c r="X523" s="4" t="inlineStr"/>
       <c r="Y523" s="5" t="n">
-        <v>46186.22807320386</v>
+        <v>46186.23290213426</v>
       </c>
       <c r="Z523" s="4" t="inlineStr"/>
     </row>
@@ -34651,7 +34703,7 @@
       <c r="W524" s="4" t="inlineStr"/>
       <c r="X524" s="4" t="inlineStr"/>
       <c r="Y524" s="5" t="n">
-        <v>46186.2280732075</v>
+        <v>46186.23290213622</v>
       </c>
       <c r="Z524" s="4" t="inlineStr"/>
     </row>
@@ -34707,7 +34759,7 @@
       <c r="W525" s="4" t="inlineStr"/>
       <c r="X525" s="4" t="inlineStr"/>
       <c r="Y525" s="5" t="n">
-        <v>46186.22807320794</v>
+        <v>46186.23290213651</v>
       </c>
       <c r="Z525" s="4" t="inlineStr"/>
     </row>
@@ -34775,7 +34827,7 @@
       <c r="W526" s="4" t="inlineStr"/>
       <c r="X526" s="4" t="inlineStr"/>
       <c r="Y526" s="5" t="n">
-        <v>46186.2280732083</v>
+        <v>46186.23290213683</v>
       </c>
       <c r="Z526" s="4" t="inlineStr"/>
     </row>
@@ -34843,7 +34895,7 @@
       <c r="W527" s="4" t="inlineStr"/>
       <c r="X527" s="4" t="inlineStr"/>
       <c r="Y527" s="5" t="n">
-        <v>46186.22807320864</v>
+        <v>46186.23290213714</v>
       </c>
       <c r="Z527" s="4" t="inlineStr"/>
     </row>
@@ -34911,7 +34963,7 @@
       <c r="W528" s="4" t="inlineStr"/>
       <c r="X528" s="4" t="inlineStr"/>
       <c r="Y528" s="5" t="n">
-        <v>46186.22807320901</v>
+        <v>46186.23290213748</v>
       </c>
       <c r="Z528" s="4" t="inlineStr"/>
     </row>
@@ -34979,7 +35031,7 @@
       <c r="W529" s="4" t="inlineStr"/>
       <c r="X529" s="4" t="inlineStr"/>
       <c r="Y529" s="5" t="n">
-        <v>46186.22807320928</v>
+        <v>46186.23290213772</v>
       </c>
       <c r="Z529" s="4" t="inlineStr"/>
     </row>
@@ -35047,7 +35099,7 @@
       <c r="W530" s="4" t="inlineStr"/>
       <c r="X530" s="4" t="inlineStr"/>
       <c r="Y530" s="5" t="n">
-        <v>46186.22807320956</v>
+        <v>46186.23290213798</v>
       </c>
       <c r="Z530" s="4" t="inlineStr"/>
     </row>
@@ -35115,7 +35167,7 @@
       <c r="W531" s="4" t="inlineStr"/>
       <c r="X531" s="4" t="inlineStr"/>
       <c r="Y531" s="5" t="n">
-        <v>46186.22807320986</v>
+        <v>46186.23290213828</v>
       </c>
       <c r="Z531" s="4" t="inlineStr"/>
     </row>
@@ -35183,7 +35235,7 @@
       <c r="W532" s="4" t="inlineStr"/>
       <c r="X532" s="4" t="inlineStr"/>
       <c r="Y532" s="5" t="n">
-        <v>46186.22807321014</v>
+        <v>46186.23290213853</v>
       </c>
       <c r="Z532" s="4" t="inlineStr"/>
     </row>
@@ -35235,7 +35287,7 @@
       <c r="W533" s="4" t="inlineStr"/>
       <c r="X533" s="4" t="inlineStr"/>
       <c r="Y533" s="5" t="n">
-        <v>46186.2280732104</v>
+        <v>46186.2329021388</v>
       </c>
       <c r="Z533" s="4" t="inlineStr"/>
     </row>
@@ -35303,7 +35355,7 @@
       <c r="W534" s="4" t="inlineStr"/>
       <c r="X534" s="4" t="inlineStr"/>
       <c r="Y534" s="5" t="n">
-        <v>46186.22807321075</v>
+        <v>46186.23290213914</v>
       </c>
       <c r="Z534" s="4" t="inlineStr"/>
     </row>
@@ -35371,7 +35423,7 @@
       <c r="W535" s="4" t="inlineStr"/>
       <c r="X535" s="4" t="inlineStr"/>
       <c r="Y535" s="5" t="n">
-        <v>46186.22807321104</v>
+        <v>46186.23290214012</v>
       </c>
       <c r="Z535" s="4" t="inlineStr"/>
     </row>
@@ -35427,7 +35479,7 @@
       <c r="W536" s="8" t="inlineStr"/>
       <c r="X536" s="8" t="inlineStr"/>
       <c r="Y536" s="9" t="n">
-        <v>46186.22807321128</v>
+        <v>46186.23290214052</v>
       </c>
       <c r="Z536" s="8" t="inlineStr"/>
     </row>
@@ -35495,7 +35547,7 @@
       <c r="W537" s="4" t="inlineStr"/>
       <c r="X537" s="4" t="inlineStr"/>
       <c r="Y537" s="5" t="n">
-        <v>46186.2280732116</v>
+        <v>46186.23290214087</v>
       </c>
       <c r="Z537" s="4" t="inlineStr"/>
     </row>
@@ -35563,7 +35615,7 @@
       <c r="W538" s="4" t="inlineStr"/>
       <c r="X538" s="4" t="inlineStr"/>
       <c r="Y538" s="5" t="n">
-        <v>46186.22807321191</v>
+        <v>46186.23290214119</v>
       </c>
       <c r="Z538" s="4" t="inlineStr"/>
     </row>
@@ -35615,7 +35667,7 @@
       <c r="W539" s="4" t="inlineStr"/>
       <c r="X539" s="4" t="inlineStr"/>
       <c r="Y539" s="5" t="n">
-        <v>46186.22807321217</v>
+        <v>46186.23290214147</v>
       </c>
       <c r="Z539" s="4" t="inlineStr"/>
     </row>
@@ -35683,7 +35735,7 @@
       <c r="W540" s="4" t="inlineStr"/>
       <c r="X540" s="4" t="inlineStr"/>
       <c r="Y540" s="5" t="n">
-        <v>46186.22807321242</v>
+        <v>46186.23290214174</v>
       </c>
       <c r="Z540" s="4" t="inlineStr"/>
     </row>
@@ -35751,7 +35803,7 @@
       <c r="W541" s="4" t="inlineStr"/>
       <c r="X541" s="4" t="inlineStr"/>
       <c r="Y541" s="5" t="n">
-        <v>46186.22807321267</v>
+        <v>46186.23290214228</v>
       </c>
       <c r="Z541" s="4" t="inlineStr"/>
     </row>
@@ -35819,7 +35871,7 @@
       <c r="W542" s="4" t="inlineStr"/>
       <c r="X542" s="4" t="inlineStr"/>
       <c r="Y542" s="5" t="n">
-        <v>46186.22807321289</v>
+        <v>46186.23290214265</v>
       </c>
       <c r="Z542" s="4" t="inlineStr"/>
     </row>
@@ -35883,7 +35935,7 @@
       <c r="W543" s="4" t="inlineStr"/>
       <c r="X543" s="4" t="inlineStr"/>
       <c r="Y543" s="5" t="n">
-        <v>46186.22807321313</v>
+        <v>46186.23290214294</v>
       </c>
       <c r="Z543" s="4" t="inlineStr"/>
     </row>
@@ -35951,7 +36003,7 @@
       <c r="W544" s="4" t="inlineStr"/>
       <c r="X544" s="4" t="inlineStr"/>
       <c r="Y544" s="5" t="n">
-        <v>46186.22807321337</v>
+        <v>46186.23290214319</v>
       </c>
       <c r="Z544" s="4" t="inlineStr"/>
     </row>
@@ -36019,7 +36071,7 @@
       <c r="W545" s="4" t="inlineStr"/>
       <c r="X545" s="4" t="inlineStr"/>
       <c r="Y545" s="5" t="n">
-        <v>46186.22807321358</v>
+        <v>46186.23290214343</v>
       </c>
       <c r="Z545" s="4" t="inlineStr"/>
     </row>
@@ -36087,7 +36139,7 @@
       <c r="W546" s="4" t="inlineStr"/>
       <c r="X546" s="4" t="inlineStr"/>
       <c r="Y546" s="5" t="n">
-        <v>46186.22807321393</v>
+        <v>46186.23290214373</v>
       </c>
       <c r="Z546" s="4" t="inlineStr"/>
     </row>
@@ -36155,7 +36207,7 @@
       <c r="W547" s="4" t="inlineStr"/>
       <c r="X547" s="4" t="inlineStr"/>
       <c r="Y547" s="5" t="n">
-        <v>46186.22807321421</v>
+        <v>46186.232902144</v>
       </c>
       <c r="Z547" s="4" t="inlineStr"/>
     </row>
@@ -36223,7 +36275,7 @@
       <c r="W548" s="4" t="inlineStr"/>
       <c r="X548" s="4" t="inlineStr"/>
       <c r="Y548" s="5" t="n">
-        <v>46186.22807321452</v>
+        <v>46186.23290214429</v>
       </c>
       <c r="Z548" s="4" t="inlineStr"/>
     </row>
@@ -36295,7 +36347,7 @@
       <c r="W549" s="4" t="inlineStr"/>
       <c r="X549" s="4" t="inlineStr"/>
       <c r="Y549" s="5" t="n">
-        <v>46186.22807321477</v>
+        <v>46186.23290214455</v>
       </c>
       <c r="Z549" s="4" t="inlineStr"/>
     </row>
@@ -36363,7 +36415,7 @@
       <c r="W550" s="4" t="inlineStr"/>
       <c r="X550" s="4" t="inlineStr"/>
       <c r="Y550" s="5" t="n">
-        <v>46186.22807321503</v>
+        <v>46186.2329021448</v>
       </c>
       <c r="Z550" s="4" t="inlineStr"/>
     </row>
@@ -36431,7 +36483,7 @@
       <c r="W551" s="4" t="inlineStr"/>
       <c r="X551" s="4" t="inlineStr"/>
       <c r="Y551" s="5" t="n">
-        <v>46186.22807321534</v>
+        <v>46186.23290214512</v>
       </c>
       <c r="Z551" s="4" t="inlineStr"/>
     </row>
@@ -36499,7 +36551,7 @@
       <c r="W552" s="4" t="inlineStr"/>
       <c r="X552" s="4" t="inlineStr"/>
       <c r="Y552" s="5" t="n">
-        <v>46186.22807321558</v>
+        <v>46186.23290214535</v>
       </c>
       <c r="Z552" s="4" t="inlineStr"/>
     </row>
@@ -36555,7 +36607,7 @@
       <c r="W553" s="4" t="inlineStr"/>
       <c r="X553" s="4" t="inlineStr"/>
       <c r="Y553" s="5" t="n">
-        <v>46186.22807321587</v>
+        <v>46186.23290214598</v>
       </c>
       <c r="Z553" s="4" t="inlineStr"/>
     </row>
@@ -36623,7 +36675,7 @@
       <c r="W554" s="4" t="inlineStr"/>
       <c r="X554" s="4" t="inlineStr"/>
       <c r="Y554" s="5" t="n">
-        <v>46186.22807321615</v>
+        <v>46186.23290214639</v>
       </c>
       <c r="Z554" s="4" t="inlineStr"/>
     </row>
@@ -36695,7 +36747,7 @@
       <c r="W555" s="4" t="inlineStr"/>
       <c r="X555" s="4" t="inlineStr"/>
       <c r="Y555" s="5" t="n">
-        <v>46186.22807321641</v>
+        <v>46186.23290214697</v>
       </c>
       <c r="Z555" s="4" t="inlineStr"/>
     </row>
@@ -36763,7 +36815,7 @@
       <c r="W556" s="4" t="inlineStr"/>
       <c r="X556" s="4" t="inlineStr"/>
       <c r="Y556" s="5" t="n">
-        <v>46186.22807321665</v>
+        <v>46186.23290214735</v>
       </c>
       <c r="Z556" s="4" t="inlineStr"/>
     </row>
@@ -36819,7 +36871,7 @@
       <c r="W557" s="4" t="inlineStr"/>
       <c r="X557" s="4" t="inlineStr"/>
       <c r="Y557" s="5" t="n">
-        <v>46186.22807321687</v>
+        <v>46186.2329021476</v>
       </c>
       <c r="Z557" s="4" t="inlineStr"/>
     </row>
@@ -36875,7 +36927,7 @@
       <c r="W558" s="4" t="inlineStr"/>
       <c r="X558" s="4" t="inlineStr"/>
       <c r="Y558" s="5" t="n">
-        <v>46186.22807321711</v>
+        <v>46186.23290214786</v>
       </c>
       <c r="Z558" s="4" t="inlineStr"/>
     </row>
@@ -36947,7 +36999,7 @@
       <c r="W559" s="4" t="inlineStr"/>
       <c r="X559" s="4" t="inlineStr"/>
       <c r="Y559" s="5" t="n">
-        <v>46186.22807321737</v>
+        <v>46186.23290214813</v>
       </c>
       <c r="Z559" s="4" t="inlineStr"/>
     </row>
@@ -37015,7 +37067,7 @@
       <c r="W560" s="4" t="inlineStr"/>
       <c r="X560" s="4" t="inlineStr"/>
       <c r="Y560" s="5" t="n">
-        <v>46186.22807321762</v>
+        <v>46186.23290214838</v>
       </c>
       <c r="Z560" s="4" t="inlineStr"/>
     </row>
@@ -37083,7 +37135,7 @@
       <c r="W561" s="4" t="inlineStr"/>
       <c r="X561" s="4" t="inlineStr"/>
       <c r="Y561" s="5" t="n">
-        <v>46186.22807321788</v>
+        <v>46186.23290214866</v>
       </c>
       <c r="Z561" s="4" t="inlineStr"/>
     </row>
@@ -37155,7 +37207,7 @@
       <c r="W562" s="4" t="inlineStr"/>
       <c r="X562" s="4" t="inlineStr"/>
       <c r="Y562" s="5" t="n">
-        <v>46186.22807321815</v>
+        <v>46186.23290214895</v>
       </c>
       <c r="Z562" s="4" t="inlineStr"/>
     </row>
@@ -37223,7 +37275,7 @@
       <c r="W563" s="4" t="inlineStr"/>
       <c r="X563" s="4" t="inlineStr"/>
       <c r="Y563" s="5" t="n">
-        <v>46186.22807321881</v>
+        <v>46186.23290214923</v>
       </c>
       <c r="Z563" s="4" t="inlineStr"/>
     </row>
@@ -37243,7 +37295,11 @@
           <t>Package Submission - DCP2 - Al Ruwayyah Depot Landscape Design: DE.DPT.GN00.LDS.L0.D2_Rev C01</t>
         </is>
       </c>
-      <c r="F564" s="4" t="inlineStr"/>
+      <c r="F564" s="4" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
       <c r="G564" s="4" t="inlineStr"/>
       <c r="H564" s="4" t="inlineStr"/>
       <c r="I564" s="4" t="inlineStr"/>
@@ -37275,7 +37331,7 @@
       <c r="W564" s="4" t="inlineStr"/>
       <c r="X564" s="4" t="inlineStr"/>
       <c r="Y564" s="5" t="n">
-        <v>46186.22807321916</v>
+        <v>46186.23290214947</v>
       </c>
       <c r="Z564" s="4" t="inlineStr"/>
     </row>
@@ -37343,7 +37399,7 @@
       <c r="W565" s="4" t="inlineStr"/>
       <c r="X565" s="4" t="inlineStr"/>
       <c r="Y565" s="5" t="n">
-        <v>46186.22807321946</v>
+        <v>46186.23290214971</v>
       </c>
       <c r="Z565" s="4" t="inlineStr"/>
     </row>
@@ -37411,7 +37467,7 @@
       <c r="W566" s="4" t="inlineStr"/>
       <c r="X566" s="4" t="inlineStr"/>
       <c r="Y566" s="5" t="n">
-        <v>46186.22807321977</v>
+        <v>46186.23290214995</v>
       </c>
       <c r="Z566" s="4" t="inlineStr"/>
     </row>
@@ -37479,7 +37535,7 @@
       <c r="W567" s="4" t="inlineStr"/>
       <c r="X567" s="4" t="inlineStr"/>
       <c r="Y567" s="5" t="n">
-        <v>46186.22807322024</v>
+        <v>46186.23290215094</v>
       </c>
       <c r="Z567" s="4" t="inlineStr"/>
     </row>
@@ -37535,7 +37591,7 @@
       <c r="W568" s="4" t="inlineStr"/>
       <c r="X568" s="4" t="inlineStr"/>
       <c r="Y568" s="5" t="n">
-        <v>46186.22807322058</v>
+        <v>46186.23290215127</v>
       </c>
       <c r="Z568" s="4" t="inlineStr"/>
     </row>
@@ -37607,7 +37663,7 @@
       <c r="W569" s="4" t="inlineStr"/>
       <c r="X569" s="4" t="inlineStr"/>
       <c r="Y569" s="5" t="n">
-        <v>46186.22807322086</v>
+        <v>46186.23290215156</v>
       </c>
       <c r="Z569" s="4" t="inlineStr"/>
     </row>
@@ -37659,7 +37715,7 @@
       <c r="W570" s="4" t="inlineStr"/>
       <c r="X570" s="4" t="inlineStr"/>
       <c r="Y570" s="5" t="n">
-        <v>46186.22807322112</v>
+        <v>46186.23290215183</v>
       </c>
       <c r="Z570" s="4" t="inlineStr"/>
     </row>
@@ -37715,7 +37771,7 @@
       <c r="W571" s="4" t="inlineStr"/>
       <c r="X571" s="4" t="inlineStr"/>
       <c r="Y571" s="5" t="n">
-        <v>46186.2280732214</v>
+        <v>46186.23290215207</v>
       </c>
       <c r="Z571" s="4" t="inlineStr"/>
     </row>
@@ -37771,7 +37827,7 @@
       <c r="W572" s="4" t="inlineStr"/>
       <c r="X572" s="4" t="inlineStr"/>
       <c r="Y572" s="5" t="n">
-        <v>46186.22807322163</v>
+        <v>46186.2329021523</v>
       </c>
       <c r="Z572" s="4" t="inlineStr"/>
     </row>
@@ -37795,7 +37851,11 @@
           <t>Specification Submission - DCP2 - Traction System Design Specification and System Architecture (RLS.1.1.2.2.2): MLCC-N0003-PDS-MPD-TRP-SPC-51000_Rev C04</t>
         </is>
       </c>
-      <c r="F573" s="4" t="inlineStr"/>
+      <c r="F573" s="4" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
       <c r="G573" s="4" t="inlineStr"/>
       <c r="H573" s="4" t="inlineStr">
         <is>
@@ -37839,7 +37899,7 @@
       <c r="W573" s="4" t="inlineStr"/>
       <c r="X573" s="4" t="inlineStr"/>
       <c r="Y573" s="5" t="n">
-        <v>46186.2280732219</v>
+        <v>46186.23290215257</v>
       </c>
       <c r="Z573" s="4" t="inlineStr"/>
     </row>
@@ -37907,7 +37967,7 @@
       <c r="W574" s="4" t="inlineStr"/>
       <c r="X574" s="4" t="inlineStr"/>
       <c r="Y574" s="5" t="n">
-        <v>46186.22807322216</v>
+        <v>46186.23290215283</v>
       </c>
       <c r="Z574" s="4" t="inlineStr"/>
     </row>
@@ -37975,7 +38035,7 @@
       <c r="W575" s="4" t="inlineStr"/>
       <c r="X575" s="4" t="inlineStr"/>
       <c r="Y575" s="5" t="n">
-        <v>46186.22807322259</v>
+        <v>46186.23290215446</v>
       </c>
       <c r="Z575" s="4" t="inlineStr"/>
     </row>
@@ -38047,7 +38107,7 @@
       <c r="W576" s="4" t="inlineStr"/>
       <c r="X576" s="4" t="inlineStr"/>
       <c r="Y576" s="5" t="n">
-        <v>46186.22807322285</v>
+        <v>46186.23290215485</v>
       </c>
       <c r="Z576" s="4" t="inlineStr"/>
     </row>
@@ -38115,7 +38175,7 @@
       <c r="W577" s="4" t="inlineStr"/>
       <c r="X577" s="4" t="inlineStr"/>
       <c r="Y577" s="5" t="n">
-        <v>46186.2280732231</v>
+        <v>46186.23290215515</v>
       </c>
       <c r="Z577" s="4" t="inlineStr"/>
     </row>
@@ -38183,7 +38243,7 @@
       <c r="W578" s="4" t="inlineStr"/>
       <c r="X578" s="4" t="inlineStr"/>
       <c r="Y578" s="5" t="n">
-        <v>46186.22807322336</v>
+        <v>46186.23290215542</v>
       </c>
       <c r="Z578" s="4" t="inlineStr"/>
     </row>
@@ -38251,7 +38311,7 @@
       <c r="W579" s="4" t="inlineStr"/>
       <c r="X579" s="4" t="inlineStr"/>
       <c r="Y579" s="5" t="n">
-        <v>46186.22807322357</v>
+        <v>46186.23290215566</v>
       </c>
       <c r="Z579" s="4" t="inlineStr"/>
     </row>
@@ -38319,7 +38379,7 @@
       <c r="W580" s="4" t="inlineStr"/>
       <c r="X580" s="4" t="inlineStr"/>
       <c r="Y580" s="5" t="n">
-        <v>46186.2280732238</v>
+        <v>46186.23290215589</v>
       </c>
       <c r="Z580" s="4" t="inlineStr"/>
     </row>
@@ -38387,7 +38447,7 @@
       <c r="W581" s="4" t="inlineStr"/>
       <c r="X581" s="4" t="inlineStr"/>
       <c r="Y581" s="5" t="n">
-        <v>46186.22807322403</v>
+        <v>46186.23290215613</v>
       </c>
       <c r="Z581" s="4" t="inlineStr"/>
     </row>
@@ -38455,7 +38515,7 @@
       <c r="W582" s="4" t="inlineStr"/>
       <c r="X582" s="4" t="inlineStr"/>
       <c r="Y582" s="5" t="n">
-        <v>46186.22807322429</v>
+        <v>46186.23290215639</v>
       </c>
       <c r="Z582" s="4" t="inlineStr"/>
     </row>
@@ -38523,7 +38583,7 @@
       <c r="W583" s="8" t="inlineStr"/>
       <c r="X583" s="8" t="inlineStr"/>
       <c r="Y583" s="9" t="n">
-        <v>46186.22807322457</v>
+        <v>46186.23290215665</v>
       </c>
       <c r="Z583" s="8" t="inlineStr"/>
     </row>
@@ -38591,7 +38651,7 @@
       <c r="W584" s="8" t="inlineStr"/>
       <c r="X584" s="8" t="inlineStr"/>
       <c r="Y584" s="9" t="n">
-        <v>46186.22807322498</v>
+        <v>46186.23290215695</v>
       </c>
       <c r="Z584" s="8" t="inlineStr"/>
     </row>
@@ -38659,7 +38719,7 @@
       <c r="W585" s="8" t="inlineStr"/>
       <c r="X585" s="8" t="inlineStr"/>
       <c r="Y585" s="9" t="n">
-        <v>46186.22807322536</v>
+        <v>46186.23290215718</v>
       </c>
       <c r="Z585" s="8" t="inlineStr"/>
     </row>
@@ -38731,7 +38791,7 @@
       <c r="W586" s="8" t="inlineStr"/>
       <c r="X586" s="8" t="inlineStr"/>
       <c r="Y586" s="9" t="n">
-        <v>46186.22807322567</v>
+        <v>46186.23290215746</v>
       </c>
       <c r="Z586" s="8" t="inlineStr"/>
     </row>
@@ -38799,7 +38859,7 @@
       <c r="W587" s="4" t="inlineStr"/>
       <c r="X587" s="4" t="inlineStr"/>
       <c r="Y587" s="5" t="n">
-        <v>46186.22807322598</v>
+        <v>46186.23290215807</v>
       </c>
       <c r="Z587" s="4" t="inlineStr"/>
     </row>
@@ -38871,7 +38931,7 @@
       <c r="W588" s="8" t="inlineStr"/>
       <c r="X588" s="8" t="inlineStr"/>
       <c r="Y588" s="9" t="n">
-        <v>46186.22807322625</v>
+        <v>46186.23290215846</v>
       </c>
       <c r="Z588" s="8" t="inlineStr"/>
     </row>
@@ -38943,7 +39003,7 @@
       <c r="W589" s="8" t="inlineStr"/>
       <c r="X589" s="8" t="inlineStr"/>
       <c r="Y589" s="9" t="n">
-        <v>46186.22807322649</v>
+        <v>46186.23290215874</v>
       </c>
       <c r="Z589" s="8" t="inlineStr"/>
     </row>
@@ -39011,7 +39071,7 @@
       <c r="W590" s="4" t="inlineStr"/>
       <c r="X590" s="4" t="inlineStr"/>
       <c r="Y590" s="5" t="n">
-        <v>46186.22807322672</v>
+        <v>46186.232902159</v>
       </c>
       <c r="Z590" s="4" t="inlineStr"/>
     </row>
@@ -39083,7 +39143,7 @@
       <c r="W591" s="8" t="inlineStr"/>
       <c r="X591" s="8" t="inlineStr"/>
       <c r="Y591" s="9" t="n">
-        <v>46186.22807322698</v>
+        <v>46186.23290215926</v>
       </c>
       <c r="Z591" s="8" t="inlineStr"/>
     </row>
@@ -39151,7 +39211,7 @@
       <c r="W592" s="4" t="inlineStr"/>
       <c r="X592" s="4" t="inlineStr"/>
       <c r="Y592" s="5" t="n">
-        <v>46186.22807322722</v>
+        <v>46186.23290215953</v>
       </c>
       <c r="Z592" s="4" t="inlineStr"/>
     </row>
@@ -39219,7 +39279,7 @@
       <c r="W593" s="8" t="inlineStr"/>
       <c r="X593" s="8" t="inlineStr"/>
       <c r="Y593" s="9" t="n">
-        <v>46186.22807322745</v>
+        <v>46186.23290215977</v>
       </c>
       <c r="Z593" s="8" t="inlineStr"/>
     </row>
@@ -39291,7 +39351,7 @@
       <c r="W594" s="8" t="inlineStr"/>
       <c r="X594" s="8" t="inlineStr"/>
       <c r="Y594" s="9" t="n">
-        <v>46186.22807322774</v>
+        <v>46186.23290216032</v>
       </c>
       <c r="Z594" s="8" t="inlineStr"/>
     </row>
@@ -39363,7 +39423,7 @@
       <c r="W595" s="8" t="inlineStr"/>
       <c r="X595" s="8" t="inlineStr"/>
       <c r="Y595" s="9" t="n">
-        <v>46186.22807322798</v>
+        <v>46186.23290216071</v>
       </c>
       <c r="Z595" s="8" t="inlineStr"/>
     </row>
@@ -39387,7 +39447,11 @@
           <t>Re: Specification Submission - DCP2 - MV System Design Specification and System Architecture (RLS.1.1.2.2.2) : MLCC-N0003-PDS-MPD-MVN-SPC-51001_Rev C03</t>
         </is>
       </c>
-      <c r="F596" s="8" t="inlineStr"/>
+      <c r="F596" s="8" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
       <c r="G596" s="8" t="inlineStr"/>
       <c r="H596" s="8" t="inlineStr">
         <is>
@@ -39431,7 +39495,7 @@
       <c r="W596" s="8" t="inlineStr"/>
       <c r="X596" s="8" t="inlineStr"/>
       <c r="Y596" s="9" t="n">
-        <v>46186.22807322822</v>
+        <v>46186.23290216097</v>
       </c>
       <c r="Z596" s="8" t="inlineStr"/>
     </row>
@@ -39503,7 +39567,7 @@
       <c r="W597" s="8" t="inlineStr"/>
       <c r="X597" s="8" t="inlineStr"/>
       <c r="Y597" s="9" t="n">
-        <v>46186.22807322847</v>
+        <v>46186.23290216125</v>
       </c>
       <c r="Z597" s="8" t="inlineStr"/>
     </row>
@@ -39575,7 +39639,7 @@
       <c r="W598" s="8" t="inlineStr"/>
       <c r="X598" s="8" t="inlineStr"/>
       <c r="Y598" s="9" t="n">
-        <v>46186.22807322873</v>
+        <v>46186.23290216151</v>
       </c>
       <c r="Z598" s="8" t="inlineStr"/>
     </row>
@@ -39647,7 +39711,7 @@
       <c r="W599" s="8" t="inlineStr"/>
       <c r="X599" s="8" t="inlineStr"/>
       <c r="Y599" s="9" t="n">
-        <v>46186.22807322897</v>
+        <v>46186.23290216176</v>
       </c>
       <c r="Z599" s="8" t="inlineStr"/>
     </row>
@@ -39715,7 +39779,7 @@
       <c r="W600" s="8" t="inlineStr"/>
       <c r="X600" s="8" t="inlineStr"/>
       <c r="Y600" s="9" t="n">
-        <v>46186.2280732292</v>
+        <v>46186.23290216204</v>
       </c>
       <c r="Z600" s="8" t="inlineStr"/>
     </row>
@@ -39787,7 +39851,7 @@
       <c r="W601" s="8" t="inlineStr"/>
       <c r="X601" s="8" t="inlineStr"/>
       <c r="Y601" s="9" t="n">
-        <v>46186.22807322945</v>
+        <v>46186.23290216266</v>
       </c>
       <c r="Z601" s="8" t="inlineStr"/>
     </row>
@@ -39855,7 +39919,7 @@
       <c r="W602" s="8" t="inlineStr"/>
       <c r="X602" s="8" t="inlineStr"/>
       <c r="Y602" s="9" t="n">
-        <v>46186.22807322971</v>
+        <v>46186.23290216304</v>
       </c>
       <c r="Z602" s="8" t="inlineStr"/>
     </row>
@@ -39875,7 +39939,11 @@
           <t>Re: Package Submission - DCP2 - BB03 - Academic City Station (GLE-11) Architecture Design Package: DE.ELS.GE11.ARC.A2.D2_Rev C04</t>
         </is>
       </c>
-      <c r="F603" s="8" t="inlineStr"/>
+      <c r="F603" s="8" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
       <c r="G603" s="8" t="inlineStr"/>
       <c r="H603" s="8" t="inlineStr"/>
       <c r="I603" s="8" t="inlineStr"/>
@@ -39907,7 +39975,7 @@
       <c r="W603" s="8" t="inlineStr"/>
       <c r="X603" s="8" t="inlineStr"/>
       <c r="Y603" s="9" t="n">
-        <v>46186.22807323037</v>
+        <v>46186.23290216394</v>
       </c>
       <c r="Z603" s="8" t="inlineStr"/>
     </row>
@@ -39979,7 +40047,7 @@
       <c r="W604" s="8" t="inlineStr"/>
       <c r="X604" s="8" t="inlineStr"/>
       <c r="Y604" s="9" t="n">
-        <v>46186.22807323078</v>
+        <v>46186.23290216435</v>
       </c>
       <c r="Z604" s="8" t="inlineStr"/>
     </row>
@@ -40051,7 +40119,7 @@
       <c r="W605" s="8" t="inlineStr"/>
       <c r="X605" s="8" t="inlineStr"/>
       <c r="Y605" s="9" t="n">
-        <v>46186.22807323112</v>
+        <v>46186.23290216467</v>
       </c>
       <c r="Z605" s="8" t="inlineStr"/>
     </row>
@@ -40123,7 +40191,7 @@
       <c r="W606" s="8" t="inlineStr"/>
       <c r="X606" s="8" t="inlineStr"/>
       <c r="Y606" s="9" t="n">
-        <v>46186.2280732314</v>
+        <v>46186.23290216496</v>
       </c>
       <c r="Z606" s="8" t="inlineStr"/>
     </row>
@@ -40195,7 +40263,7 @@
       <c r="W607" s="8" t="inlineStr"/>
       <c r="X607" s="8" t="inlineStr"/>
       <c r="Y607" s="9" t="n">
-        <v>46186.22807323166</v>
+        <v>46186.23290216558</v>
       </c>
       <c r="Z607" s="8" t="inlineStr"/>
     </row>
@@ -40251,7 +40319,7 @@
       <c r="W608" s="8" t="inlineStr"/>
       <c r="X608" s="8" t="inlineStr"/>
       <c r="Y608" s="9" t="n">
-        <v>46186.22807323191</v>
+        <v>46186.23290216592</v>
       </c>
       <c r="Z608" s="8" t="inlineStr"/>
     </row>
@@ -40319,7 +40387,7 @@
       <c r="W609" s="4" t="inlineStr"/>
       <c r="X609" s="4" t="inlineStr"/>
       <c r="Y609" s="5" t="n">
-        <v>46186.22807323217</v>
+        <v>46186.23290216623</v>
       </c>
       <c r="Z609" s="4" t="inlineStr"/>
     </row>
@@ -40375,7 +40443,7 @@
       <c r="W610" s="8" t="inlineStr"/>
       <c r="X610" s="8" t="inlineStr"/>
       <c r="Y610" s="9" t="n">
-        <v>46186.2280732325</v>
+        <v>46186.23290216684</v>
       </c>
       <c r="Z610" s="8" t="inlineStr"/>
     </row>
@@ -40431,7 +40499,7 @@
       <c r="W611" s="8" t="inlineStr"/>
       <c r="X611" s="8" t="inlineStr"/>
       <c r="Y611" s="9" t="n">
-        <v>46186.22807323273</v>
+        <v>46186.2329021672</v>
       </c>
       <c r="Z611" s="8" t="inlineStr"/>
     </row>
@@ -40487,7 +40555,7 @@
       <c r="W612" s="8" t="inlineStr"/>
       <c r="X612" s="8" t="inlineStr"/>
       <c r="Y612" s="9" t="n">
-        <v>46186.22807323293</v>
+        <v>46186.23290216745</v>
       </c>
       <c r="Z612" s="8" t="inlineStr"/>
     </row>
@@ -40543,7 +40611,7 @@
       <c r="W613" s="8" t="inlineStr"/>
       <c r="X613" s="8" t="inlineStr"/>
       <c r="Y613" s="9" t="n">
-        <v>46186.22807323316</v>
+        <v>46186.23290216772</v>
       </c>
       <c r="Z613" s="8" t="inlineStr"/>
     </row>
@@ -40611,7 +40679,7 @@
       <c r="W614" s="8" t="inlineStr"/>
       <c r="X614" s="8" t="inlineStr"/>
       <c r="Y614" s="9" t="n">
-        <v>46186.22807323339</v>
+        <v>46186.23290216798</v>
       </c>
       <c r="Z614" s="8" t="inlineStr"/>
     </row>
@@ -40663,7 +40731,7 @@
       <c r="W615" s="8" t="inlineStr"/>
       <c r="X615" s="8" t="inlineStr"/>
       <c r="Y615" s="9" t="n">
-        <v>46186.2280732337</v>
+        <v>46186.23290216861</v>
       </c>
       <c r="Z615" s="8" t="inlineStr"/>
     </row>
@@ -40731,7 +40799,7 @@
       <c r="W616" s="8" t="inlineStr"/>
       <c r="X616" s="8" t="inlineStr"/>
       <c r="Y616" s="9" t="n">
-        <v>46186.22807323393</v>
+        <v>46186.23290216899</v>
       </c>
       <c r="Z616" s="8" t="inlineStr"/>
     </row>
@@ -40787,7 +40855,7 @@
       <c r="W617" s="8" t="inlineStr"/>
       <c r="X617" s="8" t="inlineStr"/>
       <c r="Y617" s="9" t="n">
-        <v>46186.22807323419</v>
+        <v>46186.23290216927</v>
       </c>
       <c r="Z617" s="8" t="inlineStr"/>
     </row>
@@ -40855,7 +40923,7 @@
       <c r="W618" s="8" t="inlineStr"/>
       <c r="X618" s="8" t="inlineStr"/>
       <c r="Y618" s="9" t="n">
-        <v>46186.22807323444</v>
+        <v>46186.23290216954</v>
       </c>
       <c r="Z618" s="8" t="inlineStr"/>
     </row>
@@ -40911,7 +40979,7 @@
       <c r="W619" s="8" t="inlineStr"/>
       <c r="X619" s="8" t="inlineStr"/>
       <c r="Y619" s="9" t="n">
-        <v>46186.22807323466</v>
+        <v>46186.23290216978</v>
       </c>
       <c r="Z619" s="8" t="inlineStr"/>
     </row>
@@ -40983,7 +41051,7 @@
       <c r="W620" s="8" t="inlineStr"/>
       <c r="X620" s="8" t="inlineStr"/>
       <c r="Y620" s="9" t="n">
-        <v>46186.2280732349</v>
+        <v>46186.23290217002</v>
       </c>
       <c r="Z620" s="8" t="inlineStr"/>
     </row>
@@ -41051,7 +41119,7 @@
       <c r="W621" s="8" t="inlineStr"/>
       <c r="X621" s="8" t="inlineStr"/>
       <c r="Y621" s="9" t="n">
-        <v>46186.22807323514</v>
+        <v>46186.23290217027</v>
       </c>
       <c r="Z621" s="8" t="inlineStr"/>
     </row>
@@ -41119,7 +41187,7 @@
       <c r="W622" s="8" t="inlineStr"/>
       <c r="X622" s="8" t="inlineStr"/>
       <c r="Y622" s="9" t="n">
-        <v>46186.2280732354</v>
+        <v>46186.23290217053</v>
       </c>
       <c r="Z622" s="8" t="inlineStr"/>
     </row>
@@ -41187,7 +41255,7 @@
       <c r="W623" s="8" t="inlineStr"/>
       <c r="X623" s="8" t="inlineStr"/>
       <c r="Y623" s="9" t="n">
-        <v>46186.22807323572</v>
+        <v>46186.23290217139</v>
       </c>
       <c r="Z623" s="8" t="inlineStr"/>
     </row>
@@ -41243,7 +41311,7 @@
       <c r="W624" s="4" t="inlineStr"/>
       <c r="X624" s="4" t="inlineStr"/>
       <c r="Y624" s="5" t="n">
-        <v>46186.22807323595</v>
+        <v>46186.23290217175</v>
       </c>
       <c r="Z624" s="4" t="inlineStr"/>
     </row>
@@ -41299,7 +41367,7 @@
       <c r="W625" s="4" t="inlineStr"/>
       <c r="X625" s="4" t="inlineStr"/>
       <c r="Y625" s="5" t="n">
-        <v>46186.22807323619</v>
+        <v>46186.23290217201</v>
       </c>
       <c r="Z625" s="4" t="inlineStr"/>
     </row>
@@ -41367,7 +41435,7 @@
       <c r="W626" s="4" t="inlineStr"/>
       <c r="X626" s="4" t="inlineStr"/>
       <c r="Y626" s="5" t="n">
-        <v>46186.22807323644</v>
+        <v>46186.23290217227</v>
       </c>
       <c r="Z626" s="4" t="inlineStr"/>
     </row>
@@ -41435,7 +41503,7 @@
       <c r="W627" s="4" t="inlineStr"/>
       <c r="X627" s="4" t="inlineStr"/>
       <c r="Y627" s="5" t="n">
-        <v>46186.22807323666</v>
+        <v>46186.23290217251</v>
       </c>
       <c r="Z627" s="4" t="inlineStr"/>
     </row>
@@ -41507,7 +41575,7 @@
       <c r="W628" s="4" t="inlineStr"/>
       <c r="X628" s="4" t="inlineStr"/>
       <c r="Y628" s="5" t="n">
-        <v>46186.22807323698</v>
+        <v>46186.23290217278</v>
       </c>
       <c r="Z628" s="4" t="inlineStr"/>
     </row>
@@ -41563,7 +41631,7 @@
       <c r="W629" s="4" t="inlineStr"/>
       <c r="X629" s="4" t="inlineStr"/>
       <c r="Y629" s="5" t="n">
-        <v>46186.22807323721</v>
+        <v>46186.232902173</v>
       </c>
       <c r="Z629" s="4" t="inlineStr"/>
     </row>
@@ -41644,7 +41712,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13/06/2026 05:28</t>
+          <t>13/06/2026 05:35</t>
         </is>
       </c>
     </row>

--- a/output_transmittal_register.xlsx
+++ b/output_transmittal_register.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 13/06/2026 05:41</t>
+          <t>Generated: 13/06/2026 06:32</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
       <c r="Y9" s="5" t="n">
-        <v>46186.23724710854</v>
+        <v>46186.27264108857</v>
       </c>
       <c r="Z9" s="4" t="inlineStr"/>
     </row>
@@ -947,7 +947,7 @@
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr"/>
       <c r="Y10" s="5" t="n">
-        <v>46186.23724710914</v>
+        <v>46186.27264108917</v>
       </c>
       <c r="Z10" s="4" t="inlineStr"/>
     </row>
@@ -1015,7 +1015,7 @@
       <c r="W11" s="8" t="inlineStr"/>
       <c r="X11" s="8" t="inlineStr"/>
       <c r="Y11" s="9" t="n">
-        <v>46186.23724710995</v>
+        <v>46186.2726410895</v>
       </c>
       <c r="Z11" s="8" t="inlineStr"/>
     </row>
@@ -1083,7 +1083,7 @@
       <c r="W12" s="8" t="inlineStr"/>
       <c r="X12" s="8" t="inlineStr"/>
       <c r="Y12" s="9" t="n">
-        <v>46186.23724711032</v>
+        <v>46186.2726410898</v>
       </c>
       <c r="Z12" s="8" t="inlineStr"/>
     </row>
@@ -1155,7 +1155,7 @@
       <c r="W13" s="8" t="inlineStr"/>
       <c r="X13" s="8" t="inlineStr"/>
       <c r="Y13" s="9" t="n">
-        <v>46186.23724711061</v>
+        <v>46186.27264109007</v>
       </c>
       <c r="Z13" s="8" t="inlineStr"/>
     </row>
@@ -1223,7 +1223,7 @@
       <c r="W14" s="8" t="inlineStr"/>
       <c r="X14" s="8" t="inlineStr"/>
       <c r="Y14" s="9" t="n">
-        <v>46186.23724711094</v>
+        <v>46186.27264109039</v>
       </c>
       <c r="Z14" s="8" t="inlineStr"/>
     </row>
@@ -1291,7 +1291,7 @@
       <c r="W15" s="8" t="inlineStr"/>
       <c r="X15" s="8" t="inlineStr"/>
       <c r="Y15" s="9" t="n">
-        <v>46186.23724711148</v>
+        <v>46186.27264109098</v>
       </c>
       <c r="Z15" s="8" t="inlineStr"/>
     </row>
@@ -1355,7 +1355,7 @@
       <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="5" t="n">
-        <v>46186.23724711181</v>
+        <v>46186.27264109131</v>
       </c>
       <c r="Z16" s="4" t="inlineStr"/>
     </row>
@@ -1419,7 +1419,7 @@
       <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="5" t="n">
-        <v>46186.23724711206</v>
+        <v>46186.27264109156</v>
       </c>
       <c r="Z17" s="4" t="inlineStr"/>
     </row>
@@ -1483,7 +1483,7 @@
       <c r="W18" s="4" t="inlineStr"/>
       <c r="X18" s="4" t="inlineStr"/>
       <c r="Y18" s="5" t="n">
-        <v>46186.23724711228</v>
+        <v>46186.27264109178</v>
       </c>
       <c r="Z18" s="4" t="inlineStr"/>
     </row>
@@ -1547,7 +1547,7 @@
       <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="5" t="n">
-        <v>46186.23724711246</v>
+        <v>46186.2726410925</v>
       </c>
       <c r="Z19" s="4" t="inlineStr"/>
     </row>
@@ -1611,7 +1611,7 @@
       <c r="W20" s="8" t="inlineStr"/>
       <c r="X20" s="8" t="inlineStr"/>
       <c r="Y20" s="9" t="n">
-        <v>46186.23724711271</v>
+        <v>46186.27264109282</v>
       </c>
       <c r="Z20" s="8" t="inlineStr"/>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="W21" s="8" t="inlineStr"/>
       <c r="X21" s="8" t="inlineStr"/>
       <c r="Y21" s="9" t="n">
-        <v>46186.23724711293</v>
+        <v>46186.27264109306</v>
       </c>
       <c r="Z21" s="8" t="inlineStr"/>
     </row>
@@ -1689,7 +1689,11 @@
       <c r="C22" s="9" t="n">
         <v>46185</v>
       </c>
-      <c r="D22" s="8" t="inlineStr"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>DE.TNL.CC02.STR.T2.D3</t>
+        </is>
+      </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Re: Design Drawing Submission - DCP3 - Cut &amp; Cover BB05 Slabs - (DE.TNL.CC02.STR.T2.D3) - Rev.C01</t>
@@ -1723,7 +1727,7 @@
       <c r="W22" s="8" t="inlineStr"/>
       <c r="X22" s="8" t="inlineStr"/>
       <c r="Y22" s="9" t="n">
-        <v>46186.23724711312</v>
+        <v>46186.2726410933</v>
       </c>
       <c r="Z22" s="8" t="inlineStr"/>
     </row>
@@ -1791,7 +1795,7 @@
       <c r="W23" s="8" t="inlineStr"/>
       <c r="X23" s="8" t="inlineStr"/>
       <c r="Y23" s="9" t="n">
-        <v>46186.23724711408</v>
+        <v>46186.27264109354</v>
       </c>
       <c r="Z23" s="8" t="inlineStr"/>
     </row>
@@ -1855,7 +1859,7 @@
       <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="5" t="n">
-        <v>46186.2372471144</v>
+        <v>46186.27264109375</v>
       </c>
       <c r="Z24" s="4" t="inlineStr"/>
     </row>
@@ -1923,7 +1927,7 @@
       <c r="W25" s="8" t="inlineStr"/>
       <c r="X25" s="8" t="inlineStr"/>
       <c r="Y25" s="9" t="n">
-        <v>46186.23724711475</v>
+        <v>46186.27264109406</v>
       </c>
       <c r="Z25" s="8" t="inlineStr"/>
     </row>
@@ -1991,7 +1995,7 @@
       <c r="W26" s="8" t="inlineStr"/>
       <c r="X26" s="8" t="inlineStr"/>
       <c r="Y26" s="9" t="n">
-        <v>46186.237247115</v>
+        <v>46186.27264109429</v>
       </c>
       <c r="Z26" s="8" t="inlineStr"/>
     </row>
@@ -2055,7 +2059,7 @@
       <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="5" t="n">
-        <v>46186.23724711541</v>
+        <v>46186.2726410945</v>
       </c>
       <c r="Z27" s="4" t="inlineStr"/>
     </row>
@@ -2119,7 +2123,7 @@
       <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="5" t="n">
-        <v>46186.23724711567</v>
+        <v>46186.27264109499</v>
       </c>
       <c r="Z28" s="4" t="inlineStr"/>
     </row>
@@ -2183,7 +2187,7 @@
       <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="5" t="n">
-        <v>46186.23724711593</v>
+        <v>46186.27264109537</v>
       </c>
       <c r="Z29" s="4" t="inlineStr"/>
     </row>
@@ -2247,7 +2251,7 @@
       <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="5" t="n">
-        <v>46186.23724711659</v>
+        <v>46186.27264109598</v>
       </c>
       <c r="Z30" s="4" t="inlineStr"/>
     </row>
@@ -2311,7 +2315,7 @@
       <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="5" t="n">
-        <v>46186.23724711692</v>
+        <v>46186.27264109633</v>
       </c>
       <c r="Z31" s="4" t="inlineStr"/>
     </row>
@@ -2325,7 +2329,11 @@
       <c r="C32" s="5" t="n">
         <v>46185</v>
       </c>
-      <c r="D32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>DE.UGS.GE09.MEP.M4</t>
+        </is>
+      </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP2 - Underground Station BB05 MEP VAC: DE.UGS.GE09.MEP.M4.D3_Rev.C01</t>
@@ -2363,7 +2371,7 @@
       <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="5" t="n">
-        <v>46186.23724711713</v>
+        <v>46186.2726410966</v>
       </c>
       <c r="Z32" s="4" t="inlineStr"/>
     </row>
@@ -2427,7 +2435,7 @@
       <c r="W33" s="4" t="inlineStr"/>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="5" t="n">
-        <v>46186.23724711739</v>
+        <v>46186.27264109686</v>
       </c>
       <c r="Z33" s="4" t="inlineStr"/>
     </row>
@@ -2495,7 +2503,7 @@
       <c r="W34" s="4" t="inlineStr"/>
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="5" t="n">
-        <v>46186.23724711759</v>
+        <v>46186.27264109707</v>
       </c>
       <c r="Z34" s="4" t="inlineStr"/>
     </row>
@@ -2559,7 +2567,7 @@
       <c r="W35" s="4" t="inlineStr"/>
       <c r="X35" s="4" t="inlineStr"/>
       <c r="Y35" s="5" t="n">
-        <v>46186.23724711779</v>
+        <v>46186.27264109728</v>
       </c>
       <c r="Z35" s="4" t="inlineStr"/>
     </row>
@@ -2627,7 +2635,7 @@
       <c r="W36" s="8" t="inlineStr"/>
       <c r="X36" s="8" t="inlineStr"/>
       <c r="Y36" s="9" t="n">
-        <v>46186.23724711801</v>
+        <v>46186.27264109749</v>
       </c>
       <c r="Z36" s="8" t="inlineStr"/>
     </row>
@@ -2691,7 +2699,7 @@
       <c r="W37" s="8" t="inlineStr"/>
       <c r="X37" s="8" t="inlineStr"/>
       <c r="Y37" s="9" t="n">
-        <v>46186.23724711822</v>
+        <v>46186.2726410977</v>
       </c>
       <c r="Z37" s="8" t="inlineStr"/>
     </row>
@@ -2739,7 +2747,7 @@
       <c r="W38" s="4" t="inlineStr"/>
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="5" t="n">
-        <v>46186.23724711841</v>
+        <v>46186.27264109794</v>
       </c>
       <c r="Z38" s="4" t="inlineStr"/>
     </row>
@@ -2803,7 +2811,7 @@
       <c r="W39" s="8" t="inlineStr"/>
       <c r="X39" s="8" t="inlineStr"/>
       <c r="Y39" s="9" t="n">
-        <v>46186.23724711863</v>
+        <v>46186.27264109817</v>
       </c>
       <c r="Z39" s="8" t="inlineStr"/>
     </row>
@@ -2867,7 +2875,7 @@
       <c r="W40" s="8" t="inlineStr"/>
       <c r="X40" s="8" t="inlineStr"/>
       <c r="Y40" s="9" t="n">
-        <v>46186.23724711886</v>
+        <v>46186.2726410984</v>
       </c>
       <c r="Z40" s="8" t="inlineStr"/>
     </row>
@@ -2931,7 +2939,7 @@
       <c r="W41" s="8" t="inlineStr"/>
       <c r="X41" s="8" t="inlineStr"/>
       <c r="Y41" s="9" t="n">
-        <v>46186.23724711908</v>
+        <v>46186.27264109862</v>
       </c>
       <c r="Z41" s="8" t="inlineStr"/>
     </row>
@@ -2999,7 +3007,7 @@
       <c r="W42" s="8" t="inlineStr"/>
       <c r="X42" s="8" t="inlineStr"/>
       <c r="Y42" s="9" t="n">
-        <v>46186.23724711929</v>
+        <v>46186.27264109884</v>
       </c>
       <c r="Z42" s="8" t="inlineStr"/>
     </row>
@@ -3063,7 +3071,7 @@
       <c r="W43" s="8" t="inlineStr"/>
       <c r="X43" s="8" t="inlineStr"/>
       <c r="Y43" s="9" t="n">
-        <v>46186.23724711949</v>
+        <v>46186.27264109904</v>
       </c>
       <c r="Z43" s="8" t="inlineStr"/>
     </row>
@@ -3077,7 +3085,11 @@
       <c r="C44" s="9" t="n">
         <v>46185</v>
       </c>
-      <c r="D44" s="8" t="inlineStr"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE10.MEP.M2</t>
+        </is>
+      </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Station BB04 - Water Supply, Drainage and Waste : DE.ELS.GE10.MEP.M2.D2_Rev.C02</t>
@@ -3115,7 +3127,7 @@
       <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="8" t="inlineStr"/>
       <c r="Y44" s="9" t="n">
-        <v>46186.23724711968</v>
+        <v>46186.27264109925</v>
       </c>
       <c r="Z44" s="8" t="inlineStr"/>
     </row>
@@ -3179,7 +3191,7 @@
       <c r="W45" s="8" t="inlineStr"/>
       <c r="X45" s="8" t="inlineStr"/>
       <c r="Y45" s="9" t="n">
-        <v>46186.2372471199</v>
+        <v>46186.27264109946</v>
       </c>
       <c r="Z45" s="8" t="inlineStr"/>
     </row>
@@ -3193,7 +3205,11 @@
       <c r="C46" s="9" t="n">
         <v>46185</v>
       </c>
-      <c r="D46" s="8" t="inlineStr"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE01.MEP.M4</t>
+        </is>
+      </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Elevated Station-MEP-BG32-VAC : DE.ELS.GE01.MEP.M4.D2_Rev.C02 (RCS Resubmission)</t>
@@ -3231,7 +3247,7 @@
       <c r="W46" s="8" t="inlineStr"/>
       <c r="X46" s="8" t="inlineStr"/>
       <c r="Y46" s="9" t="n">
-        <v>46186.23724712009</v>
+        <v>46186.27264109969</v>
       </c>
       <c r="Z46" s="8" t="inlineStr"/>
     </row>
@@ -3245,7 +3261,11 @@
       <c r="C47" s="9" t="n">
         <v>46185</v>
       </c>
-      <c r="D47" s="8" t="inlineStr"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE01.MEP.M3</t>
+        </is>
+      </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Elevated Station-MEP-BG32-FPS - MEP Fire Protection System FPS: DE.ELS.GE01.MEP.M3.D2_Rev.C01 (RCS Resubmission)</t>
@@ -3283,7 +3303,7 @@
       <c r="W47" s="8" t="inlineStr"/>
       <c r="X47" s="8" t="inlineStr"/>
       <c r="Y47" s="9" t="n">
-        <v>46186.23724712027</v>
+        <v>46186.27264110021</v>
       </c>
       <c r="Z47" s="8" t="inlineStr"/>
     </row>
@@ -3351,7 +3371,7 @@
       <c r="W48" s="8" t="inlineStr"/>
       <c r="X48" s="8" t="inlineStr"/>
       <c r="Y48" s="9" t="n">
-        <v>46186.23724712049</v>
+        <v>46186.27264110056</v>
       </c>
       <c r="Z48" s="8" t="inlineStr"/>
     </row>
@@ -3365,7 +3385,11 @@
       <c r="C49" s="9" t="n">
         <v>46185</v>
       </c>
-      <c r="D49" s="8" t="inlineStr"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>DE.ANX.AX01.STR.S0</t>
+        </is>
+      </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Annex Structure - BL-EES09 : DE.ANX.AX01.STR.S0.D2_Rev.C01</t>
@@ -3403,7 +3427,7 @@
       <c r="W49" s="8" t="inlineStr"/>
       <c r="X49" s="8" t="inlineStr"/>
       <c r="Y49" s="9" t="n">
-        <v>46186.23724712066</v>
+        <v>46186.27264110082</v>
       </c>
       <c r="Z49" s="8" t="inlineStr"/>
     </row>
@@ -3471,7 +3495,7 @@
       <c r="W50" s="8" t="inlineStr"/>
       <c r="X50" s="8" t="inlineStr"/>
       <c r="Y50" s="9" t="n">
-        <v>46186.23724712118</v>
+        <v>46186.27264110146</v>
       </c>
       <c r="Z50" s="8" t="inlineStr"/>
     </row>
@@ -3539,7 +3563,7 @@
       <c r="W51" s="8" t="inlineStr"/>
       <c r="X51" s="8" t="inlineStr"/>
       <c r="Y51" s="9" t="n">
-        <v>46186.23724712182</v>
+        <v>46186.27264110182</v>
       </c>
       <c r="Z51" s="8" t="inlineStr"/>
     </row>
@@ -3553,7 +3577,11 @@
       <c r="C52" s="9" t="n">
         <v>46185</v>
       </c>
-      <c r="D52" s="8" t="inlineStr"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>DE.UGS.RE02.STR.S3</t>
+        </is>
+      </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BR08 - Structure Concourse Slab Level Submission : DE.UGS.RE02.STR.S3.D3_Rev.C03</t>
@@ -3591,7 +3619,7 @@
       <c r="W52" s="8" t="inlineStr"/>
       <c r="X52" s="8" t="inlineStr"/>
       <c r="Y52" s="9" t="n">
-        <v>46186.23724712213</v>
+        <v>46186.27264110227</v>
       </c>
       <c r="Z52" s="8" t="inlineStr"/>
     </row>
@@ -3605,7 +3633,11 @@
       <c r="C53" s="5" t="n">
         <v>46185</v>
       </c>
-      <c r="D53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>DE.ANX.AX01.STR.S0</t>
+        </is>
+      </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
           <t>NOC Drawing Submission - Annex-BL-EES-09 - Structure &amp; Viaduct Tunnel : DE.ANX.AX01.STR.S0.NC_Rev.C03</t>
@@ -3639,7 +3671,7 @@
       <c r="W53" s="4" t="inlineStr"/>
       <c r="X53" s="4" t="inlineStr"/>
       <c r="Y53" s="5" t="n">
-        <v>46186.23724712237</v>
+        <v>46186.27264110262</v>
       </c>
       <c r="Z53" s="4" t="inlineStr"/>
     </row>
@@ -3703,7 +3735,7 @@
       <c r="W54" s="8" t="inlineStr"/>
       <c r="X54" s="8" t="inlineStr"/>
       <c r="Y54" s="9" t="n">
-        <v>46186.23724712262</v>
+        <v>46186.27264110287</v>
       </c>
       <c r="Z54" s="8" t="inlineStr"/>
     </row>
@@ -3767,7 +3799,7 @@
       <c r="W55" s="4" t="inlineStr"/>
       <c r="X55" s="4" t="inlineStr"/>
       <c r="Y55" s="5" t="n">
-        <v>46186.23724712284</v>
+        <v>46186.27264110308</v>
       </c>
       <c r="Z55" s="4" t="inlineStr"/>
     </row>
@@ -3781,7 +3813,11 @@
       <c r="C56" s="5" t="n">
         <v>46185</v>
       </c>
-      <c r="D56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>DE.ZNE.ZN03.UTI.U2</t>
+        </is>
+      </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP2 - Z0042 Utility Package : DE.ZNE.ZN03.UTI.U2.D2_Rev.C01</t>
@@ -3819,7 +3855,7 @@
       <c r="W56" s="4" t="inlineStr"/>
       <c r="X56" s="4" t="inlineStr"/>
       <c r="Y56" s="5" t="n">
-        <v>46186.23724712301</v>
+        <v>46186.27264110329</v>
       </c>
       <c r="Z56" s="4" t="inlineStr"/>
     </row>
@@ -3883,7 +3919,7 @@
       <c r="W57" s="8" t="inlineStr"/>
       <c r="X57" s="8" t="inlineStr"/>
       <c r="Y57" s="9" t="n">
-        <v>46186.23724712324</v>
+        <v>46186.2726411035</v>
       </c>
       <c r="Z57" s="8" t="inlineStr"/>
     </row>
@@ -3939,7 +3975,7 @@
       <c r="W58" s="4" t="inlineStr"/>
       <c r="X58" s="4" t="inlineStr"/>
       <c r="Y58" s="5" t="n">
-        <v>46186.23724712343</v>
+        <v>46186.27264110373</v>
       </c>
       <c r="Z58" s="4" t="inlineStr"/>
     </row>
@@ -3953,7 +3989,11 @@
       <c r="C59" s="5" t="n">
         <v>46185</v>
       </c>
-      <c r="D59" s="4" t="inlineStr"/>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>DE.UGS.GE09.MEP.M2</t>
+        </is>
+      </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Underground Station BB05 MEP Drainage and Waste &amp; Water Supply: DE.UGS.GE09.MEP.M2.D3_Rev.C01</t>
@@ -3991,7 +4031,7 @@
       <c r="W59" s="4" t="inlineStr"/>
       <c r="X59" s="4" t="inlineStr"/>
       <c r="Y59" s="5" t="n">
-        <v>46186.2372471236</v>
+        <v>46186.27264110399</v>
       </c>
       <c r="Z59" s="4" t="inlineStr"/>
     </row>
@@ -4055,7 +4095,7 @@
       <c r="W60" s="4" t="inlineStr"/>
       <c r="X60" s="4" t="inlineStr"/>
       <c r="Y60" s="5" t="n">
-        <v>46186.23724712382</v>
+        <v>46186.27264110421</v>
       </c>
       <c r="Z60" s="4" t="inlineStr"/>
     </row>
@@ -4119,7 +4159,7 @@
       <c r="W61" s="8" t="inlineStr"/>
       <c r="X61" s="8" t="inlineStr"/>
       <c r="Y61" s="9" t="n">
-        <v>46186.23724712402</v>
+        <v>46186.27264110441</v>
       </c>
       <c r="Z61" s="8" t="inlineStr"/>
     </row>
@@ -4183,7 +4223,7 @@
       <c r="W62" s="4" t="inlineStr"/>
       <c r="X62" s="4" t="inlineStr"/>
       <c r="Y62" s="5" t="n">
-        <v>46186.23724712426</v>
+        <v>46186.27264110465</v>
       </c>
       <c r="Z62" s="4" t="inlineStr"/>
     </row>
@@ -4247,7 +4287,7 @@
       <c r="W63" s="4" t="inlineStr"/>
       <c r="X63" s="4" t="inlineStr"/>
       <c r="Y63" s="5" t="n">
-        <v>46186.23724712447</v>
+        <v>46186.27264110485</v>
       </c>
       <c r="Z63" s="4" t="inlineStr"/>
     </row>
@@ -4261,7 +4301,11 @@
       <c r="C64" s="5" t="n">
         <v>46185</v>
       </c>
-      <c r="D64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>DE.UGS.RE01.STR.S5</t>
+        </is>
+      </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BR09 - Structure Base Slab : DE.UGS.RE01.STR.S5.D3_Rev.C01 (IDV Certificate Submission)</t>
@@ -4299,7 +4343,7 @@
       <c r="W64" s="4" t="inlineStr"/>
       <c r="X64" s="4" t="inlineStr"/>
       <c r="Y64" s="5" t="n">
-        <v>46186.23724712466</v>
+        <v>46186.27264110507</v>
       </c>
       <c r="Z64" s="4" t="inlineStr"/>
     </row>
@@ -4363,7 +4407,7 @@
       <c r="W65" s="4" t="inlineStr"/>
       <c r="X65" s="4" t="inlineStr"/>
       <c r="Y65" s="5" t="n">
-        <v>46186.23724712486</v>
+        <v>46186.27264110526</v>
       </c>
       <c r="Z65" s="4" t="inlineStr"/>
     </row>
@@ -4427,7 +4471,7 @@
       <c r="W66" s="4" t="inlineStr"/>
       <c r="X66" s="4" t="inlineStr"/>
       <c r="Y66" s="5" t="n">
-        <v>46186.23724712506</v>
+        <v>46186.27264110546</v>
       </c>
       <c r="Z66" s="4" t="inlineStr"/>
     </row>
@@ -4479,7 +4523,7 @@
       <c r="W67" s="4" t="inlineStr"/>
       <c r="X67" s="4" t="inlineStr"/>
       <c r="Y67" s="5" t="n">
-        <v>46186.23724712523</v>
+        <v>46186.27264110566</v>
       </c>
       <c r="Z67" s="4" t="inlineStr"/>
     </row>
@@ -4543,7 +4587,7 @@
       <c r="W68" s="4" t="inlineStr"/>
       <c r="X68" s="4" t="inlineStr"/>
       <c r="Y68" s="5" t="n">
-        <v>46186.23724712544</v>
+        <v>46186.27264110587</v>
       </c>
       <c r="Z68" s="4" t="inlineStr"/>
     </row>
@@ -4595,7 +4639,7 @@
       <c r="W69" s="4" t="inlineStr"/>
       <c r="X69" s="4" t="inlineStr"/>
       <c r="Y69" s="5" t="n">
-        <v>46186.23724712562</v>
+        <v>46186.27264110606</v>
       </c>
       <c r="Z69" s="4" t="inlineStr"/>
     </row>
@@ -4659,7 +4703,7 @@
       <c r="W70" s="4" t="inlineStr"/>
       <c r="X70" s="4" t="inlineStr"/>
       <c r="Y70" s="5" t="n">
-        <v>46186.23724712581</v>
+        <v>46186.27264110673</v>
       </c>
       <c r="Z70" s="4" t="inlineStr"/>
     </row>
@@ -4723,7 +4767,7 @@
       <c r="W71" s="4" t="inlineStr"/>
       <c r="X71" s="4" t="inlineStr"/>
       <c r="Y71" s="5" t="n">
-        <v>46186.237247126</v>
+        <v>46186.27264110708</v>
       </c>
       <c r="Z71" s="4" t="inlineStr"/>
     </row>
@@ -4791,7 +4835,7 @@
       <c r="W72" s="4" t="inlineStr"/>
       <c r="X72" s="4" t="inlineStr"/>
       <c r="Y72" s="5" t="n">
-        <v>46186.23724712621</v>
+        <v>46186.27264110732</v>
       </c>
       <c r="Z72" s="4" t="inlineStr"/>
     </row>
@@ -4855,7 +4899,7 @@
       <c r="W73" s="4" t="inlineStr"/>
       <c r="X73" s="4" t="inlineStr"/>
       <c r="Y73" s="5" t="n">
-        <v>46186.2372471264</v>
+        <v>46186.27264110753</v>
       </c>
       <c r="Z73" s="4" t="inlineStr"/>
     </row>
@@ -4919,7 +4963,7 @@
       <c r="W74" s="4" t="inlineStr"/>
       <c r="X74" s="4" t="inlineStr"/>
       <c r="Y74" s="5" t="n">
-        <v>46186.23724712658</v>
+        <v>46186.27264110773</v>
       </c>
       <c r="Z74" s="4" t="inlineStr"/>
     </row>
@@ -4983,7 +5027,7 @@
       <c r="W75" s="4" t="inlineStr"/>
       <c r="X75" s="4" t="inlineStr"/>
       <c r="Y75" s="5" t="n">
-        <v>46186.23724712676</v>
+        <v>46186.27264110792</v>
       </c>
       <c r="Z75" s="4" t="inlineStr"/>
     </row>
@@ -5051,7 +5095,7 @@
       <c r="W76" s="4" t="inlineStr"/>
       <c r="X76" s="4" t="inlineStr"/>
       <c r="Y76" s="5" t="n">
-        <v>46186.23724712701</v>
+        <v>46186.27264110938</v>
       </c>
       <c r="Z76" s="4" t="inlineStr"/>
     </row>
@@ -5119,7 +5163,7 @@
       <c r="W77" s="8" t="inlineStr"/>
       <c r="X77" s="8" t="inlineStr"/>
       <c r="Y77" s="9" t="n">
-        <v>46186.23724712727</v>
+        <v>46186.2726411098</v>
       </c>
       <c r="Z77" s="8" t="inlineStr"/>
     </row>
@@ -5183,7 +5227,7 @@
       <c r="W78" s="8" t="inlineStr"/>
       <c r="X78" s="8" t="inlineStr"/>
       <c r="Y78" s="9" t="n">
-        <v>46186.23724712749</v>
+        <v>46186.27264111004</v>
       </c>
       <c r="Z78" s="8" t="inlineStr"/>
     </row>
@@ -5197,7 +5241,11 @@
       <c r="C79" s="9" t="n">
         <v>46185</v>
       </c>
-      <c r="D79" s="8" t="inlineStr"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>DE.TPS.TPS1.MEP.M0</t>
+        </is>
+      </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Al Ruwayyah Depot BDR19 - TPS - MEP : DE.TPS.TPS1.MEP.M0.D2_Rev.C01</t>
@@ -5235,7 +5283,7 @@
       <c r="W79" s="8" t="inlineStr"/>
       <c r="X79" s="8" t="inlineStr"/>
       <c r="Y79" s="9" t="n">
-        <v>46186.23724712765</v>
+        <v>46186.27264111028</v>
       </c>
       <c r="Z79" s="8" t="inlineStr"/>
     </row>
@@ -5303,7 +5351,7 @@
       <c r="W80" s="8" t="inlineStr"/>
       <c r="X80" s="8" t="inlineStr"/>
       <c r="Y80" s="9" t="n">
-        <v>46186.23724712831</v>
+        <v>46186.27264111049</v>
       </c>
       <c r="Z80" s="8" t="inlineStr"/>
     </row>
@@ -5371,7 +5419,7 @@
       <c r="W81" s="8" t="inlineStr"/>
       <c r="X81" s="8" t="inlineStr"/>
       <c r="Y81" s="9" t="n">
-        <v>46186.23724712856</v>
+        <v>46186.27264111069</v>
       </c>
       <c r="Z81" s="8" t="inlineStr"/>
     </row>
@@ -5439,7 +5487,7 @@
       <c r="W82" s="8" t="inlineStr"/>
       <c r="X82" s="8" t="inlineStr"/>
       <c r="Y82" s="9" t="n">
-        <v>46186.23724712878</v>
+        <v>46186.27264111087</v>
       </c>
       <c r="Z82" s="8" t="inlineStr"/>
     </row>
@@ -5503,7 +5551,7 @@
       <c r="W83" s="4" t="inlineStr"/>
       <c r="X83" s="4" t="inlineStr"/>
       <c r="Y83" s="5" t="n">
-        <v>46186.23724712898</v>
+        <v>46186.27264111106</v>
       </c>
       <c r="Z83" s="4" t="inlineStr"/>
     </row>
@@ -5517,7 +5565,11 @@
       <c r="C84" s="9" t="n">
         <v>46185</v>
       </c>
-      <c r="D84" s="8" t="inlineStr"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE06.ARC.A2</t>
+        </is>
+      </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
           <t>Re: NOC Drawing Submission - Station BG36 Entrance POD : DE.ELS.GE06.ARC.A2.NC_Rev.C01</t>
@@ -5551,7 +5603,7 @@
       <c r="W84" s="8" t="inlineStr"/>
       <c r="X84" s="8" t="inlineStr"/>
       <c r="Y84" s="9" t="n">
-        <v>46186.23724712915</v>
+        <v>46186.27264111125</v>
       </c>
       <c r="Z84" s="8" t="inlineStr"/>
     </row>
@@ -5565,7 +5617,11 @@
       <c r="C85" s="5" t="n">
         <v>46185</v>
       </c>
-      <c r="D85" s="4" t="inlineStr"/>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>DE.TNL.GN00.STR.T1</t>
+        </is>
+      </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Bored Tunnel Special Segment Global Package : DE.TNL.GN00.STR.T1.D3_Rev.C01</t>
@@ -5603,7 +5659,7 @@
       <c r="W85" s="4" t="inlineStr"/>
       <c r="X85" s="4" t="inlineStr"/>
       <c r="Y85" s="5" t="n">
-        <v>46186.23724712933</v>
+        <v>46186.27264111146</v>
       </c>
       <c r="Z85" s="4" t="inlineStr"/>
     </row>
@@ -5667,7 +5723,7 @@
       <c r="W86" s="8" t="inlineStr"/>
       <c r="X86" s="8" t="inlineStr"/>
       <c r="Y86" s="9" t="n">
-        <v>46186.23724712955</v>
+        <v>46186.27264111169</v>
       </c>
       <c r="Z86" s="8" t="inlineStr"/>
     </row>
@@ -5731,7 +5787,7 @@
       <c r="W87" s="8" t="inlineStr"/>
       <c r="X87" s="8" t="inlineStr"/>
       <c r="Y87" s="9" t="n">
-        <v>46186.23724712977</v>
+        <v>46186.2726411119</v>
       </c>
       <c r="Z87" s="8" t="inlineStr"/>
     </row>
@@ -5799,7 +5855,7 @@
       <c r="W88" s="8" t="inlineStr"/>
       <c r="X88" s="8" t="inlineStr"/>
       <c r="Y88" s="9" t="n">
-        <v>46186.23724712998</v>
+        <v>46186.2726411121</v>
       </c>
       <c r="Z88" s="8" t="inlineStr"/>
     </row>
@@ -5863,7 +5919,7 @@
       <c r="W89" s="4" t="inlineStr"/>
       <c r="X89" s="4" t="inlineStr"/>
       <c r="Y89" s="5" t="n">
-        <v>46186.23724713015</v>
+        <v>46186.27264111228</v>
       </c>
       <c r="Z89" s="4" t="inlineStr"/>
     </row>
@@ -5931,7 +5987,7 @@
       <c r="W90" s="8" t="inlineStr"/>
       <c r="X90" s="8" t="inlineStr"/>
       <c r="Y90" s="9" t="n">
-        <v>46186.23724713035</v>
+        <v>46186.27264111298</v>
       </c>
       <c r="Z90" s="8" t="inlineStr"/>
     </row>
@@ -5945,7 +6001,11 @@
       <c r="C91" s="9" t="n">
         <v>46185</v>
       </c>
-      <c r="D91" s="8" t="inlineStr"/>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE03.STR.S1</t>
+        </is>
+      </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BG34 - Structure – (Concourse above pier and Transverse Beam) : DE.ELS.GE03.STR.S1.D3_Rev.C03 (RCS Resubmission)</t>
@@ -5987,7 +6047,7 @@
       <c r="W91" s="8" t="inlineStr"/>
       <c r="X91" s="8" t="inlineStr"/>
       <c r="Y91" s="9" t="n">
-        <v>46186.23724713058</v>
+        <v>46186.27264111337</v>
       </c>
       <c r="Z91" s="8" t="inlineStr"/>
     </row>
@@ -6055,7 +6115,7 @@
       <c r="W92" s="8" t="inlineStr"/>
       <c r="X92" s="8" t="inlineStr"/>
       <c r="Y92" s="9" t="n">
-        <v>46186.23724713131</v>
+        <v>46186.27264111369</v>
       </c>
       <c r="Z92" s="8" t="inlineStr"/>
     </row>
@@ -6119,7 +6179,7 @@
       <c r="W93" s="8" t="inlineStr"/>
       <c r="X93" s="8" t="inlineStr"/>
       <c r="Y93" s="9" t="n">
-        <v>46186.2372471316</v>
+        <v>46186.27264111392</v>
       </c>
       <c r="Z93" s="8" t="inlineStr"/>
     </row>
@@ -6183,7 +6243,7 @@
       <c r="W94" s="8" t="inlineStr"/>
       <c r="X94" s="8" t="inlineStr"/>
       <c r="Y94" s="9" t="n">
-        <v>46186.23724713184</v>
+        <v>46186.27264111416</v>
       </c>
       <c r="Z94" s="8" t="inlineStr"/>
     </row>
@@ -6197,7 +6257,11 @@
       <c r="C95" s="9" t="n">
         <v>46185</v>
       </c>
-      <c r="D95" s="8" t="inlineStr"/>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>DE.UGS.GE09.ARC.A2</t>
+        </is>
+      </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Station BB05 Underground Station Architecture : DE.UGS.GE09.ARC.A2.D2_Rev.C03</t>
@@ -6235,7 +6299,7 @@
       <c r="W95" s="8" t="inlineStr"/>
       <c r="X95" s="8" t="inlineStr"/>
       <c r="Y95" s="9" t="n">
-        <v>46186.23724713203</v>
+        <v>46186.27264111437</v>
       </c>
       <c r="Z95" s="8" t="inlineStr"/>
     </row>
@@ -6249,7 +6313,11 @@
       <c r="C96" s="5" t="n">
         <v>46185</v>
       </c>
-      <c r="D96" s="4" t="inlineStr"/>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>DE.DPT.YPPC.STR.S0</t>
+        </is>
+      </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Depot BDR04 - Structure Yellow Plant Building: DE.DPT.YPPC.STR.S0.D3_Rev.C01</t>
@@ -6287,7 +6355,7 @@
       <c r="W96" s="4" t="inlineStr"/>
       <c r="X96" s="4" t="inlineStr"/>
       <c r="Y96" s="5" t="n">
-        <v>46186.23724713222</v>
+        <v>46186.27264111459</v>
       </c>
       <c r="Z96" s="4" t="inlineStr"/>
     </row>
@@ -6301,7 +6369,11 @@
       <c r="C97" s="5" t="n">
         <v>46185</v>
       </c>
-      <c r="D97" s="4" t="inlineStr"/>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>DE.DPT.OHBD.STR.S0</t>
+        </is>
+      </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Depot BDR03 Overhaul Workshop Building (APDP) - Structure: DE.DPT.OHBD.STR.S0.D3_Rev.C01</t>
@@ -6339,7 +6411,7 @@
       <c r="W97" s="4" t="inlineStr"/>
       <c r="X97" s="4" t="inlineStr"/>
       <c r="Y97" s="5" t="n">
-        <v>46186.23724713264</v>
+        <v>46186.27264111482</v>
       </c>
       <c r="Z97" s="4" t="inlineStr"/>
     </row>
@@ -6407,7 +6479,7 @@
       <c r="W98" s="4" t="inlineStr"/>
       <c r="X98" s="4" t="inlineStr"/>
       <c r="Y98" s="5" t="n">
-        <v>46186.23724713299</v>
+        <v>46186.27264111502</v>
       </c>
       <c r="Z98" s="4" t="inlineStr"/>
     </row>
@@ -6421,7 +6493,11 @@
       <c r="C99" s="5" t="n">
         <v>46185</v>
       </c>
-      <c r="D99" s="4" t="inlineStr"/>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>DE.UGS.RE01.STR.S6</t>
+        </is>
+      </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BR09 - Structure Top Slab Submission : DE.UGS.RE01.STR.S6.D3_Rev.C04 (IDV Certificate Submission)</t>
@@ -6463,7 +6539,7 @@
       <c r="W99" s="4" t="inlineStr"/>
       <c r="X99" s="4" t="inlineStr"/>
       <c r="Y99" s="5" t="n">
-        <v>46186.23724713322</v>
+        <v>46186.27264111523</v>
       </c>
       <c r="Z99" s="4" t="inlineStr"/>
     </row>
@@ -6477,7 +6553,11 @@
       <c r="C100" s="5" t="n">
         <v>46185</v>
       </c>
-      <c r="D100" s="4" t="inlineStr"/>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>DE.UGS.GE09.MEP.M4</t>
+        </is>
+      </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Station BB05 MEP TVS : DE.UGS.GE09.MEP.M4.D3_Rev.C01</t>
@@ -6519,7 +6599,7 @@
       <c r="W100" s="4" t="inlineStr"/>
       <c r="X100" s="4" t="inlineStr"/>
       <c r="Y100" s="5" t="n">
-        <v>46186.23724713339</v>
+        <v>46186.27264111543</v>
       </c>
       <c r="Z100" s="4" t="inlineStr"/>
     </row>
@@ -6587,7 +6667,7 @@
       <c r="W101" s="4" t="inlineStr"/>
       <c r="X101" s="4" t="inlineStr"/>
       <c r="Y101" s="5" t="n">
-        <v>46186.23724713363</v>
+        <v>46186.27264111567</v>
       </c>
       <c r="Z101" s="4" t="inlineStr"/>
     </row>
@@ -6659,7 +6739,7 @@
       <c r="W102" s="4" t="inlineStr"/>
       <c r="X102" s="4" t="inlineStr"/>
       <c r="Y102" s="5" t="n">
-        <v>46186.23724713387</v>
+        <v>46186.27264111589</v>
       </c>
       <c r="Z102" s="4" t="inlineStr"/>
     </row>
@@ -6727,7 +6807,7 @@
       <c r="W103" s="4" t="inlineStr"/>
       <c r="X103" s="4" t="inlineStr"/>
       <c r="Y103" s="5" t="n">
-        <v>46186.23724713405</v>
+        <v>46186.27264111608</v>
       </c>
       <c r="Z103" s="4" t="inlineStr"/>
     </row>
@@ -6795,7 +6875,7 @@
       <c r="W104" s="4" t="inlineStr"/>
       <c r="X104" s="4" t="inlineStr"/>
       <c r="Y104" s="5" t="n">
-        <v>46186.23724713425</v>
+        <v>46186.27264111669</v>
       </c>
       <c r="Z104" s="4" t="inlineStr"/>
     </row>
@@ -6863,7 +6943,7 @@
       <c r="W105" s="4" t="inlineStr"/>
       <c r="X105" s="4" t="inlineStr"/>
       <c r="Y105" s="5" t="n">
-        <v>46186.23724713444</v>
+        <v>46186.27264111694</v>
       </c>
       <c r="Z105" s="4" t="inlineStr"/>
     </row>
@@ -6935,7 +7015,7 @@
       <c r="W106" s="4" t="inlineStr"/>
       <c r="X106" s="4" t="inlineStr"/>
       <c r="Y106" s="5" t="n">
-        <v>46186.23724713462</v>
+        <v>46186.27264111714</v>
       </c>
       <c r="Z106" s="4" t="inlineStr"/>
     </row>
@@ -7003,7 +7083,7 @@
       <c r="W107" s="4" t="inlineStr"/>
       <c r="X107" s="4" t="inlineStr"/>
       <c r="Y107" s="5" t="n">
-        <v>46186.23724713483</v>
+        <v>46186.27264111735</v>
       </c>
       <c r="Z107" s="4" t="inlineStr"/>
     </row>
@@ -7071,7 +7151,7 @@
       <c r="W108" s="4" t="inlineStr"/>
       <c r="X108" s="4" t="inlineStr"/>
       <c r="Y108" s="5" t="n">
-        <v>46186.23724713548</v>
+        <v>46186.27264111756</v>
       </c>
       <c r="Z108" s="4" t="inlineStr"/>
     </row>
@@ -7139,7 +7219,7 @@
       <c r="W109" s="4" t="inlineStr"/>
       <c r="X109" s="4" t="inlineStr"/>
       <c r="Y109" s="5" t="n">
-        <v>46186.23724713574</v>
+        <v>46186.27264111774</v>
       </c>
       <c r="Z109" s="4" t="inlineStr"/>
     </row>
@@ -7207,7 +7287,7 @@
       <c r="W110" s="4" t="inlineStr"/>
       <c r="X110" s="4" t="inlineStr"/>
       <c r="Y110" s="5" t="n">
-        <v>46186.23724713597</v>
+        <v>46186.27264111827</v>
       </c>
       <c r="Z110" s="4" t="inlineStr"/>
     </row>
@@ -7271,7 +7351,7 @@
       <c r="W111" s="4" t="inlineStr"/>
       <c r="X111" s="4" t="inlineStr"/>
       <c r="Y111" s="5" t="n">
-        <v>46186.23724713618</v>
+        <v>46186.27264111856</v>
       </c>
       <c r="Z111" s="4" t="inlineStr"/>
     </row>
@@ -7285,7 +7365,11 @@
       <c r="C112" s="5" t="n">
         <v>46184</v>
       </c>
-      <c r="D112" s="4" t="inlineStr"/>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST06.STR.V1</t>
+        </is>
+      </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
           <t>Re: Shop Drawing Submission - Stretch-06.2 - Viaduct Structure Foundation - Pilecap Shop Drawing BC-3SP-72-09_PM197 AND PM200 : DE.VDT.ST06.STR.V1.D5_Rev.C01 (RCS Resubmission)</t>
@@ -7323,7 +7407,7 @@
       <c r="W112" s="4" t="inlineStr"/>
       <c r="X112" s="4" t="inlineStr"/>
       <c r="Y112" s="5" t="n">
-        <v>46186.2372471364</v>
+        <v>46186.27264111884</v>
       </c>
       <c r="Z112" s="4" t="inlineStr"/>
     </row>
@@ -7391,7 +7475,7 @@
       <c r="W113" s="4" t="inlineStr"/>
       <c r="X113" s="4" t="inlineStr"/>
       <c r="Y113" s="5" t="n">
-        <v>46186.23724713665</v>
+        <v>46186.2726411191</v>
       </c>
       <c r="Z113" s="4" t="inlineStr"/>
     </row>
@@ -7459,7 +7543,7 @@
       <c r="W114" s="4" t="inlineStr"/>
       <c r="X114" s="4" t="inlineStr"/>
       <c r="Y114" s="5" t="n">
-        <v>46186.23724713687</v>
+        <v>46186.27264111931</v>
       </c>
       <c r="Z114" s="4" t="inlineStr"/>
     </row>
@@ -7507,7 +7591,7 @@
       <c r="W115" s="4" t="inlineStr"/>
       <c r="X115" s="4" t="inlineStr"/>
       <c r="Y115" s="5" t="n">
-        <v>46186.23724713706</v>
+        <v>46186.27264111954</v>
       </c>
       <c r="Z115" s="4" t="inlineStr"/>
     </row>
@@ -7555,7 +7639,7 @@
       <c r="W116" s="4" t="inlineStr"/>
       <c r="X116" s="4" t="inlineStr"/>
       <c r="Y116" s="5" t="n">
-        <v>46186.23724713724</v>
+        <v>46186.27264111974</v>
       </c>
       <c r="Z116" s="4" t="inlineStr"/>
     </row>
@@ -7623,7 +7707,7 @@
       <c r="W117" s="4" t="inlineStr"/>
       <c r="X117" s="4" t="inlineStr"/>
       <c r="Y117" s="5" t="n">
-        <v>46186.23724713743</v>
+        <v>46186.27264111995</v>
       </c>
       <c r="Z117" s="4" t="inlineStr"/>
     </row>
@@ -7687,7 +7771,7 @@
       <c r="W118" s="8" t="inlineStr"/>
       <c r="X118" s="8" t="inlineStr"/>
       <c r="Y118" s="9" t="n">
-        <v>46186.23724713764</v>
+        <v>46186.27264112017</v>
       </c>
       <c r="Z118" s="8" t="inlineStr"/>
     </row>
@@ -7755,7 +7839,7 @@
       <c r="W119" s="4" t="inlineStr"/>
       <c r="X119" s="4" t="inlineStr"/>
       <c r="Y119" s="5" t="n">
-        <v>46186.23724713783</v>
+        <v>46186.27264112037</v>
       </c>
       <c r="Z119" s="4" t="inlineStr"/>
     </row>
@@ -7823,7 +7907,7 @@
       <c r="W120" s="8" t="inlineStr"/>
       <c r="X120" s="8" t="inlineStr"/>
       <c r="Y120" s="9" t="n">
-        <v>46186.23724713814</v>
+        <v>46186.27264112066</v>
       </c>
       <c r="Z120" s="8" t="inlineStr"/>
     </row>
@@ -7887,7 +7971,7 @@
       <c r="W121" s="8" t="inlineStr"/>
       <c r="X121" s="8" t="inlineStr"/>
       <c r="Y121" s="9" t="n">
-        <v>46186.23724713842</v>
+        <v>46186.27264112096</v>
       </c>
       <c r="Z121" s="8" t="inlineStr"/>
     </row>
@@ -7955,7 +8039,7 @@
       <c r="W122" s="8" t="inlineStr"/>
       <c r="X122" s="8" t="inlineStr"/>
       <c r="Y122" s="9" t="n">
-        <v>46186.23724713868</v>
+        <v>46186.27264112127</v>
       </c>
       <c r="Z122" s="8" t="inlineStr"/>
     </row>
@@ -8023,7 +8107,7 @@
       <c r="W123" s="4" t="inlineStr"/>
       <c r="X123" s="4" t="inlineStr"/>
       <c r="Y123" s="5" t="n">
-        <v>46186.23724713895</v>
+        <v>46186.27264112152</v>
       </c>
       <c r="Z123" s="4" t="inlineStr"/>
     </row>
@@ -8091,7 +8175,7 @@
       <c r="W124" s="4" t="inlineStr"/>
       <c r="X124" s="4" t="inlineStr"/>
       <c r="Y124" s="5" t="n">
-        <v>46186.23724713916</v>
+        <v>46186.27264112172</v>
       </c>
       <c r="Z124" s="4" t="inlineStr"/>
     </row>
@@ -8159,7 +8243,7 @@
       <c r="W125" s="4" t="inlineStr"/>
       <c r="X125" s="4" t="inlineStr"/>
       <c r="Y125" s="5" t="n">
-        <v>46186.23724713936</v>
+        <v>46186.27264112194</v>
       </c>
       <c r="Z125" s="4" t="inlineStr"/>
     </row>
@@ -8227,7 +8311,7 @@
       <c r="W126" s="4" t="inlineStr"/>
       <c r="X126" s="4" t="inlineStr"/>
       <c r="Y126" s="5" t="n">
-        <v>46186.23724714002</v>
+        <v>46186.27264112215</v>
       </c>
       <c r="Z126" s="4" t="inlineStr"/>
     </row>
@@ -8295,7 +8379,7 @@
       <c r="W127" s="4" t="inlineStr"/>
       <c r="X127" s="4" t="inlineStr"/>
       <c r="Y127" s="5" t="n">
-        <v>46186.23724714034</v>
+        <v>46186.27264112235</v>
       </c>
       <c r="Z127" s="4" t="inlineStr"/>
     </row>
@@ -8363,7 +8447,7 @@
       <c r="W128" s="4" t="inlineStr"/>
       <c r="X128" s="4" t="inlineStr"/>
       <c r="Y128" s="5" t="n">
-        <v>46186.23724714055</v>
+        <v>46186.27264112252</v>
       </c>
       <c r="Z128" s="4" t="inlineStr"/>
     </row>
@@ -8431,7 +8515,7 @@
       <c r="W129" s="4" t="inlineStr"/>
       <c r="X129" s="4" t="inlineStr"/>
       <c r="Y129" s="5" t="n">
-        <v>46186.23724714075</v>
+        <v>46186.27264112272</v>
       </c>
       <c r="Z129" s="4" t="inlineStr"/>
     </row>
@@ -8499,7 +8583,7 @@
       <c r="W130" s="4" t="inlineStr"/>
       <c r="X130" s="4" t="inlineStr"/>
       <c r="Y130" s="5" t="n">
-        <v>46186.23724714097</v>
+        <v>46186.27264112291</v>
       </c>
       <c r="Z130" s="4" t="inlineStr"/>
     </row>
@@ -8567,7 +8651,7 @@
       <c r="W131" s="4" t="inlineStr"/>
       <c r="X131" s="4" t="inlineStr"/>
       <c r="Y131" s="5" t="n">
-        <v>46186.23724714119</v>
+        <v>46186.27264112311</v>
       </c>
       <c r="Z131" s="4" t="inlineStr"/>
     </row>
@@ -8581,7 +8665,11 @@
       <c r="C132" s="5" t="n">
         <v>46184</v>
       </c>
-      <c r="D132" s="4" t="inlineStr"/>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>DE.ANX.AX17.STR.S0</t>
+        </is>
+      </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Annex Structure - BL-EES08 Structure : DE.ANX.AX17.STR.S0.D2_Rev.C01</t>
@@ -8623,7 +8711,7 @@
       <c r="W132" s="4" t="inlineStr"/>
       <c r="X132" s="4" t="inlineStr"/>
       <c r="Y132" s="5" t="n">
-        <v>46186.23724714137</v>
+        <v>46186.2726411237</v>
       </c>
       <c r="Z132" s="4" t="inlineStr"/>
     </row>
@@ -8691,7 +8779,7 @@
       <c r="W133" s="4" t="inlineStr"/>
       <c r="X133" s="4" t="inlineStr"/>
       <c r="Y133" s="5" t="n">
-        <v>46186.23724714155</v>
+        <v>46186.27264112404</v>
       </c>
       <c r="Z133" s="4" t="inlineStr"/>
     </row>
@@ -8759,7 +8847,7 @@
       <c r="W134" s="4" t="inlineStr"/>
       <c r="X134" s="4" t="inlineStr"/>
       <c r="Y134" s="5" t="n">
-        <v>46186.23724714176</v>
+        <v>46186.27264112428</v>
       </c>
       <c r="Z134" s="4" t="inlineStr"/>
     </row>
@@ -8827,7 +8915,7 @@
       <c r="W135" s="4" t="inlineStr"/>
       <c r="X135" s="4" t="inlineStr"/>
       <c r="Y135" s="5" t="n">
-        <v>46186.23724714198</v>
+        <v>46186.27264112454</v>
       </c>
       <c r="Z135" s="4" t="inlineStr"/>
     </row>
@@ -8841,7 +8929,11 @@
       <c r="C136" s="5" t="n">
         <v>46184</v>
       </c>
-      <c r="D136" s="4" t="inlineStr"/>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>DE.DPT.TBG1.STR.S0</t>
+        </is>
+      </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Depot BDR14 -Structure TPS : DE.DPT.TBG1.STR.S0.D3_Rev.C01</t>
@@ -8883,7 +8975,7 @@
       <c r="W136" s="4" t="inlineStr"/>
       <c r="X136" s="4" t="inlineStr"/>
       <c r="Y136" s="5" t="n">
-        <v>46186.23724714248</v>
+        <v>46186.27264112476</v>
       </c>
       <c r="Z136" s="4" t="inlineStr"/>
     </row>
@@ -8897,7 +8989,11 @@
       <c r="C137" s="5" t="n">
         <v>46184</v>
       </c>
-      <c r="D137" s="4" t="inlineStr"/>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE00.GEO.G1</t>
+        </is>
+      </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Technical Note-Working Pile Load test at BG31 (SOP-23) : DE.ELS.GE00.GEO.G1.D3_Rev.C01</t>
@@ -8939,7 +9035,7 @@
       <c r="W137" s="4" t="inlineStr"/>
       <c r="X137" s="4" t="inlineStr"/>
       <c r="Y137" s="5" t="n">
-        <v>46186.23724714279</v>
+        <v>46186.27264112498</v>
       </c>
       <c r="Z137" s="4" t="inlineStr"/>
     </row>
@@ -9007,7 +9103,7 @@
       <c r="W138" s="4" t="inlineStr"/>
       <c r="X138" s="4" t="inlineStr"/>
       <c r="Y138" s="5" t="n">
-        <v>46186.23724714306</v>
+        <v>46186.27264112527</v>
       </c>
       <c r="Z138" s="4" t="inlineStr"/>
     </row>
@@ -9075,7 +9171,7 @@
       <c r="W139" s="4" t="inlineStr"/>
       <c r="X139" s="4" t="inlineStr"/>
       <c r="Y139" s="5" t="n">
-        <v>46186.2372471433</v>
+        <v>46186.27264112548</v>
       </c>
       <c r="Z139" s="4" t="inlineStr"/>
     </row>
@@ -9143,7 +9239,7 @@
       <c r="W140" s="4" t="inlineStr"/>
       <c r="X140" s="4" t="inlineStr"/>
       <c r="Y140" s="5" t="n">
-        <v>46186.23724714353</v>
+        <v>46186.2726411257</v>
       </c>
       <c r="Z140" s="4" t="inlineStr"/>
     </row>
@@ -9211,7 +9307,7 @@
       <c r="W141" s="4" t="inlineStr"/>
       <c r="X141" s="4" t="inlineStr"/>
       <c r="Y141" s="5" t="n">
-        <v>46186.23724714375</v>
+        <v>46186.27264112591</v>
       </c>
       <c r="Z141" s="4" t="inlineStr"/>
     </row>
@@ -9279,7 +9375,7 @@
       <c r="W142" s="4" t="inlineStr"/>
       <c r="X142" s="4" t="inlineStr"/>
       <c r="Y142" s="5" t="n">
-        <v>46186.23724714421</v>
+        <v>46186.27264112647</v>
       </c>
       <c r="Z142" s="4" t="inlineStr"/>
     </row>
@@ -9347,7 +9443,7 @@
       <c r="W143" s="4" t="inlineStr"/>
       <c r="X143" s="4" t="inlineStr"/>
       <c r="Y143" s="5" t="n">
-        <v>46186.23724714459</v>
+        <v>46186.27264112682</v>
       </c>
       <c r="Z143" s="4" t="inlineStr"/>
     </row>
@@ -9415,7 +9511,7 @@
       <c r="W144" s="4" t="inlineStr"/>
       <c r="X144" s="4" t="inlineStr"/>
       <c r="Y144" s="5" t="n">
-        <v>46186.2372471452</v>
+        <v>46186.27264112705</v>
       </c>
       <c r="Z144" s="4" t="inlineStr"/>
     </row>
@@ -9483,7 +9579,7 @@
       <c r="W145" s="4" t="inlineStr"/>
       <c r="X145" s="4" t="inlineStr"/>
       <c r="Y145" s="5" t="n">
-        <v>46186.23724714553</v>
+        <v>46186.27264112727</v>
       </c>
       <c r="Z145" s="4" t="inlineStr"/>
     </row>
@@ -9551,7 +9647,7 @@
       <c r="W146" s="4" t="inlineStr"/>
       <c r="X146" s="4" t="inlineStr"/>
       <c r="Y146" s="5" t="n">
-        <v>46186.23724714579</v>
+        <v>46186.27264112749</v>
       </c>
       <c r="Z146" s="4" t="inlineStr"/>
     </row>
@@ -9615,7 +9711,7 @@
       <c r="W147" s="8" t="inlineStr"/>
       <c r="X147" s="8" t="inlineStr"/>
       <c r="Y147" s="9" t="n">
-        <v>46186.237247146</v>
+        <v>46186.27264112767</v>
       </c>
       <c r="Z147" s="8" t="inlineStr"/>
     </row>
@@ -9679,7 +9775,7 @@
       <c r="W148" s="8" t="inlineStr"/>
       <c r="X148" s="8" t="inlineStr"/>
       <c r="Y148" s="9" t="n">
-        <v>46186.23724714623</v>
+        <v>46186.27264112789</v>
       </c>
       <c r="Z148" s="8" t="inlineStr"/>
     </row>
@@ -9743,7 +9839,7 @@
       <c r="W149" s="8" t="inlineStr"/>
       <c r="X149" s="8" t="inlineStr"/>
       <c r="Y149" s="9" t="n">
-        <v>46186.23724714643</v>
+        <v>46186.27264112805</v>
       </c>
       <c r="Z149" s="8" t="inlineStr"/>
     </row>
@@ -9807,7 +9903,7 @@
       <c r="W150" s="8" t="inlineStr"/>
       <c r="X150" s="8" t="inlineStr"/>
       <c r="Y150" s="9" t="n">
-        <v>46186.23724714663</v>
+        <v>46186.27264112823</v>
       </c>
       <c r="Z150" s="8" t="inlineStr"/>
     </row>
@@ -9875,7 +9971,7 @@
       <c r="W151" s="4" t="inlineStr"/>
       <c r="X151" s="4" t="inlineStr"/>
       <c r="Y151" s="5" t="n">
-        <v>46186.23724714682</v>
+        <v>46186.2726411284</v>
       </c>
       <c r="Z151" s="4" t="inlineStr"/>
     </row>
@@ -9939,7 +10035,7 @@
       <c r="W152" s="8" t="inlineStr"/>
       <c r="X152" s="8" t="inlineStr"/>
       <c r="Y152" s="9" t="n">
-        <v>46186.23724714704</v>
+        <v>46186.27264112859</v>
       </c>
       <c r="Z152" s="8" t="inlineStr"/>
     </row>
@@ -9987,7 +10083,7 @@
       <c r="W153" s="8" t="inlineStr"/>
       <c r="X153" s="8" t="inlineStr"/>
       <c r="Y153" s="9" t="n">
-        <v>46186.23724714727</v>
+        <v>46186.27264112885</v>
       </c>
       <c r="Z153" s="8" t="inlineStr"/>
     </row>
@@ -10055,7 +10151,7 @@
       <c r="W154" s="8" t="inlineStr"/>
       <c r="X154" s="8" t="inlineStr"/>
       <c r="Y154" s="9" t="n">
-        <v>46186.23724714749</v>
+        <v>46186.27264112907</v>
       </c>
       <c r="Z154" s="8" t="inlineStr"/>
     </row>
@@ -10123,7 +10219,7 @@
       <c r="W155" s="8" t="inlineStr"/>
       <c r="X155" s="8" t="inlineStr"/>
       <c r="Y155" s="9" t="n">
-        <v>46186.23724714774</v>
+        <v>46186.27264112932</v>
       </c>
       <c r="Z155" s="8" t="inlineStr"/>
     </row>
@@ -10137,7 +10233,11 @@
       <c r="C156" s="5" t="n">
         <v>46184</v>
       </c>
-      <c r="D156" s="4" t="inlineStr"/>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE11.MEP.M2</t>
+        </is>
+      </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Elevated Station BB03 MEP-DAW-WTS :  DE.ELS.GE11.MEP.M2.D3_Rev.C01</t>
@@ -10179,7 +10279,7 @@
       <c r="W156" s="4" t="inlineStr"/>
       <c r="X156" s="4" t="inlineStr"/>
       <c r="Y156" s="5" t="n">
-        <v>46186.23724714792</v>
+        <v>46186.27264112984</v>
       </c>
       <c r="Z156" s="4" t="inlineStr"/>
     </row>
@@ -10193,7 +10293,11 @@
       <c r="C157" s="5" t="n">
         <v>46184</v>
       </c>
-      <c r="D157" s="4" t="inlineStr"/>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE11.MEP.M1</t>
+        </is>
+      </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Elevated Station BB03 MEP-Electrical :  DE.ELS.GE11.MEP.M1.D3_Rev.C01</t>
@@ -10235,7 +10339,7 @@
       <c r="W157" s="4" t="inlineStr"/>
       <c r="X157" s="4" t="inlineStr"/>
       <c r="Y157" s="5" t="n">
-        <v>46186.2372471481</v>
+        <v>46186.27264113009</v>
       </c>
       <c r="Z157" s="4" t="inlineStr"/>
     </row>
@@ -10249,7 +10353,11 @@
       <c r="C158" s="5" t="n">
         <v>46184</v>
       </c>
-      <c r="D158" s="4" t="inlineStr"/>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE11.MEP.M3</t>
+        </is>
+      </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Elevated Station BB03 MEP-FPS : DE.ELS.GE11.MEP.M3.D3_Rev.C01</t>
@@ -10291,7 +10399,7 @@
       <c r="W158" s="4" t="inlineStr"/>
       <c r="X158" s="4" t="inlineStr"/>
       <c r="Y158" s="5" t="n">
-        <v>46186.23724714825</v>
+        <v>46186.2726411303</v>
       </c>
       <c r="Z158" s="4" t="inlineStr"/>
     </row>
@@ -10355,7 +10463,7 @@
       <c r="W159" s="8" t="inlineStr"/>
       <c r="X159" s="8" t="inlineStr"/>
       <c r="Y159" s="9" t="n">
-        <v>46186.23724714849</v>
+        <v>46186.27264113054</v>
       </c>
       <c r="Z159" s="8" t="inlineStr"/>
     </row>
@@ -10369,7 +10477,11 @@
       <c r="C160" s="9" t="n">
         <v>46184</v>
       </c>
-      <c r="D160" s="8" t="inlineStr"/>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST02.STR.V2</t>
+        </is>
+      </c>
       <c r="E160" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Stretch 02 - Viaduct Structure Bearing Schedule BC-3SP-72-02 : DE.VDT.ST02.STR.V2.D3_Rev.C01</t>
@@ -10407,7 +10519,7 @@
       <c r="W160" s="8" t="inlineStr"/>
       <c r="X160" s="8" t="inlineStr"/>
       <c r="Y160" s="9" t="n">
-        <v>46186.23724714868</v>
+        <v>46186.27264113077</v>
       </c>
       <c r="Z160" s="8" t="inlineStr"/>
     </row>
@@ -10421,7 +10533,11 @@
       <c r="C161" s="9" t="n">
         <v>46184</v>
       </c>
-      <c r="D161" s="8" t="inlineStr"/>
+      <c r="D161" s="8" t="inlineStr">
+        <is>
+          <t>DE.ZNE.ZN06.ARD.R0</t>
+        </is>
+      </c>
       <c r="E161" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Zone 06 Roads Z0046 Package : DE.ZNE.ZN06.ARD.R0.D2_Rev.C01 (RCS Resubmission)</t>
@@ -10459,7 +10575,7 @@
       <c r="W161" s="8" t="inlineStr"/>
       <c r="X161" s="8" t="inlineStr"/>
       <c r="Y161" s="9" t="n">
-        <v>46186.23724714886</v>
+        <v>46186.27264113138</v>
       </c>
       <c r="Z161" s="8" t="inlineStr"/>
     </row>
@@ -10473,7 +10589,11 @@
       <c r="C162" s="9" t="n">
         <v>46184</v>
       </c>
-      <c r="D162" s="8" t="inlineStr"/>
+      <c r="D162" s="8" t="inlineStr">
+        <is>
+          <t>DE.ZNE.ZN01.ARD.R0</t>
+        </is>
+      </c>
       <c r="E162" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Roads Z0039 Package: DE.ZNE.ZN01.ARD.R0.D2_Rev.C01 (RCS Resubmission)</t>
@@ -10511,7 +10631,7 @@
       <c r="W162" s="8" t="inlineStr"/>
       <c r="X162" s="8" t="inlineStr"/>
       <c r="Y162" s="9" t="n">
-        <v>46186.23724714902</v>
+        <v>46186.27264113163</v>
       </c>
       <c r="Z162" s="8" t="inlineStr"/>
     </row>
@@ -10525,7 +10645,11 @@
       <c r="C163" s="9" t="n">
         <v>46184</v>
       </c>
-      <c r="D163" s="8" t="inlineStr"/>
+      <c r="D163" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE11.STR.S7</t>
+        </is>
+      </c>
       <c r="E163" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BB03 - Structure Steel - Footbridge : DE.ELS.GE11.STR.S7.D3_Rev.C01</t>
@@ -10563,7 +10687,7 @@
       <c r="W163" s="8" t="inlineStr"/>
       <c r="X163" s="8" t="inlineStr"/>
       <c r="Y163" s="9" t="n">
-        <v>46186.23724714915</v>
+        <v>46186.27264113185</v>
       </c>
       <c r="Z163" s="8" t="inlineStr"/>
     </row>
@@ -10627,7 +10751,7 @@
       <c r="W164" s="8" t="inlineStr"/>
       <c r="X164" s="8" t="inlineStr"/>
       <c r="Y164" s="9" t="n">
-        <v>46186.23724714937</v>
+        <v>46186.27264113207</v>
       </c>
       <c r="Z164" s="8" t="inlineStr"/>
     </row>
@@ -10691,7 +10815,7 @@
       <c r="W165" s="8" t="inlineStr"/>
       <c r="X165" s="8" t="inlineStr"/>
       <c r="Y165" s="9" t="n">
-        <v>46186.23724715009</v>
+        <v>46186.27264113228</v>
       </c>
       <c r="Z165" s="8" t="inlineStr"/>
     </row>
@@ -10759,7 +10883,7 @@
       <c r="W166" s="8" t="inlineStr"/>
       <c r="X166" s="8" t="inlineStr"/>
       <c r="Y166" s="9" t="n">
-        <v>46186.23724715036</v>
+        <v>46186.27264113249</v>
       </c>
       <c r="Z166" s="8" t="inlineStr"/>
     </row>
@@ -10827,7 +10951,7 @@
       <c r="W167" s="8" t="inlineStr"/>
       <c r="X167" s="8" t="inlineStr"/>
       <c r="Y167" s="9" t="n">
-        <v>46186.23724715062</v>
+        <v>46186.27264113272</v>
       </c>
       <c r="Z167" s="8" t="inlineStr"/>
     </row>
@@ -10895,7 +11019,7 @@
       <c r="W168" s="8" t="inlineStr"/>
       <c r="X168" s="8" t="inlineStr"/>
       <c r="Y168" s="9" t="n">
-        <v>46186.23724715088</v>
+        <v>46186.27264113295</v>
       </c>
       <c r="Z168" s="8" t="inlineStr"/>
     </row>
@@ -10909,7 +11033,11 @@
       <c r="C169" s="9" t="n">
         <v>46184</v>
       </c>
-      <c r="D169" s="8" t="inlineStr"/>
+      <c r="D169" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE03.STR.S1</t>
+        </is>
+      </c>
       <c r="E169" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BG34 - (GLE03) Structural : DE.ELS.GE03.STR.S1.D3_Rev.C05 (Partial Submission)</t>
@@ -10947,7 +11075,7 @@
       <c r="W169" s="8" t="inlineStr"/>
       <c r="X169" s="8" t="inlineStr"/>
       <c r="Y169" s="9" t="n">
-        <v>46186.23724715108</v>
+        <v>46186.27264113316</v>
       </c>
       <c r="Z169" s="8" t="inlineStr"/>
     </row>
@@ -10961,7 +11089,11 @@
       <c r="C170" s="9" t="n">
         <v>46184</v>
       </c>
-      <c r="D170" s="8" t="inlineStr"/>
+      <c r="D170" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE03.STR.S3</t>
+        </is>
+      </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Stations BG34 (GLE03) - Structure : DE.ELS.GE03.STR.S3.D2_Rev.C01 (RCS Resubmission)</t>
@@ -10999,7 +11131,7 @@
       <c r="W170" s="8" t="inlineStr"/>
       <c r="X170" s="8" t="inlineStr"/>
       <c r="Y170" s="9" t="n">
-        <v>46186.23724715126</v>
+        <v>46186.27264113334</v>
       </c>
       <c r="Z170" s="8" t="inlineStr"/>
     </row>
@@ -11063,7 +11195,7 @@
       <c r="W171" s="8" t="inlineStr"/>
       <c r="X171" s="8" t="inlineStr"/>
       <c r="Y171" s="9" t="n">
-        <v>46186.23724715152</v>
+        <v>46186.27264113357</v>
       </c>
       <c r="Z171" s="8" t="inlineStr"/>
     </row>
@@ -11127,7 +11259,7 @@
       <c r="W172" s="8" t="inlineStr"/>
       <c r="X172" s="8" t="inlineStr"/>
       <c r="Y172" s="9" t="n">
-        <v>46186.23724715172</v>
+        <v>46186.27264113377</v>
       </c>
       <c r="Z172" s="8" t="inlineStr"/>
     </row>
@@ -11191,7 +11323,7 @@
       <c r="W173" s="8" t="inlineStr"/>
       <c r="X173" s="8" t="inlineStr"/>
       <c r="Y173" s="9" t="n">
-        <v>46186.23724715193</v>
+        <v>46186.27264113396</v>
       </c>
       <c r="Z173" s="8" t="inlineStr"/>
     </row>
@@ -11255,7 +11387,7 @@
       <c r="W174" s="8" t="inlineStr"/>
       <c r="X174" s="8" t="inlineStr"/>
       <c r="Y174" s="9" t="n">
-        <v>46186.23724715213</v>
+        <v>46186.27264113414</v>
       </c>
       <c r="Z174" s="8" t="inlineStr"/>
     </row>
@@ -11319,7 +11451,7 @@
       <c r="W175" s="8" t="inlineStr"/>
       <c r="X175" s="8" t="inlineStr"/>
       <c r="Y175" s="9" t="n">
-        <v>46186.23724715238</v>
+        <v>46186.27264113438</v>
       </c>
       <c r="Z175" s="8" t="inlineStr"/>
     </row>
@@ -11387,7 +11519,7 @@
       <c r="W176" s="8" t="inlineStr"/>
       <c r="X176" s="8" t="inlineStr"/>
       <c r="Y176" s="9" t="n">
-        <v>46186.23724715262</v>
+        <v>46186.27264113459</v>
       </c>
       <c r="Z176" s="8" t="inlineStr"/>
     </row>
@@ -11451,7 +11583,7 @@
       <c r="W177" s="8" t="inlineStr"/>
       <c r="X177" s="8" t="inlineStr"/>
       <c r="Y177" s="9" t="n">
-        <v>46186.23724715281</v>
+        <v>46186.27264113479</v>
       </c>
       <c r="Z177" s="8" t="inlineStr"/>
     </row>
@@ -11515,7 +11647,7 @@
       <c r="W178" s="8" t="inlineStr"/>
       <c r="X178" s="8" t="inlineStr"/>
       <c r="Y178" s="9" t="n">
-        <v>46186.23724715301</v>
+        <v>46186.27264113498</v>
       </c>
       <c r="Z178" s="8" t="inlineStr"/>
     </row>
@@ -11579,7 +11711,7 @@
       <c r="W179" s="8" t="inlineStr"/>
       <c r="X179" s="8" t="inlineStr"/>
       <c r="Y179" s="9" t="n">
-        <v>46186.23724715319</v>
+        <v>46186.27264113516</v>
       </c>
       <c r="Z179" s="8" t="inlineStr"/>
     </row>
@@ -11593,7 +11725,11 @@
       <c r="C180" s="5" t="n">
         <v>46184</v>
       </c>
-      <c r="D180" s="4" t="inlineStr"/>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>DE.TNL.GN00.TWK.P1</t>
+        </is>
+      </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 -Al Ruwayyah Depot Contact Rail System Design  : DE.TNL.GN00.TWK.P1.D2_Rev.C01</t>
@@ -11635,7 +11771,7 @@
       <c r="W180" s="4" t="inlineStr"/>
       <c r="X180" s="4" t="inlineStr"/>
       <c r="Y180" s="5" t="n">
-        <v>46186.23724715336</v>
+        <v>46186.27264113535</v>
       </c>
       <c r="Z180" s="4" t="inlineStr"/>
     </row>
@@ -11649,7 +11785,11 @@
       <c r="C181" s="9" t="n">
         <v>46184</v>
       </c>
-      <c r="D181" s="8" t="inlineStr"/>
+      <c r="D181" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST03.STR.V2</t>
+        </is>
+      </c>
       <c r="E181" s="10" t="inlineStr">
         <is>
           <t>Re: Shop Drawing Submission - Stretch-03 - Viaduct Structure Pierhead -PM74, Inserts, Coordinates &amp; Bearing BBS : DE.VDT.ST03.STR.V2.D5_Rev.C01</t>
@@ -11687,7 +11827,7 @@
       <c r="W181" s="8" t="inlineStr"/>
       <c r="X181" s="8" t="inlineStr"/>
       <c r="Y181" s="9" t="n">
-        <v>46186.23724715354</v>
+        <v>46186.27264113558</v>
       </c>
       <c r="Z181" s="8" t="inlineStr"/>
     </row>
@@ -11755,7 +11895,7 @@
       <c r="W182" s="8" t="inlineStr"/>
       <c r="X182" s="8" t="inlineStr"/>
       <c r="Y182" s="9" t="n">
-        <v>46186.23724715382</v>
+        <v>46186.27264113585</v>
       </c>
       <c r="Z182" s="8" t="inlineStr"/>
     </row>
@@ -11819,7 +11959,7 @@
       <c r="W183" s="8" t="inlineStr"/>
       <c r="X183" s="8" t="inlineStr"/>
       <c r="Y183" s="9" t="n">
-        <v>46186.23724715403</v>
+        <v>46186.27264113604</v>
       </c>
       <c r="Z183" s="8" t="inlineStr"/>
     </row>
@@ -11887,7 +12027,7 @@
       <c r="W184" s="4" t="inlineStr"/>
       <c r="X184" s="4" t="inlineStr"/>
       <c r="Y184" s="5" t="n">
-        <v>46186.23724715423</v>
+        <v>46186.27264113624</v>
       </c>
       <c r="Z184" s="4" t="inlineStr"/>
     </row>
@@ -11955,7 +12095,7 @@
       <c r="W185" s="4" t="inlineStr"/>
       <c r="X185" s="4" t="inlineStr"/>
       <c r="Y185" s="5" t="n">
-        <v>46186.23724715442</v>
+        <v>46186.27264113641</v>
       </c>
       <c r="Z185" s="4" t="inlineStr"/>
     </row>
@@ -12023,7 +12163,7 @@
       <c r="W186" s="4" t="inlineStr"/>
       <c r="X186" s="4" t="inlineStr"/>
       <c r="Y186" s="5" t="n">
-        <v>46186.2372471546</v>
+        <v>46186.27264113659</v>
       </c>
       <c r="Z186" s="4" t="inlineStr"/>
     </row>
@@ -12037,7 +12177,11 @@
       <c r="C187" s="5" t="n">
         <v>46184</v>
       </c>
-      <c r="D187" s="4" t="inlineStr"/>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>DE.TNL.GN00.TWK.P1</t>
+        </is>
+      </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Contact Rail System Layout Cross Section (Main Line) And Report: DE.TNL.GN00.TWK.P1.D2_Rev.C01</t>
@@ -12079,7 +12223,7 @@
       <c r="W187" s="4" t="inlineStr"/>
       <c r="X187" s="4" t="inlineStr"/>
       <c r="Y187" s="5" t="n">
-        <v>46186.23724715478</v>
+        <v>46186.2726411369</v>
       </c>
       <c r="Z187" s="4" t="inlineStr"/>
     </row>
@@ -12147,7 +12291,7 @@
       <c r="W188" s="4" t="inlineStr"/>
       <c r="X188" s="4" t="inlineStr"/>
       <c r="Y188" s="5" t="n">
-        <v>46186.23724715498</v>
+        <v>46186.2726411371</v>
       </c>
       <c r="Z188" s="4" t="inlineStr"/>
     </row>
@@ -12215,7 +12359,7 @@
       <c r="W189" s="4" t="inlineStr"/>
       <c r="X189" s="4" t="inlineStr"/>
       <c r="Y189" s="5" t="n">
-        <v>46186.23724715516</v>
+        <v>46186.27264113761</v>
       </c>
       <c r="Z189" s="4" t="inlineStr"/>
     </row>
@@ -12283,7 +12427,7 @@
       <c r="W190" s="4" t="inlineStr"/>
       <c r="X190" s="4" t="inlineStr"/>
       <c r="Y190" s="5" t="n">
-        <v>46186.23724715535</v>
+        <v>46186.27264113795</v>
       </c>
       <c r="Z190" s="4" t="inlineStr"/>
     </row>
@@ -12351,7 +12495,7 @@
       <c r="W191" s="4" t="inlineStr"/>
       <c r="X191" s="4" t="inlineStr"/>
       <c r="Y191" s="5" t="n">
-        <v>46186.23724715552</v>
+        <v>46186.2726411382</v>
       </c>
       <c r="Z191" s="4" t="inlineStr"/>
     </row>
@@ -12419,7 +12563,7 @@
       <c r="W192" s="4" t="inlineStr"/>
       <c r="X192" s="4" t="inlineStr"/>
       <c r="Y192" s="5" t="n">
-        <v>46186.23724715615</v>
+        <v>46186.2726411384</v>
       </c>
       <c r="Z192" s="4" t="inlineStr"/>
     </row>
@@ -12483,7 +12627,7 @@
       <c r="W193" s="8" t="inlineStr"/>
       <c r="X193" s="8" t="inlineStr"/>
       <c r="Y193" s="9" t="n">
-        <v>46186.23724715677</v>
+        <v>46186.27264113862</v>
       </c>
       <c r="Z193" s="8" t="inlineStr"/>
     </row>
@@ -12551,7 +12695,7 @@
       <c r="W194" s="8" t="inlineStr"/>
       <c r="X194" s="8" t="inlineStr"/>
       <c r="Y194" s="9" t="n">
-        <v>46186.23724715714</v>
+        <v>46186.27264113886</v>
       </c>
       <c r="Z194" s="8" t="inlineStr"/>
     </row>
@@ -12615,7 +12759,7 @@
       <c r="W195" s="8" t="inlineStr"/>
       <c r="X195" s="8" t="inlineStr"/>
       <c r="Y195" s="9" t="n">
-        <v>46186.23724715744</v>
+        <v>46186.27264113908</v>
       </c>
       <c r="Z195" s="8" t="inlineStr"/>
     </row>
@@ -12629,7 +12773,11 @@
       <c r="C196" s="9" t="n">
         <v>46184</v>
       </c>
-      <c r="D196" s="8" t="inlineStr"/>
+      <c r="D196" s="8" t="inlineStr">
+        <is>
+          <t>DE.DPT.STBD.STR.S0</t>
+        </is>
+      </c>
       <c r="E196" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Depot BDR01- Stabling Building Structure : DE.DPT.STBD.STR.S0.D3_Rev.C03</t>
@@ -12667,7 +12815,7 @@
       <c r="W196" s="8" t="inlineStr"/>
       <c r="X196" s="8" t="inlineStr"/>
       <c r="Y196" s="9" t="n">
-        <v>46186.23724715764</v>
+        <v>46186.27264113929</v>
       </c>
       <c r="Z196" s="8" t="inlineStr"/>
     </row>
@@ -12681,7 +12829,11 @@
       <c r="C197" s="9" t="n">
         <v>46184</v>
       </c>
-      <c r="D197" s="8" t="inlineStr"/>
+      <c r="D197" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE03.GEO.G1</t>
+        </is>
+      </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Geotechnical - Technical Note-Working Pile Load Test at BG34 (GLE03) (SOP-65 and SOP-154): DE.ELS.GE03.GEO.G1.D3_Rev C04</t>
@@ -12719,7 +12871,7 @@
       <c r="W197" s="8" t="inlineStr"/>
       <c r="X197" s="8" t="inlineStr"/>
       <c r="Y197" s="9" t="n">
-        <v>46186.23724715783</v>
+        <v>46186.27264113951</v>
       </c>
       <c r="Z197" s="8" t="inlineStr"/>
     </row>
@@ -12733,7 +12885,11 @@
       <c r="C198" s="9" t="n">
         <v>46184</v>
       </c>
-      <c r="D198" s="8" t="inlineStr"/>
+      <c r="D198" s="8" t="inlineStr">
+        <is>
+          <t>DE.TNL.CC02.STR.T2.D3</t>
+        </is>
+      </c>
       <c r="E198" s="10" t="inlineStr">
         <is>
           <t>Re: Design Drawing Submission - DCP3 - Cut &amp; Cover BB05 Slabs - (DE.TNL.CC02.STR.T2.D3) - Rev.C01</t>
@@ -12767,7 +12923,7 @@
       <c r="W198" s="8" t="inlineStr"/>
       <c r="X198" s="8" t="inlineStr"/>
       <c r="Y198" s="9" t="n">
-        <v>46186.23724715799</v>
+        <v>46186.27264113971</v>
       </c>
       <c r="Z198" s="8" t="inlineStr"/>
     </row>
@@ -12831,7 +12987,7 @@
       <c r="W199" s="8" t="inlineStr"/>
       <c r="X199" s="8" t="inlineStr"/>
       <c r="Y199" s="9" t="n">
-        <v>46186.23724715824</v>
+        <v>46186.27264113992</v>
       </c>
       <c r="Z199" s="8" t="inlineStr"/>
     </row>
@@ -12845,7 +13001,11 @@
       <c r="C200" s="9" t="n">
         <v>46184</v>
       </c>
-      <c r="D200" s="8" t="inlineStr"/>
+      <c r="D200" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST04.GEO.G1</t>
+        </is>
+      </c>
       <c r="E200" s="10" t="inlineStr">
         <is>
           <t>Re: Report Submission - DCP3 - Geotechnical Design Report for Viaduct - Stretch 4 Balanced Cantilever Pier PM-95,96,97,98 : DE.VDT.ST04.GEO.G1.D3_Rev.C01</t>
@@ -12883,7 +13043,7 @@
       <c r="W200" s="8" t="inlineStr"/>
       <c r="X200" s="8" t="inlineStr"/>
       <c r="Y200" s="9" t="n">
-        <v>46186.23724715844</v>
+        <v>46186.27264114014</v>
       </c>
       <c r="Z200" s="8" t="inlineStr"/>
     </row>
@@ -12897,7 +13057,11 @@
       <c r="C201" s="9" t="n">
         <v>46184</v>
       </c>
-      <c r="D201" s="8" t="inlineStr"/>
+      <c r="D201" s="8" t="inlineStr">
+        <is>
+          <t>DE.UGS.RE01.STR.S7</t>
+        </is>
+      </c>
       <c r="E201" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BR09 - Structure D-Wall Ancillary 02 : DE.UGS.RE01.STR.S7.D3_Rev.C02</t>
@@ -12935,7 +13099,7 @@
       <c r="W201" s="8" t="inlineStr"/>
       <c r="X201" s="8" t="inlineStr"/>
       <c r="Y201" s="9" t="n">
-        <v>46186.23724715861</v>
+        <v>46186.27264114035</v>
       </c>
       <c r="Z201" s="8" t="inlineStr"/>
     </row>
@@ -13003,7 +13167,7 @@
       <c r="W202" s="4" t="inlineStr"/>
       <c r="X202" s="4" t="inlineStr"/>
       <c r="Y202" s="5" t="n">
-        <v>46186.23724715885</v>
+        <v>46186.27264114058</v>
       </c>
       <c r="Z202" s="4" t="inlineStr"/>
     </row>
@@ -13017,7 +13181,11 @@
       <c r="C203" s="5" t="n">
         <v>46184</v>
       </c>
-      <c r="D203" s="4" t="inlineStr"/>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST02.STR.V3</t>
+        </is>
+      </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Stretch-02.1 &amp; 02.2 - Viaduct Structure Superstructure ISO Spans : DE.VDT.ST02.STR.V3.D3_Rev.C03</t>
@@ -13059,7 +13227,7 @@
       <c r="W203" s="4" t="inlineStr"/>
       <c r="X203" s="4" t="inlineStr"/>
       <c r="Y203" s="5" t="n">
-        <v>46186.23724715903</v>
+        <v>46186.2726411408</v>
       </c>
       <c r="Z203" s="4" t="inlineStr"/>
     </row>
@@ -13127,7 +13295,7 @@
       <c r="W204" s="4" t="inlineStr"/>
       <c r="X204" s="4" t="inlineStr"/>
       <c r="Y204" s="5" t="n">
-        <v>46186.23724715924</v>
+        <v>46186.2726411413</v>
       </c>
       <c r="Z204" s="4" t="inlineStr"/>
     </row>
@@ -13191,7 +13359,7 @@
       <c r="W205" s="4" t="inlineStr"/>
       <c r="X205" s="4" t="inlineStr"/>
       <c r="Y205" s="5" t="n">
-        <v>46186.23724715946</v>
+        <v>46186.27264114165</v>
       </c>
       <c r="Z205" s="4" t="inlineStr"/>
     </row>
@@ -13259,7 +13427,7 @@
       <c r="W206" s="4" t="inlineStr"/>
       <c r="X206" s="4" t="inlineStr"/>
       <c r="Y206" s="5" t="n">
-        <v>46186.23724716003</v>
+        <v>46186.27264114228</v>
       </c>
       <c r="Z206" s="4" t="inlineStr"/>
     </row>
@@ -13273,7 +13441,11 @@
       <c r="C207" s="5" t="n">
         <v>46184</v>
       </c>
-      <c r="D207" s="4" t="inlineStr"/>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>DE.UGS.RE03.STR.S3</t>
+        </is>
+      </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BR07 - Structure - Concourse Slab Submission -: DE.UGS.RE03.STR.S3.D3_Rev.C04 (Partial Submission) (IDV Certificate Submission)</t>
@@ -13315,7 +13487,7 @@
       <c r="W207" s="4" t="inlineStr"/>
       <c r="X207" s="4" t="inlineStr"/>
       <c r="Y207" s="5" t="n">
-        <v>46186.23724716032</v>
+        <v>46186.2726411426</v>
       </c>
       <c r="Z207" s="4" t="inlineStr"/>
     </row>
@@ -13329,7 +13501,11 @@
       <c r="C208" s="5" t="n">
         <v>46184</v>
       </c>
-      <c r="D208" s="4" t="inlineStr"/>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE00.STR.S1</t>
+        </is>
+      </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BG31 – Structural – Link Bridge-Pile Caps : DE.ELS.GE00.STR.S1.D3_Rev.C02</t>
@@ -13371,7 +13547,7 @@
       <c r="W208" s="4" t="inlineStr"/>
       <c r="X208" s="4" t="inlineStr"/>
       <c r="Y208" s="5" t="n">
-        <v>46186.23724716061</v>
+        <v>46186.2726411429</v>
       </c>
       <c r="Z208" s="4" t="inlineStr"/>
     </row>
@@ -13427,7 +13603,7 @@
       <c r="W209" s="4" t="inlineStr"/>
       <c r="X209" s="4" t="inlineStr"/>
       <c r="Y209" s="5" t="n">
-        <v>46186.23724716077</v>
+        <v>46186.27264114311</v>
       </c>
       <c r="Z209" s="4" t="inlineStr"/>
     </row>
@@ -13495,7 +13671,7 @@
       <c r="W210" s="4" t="inlineStr"/>
       <c r="X210" s="4" t="inlineStr"/>
       <c r="Y210" s="5" t="n">
-        <v>46186.23724716101</v>
+        <v>46186.27264114335</v>
       </c>
       <c r="Z210" s="4" t="inlineStr"/>
     </row>
@@ -13563,7 +13739,7 @@
       <c r="W211" s="4" t="inlineStr"/>
       <c r="X211" s="4" t="inlineStr"/>
       <c r="Y211" s="5" t="n">
-        <v>46186.23724716125</v>
+        <v>46186.27264114358</v>
       </c>
       <c r="Z211" s="4" t="inlineStr"/>
     </row>
@@ -13631,7 +13807,7 @@
       <c r="W212" s="4" t="inlineStr"/>
       <c r="X212" s="4" t="inlineStr"/>
       <c r="Y212" s="5" t="n">
-        <v>46186.23724716147</v>
+        <v>46186.27264114378</v>
       </c>
       <c r="Z212" s="4" t="inlineStr"/>
     </row>
@@ -13699,7 +13875,7 @@
       <c r="W213" s="4" t="inlineStr"/>
       <c r="X213" s="4" t="inlineStr"/>
       <c r="Y213" s="5" t="n">
-        <v>46186.23724716179</v>
+        <v>46186.27264114399</v>
       </c>
       <c r="Z213" s="4" t="inlineStr"/>
     </row>
@@ -13767,7 +13943,7 @@
       <c r="W214" s="4" t="inlineStr"/>
       <c r="X214" s="4" t="inlineStr"/>
       <c r="Y214" s="5" t="n">
-        <v>46186.23724716199</v>
+        <v>46186.2726411442</v>
       </c>
       <c r="Z214" s="4" t="inlineStr"/>
     </row>
@@ -13835,7 +14011,7 @@
       <c r="W215" s="4" t="inlineStr"/>
       <c r="X215" s="4" t="inlineStr"/>
       <c r="Y215" s="5" t="n">
-        <v>46186.23724716221</v>
+        <v>46186.27264114442</v>
       </c>
       <c r="Z215" s="4" t="inlineStr"/>
     </row>
@@ -13891,7 +14067,7 @@
       <c r="W216" s="4" t="inlineStr"/>
       <c r="X216" s="4" t="inlineStr"/>
       <c r="Y216" s="5" t="n">
-        <v>46186.23724716238</v>
+        <v>46186.27264114461</v>
       </c>
       <c r="Z216" s="4" t="inlineStr"/>
     </row>
@@ -13947,7 +14123,7 @@
       <c r="W217" s="4" t="inlineStr"/>
       <c r="X217" s="4" t="inlineStr"/>
       <c r="Y217" s="5" t="n">
-        <v>46186.23724716256</v>
+        <v>46186.27264114511</v>
       </c>
       <c r="Z217" s="4" t="inlineStr"/>
     </row>
@@ -14003,7 +14179,7 @@
       <c r="W218" s="4" t="inlineStr"/>
       <c r="X218" s="4" t="inlineStr"/>
       <c r="Y218" s="5" t="n">
-        <v>46186.23724716269</v>
+        <v>46186.27264114544</v>
       </c>
       <c r="Z218" s="4" t="inlineStr"/>
     </row>
@@ -14059,7 +14235,7 @@
       <c r="W219" s="4" t="inlineStr"/>
       <c r="X219" s="4" t="inlineStr"/>
       <c r="Y219" s="5" t="n">
-        <v>46186.23724716285</v>
+        <v>46186.27264114566</v>
       </c>
       <c r="Z219" s="4" t="inlineStr"/>
     </row>
@@ -14127,7 +14303,7 @@
       <c r="W220" s="4" t="inlineStr"/>
       <c r="X220" s="4" t="inlineStr"/>
       <c r="Y220" s="5" t="n">
-        <v>46186.23724716306</v>
+        <v>46186.2726411459</v>
       </c>
       <c r="Z220" s="4" t="inlineStr"/>
     </row>
@@ -14195,7 +14371,7 @@
       <c r="W221" s="4" t="inlineStr"/>
       <c r="X221" s="4" t="inlineStr"/>
       <c r="Y221" s="5" t="n">
-        <v>46186.23724716355</v>
+        <v>46186.27264114613</v>
       </c>
       <c r="Z221" s="4" t="inlineStr"/>
     </row>
@@ -14263,7 +14439,7 @@
       <c r="W222" s="4" t="inlineStr"/>
       <c r="X222" s="4" t="inlineStr"/>
       <c r="Y222" s="5" t="n">
-        <v>46186.23724716393</v>
+        <v>46186.27264114637</v>
       </c>
       <c r="Z222" s="4" t="inlineStr"/>
     </row>
@@ -14331,7 +14507,7 @@
       <c r="W223" s="4" t="inlineStr"/>
       <c r="X223" s="4" t="inlineStr"/>
       <c r="Y223" s="5" t="n">
-        <v>46186.23724716419</v>
+        <v>46186.27264114658</v>
       </c>
       <c r="Z223" s="4" t="inlineStr"/>
     </row>
@@ -14399,7 +14575,7 @@
       <c r="W224" s="4" t="inlineStr"/>
       <c r="X224" s="4" t="inlineStr"/>
       <c r="Y224" s="5" t="n">
-        <v>46186.23724716442</v>
+        <v>46186.27264114682</v>
       </c>
       <c r="Z224" s="4" t="inlineStr"/>
     </row>
@@ -14467,7 +14643,7 @@
       <c r="W225" s="4" t="inlineStr"/>
       <c r="X225" s="4" t="inlineStr"/>
       <c r="Y225" s="5" t="n">
-        <v>46186.23724716464</v>
+        <v>46186.27264114703</v>
       </c>
       <c r="Z225" s="4" t="inlineStr"/>
     </row>
@@ -14535,7 +14711,7 @@
       <c r="W226" s="4" t="inlineStr"/>
       <c r="X226" s="4" t="inlineStr"/>
       <c r="Y226" s="5" t="n">
-        <v>46186.23724716485</v>
+        <v>46186.27264114723</v>
       </c>
       <c r="Z226" s="4" t="inlineStr"/>
     </row>
@@ -14603,7 +14779,7 @@
       <c r="W227" s="4" t="inlineStr"/>
       <c r="X227" s="4" t="inlineStr"/>
       <c r="Y227" s="5" t="n">
-        <v>46186.23724716502</v>
+        <v>46186.27264114741</v>
       </c>
       <c r="Z227" s="4" t="inlineStr"/>
     </row>
@@ -14671,7 +14847,7 @@
       <c r="W228" s="4" t="inlineStr"/>
       <c r="X228" s="4" t="inlineStr"/>
       <c r="Y228" s="5" t="n">
-        <v>46186.23724716522</v>
+        <v>46186.2726411476</v>
       </c>
       <c r="Z228" s="4" t="inlineStr"/>
     </row>
@@ -14685,7 +14861,11 @@
       <c r="C229" s="5" t="n">
         <v>46183</v>
       </c>
-      <c r="D229" s="4" t="inlineStr"/>
+      <c r="D229" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.GN00.STR.03.D5</t>
+        </is>
+      </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
           <t>Shop Drawing Submission - Global - Viaduct Structure Balanced Cantilever (BC-3SP-72) Reinf. Shop Dwg : (DE.VDT.GN00.STR.03.D5) :MLCC-N0003-CIV-VBR-3SP-DRW-84201 - 84211_Rev.C01</t>
@@ -14723,7 +14903,7 @@
       <c r="W229" s="4" t="inlineStr"/>
       <c r="X229" s="4" t="inlineStr"/>
       <c r="Y229" s="5" t="n">
-        <v>46186.23724716544</v>
+        <v>46186.27264114784</v>
       </c>
       <c r="Z229" s="4" t="inlineStr"/>
     </row>
@@ -14791,7 +14971,7 @@
       <c r="W230" s="4" t="inlineStr"/>
       <c r="X230" s="4" t="inlineStr"/>
       <c r="Y230" s="5" t="n">
-        <v>46186.23724716565</v>
+        <v>46186.27264114805</v>
       </c>
       <c r="Z230" s="4" t="inlineStr"/>
     </row>
@@ -14863,7 +15043,7 @@
       <c r="W231" s="4" t="inlineStr"/>
       <c r="X231" s="4" t="inlineStr"/>
       <c r="Y231" s="5" t="n">
-        <v>46186.23724716589</v>
+        <v>46186.27264114827</v>
       </c>
       <c r="Z231" s="4" t="inlineStr"/>
     </row>
@@ -14931,7 +15111,7 @@
       <c r="W232" s="4" t="inlineStr"/>
       <c r="X232" s="4" t="inlineStr"/>
       <c r="Y232" s="5" t="n">
-        <v>46186.23724716608</v>
+        <v>46186.27264114853</v>
       </c>
       <c r="Z232" s="4" t="inlineStr"/>
     </row>
@@ -14945,7 +15125,11 @@
       <c r="C233" s="5" t="n">
         <v>46183</v>
       </c>
-      <c r="D233" s="4" t="inlineStr"/>
+      <c r="D233" s="4" t="inlineStr">
+        <is>
+          <t>DE.UGS.RE03.STR.S4</t>
+        </is>
+      </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Station BR07 - Structure - Platform Slab : DE.UGS.RE03.STR.S4.D3_Rev.C01</t>
@@ -14987,7 +15171,7 @@
       <c r="W233" s="4" t="inlineStr"/>
       <c r="X233" s="4" t="inlineStr"/>
       <c r="Y233" s="5" t="n">
-        <v>46186.23724716625</v>
+        <v>46186.27264114874</v>
       </c>
       <c r="Z233" s="4" t="inlineStr"/>
     </row>
@@ -15055,7 +15239,7 @@
       <c r="W234" s="4" t="inlineStr"/>
       <c r="X234" s="4" t="inlineStr"/>
       <c r="Y234" s="5" t="n">
-        <v>46186.23724716646</v>
+        <v>46186.27264114895</v>
       </c>
       <c r="Z234" s="4" t="inlineStr"/>
     </row>
@@ -15123,7 +15307,7 @@
       <c r="W235" s="4" t="inlineStr"/>
       <c r="X235" s="4" t="inlineStr"/>
       <c r="Y235" s="5" t="n">
-        <v>46186.23724716673</v>
+        <v>46186.2726411492</v>
       </c>
       <c r="Z235" s="4" t="inlineStr"/>
     </row>
@@ -15191,7 +15375,7 @@
       <c r="W236" s="4" t="inlineStr"/>
       <c r="X236" s="4" t="inlineStr"/>
       <c r="Y236" s="5" t="n">
-        <v>46186.237247167</v>
+        <v>46186.27264114948</v>
       </c>
       <c r="Z236" s="4" t="inlineStr"/>
     </row>
@@ -15259,7 +15443,7 @@
       <c r="W237" s="4" t="inlineStr"/>
       <c r="X237" s="4" t="inlineStr"/>
       <c r="Y237" s="5" t="n">
-        <v>46186.2372471675</v>
+        <v>46186.27264114966</v>
       </c>
       <c r="Z237" s="4" t="inlineStr"/>
     </row>
@@ -15327,7 +15511,7 @@
       <c r="W238" s="4" t="inlineStr"/>
       <c r="X238" s="4" t="inlineStr"/>
       <c r="Y238" s="5" t="n">
-        <v>46186.23724716781</v>
+        <v>46186.27264114986</v>
       </c>
       <c r="Z238" s="4" t="inlineStr"/>
     </row>
@@ -15395,7 +15579,7 @@
       <c r="W239" s="4" t="inlineStr"/>
       <c r="X239" s="4" t="inlineStr"/>
       <c r="Y239" s="5" t="n">
-        <v>46186.23724716804</v>
+        <v>46186.27264115006</v>
       </c>
       <c r="Z239" s="4" t="inlineStr"/>
     </row>
@@ -15463,7 +15647,7 @@
       <c r="W240" s="4" t="inlineStr"/>
       <c r="X240" s="4" t="inlineStr"/>
       <c r="Y240" s="5" t="n">
-        <v>46186.23724716825</v>
+        <v>46186.27264115027</v>
       </c>
       <c r="Z240" s="4" t="inlineStr"/>
     </row>
@@ -15531,7 +15715,7 @@
       <c r="W241" s="4" t="inlineStr"/>
       <c r="X241" s="4" t="inlineStr"/>
       <c r="Y241" s="5" t="n">
-        <v>46186.23724716847</v>
+        <v>46186.27264115048</v>
       </c>
       <c r="Z241" s="4" t="inlineStr"/>
     </row>
@@ -15595,7 +15779,7 @@
       <c r="W242" s="8" t="inlineStr"/>
       <c r="X242" s="8" t="inlineStr"/>
       <c r="Y242" s="9" t="n">
-        <v>46186.23724716868</v>
+        <v>46186.27264115067</v>
       </c>
       <c r="Z242" s="8" t="inlineStr"/>
     </row>
@@ -15663,7 +15847,7 @@
       <c r="W243" s="8" t="inlineStr"/>
       <c r="X243" s="8" t="inlineStr"/>
       <c r="Y243" s="9" t="n">
-        <v>46186.23724716888</v>
+        <v>46186.27264115087</v>
       </c>
       <c r="Z243" s="8" t="inlineStr"/>
     </row>
@@ -15731,7 +15915,7 @@
       <c r="W244" s="8" t="inlineStr"/>
       <c r="X244" s="8" t="inlineStr"/>
       <c r="Y244" s="9" t="n">
-        <v>46186.23724716908</v>
+        <v>46186.27264115107</v>
       </c>
       <c r="Z244" s="8" t="inlineStr"/>
     </row>
@@ -15799,7 +15983,7 @@
       <c r="W245" s="4" t="inlineStr"/>
       <c r="X245" s="4" t="inlineStr"/>
       <c r="Y245" s="5" t="n">
-        <v>46186.23724716928</v>
+        <v>46186.27264115126</v>
       </c>
       <c r="Z245" s="4" t="inlineStr"/>
     </row>
@@ -15863,7 +16047,7 @@
       <c r="W246" s="8" t="inlineStr"/>
       <c r="X246" s="8" t="inlineStr"/>
       <c r="Y246" s="9" t="n">
-        <v>46186.23724716951</v>
+        <v>46186.2726411519</v>
       </c>
       <c r="Z246" s="8" t="inlineStr"/>
     </row>
@@ -15931,7 +16115,7 @@
       <c r="W247" s="4" t="inlineStr"/>
       <c r="X247" s="4" t="inlineStr"/>
       <c r="Y247" s="5" t="n">
-        <v>46186.23724716969</v>
+        <v>46186.27264115213</v>
       </c>
       <c r="Z247" s="4" t="inlineStr"/>
     </row>
@@ -15945,7 +16129,11 @@
       <c r="C248" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D248" s="8" t="inlineStr"/>
+      <c r="D248" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST02.STR.V3</t>
+        </is>
+      </c>
       <c r="E248" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Stretch-02 - Viaduct Structure Balanced Cantilever (BC-3SP-72-02) Superstructure : DE.VDT.ST02.STR.V3.D3_Rev.C01</t>
@@ -15983,7 +16171,7 @@
       <c r="W248" s="8" t="inlineStr"/>
       <c r="X248" s="8" t="inlineStr"/>
       <c r="Y248" s="9" t="n">
-        <v>46186.23724716987</v>
+        <v>46186.27264115235</v>
       </c>
       <c r="Z248" s="8" t="inlineStr"/>
     </row>
@@ -16047,7 +16235,7 @@
       <c r="W249" s="8" t="inlineStr"/>
       <c r="X249" s="8" t="inlineStr"/>
       <c r="Y249" s="9" t="n">
-        <v>46186.23724717007</v>
+        <v>46186.27264115286</v>
       </c>
       <c r="Z249" s="8" t="inlineStr"/>
     </row>
@@ -16061,7 +16249,11 @@
       <c r="C250" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D250" s="8" t="inlineStr"/>
+      <c r="D250" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST51.STR.V2</t>
+        </is>
+      </c>
       <c r="E250" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3-Stretch 05.1-Viaduct Structure Bearing Schedule ISO &amp; 2SP Span:DE.VDT.ST51.STR.V2.D3_Rev.C01</t>
@@ -16099,7 +16291,7 @@
       <c r="W250" s="8" t="inlineStr"/>
       <c r="X250" s="8" t="inlineStr"/>
       <c r="Y250" s="9" t="n">
-        <v>46186.23724717067</v>
+        <v>46186.27264115316</v>
       </c>
       <c r="Z250" s="8" t="inlineStr"/>
     </row>
@@ -16167,7 +16359,7 @@
       <c r="W251" s="8" t="inlineStr"/>
       <c r="X251" s="8" t="inlineStr"/>
       <c r="Y251" s="9" t="n">
-        <v>46186.23724717092</v>
+        <v>46186.27264115338</v>
       </c>
       <c r="Z251" s="8" t="inlineStr"/>
     </row>
@@ -16235,7 +16427,7 @@
       <c r="W252" s="4" t="inlineStr"/>
       <c r="X252" s="4" t="inlineStr"/>
       <c r="Y252" s="5" t="n">
-        <v>46186.23724717122</v>
+        <v>46186.27264115366</v>
       </c>
       <c r="Z252" s="4" t="inlineStr"/>
     </row>
@@ -16299,7 +16491,7 @@
       <c r="W253" s="8" t="inlineStr"/>
       <c r="X253" s="8" t="inlineStr"/>
       <c r="Y253" s="9" t="n">
-        <v>46186.23724717143</v>
+        <v>46186.27264115389</v>
       </c>
       <c r="Z253" s="8" t="inlineStr"/>
     </row>
@@ -16367,7 +16559,7 @@
       <c r="W254" s="4" t="inlineStr"/>
       <c r="X254" s="4" t="inlineStr"/>
       <c r="Y254" s="5" t="n">
-        <v>46186.23724717163</v>
+        <v>46186.27264115407</v>
       </c>
       <c r="Z254" s="4" t="inlineStr"/>
     </row>
@@ -16435,7 +16627,7 @@
       <c r="W255" s="8" t="inlineStr"/>
       <c r="X255" s="8" t="inlineStr"/>
       <c r="Y255" s="9" t="n">
-        <v>46186.23724717184</v>
+        <v>46186.27264115427</v>
       </c>
       <c r="Z255" s="8" t="inlineStr"/>
     </row>
@@ -16499,7 +16691,7 @@
       <c r="W256" s="8" t="inlineStr"/>
       <c r="X256" s="8" t="inlineStr"/>
       <c r="Y256" s="9" t="n">
-        <v>46186.23724717207</v>
+        <v>46186.2726411545</v>
       </c>
       <c r="Z256" s="8" t="inlineStr"/>
     </row>
@@ -16571,7 +16763,7 @@
       <c r="W257" s="4" t="inlineStr"/>
       <c r="X257" s="4" t="inlineStr"/>
       <c r="Y257" s="5" t="n">
-        <v>46186.23724717226</v>
+        <v>46186.27264115517</v>
       </c>
       <c r="Z257" s="4" t="inlineStr"/>
     </row>
@@ -16585,7 +16777,11 @@
       <c r="C258" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D258" s="8" t="inlineStr"/>
+      <c r="D258" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST02.STR.V3</t>
+        </is>
+      </c>
       <c r="E258" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Stretch-02 - Viaduct Structure Balanced Cantilever (BC-3SP-72-03) Superstructure -: DE.VDT.ST02.STR.V3.D3_Rev.C01</t>
@@ -16623,7 +16819,7 @@
       <c r="W258" s="8" t="inlineStr"/>
       <c r="X258" s="8" t="inlineStr"/>
       <c r="Y258" s="9" t="n">
-        <v>46186.23724717243</v>
+        <v>46186.27264115548</v>
       </c>
       <c r="Z258" s="8" t="inlineStr"/>
     </row>
@@ -16687,7 +16883,7 @@
       <c r="W259" s="8" t="inlineStr"/>
       <c r="X259" s="8" t="inlineStr"/>
       <c r="Y259" s="9" t="n">
-        <v>46186.23724717264</v>
+        <v>46186.27264115573</v>
       </c>
       <c r="Z259" s="8" t="inlineStr"/>
     </row>
@@ -16755,7 +16951,7 @@
       <c r="W260" s="8" t="inlineStr"/>
       <c r="X260" s="8" t="inlineStr"/>
       <c r="Y260" s="9" t="n">
-        <v>46186.23724717284</v>
+        <v>46186.27264115632</v>
       </c>
       <c r="Z260" s="8" t="inlineStr"/>
     </row>
@@ -16807,7 +17003,7 @@
       <c r="W261" s="8" t="inlineStr"/>
       <c r="X261" s="8" t="inlineStr"/>
       <c r="Y261" s="9" t="n">
-        <v>46186.237247173</v>
+        <v>46186.27264115661</v>
       </c>
       <c r="Z261" s="8" t="inlineStr"/>
     </row>
@@ -16879,7 +17075,7 @@
       <c r="W262" s="8" t="inlineStr"/>
       <c r="X262" s="8" t="inlineStr"/>
       <c r="Y262" s="9" t="n">
-        <v>46186.23724717361</v>
+        <v>46186.27264115684</v>
       </c>
       <c r="Z262" s="8" t="inlineStr"/>
     </row>
@@ -16893,7 +17089,11 @@
       <c r="C263" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D263" s="8" t="inlineStr"/>
+      <c r="D263" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST42.STR.V3</t>
+        </is>
+      </c>
       <c r="E263" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Stretch-04.1 - Viaduct Structure Superstructure 2SP Spans Part 2 : DE.VDT.ST42.STR.V3.D3_Rev.C01</t>
@@ -16931,7 +17131,7 @@
       <c r="W263" s="8" t="inlineStr"/>
       <c r="X263" s="8" t="inlineStr"/>
       <c r="Y263" s="9" t="n">
-        <v>46186.23724717388</v>
+        <v>46186.27264115705</v>
       </c>
       <c r="Z263" s="8" t="inlineStr"/>
     </row>
@@ -16945,7 +17145,11 @@
       <c r="C264" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D264" s="8" t="inlineStr"/>
+      <c r="D264" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE11.STR.S9</t>
+        </is>
+      </c>
       <c r="E264" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BB03 - Structural (CHILLER YARD): DE.ELS.GE11.STR.S9.D3_Rev.C01</t>
@@ -16983,7 +17187,7 @@
       <c r="W264" s="8" t="inlineStr"/>
       <c r="X264" s="8" t="inlineStr"/>
       <c r="Y264" s="9" t="n">
-        <v>46186.23724717407</v>
+        <v>46186.27264115726</v>
       </c>
       <c r="Z264" s="8" t="inlineStr"/>
     </row>
@@ -17047,7 +17251,7 @@
       <c r="W265" s="8" t="inlineStr"/>
       <c r="X265" s="8" t="inlineStr"/>
       <c r="Y265" s="9" t="n">
-        <v>46186.23724717431</v>
+        <v>46186.27264115745</v>
       </c>
       <c r="Z265" s="8" t="inlineStr"/>
     </row>
@@ -17111,7 +17315,7 @@
       <c r="W266" s="8" t="inlineStr"/>
       <c r="X266" s="8" t="inlineStr"/>
       <c r="Y266" s="9" t="n">
-        <v>46186.23724717453</v>
+        <v>46186.27264115766</v>
       </c>
       <c r="Z266" s="8" t="inlineStr"/>
     </row>
@@ -17175,7 +17379,7 @@
       <c r="W267" s="8" t="inlineStr"/>
       <c r="X267" s="8" t="inlineStr"/>
       <c r="Y267" s="9" t="n">
-        <v>46186.23724717472</v>
+        <v>46186.27264115785</v>
       </c>
       <c r="Z267" s="8" t="inlineStr"/>
     </row>
@@ -17239,7 +17443,7 @@
       <c r="W268" s="8" t="inlineStr"/>
       <c r="X268" s="8" t="inlineStr"/>
       <c r="Y268" s="9" t="n">
-        <v>46186.23724717492</v>
+        <v>46186.27264115804</v>
       </c>
       <c r="Z268" s="8" t="inlineStr"/>
     </row>
@@ -17307,7 +17511,7 @@
       <c r="W269" s="4" t="inlineStr"/>
       <c r="X269" s="4" t="inlineStr"/>
       <c r="Y269" s="5" t="n">
-        <v>46186.23724717511</v>
+        <v>46186.27264115823</v>
       </c>
       <c r="Z269" s="4" t="inlineStr"/>
     </row>
@@ -17375,7 +17579,7 @@
       <c r="W270" s="4" t="inlineStr"/>
       <c r="X270" s="4" t="inlineStr"/>
       <c r="Y270" s="5" t="n">
-        <v>46186.2372471753</v>
+        <v>46186.27264115842</v>
       </c>
       <c r="Z270" s="4" t="inlineStr"/>
     </row>
@@ -17443,7 +17647,7 @@
       <c r="W271" s="4" t="inlineStr"/>
       <c r="X271" s="4" t="inlineStr"/>
       <c r="Y271" s="5" t="n">
-        <v>46186.23724717549</v>
+        <v>46186.2726411586</v>
       </c>
       <c r="Z271" s="4" t="inlineStr"/>
     </row>
@@ -17507,7 +17711,7 @@
       <c r="W272" s="8" t="inlineStr"/>
       <c r="X272" s="8" t="inlineStr"/>
       <c r="Y272" s="9" t="n">
-        <v>46186.23724717568</v>
+        <v>46186.27264115879</v>
       </c>
       <c r="Z272" s="8" t="inlineStr"/>
     </row>
@@ -17521,7 +17725,11 @@
       <c r="C273" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D273" s="8" t="inlineStr"/>
+      <c r="D273" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE00.LDS.L2</t>
+        </is>
+      </c>
       <c r="E273" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP1 - BG31 Creek Interchange Station – Landscape Package DE.ELS.GE00.LDS.L2.D1_Rev.C01 (RCS Resubmission)</t>
@@ -17559,7 +17767,7 @@
       <c r="W273" s="8" t="inlineStr"/>
       <c r="X273" s="8" t="inlineStr"/>
       <c r="Y273" s="9" t="n">
-        <v>46186.23724717589</v>
+        <v>46186.27264115906</v>
       </c>
       <c r="Z273" s="8" t="inlineStr"/>
     </row>
@@ -17631,7 +17839,7 @@
       <c r="W274" s="4" t="inlineStr"/>
       <c r="X274" s="4" t="inlineStr"/>
       <c r="Y274" s="5" t="n">
-        <v>46186.23724717611</v>
+        <v>46186.2726411597</v>
       </c>
       <c r="Z274" s="4" t="inlineStr"/>
     </row>
@@ -17699,7 +17907,7 @@
       <c r="W275" s="4" t="inlineStr"/>
       <c r="X275" s="4" t="inlineStr"/>
       <c r="Y275" s="5" t="n">
-        <v>46186.23724717629</v>
+        <v>46186.27264116001</v>
       </c>
       <c r="Z275" s="4" t="inlineStr"/>
     </row>
@@ -17767,7 +17975,7 @@
       <c r="W276" s="4" t="inlineStr"/>
       <c r="X276" s="4" t="inlineStr"/>
       <c r="Y276" s="5" t="n">
-        <v>46186.23724717647</v>
+        <v>46186.27264116023</v>
       </c>
       <c r="Z276" s="4" t="inlineStr"/>
     </row>
@@ -17781,7 +17989,11 @@
       <c r="C277" s="5" t="n">
         <v>46183</v>
       </c>
-      <c r="D277" s="4" t="inlineStr"/>
+      <c r="D277" s="4" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE06.STR.S9</t>
+        </is>
+      </c>
       <c r="E277" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Elevated Station BG36 - Structure- Chiller Yard: DE.ELS.GE06.STR.S9.D3_Rev.C01</t>
@@ -17823,7 +18035,7 @@
       <c r="W277" s="4" t="inlineStr"/>
       <c r="X277" s="4" t="inlineStr"/>
       <c r="Y277" s="5" t="n">
-        <v>46186.23724717662</v>
+        <v>46186.27264116044</v>
       </c>
       <c r="Z277" s="4" t="inlineStr"/>
     </row>
@@ -17891,7 +18103,7 @@
       <c r="W278" s="4" t="inlineStr"/>
       <c r="X278" s="4" t="inlineStr"/>
       <c r="Y278" s="5" t="n">
-        <v>46186.23724717736</v>
+        <v>46186.27264116063</v>
       </c>
       <c r="Z278" s="4" t="inlineStr"/>
     </row>
@@ -17963,7 +18175,7 @@
       <c r="W279" s="4" t="inlineStr"/>
       <c r="X279" s="4" t="inlineStr"/>
       <c r="Y279" s="5" t="n">
-        <v>46186.23724717766</v>
+        <v>46186.27264116083</v>
       </c>
       <c r="Z279" s="4" t="inlineStr"/>
     </row>
@@ -18035,7 +18247,7 @@
       <c r="W280" s="4" t="inlineStr"/>
       <c r="X280" s="4" t="inlineStr"/>
       <c r="Y280" s="5" t="n">
-        <v>46186.23724717788</v>
+        <v>46186.27264116102</v>
       </c>
       <c r="Z280" s="4" t="inlineStr"/>
     </row>
@@ -18103,7 +18315,7 @@
       <c r="W281" s="4" t="inlineStr"/>
       <c r="X281" s="4" t="inlineStr"/>
       <c r="Y281" s="5" t="n">
-        <v>46186.23724717809</v>
+        <v>46186.27264116122</v>
       </c>
       <c r="Z281" s="4" t="inlineStr"/>
     </row>
@@ -18117,7 +18329,11 @@
       <c r="C282" s="5" t="n">
         <v>46183</v>
       </c>
-      <c r="D282" s="4" t="inlineStr"/>
+      <c r="D282" s="4" t="inlineStr">
+        <is>
+          <t>DE.ANX.AX08.ARC.A0</t>
+        </is>
+      </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP1 - Annex BL-EES16 - Architectural: DE.ANX.AX08.ARC.A0.D1_Rev.C01</t>
@@ -18155,7 +18371,7 @@
       <c r="W282" s="4" t="inlineStr"/>
       <c r="X282" s="4" t="inlineStr"/>
       <c r="Y282" s="5" t="n">
-        <v>46186.23724717827</v>
+        <v>46186.2726411614</v>
       </c>
       <c r="Z282" s="4" t="inlineStr"/>
     </row>
@@ -18211,7 +18427,7 @@
       <c r="W283" s="4" t="inlineStr"/>
       <c r="X283" s="4" t="inlineStr"/>
       <c r="Y283" s="5" t="n">
-        <v>46186.23724717844</v>
+        <v>46186.27264116161</v>
       </c>
       <c r="Z283" s="4" t="inlineStr"/>
     </row>
@@ -18279,7 +18495,7 @@
       <c r="W284" s="4" t="inlineStr"/>
       <c r="X284" s="4" t="inlineStr"/>
       <c r="Y284" s="5" t="n">
-        <v>46186.23724717864</v>
+        <v>46186.27264116182</v>
       </c>
       <c r="Z284" s="4" t="inlineStr"/>
     </row>
@@ -18347,7 +18563,7 @@
       <c r="W285" s="4" t="inlineStr"/>
       <c r="X285" s="4" t="inlineStr"/>
       <c r="Y285" s="5" t="n">
-        <v>46186.23724717923</v>
+        <v>46186.27264116199</v>
       </c>
       <c r="Z285" s="4" t="inlineStr"/>
     </row>
@@ -18419,7 +18635,7 @@
       <c r="W286" s="4" t="inlineStr"/>
       <c r="X286" s="4" t="inlineStr"/>
       <c r="Y286" s="5" t="n">
-        <v>46186.23724717949</v>
+        <v>46186.27264116218</v>
       </c>
       <c r="Z286" s="4" t="inlineStr"/>
     </row>
@@ -18487,7 +18703,7 @@
       <c r="W287" s="4" t="inlineStr"/>
       <c r="X287" s="4" t="inlineStr"/>
       <c r="Y287" s="5" t="n">
-        <v>46186.23724717978</v>
+        <v>46186.27264116242</v>
       </c>
       <c r="Z287" s="4" t="inlineStr"/>
     </row>
@@ -18555,7 +18771,7 @@
       <c r="W288" s="4" t="inlineStr"/>
       <c r="X288" s="4" t="inlineStr"/>
       <c r="Y288" s="5" t="n">
-        <v>46186.23724718</v>
+        <v>46186.27264116264</v>
       </c>
       <c r="Z288" s="4" t="inlineStr"/>
     </row>
@@ -18619,7 +18835,7 @@
       <c r="W289" s="8" t="inlineStr"/>
       <c r="X289" s="8" t="inlineStr"/>
       <c r="Y289" s="9" t="n">
-        <v>46186.23724718019</v>
+        <v>46186.27264116282</v>
       </c>
       <c r="Z289" s="8" t="inlineStr"/>
     </row>
@@ -18683,7 +18899,7 @@
       <c r="W290" s="8" t="inlineStr"/>
       <c r="X290" s="8" t="inlineStr"/>
       <c r="Y290" s="9" t="n">
-        <v>46186.23724718045</v>
+        <v>46186.27264116309</v>
       </c>
       <c r="Z290" s="8" t="inlineStr"/>
     </row>
@@ -18747,7 +18963,7 @@
       <c r="W291" s="8" t="inlineStr"/>
       <c r="X291" s="8" t="inlineStr"/>
       <c r="Y291" s="9" t="n">
-        <v>46186.23724718064</v>
+        <v>46186.27264116329</v>
       </c>
       <c r="Z291" s="8" t="inlineStr"/>
     </row>
@@ -18761,7 +18977,11 @@
       <c r="C292" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D292" s="8" t="inlineStr"/>
+      <c r="D292" s="8" t="inlineStr">
+        <is>
+          <t>DE.ANX.AX14.STR.S0</t>
+        </is>
+      </c>
       <c r="E292" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP1 - Annex Structure - BL-EES05 Structure Structure Design : DE.ANX.AX14.STR.S0.D1_Rev.C01</t>
@@ -18799,7 +19019,7 @@
       <c r="W292" s="8" t="inlineStr"/>
       <c r="X292" s="8" t="inlineStr"/>
       <c r="Y292" s="9" t="n">
-        <v>46186.23724718082</v>
+        <v>46186.27264116349</v>
       </c>
       <c r="Z292" s="8" t="inlineStr"/>
     </row>
@@ -18813,7 +19033,11 @@
       <c r="C293" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D293" s="8" t="inlineStr"/>
+      <c r="D293" s="8" t="inlineStr">
+        <is>
+          <t>DE.TNL.CC02.STR.T2.D3</t>
+        </is>
+      </c>
       <c r="E293" s="10" t="inlineStr">
         <is>
           <t>Re: Design Drawing Submission - DCP3 - Cut &amp; Cover BB05 Slabs - (DE.TNL.CC02.STR.T2.D3) - Rev.C01</t>
@@ -18847,7 +19071,7 @@
       <c r="W293" s="8" t="inlineStr"/>
       <c r="X293" s="8" t="inlineStr"/>
       <c r="Y293" s="9" t="n">
-        <v>46186.23724718099</v>
+        <v>46186.27264116369</v>
       </c>
       <c r="Z293" s="8" t="inlineStr"/>
     </row>
@@ -18861,7 +19085,11 @@
       <c r="C294" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D294" s="8" t="inlineStr"/>
+      <c r="D294" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST02.STR.V2</t>
+        </is>
+      </c>
       <c r="E294" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Stretch 02 - Viaduct Structure Bearing Schedule BC-3SP-72-02 : DE.VDT.ST02.STR.V2.D3_Rev.C01</t>
@@ -18899,7 +19127,7 @@
       <c r="W294" s="8" t="inlineStr"/>
       <c r="X294" s="8" t="inlineStr"/>
       <c r="Y294" s="9" t="n">
-        <v>46186.23724718117</v>
+        <v>46186.27264116389</v>
       </c>
       <c r="Z294" s="8" t="inlineStr"/>
     </row>
@@ -18913,7 +19141,11 @@
       <c r="C295" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D295" s="8" t="inlineStr"/>
+      <c r="D295" s="8" t="inlineStr">
+        <is>
+          <t>DE.ANX.AX15.STR.S1</t>
+        </is>
+      </c>
       <c r="E295" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Annex Structure - BL-EES06 Structure Slabs : DE.ANX.AX15.STR.S1.D3_Rev.C01</t>
@@ -18951,7 +19183,7 @@
       <c r="W295" s="8" t="inlineStr"/>
       <c r="X295" s="8" t="inlineStr"/>
       <c r="Y295" s="9" t="n">
-        <v>46186.23724718132</v>
+        <v>46186.27264116478</v>
       </c>
       <c r="Z295" s="8" t="inlineStr"/>
     </row>
@@ -18965,7 +19197,11 @@
       <c r="C296" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D296" s="8" t="inlineStr"/>
+      <c r="D296" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST05.STR.V1</t>
+        </is>
+      </c>
       <c r="E296" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Viaduct Structure Foundation &amp; Substructure-STRETCH 5.1-BC-3SP-72-07 : DE.VDT.ST05.STR.V1.D3_Rev.C03</t>
@@ -19003,7 +19239,7 @@
       <c r="W296" s="8" t="inlineStr"/>
       <c r="X296" s="8" t="inlineStr"/>
       <c r="Y296" s="9" t="n">
-        <v>46186.23724718147</v>
+        <v>46186.27264116506</v>
       </c>
       <c r="Z296" s="8" t="inlineStr"/>
     </row>
@@ -19067,7 +19303,7 @@
       <c r="W297" s="8" t="inlineStr"/>
       <c r="X297" s="8" t="inlineStr"/>
       <c r="Y297" s="9" t="n">
-        <v>46186.23724718168</v>
+        <v>46186.27264116529</v>
       </c>
       <c r="Z297" s="8" t="inlineStr"/>
     </row>
@@ -19131,7 +19367,7 @@
       <c r="W298" s="8" t="inlineStr"/>
       <c r="X298" s="8" t="inlineStr"/>
       <c r="Y298" s="9" t="n">
-        <v>46186.23724718191</v>
+        <v>46186.27264116552</v>
       </c>
       <c r="Z298" s="8" t="inlineStr"/>
     </row>
@@ -19195,7 +19431,7 @@
       <c r="W299" s="8" t="inlineStr"/>
       <c r="X299" s="8" t="inlineStr"/>
       <c r="Y299" s="9" t="n">
-        <v>46186.23724718211</v>
+        <v>46186.27264116574</v>
       </c>
       <c r="Z299" s="8" t="inlineStr"/>
     </row>
@@ -19259,7 +19495,7 @@
       <c r="W300" s="8" t="inlineStr"/>
       <c r="X300" s="8" t="inlineStr"/>
       <c r="Y300" s="9" t="n">
-        <v>46186.2372471823</v>
+        <v>46186.27264116594</v>
       </c>
       <c r="Z300" s="8" t="inlineStr"/>
     </row>
@@ -19273,7 +19509,11 @@
       <c r="C301" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D301" s="8" t="inlineStr"/>
+      <c r="D301" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE00.STR.S1</t>
+        </is>
+      </c>
       <c r="E301" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BG31 - Structural - BL Technical Level (Precast M-Girder) - DE.ELS.GE00.STR.S1.D3_Rev C01</t>
@@ -19311,7 +19551,7 @@
       <c r="W301" s="8" t="inlineStr"/>
       <c r="X301" s="8" t="inlineStr"/>
       <c r="Y301" s="9" t="n">
-        <v>46186.23724718248</v>
+        <v>46186.27264116616</v>
       </c>
       <c r="Z301" s="8" t="inlineStr"/>
     </row>
@@ -19325,7 +19565,11 @@
       <c r="C302" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D302" s="8" t="inlineStr"/>
+      <c r="D302" s="8" t="inlineStr">
+        <is>
+          <t>DE.UGS.RE01.STR.S5</t>
+        </is>
+      </c>
       <c r="E302" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BR09 - Structure Base Slab : DE.UGS.RE01.STR.S5.D3_Rev.C01</t>
@@ -19363,7 +19607,7 @@
       <c r="W302" s="8" t="inlineStr"/>
       <c r="X302" s="8" t="inlineStr"/>
       <c r="Y302" s="9" t="n">
-        <v>46186.23724718262</v>
+        <v>46186.27264116635</v>
       </c>
       <c r="Z302" s="8" t="inlineStr"/>
     </row>
@@ -19377,7 +19621,11 @@
       <c r="C303" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D303" s="8" t="inlineStr"/>
+      <c r="D303" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST03.STR.V2</t>
+        </is>
+      </c>
       <c r="E303" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Stretch 03 Viaduct Structure Pierhead-Stretch 03-BC-3SP-72-04: DE.VDT.ST03.STR.V2.D3_Rev.C02</t>
@@ -19415,7 +19663,7 @@
       <c r="W303" s="8" t="inlineStr"/>
       <c r="X303" s="8" t="inlineStr"/>
       <c r="Y303" s="9" t="n">
-        <v>46186.23724718279</v>
+        <v>46186.27264116696</v>
       </c>
       <c r="Z303" s="8" t="inlineStr"/>
     </row>
@@ -19483,7 +19731,7 @@
       <c r="W304" s="8" t="inlineStr"/>
       <c r="X304" s="8" t="inlineStr"/>
       <c r="Y304" s="9" t="n">
-        <v>46186.23724718302</v>
+        <v>46186.27264116726</v>
       </c>
       <c r="Z304" s="8" t="inlineStr"/>
     </row>
@@ -19551,7 +19799,7 @@
       <c r="W305" s="8" t="inlineStr"/>
       <c r="X305" s="8" t="inlineStr"/>
       <c r="Y305" s="9" t="n">
-        <v>46186.23724718325</v>
+        <v>46186.2726411675</v>
       </c>
       <c r="Z305" s="8" t="inlineStr"/>
     </row>
@@ -19619,7 +19867,7 @@
       <c r="W306" s="8" t="inlineStr"/>
       <c r="X306" s="8" t="inlineStr"/>
       <c r="Y306" s="9" t="n">
-        <v>46186.23724718345</v>
+        <v>46186.27264116771</v>
       </c>
       <c r="Z306" s="8" t="inlineStr"/>
     </row>
@@ -19687,7 +19935,7 @@
       <c r="W307" s="8" t="inlineStr"/>
       <c r="X307" s="8" t="inlineStr"/>
       <c r="Y307" s="9" t="n">
-        <v>46186.23724718413</v>
+        <v>46186.27264116792</v>
       </c>
       <c r="Z307" s="8" t="inlineStr"/>
     </row>
@@ -19755,7 +20003,7 @@
       <c r="W308" s="8" t="inlineStr"/>
       <c r="X308" s="8" t="inlineStr"/>
       <c r="Y308" s="9" t="n">
-        <v>46186.23724718438</v>
+        <v>46186.27264116812</v>
       </c>
       <c r="Z308" s="8" t="inlineStr"/>
     </row>
@@ -19819,7 +20067,7 @@
       <c r="W309" s="8" t="inlineStr"/>
       <c r="X309" s="8" t="inlineStr"/>
       <c r="Y309" s="9" t="n">
-        <v>46186.2372471846</v>
+        <v>46186.27264116833</v>
       </c>
       <c r="Z309" s="8" t="inlineStr"/>
     </row>
@@ -19833,7 +20081,11 @@
       <c r="C310" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D310" s="8" t="inlineStr"/>
+      <c r="D310" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.GN00.STR.01</t>
+        </is>
+      </c>
       <c r="E310" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3  - Global - Viaduct Structure ISO PKG-2 : DE.VDT.GN00.STR.01.D3_Rev.C03</t>
@@ -19871,7 +20123,7 @@
       <c r="W310" s="8" t="inlineStr"/>
       <c r="X310" s="8" t="inlineStr"/>
       <c r="Y310" s="9" t="n">
-        <v>46186.23724718485</v>
+        <v>46186.27264116852</v>
       </c>
       <c r="Z310" s="8" t="inlineStr"/>
     </row>
@@ -19885,7 +20137,11 @@
       <c r="C311" s="9" t="n">
         <v>46183</v>
       </c>
-      <c r="D311" s="8" t="inlineStr"/>
+      <c r="D311" s="8" t="inlineStr">
+        <is>
+          <t>DE.UGS.RE01.MEP.M3</t>
+        </is>
+      </c>
       <c r="E311" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 – Underground Station – BR09 Fire Protection System : DE.UGS.RE01.MEP.M3.D2_Rev.C01 (RCS Submission)</t>
@@ -19923,7 +20179,7 @@
       <c r="W311" s="8" t="inlineStr"/>
       <c r="X311" s="8" t="inlineStr"/>
       <c r="Y311" s="9" t="n">
-        <v>46186.23724718506</v>
+        <v>46186.27264116876</v>
       </c>
       <c r="Z311" s="8" t="inlineStr"/>
     </row>
@@ -19991,7 +20247,7 @@
       <c r="W312" s="4" t="inlineStr"/>
       <c r="X312" s="4" t="inlineStr"/>
       <c r="Y312" s="5" t="n">
-        <v>46186.23724718529</v>
+        <v>46186.27264116898</v>
       </c>
       <c r="Z312" s="4" t="inlineStr"/>
     </row>
@@ -20059,7 +20315,7 @@
       <c r="W313" s="4" t="inlineStr"/>
       <c r="X313" s="4" t="inlineStr"/>
       <c r="Y313" s="5" t="n">
-        <v>46186.23724718556</v>
+        <v>46186.27264116923</v>
       </c>
       <c r="Z313" s="4" t="inlineStr"/>
     </row>
@@ -20073,7 +20329,11 @@
       <c r="C314" s="5" t="n">
         <v>46183</v>
       </c>
-      <c r="D314" s="4" t="inlineStr"/>
+      <c r="D314" s="4" t="inlineStr">
+        <is>
+          <t>DE.ANX.AX10.STR.S0</t>
+        </is>
+      </c>
       <c r="E314" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP2 - Annex Structure - BL-EES01 Structure - S0703 : DE.ANX.AX10.STR.S0.D2_Rev.C01</t>
@@ -20115,7 +20375,7 @@
       <c r="W314" s="4" t="inlineStr"/>
       <c r="X314" s="4" t="inlineStr"/>
       <c r="Y314" s="5" t="n">
-        <v>46186.23724718572</v>
+        <v>46186.27264116941</v>
       </c>
       <c r="Z314" s="4" t="inlineStr"/>
     </row>
@@ -20183,7 +20443,7 @@
       <c r="W315" s="8" t="inlineStr"/>
       <c r="X315" s="8" t="inlineStr"/>
       <c r="Y315" s="9" t="n">
-        <v>46186.23724718638</v>
+        <v>46186.27264116961</v>
       </c>
       <c r="Z315" s="8" t="inlineStr"/>
     </row>
@@ -20251,7 +20511,7 @@
       <c r="W316" s="12" t="inlineStr"/>
       <c r="X316" s="12" t="inlineStr"/>
       <c r="Y316" s="13" t="n">
-        <v>46186.23724718667</v>
+        <v>46186.27264116979</v>
       </c>
       <c r="Z316" s="12" t="inlineStr">
         <is>
@@ -20319,7 +20579,7 @@
       <c r="W317" s="8" t="inlineStr"/>
       <c r="X317" s="8" t="inlineStr"/>
       <c r="Y317" s="9" t="n">
-        <v>46186.23724718691</v>
+        <v>46186.27264117002</v>
       </c>
       <c r="Z317" s="8" t="inlineStr"/>
     </row>
@@ -20387,7 +20647,7 @@
       <c r="W318" s="4" t="inlineStr"/>
       <c r="X318" s="4" t="inlineStr"/>
       <c r="Y318" s="5" t="n">
-        <v>46186.23724718716</v>
+        <v>46186.27264117025</v>
       </c>
       <c r="Z318" s="4" t="inlineStr"/>
     </row>
@@ -20455,7 +20715,7 @@
       <c r="W319" s="4" t="inlineStr"/>
       <c r="X319" s="4" t="inlineStr"/>
       <c r="Y319" s="5" t="n">
-        <v>46186.23724718738</v>
+        <v>46186.27264117046</v>
       </c>
       <c r="Z319" s="4" t="inlineStr"/>
     </row>
@@ -20527,7 +20787,7 @@
       <c r="W320" s="4" t="inlineStr"/>
       <c r="X320" s="4" t="inlineStr"/>
       <c r="Y320" s="5" t="n">
-        <v>46186.2372471876</v>
+        <v>46186.27264117067</v>
       </c>
       <c r="Z320" s="4" t="inlineStr"/>
     </row>
@@ -20595,7 +20855,7 @@
       <c r="W321" s="4" t="inlineStr"/>
       <c r="X321" s="4" t="inlineStr"/>
       <c r="Y321" s="5" t="n">
-        <v>46186.23724718781</v>
+        <v>46186.27264117123</v>
       </c>
       <c r="Z321" s="4" t="inlineStr"/>
     </row>
@@ -20667,7 +20927,7 @@
       <c r="W322" s="4" t="inlineStr"/>
       <c r="X322" s="4" t="inlineStr"/>
       <c r="Y322" s="5" t="n">
-        <v>46186.23724718842</v>
+        <v>46186.27264117158</v>
       </c>
       <c r="Z322" s="4" t="inlineStr"/>
     </row>
@@ -20735,7 +20995,7 @@
       <c r="W323" s="4" t="inlineStr"/>
       <c r="X323" s="4" t="inlineStr"/>
       <c r="Y323" s="5" t="n">
-        <v>46186.23724718879</v>
+        <v>46186.27264117186</v>
       </c>
       <c r="Z323" s="4" t="inlineStr"/>
     </row>
@@ -20803,7 +21063,7 @@
       <c r="W324" s="4" t="inlineStr"/>
       <c r="X324" s="4" t="inlineStr"/>
       <c r="Y324" s="5" t="n">
-        <v>46186.23724718904</v>
+        <v>46186.27264117209</v>
       </c>
       <c r="Z324" s="4" t="inlineStr"/>
     </row>
@@ -20871,7 +21131,7 @@
       <c r="W325" s="4" t="inlineStr"/>
       <c r="X325" s="4" t="inlineStr"/>
       <c r="Y325" s="5" t="n">
-        <v>46186.23724718926</v>
+        <v>46186.27264117228</v>
       </c>
       <c r="Z325" s="4" t="inlineStr"/>
     </row>
@@ -20885,7 +21145,11 @@
       <c r="C326" s="5" t="n">
         <v>46182</v>
       </c>
-      <c r="D326" s="4" t="inlineStr"/>
+      <c r="D326" s="4" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE03.STR.S1</t>
+        </is>
+      </c>
       <c r="E326" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BG34 - Structure – (Concourse above pier and Transverse Beam) : DE.ELS.GE03.STR.S1.D3_Rev.C03 (RCS Resubmission)</t>
@@ -20927,7 +21191,7 @@
       <c r="W326" s="4" t="inlineStr"/>
       <c r="X326" s="4" t="inlineStr"/>
       <c r="Y326" s="5" t="n">
-        <v>46186.23724718947</v>
+        <v>46186.27264117255</v>
       </c>
       <c r="Z326" s="4" t="inlineStr"/>
     </row>
@@ -20991,7 +21255,7 @@
       <c r="W327" s="8" t="inlineStr"/>
       <c r="X327" s="8" t="inlineStr"/>
       <c r="Y327" s="9" t="n">
-        <v>46186.23724718971</v>
+        <v>46186.27264117278</v>
       </c>
       <c r="Z327" s="8" t="inlineStr"/>
     </row>
@@ -21059,7 +21323,7 @@
       <c r="W328" s="8" t="inlineStr"/>
       <c r="X328" s="8" t="inlineStr"/>
       <c r="Y328" s="9" t="n">
-        <v>46186.23724718992</v>
+        <v>46186.27264117299</v>
       </c>
       <c r="Z328" s="8" t="inlineStr"/>
     </row>
@@ -21127,7 +21391,7 @@
       <c r="W329" s="8" t="inlineStr"/>
       <c r="X329" s="8" t="inlineStr"/>
       <c r="Y329" s="9" t="n">
-        <v>46186.23724719015</v>
+        <v>46186.27264117321</v>
       </c>
       <c r="Z329" s="8" t="inlineStr"/>
     </row>
@@ -21191,7 +21455,7 @@
       <c r="W330" s="8" t="inlineStr"/>
       <c r="X330" s="8" t="inlineStr"/>
       <c r="Y330" s="9" t="n">
-        <v>46186.23724719069</v>
+        <v>46186.27264117343</v>
       </c>
       <c r="Z330" s="8" t="inlineStr"/>
     </row>
@@ -21259,7 +21523,7 @@
       <c r="W331" s="8" t="inlineStr"/>
       <c r="X331" s="8" t="inlineStr"/>
       <c r="Y331" s="9" t="n">
-        <v>46186.23724719101</v>
+        <v>46186.27264117405</v>
       </c>
       <c r="Z331" s="8" t="inlineStr"/>
     </row>
@@ -21327,7 +21591,7 @@
       <c r="W332" s="8" t="inlineStr"/>
       <c r="X332" s="8" t="inlineStr"/>
       <c r="Y332" s="9" t="n">
-        <v>46186.23724719125</v>
+        <v>46186.27264117434</v>
       </c>
       <c r="Z332" s="8" t="inlineStr"/>
     </row>
@@ -21391,7 +21655,7 @@
       <c r="W333" s="8" t="inlineStr"/>
       <c r="X333" s="8" t="inlineStr"/>
       <c r="Y333" s="9" t="n">
-        <v>46186.23724719146</v>
+        <v>46186.27264117456</v>
       </c>
       <c r="Z333" s="8" t="inlineStr"/>
     </row>
@@ -21459,7 +21723,7 @@
       <c r="W334" s="8" t="inlineStr"/>
       <c r="X334" s="8" t="inlineStr"/>
       <c r="Y334" s="9" t="n">
-        <v>46186.23724719168</v>
+        <v>46186.2726411748</v>
       </c>
       <c r="Z334" s="8" t="inlineStr"/>
     </row>
@@ -21527,7 +21791,7 @@
       <c r="W335" s="4" t="inlineStr"/>
       <c r="X335" s="4" t="inlineStr"/>
       <c r="Y335" s="5" t="n">
-        <v>46186.23724719233</v>
+        <v>46186.27264117501</v>
       </c>
       <c r="Z335" s="4" t="inlineStr"/>
     </row>
@@ -21591,7 +21855,7 @@
       <c r="W336" s="8" t="inlineStr"/>
       <c r="X336" s="8" t="inlineStr"/>
       <c r="Y336" s="9" t="n">
-        <v>46186.23724719261</v>
+        <v>46186.27264117523</v>
       </c>
       <c r="Z336" s="8" t="inlineStr"/>
     </row>
@@ -21659,7 +21923,7 @@
       <c r="W337" s="4" t="inlineStr"/>
       <c r="X337" s="4" t="inlineStr"/>
       <c r="Y337" s="5" t="n">
-        <v>46186.23724719284</v>
+        <v>46186.27264117543</v>
       </c>
       <c r="Z337" s="4" t="inlineStr"/>
     </row>
@@ -21723,7 +21987,7 @@
       <c r="W338" s="8" t="inlineStr"/>
       <c r="X338" s="8" t="inlineStr"/>
       <c r="Y338" s="9" t="n">
-        <v>46186.23724719304</v>
+        <v>46186.27264117562</v>
       </c>
       <c r="Z338" s="8" t="inlineStr"/>
     </row>
@@ -21787,7 +22051,7 @@
       <c r="W339" s="8" t="inlineStr"/>
       <c r="X339" s="8" t="inlineStr"/>
       <c r="Y339" s="9" t="n">
-        <v>46186.23724719324</v>
+        <v>46186.27264117613</v>
       </c>
       <c r="Z339" s="8" t="inlineStr"/>
     </row>
@@ -21855,7 +22119,7 @@
       <c r="W340" s="4" t="inlineStr"/>
       <c r="X340" s="4" t="inlineStr"/>
       <c r="Y340" s="5" t="n">
-        <v>46186.23724719345</v>
+        <v>46186.2726411764</v>
       </c>
       <c r="Z340" s="4" t="inlineStr"/>
     </row>
@@ -21923,7 +22187,7 @@
       <c r="W341" s="4" t="inlineStr"/>
       <c r="X341" s="4" t="inlineStr"/>
       <c r="Y341" s="5" t="n">
-        <v>46186.23724719369</v>
+        <v>46186.27264117666</v>
       </c>
       <c r="Z341" s="4" t="inlineStr"/>
     </row>
@@ -21937,7 +22201,11 @@
       <c r="C342" s="5" t="n">
         <v>46182</v>
       </c>
-      <c r="D342" s="4" t="inlineStr"/>
+      <c r="D342" s="4" t="inlineStr">
+        <is>
+          <t>DE.EEP.EEP2.STR.S0</t>
+        </is>
+      </c>
       <c r="E342" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP2 - Emergency Egress Point-EEP2-STR: DE.EEP.EEP2.STR.S0.D2_Rev.C01</t>
@@ -21979,7 +22247,7 @@
       <c r="W342" s="4" t="inlineStr"/>
       <c r="X342" s="4" t="inlineStr"/>
       <c r="Y342" s="5" t="n">
-        <v>46186.23724719387</v>
+        <v>46186.27264117686</v>
       </c>
       <c r="Z342" s="4" t="inlineStr"/>
     </row>
@@ -22043,7 +22311,7 @@
       <c r="W343" s="8" t="inlineStr"/>
       <c r="X343" s="8" t="inlineStr"/>
       <c r="Y343" s="9" t="n">
-        <v>46186.23724719408</v>
+        <v>46186.27264117707</v>
       </c>
       <c r="Z343" s="8" t="inlineStr"/>
     </row>
@@ -22115,7 +22383,7 @@
       <c r="W344" s="4" t="inlineStr"/>
       <c r="X344" s="4" t="inlineStr"/>
       <c r="Y344" s="5" t="n">
-        <v>46186.23724719429</v>
+        <v>46186.27264117727</v>
       </c>
       <c r="Z344" s="4" t="inlineStr"/>
     </row>
@@ -22129,7 +22397,11 @@
       <c r="C345" s="5" t="n">
         <v>46182</v>
       </c>
-      <c r="D345" s="4" t="inlineStr"/>
+      <c r="D345" s="4" t="inlineStr">
+        <is>
+          <t>DE.UGS.SB01.STR.S7</t>
+        </is>
+      </c>
       <c r="E345" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Switchbox Base Slab (Remaining Area) : DE.UGS.SB01.STR.S7.D3_Rev.C04</t>
@@ -22171,7 +22443,7 @@
       <c r="W345" s="4" t="inlineStr"/>
       <c r="X345" s="4" t="inlineStr"/>
       <c r="Y345" s="5" t="n">
-        <v>46186.23724719447</v>
+        <v>46186.27264117748</v>
       </c>
       <c r="Z345" s="4" t="inlineStr"/>
     </row>
@@ -22243,7 +22515,7 @@
       <c r="W346" s="4" t="inlineStr"/>
       <c r="X346" s="4" t="inlineStr"/>
       <c r="Y346" s="5" t="n">
-        <v>46186.23724719467</v>
+        <v>46186.27264117767</v>
       </c>
       <c r="Z346" s="4" t="inlineStr"/>
     </row>
@@ -22311,7 +22583,7 @@
       <c r="W347" s="8" t="inlineStr"/>
       <c r="X347" s="8" t="inlineStr"/>
       <c r="Y347" s="9" t="n">
-        <v>46186.23724719486</v>
+        <v>46186.27264117787</v>
       </c>
       <c r="Z347" s="8" t="inlineStr"/>
     </row>
@@ -22379,7 +22651,7 @@
       <c r="W348" s="4" t="inlineStr"/>
       <c r="X348" s="4" t="inlineStr"/>
       <c r="Y348" s="5" t="n">
-        <v>46186.23724719508</v>
+        <v>46186.27264117809</v>
       </c>
       <c r="Z348" s="4" t="inlineStr"/>
     </row>
@@ -22447,7 +22719,7 @@
       <c r="W349" s="4" t="inlineStr"/>
       <c r="X349" s="4" t="inlineStr"/>
       <c r="Y349" s="5" t="n">
-        <v>46186.23724719528</v>
+        <v>46186.27264117829</v>
       </c>
       <c r="Z349" s="4" t="inlineStr"/>
     </row>
@@ -22461,7 +22733,11 @@
       <c r="C350" s="5" t="n">
         <v>46182</v>
       </c>
-      <c r="D350" s="4" t="inlineStr"/>
+      <c r="D350" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST51.STR.V3</t>
+        </is>
+      </c>
       <c r="E350" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Stretch-05.1 - Viaduct Structure Superstructure 2SP Spans : DE.VDT.ST51.STR.V3.D3_Rev.C01</t>
@@ -22503,7 +22779,7 @@
       <c r="W350" s="4" t="inlineStr"/>
       <c r="X350" s="4" t="inlineStr"/>
       <c r="Y350" s="5" t="n">
-        <v>46186.23724719544</v>
+        <v>46186.27264117848</v>
       </c>
       <c r="Z350" s="4" t="inlineStr"/>
     </row>
@@ -22517,7 +22793,11 @@
       <c r="C351" s="9" t="n">
         <v>46182</v>
       </c>
-      <c r="D351" s="8" t="inlineStr"/>
+      <c r="D351" s="8" t="inlineStr">
+        <is>
+          <t>DE.DPT.OCCA.ARC.A0</t>
+        </is>
+      </c>
       <c r="E351" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Depot BDR08 OCC and Administration Building - Architecture: DE.DPT.OCCA.ARC.A0.D2_Rev.C01</t>
@@ -22555,7 +22835,7 @@
       <c r="W351" s="8" t="inlineStr"/>
       <c r="X351" s="8" t="inlineStr"/>
       <c r="Y351" s="9" t="n">
-        <v>46186.23724719561</v>
+        <v>46186.27264117869</v>
       </c>
       <c r="Z351" s="8" t="inlineStr"/>
     </row>
@@ -22569,7 +22849,11 @@
       <c r="C352" s="5" t="n">
         <v>46182</v>
       </c>
-      <c r="D352" s="4" t="inlineStr"/>
+      <c r="D352" s="4" t="inlineStr">
+        <is>
+          <t>DE.UGS.RE03.STR.S3</t>
+        </is>
+      </c>
       <c r="E352" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BR07 - Structure - Concourse Slab Submission -: DE.UGS.RE03.STR.S3.D3_Rev.C04 (Partial Submission)</t>
@@ -22611,7 +22895,7 @@
       <c r="W352" s="4" t="inlineStr"/>
       <c r="X352" s="4" t="inlineStr"/>
       <c r="Y352" s="5" t="n">
-        <v>46186.23724719578</v>
+        <v>46186.27264117889</v>
       </c>
       <c r="Z352" s="4" t="inlineStr"/>
     </row>
@@ -22679,7 +22963,7 @@
       <c r="W353" s="4" t="inlineStr"/>
       <c r="X353" s="4" t="inlineStr"/>
       <c r="Y353" s="5" t="n">
-        <v>46186.23724719595</v>
+        <v>46186.27264117907</v>
       </c>
       <c r="Z353" s="4" t="inlineStr"/>
     </row>
@@ -22735,7 +23019,7 @@
       <c r="W354" s="4" t="inlineStr"/>
       <c r="X354" s="4" t="inlineStr"/>
       <c r="Y354" s="5" t="n">
-        <v>46186.2372471961</v>
+        <v>46186.27264117925</v>
       </c>
       <c r="Z354" s="4" t="inlineStr"/>
     </row>
@@ -22787,7 +23071,7 @@
       <c r="W355" s="8" t="inlineStr"/>
       <c r="X355" s="8" t="inlineStr"/>
       <c r="Y355" s="9" t="n">
-        <v>46186.23724719633</v>
+        <v>46186.27264117946</v>
       </c>
       <c r="Z355" s="8" t="inlineStr"/>
     </row>
@@ -22855,7 +23139,7 @@
       <c r="W356" s="4" t="inlineStr"/>
       <c r="X356" s="4" t="inlineStr"/>
       <c r="Y356" s="5" t="n">
-        <v>46186.23724719654</v>
+        <v>46186.27264117966</v>
       </c>
       <c r="Z356" s="4" t="inlineStr"/>
     </row>
@@ -22907,7 +23191,7 @@
       <c r="W357" s="8" t="inlineStr"/>
       <c r="X357" s="8" t="inlineStr"/>
       <c r="Y357" s="9" t="n">
-        <v>46186.23724719671</v>
+        <v>46186.27264117986</v>
       </c>
       <c r="Z357" s="8" t="inlineStr"/>
     </row>
@@ -22975,7 +23259,7 @@
       <c r="W358" s="8" t="inlineStr"/>
       <c r="X358" s="8" t="inlineStr"/>
       <c r="Y358" s="9" t="n">
-        <v>46186.23724719694</v>
+        <v>46186.2726411801</v>
       </c>
       <c r="Z358" s="8" t="inlineStr"/>
     </row>
@@ -23027,7 +23311,7 @@
       <c r="W359" s="8" t="inlineStr"/>
       <c r="X359" s="8" t="inlineStr"/>
       <c r="Y359" s="9" t="n">
-        <v>46186.23724719713</v>
+        <v>46186.27264118071</v>
       </c>
       <c r="Z359" s="8" t="inlineStr"/>
     </row>
@@ -23079,7 +23363,7 @@
       <c r="W360" s="8" t="inlineStr"/>
       <c r="X360" s="8" t="inlineStr"/>
       <c r="Y360" s="9" t="n">
-        <v>46186.23724719729</v>
+        <v>46186.27264118095</v>
       </c>
       <c r="Z360" s="8" t="inlineStr"/>
     </row>
@@ -23131,7 +23415,7 @@
       <c r="W361" s="8" t="inlineStr"/>
       <c r="X361" s="8" t="inlineStr"/>
       <c r="Y361" s="9" t="n">
-        <v>46186.23724719744</v>
+        <v>46186.27264118116</v>
       </c>
       <c r="Z361" s="8" t="inlineStr"/>
     </row>
@@ -23199,7 +23483,7 @@
       <c r="W362" s="8" t="inlineStr"/>
       <c r="X362" s="8" t="inlineStr"/>
       <c r="Y362" s="9" t="n">
-        <v>46186.23724719766</v>
+        <v>46186.2726411814</v>
       </c>
       <c r="Z362" s="8" t="inlineStr"/>
     </row>
@@ -23213,7 +23497,11 @@
       <c r="C363" s="9" t="n">
         <v>46182</v>
       </c>
-      <c r="D363" s="8" t="inlineStr"/>
+      <c r="D363" s="8" t="inlineStr">
+        <is>
+          <t>DE.TNL.CC01.STR.T2</t>
+        </is>
+      </c>
       <c r="E363" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Cut &amp; Cover Slabs, Struts And Waler Beam : DE.TNL.CC01.STR.T2.D3_Rev.C01</t>
@@ -23251,7 +23539,7 @@
       <c r="W363" s="8" t="inlineStr"/>
       <c r="X363" s="8" t="inlineStr"/>
       <c r="Y363" s="9" t="n">
-        <v>46186.23724719827</v>
+        <v>46186.27264118161</v>
       </c>
       <c r="Z363" s="8" t="inlineStr"/>
     </row>
@@ -23265,7 +23553,11 @@
       <c r="C364" s="9" t="n">
         <v>46182</v>
       </c>
-      <c r="D364" s="8" t="inlineStr"/>
+      <c r="D364" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST01.STR.V1</t>
+        </is>
+      </c>
       <c r="E364" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Stretch 01 - Viaduct Structure - PM19 &amp; PM20 : DE.VDT.ST01.STR.V1.D3_Rev.C01</t>
@@ -23303,7 +23595,7 @@
       <c r="W364" s="8" t="inlineStr"/>
       <c r="X364" s="8" t="inlineStr"/>
       <c r="Y364" s="9" t="n">
-        <v>46186.23724719849</v>
+        <v>46186.27264118181</v>
       </c>
       <c r="Z364" s="8" t="inlineStr"/>
     </row>
@@ -23367,7 +23659,7 @@
       <c r="W365" s="8" t="inlineStr"/>
       <c r="X365" s="8" t="inlineStr"/>
       <c r="Y365" s="9" t="n">
-        <v>46186.2372471988</v>
+        <v>46186.27264118208</v>
       </c>
       <c r="Z365" s="8" t="inlineStr"/>
     </row>
@@ -23431,7 +23723,7 @@
       <c r="W366" s="8" t="inlineStr"/>
       <c r="X366" s="8" t="inlineStr"/>
       <c r="Y366" s="9" t="n">
-        <v>46186.23724719905</v>
+        <v>46186.27264118234</v>
       </c>
       <c r="Z366" s="8" t="inlineStr"/>
     </row>
@@ -23499,7 +23791,7 @@
       <c r="W367" s="4" t="inlineStr"/>
       <c r="X367" s="4" t="inlineStr"/>
       <c r="Y367" s="5" t="n">
-        <v>46186.23724719926</v>
+        <v>46186.27264118254</v>
       </c>
       <c r="Z367" s="4" t="inlineStr"/>
     </row>
@@ -23567,7 +23859,7 @@
       <c r="W368" s="4" t="inlineStr"/>
       <c r="X368" s="4" t="inlineStr"/>
       <c r="Y368" s="5" t="n">
-        <v>46186.23724719945</v>
+        <v>46186.27264118277</v>
       </c>
       <c r="Z368" s="4" t="inlineStr"/>
     </row>
@@ -23631,7 +23923,7 @@
       <c r="W369" s="8" t="inlineStr"/>
       <c r="X369" s="8" t="inlineStr"/>
       <c r="Y369" s="9" t="n">
-        <v>46186.23724719965</v>
+        <v>46186.27264118295</v>
       </c>
       <c r="Z369" s="8" t="inlineStr"/>
     </row>
@@ -23699,7 +23991,7 @@
       <c r="W370" s="4" t="inlineStr"/>
       <c r="X370" s="4" t="inlineStr"/>
       <c r="Y370" s="5" t="n">
-        <v>46186.23724719988</v>
+        <v>46186.27264118322</v>
       </c>
       <c r="Z370" s="4" t="inlineStr"/>
     </row>
@@ -23767,7 +24059,7 @@
       <c r="W371" s="8" t="inlineStr"/>
       <c r="X371" s="8" t="inlineStr"/>
       <c r="Y371" s="9" t="n">
-        <v>46186.23724720014</v>
+        <v>46186.27264118347</v>
       </c>
       <c r="Z371" s="8" t="inlineStr"/>
     </row>
@@ -23831,7 +24123,7 @@
       <c r="W372" s="8" t="inlineStr"/>
       <c r="X372" s="8" t="inlineStr"/>
       <c r="Y372" s="9" t="n">
-        <v>46186.23724720033</v>
+        <v>46186.27264118366</v>
       </c>
       <c r="Z372" s="8" t="inlineStr"/>
     </row>
@@ -23899,7 +24191,7 @@
       <c r="W373" s="4" t="inlineStr"/>
       <c r="X373" s="4" t="inlineStr"/>
       <c r="Y373" s="5" t="n">
-        <v>46186.23724720053</v>
+        <v>46186.27264118385</v>
       </c>
       <c r="Z373" s="4" t="inlineStr"/>
     </row>
@@ -23967,7 +24259,7 @@
       <c r="W374" s="4" t="inlineStr"/>
       <c r="X374" s="4" t="inlineStr"/>
       <c r="Y374" s="5" t="n">
-        <v>46186.2372472007</v>
+        <v>46186.27264118402</v>
       </c>
       <c r="Z374" s="4" t="inlineStr"/>
     </row>
@@ -24035,7 +24327,7 @@
       <c r="W375" s="4" t="inlineStr"/>
       <c r="X375" s="4" t="inlineStr"/>
       <c r="Y375" s="5" t="n">
-        <v>46186.23724720096</v>
+        <v>46186.27264118436</v>
       </c>
       <c r="Z375" s="4" t="inlineStr"/>
     </row>
@@ -24103,7 +24395,7 @@
       <c r="W376" s="4" t="inlineStr"/>
       <c r="X376" s="4" t="inlineStr"/>
       <c r="Y376" s="5" t="n">
-        <v>46186.23724720116</v>
+        <v>46186.27264118455</v>
       </c>
       <c r="Z376" s="4" t="inlineStr"/>
     </row>
@@ -24171,7 +24463,7 @@
       <c r="W377" s="4" t="inlineStr"/>
       <c r="X377" s="4" t="inlineStr"/>
       <c r="Y377" s="5" t="n">
-        <v>46186.23724720137</v>
+        <v>46186.27264118475</v>
       </c>
       <c r="Z377" s="4" t="inlineStr"/>
     </row>
@@ -24239,7 +24531,7 @@
       <c r="W378" s="4" t="inlineStr"/>
       <c r="X378" s="4" t="inlineStr"/>
       <c r="Y378" s="5" t="n">
-        <v>46186.23724720155</v>
+        <v>46186.27264118532</v>
       </c>
       <c r="Z378" s="4" t="inlineStr"/>
     </row>
@@ -24307,7 +24599,7 @@
       <c r="W379" s="4" t="inlineStr"/>
       <c r="X379" s="4" t="inlineStr"/>
       <c r="Y379" s="5" t="n">
-        <v>46186.23724720236</v>
+        <v>46186.27264118563</v>
       </c>
       <c r="Z379" s="4" t="inlineStr"/>
     </row>
@@ -24379,7 +24671,7 @@
       <c r="W380" s="4" t="inlineStr"/>
       <c r="X380" s="4" t="inlineStr"/>
       <c r="Y380" s="5" t="n">
-        <v>46186.23724720271</v>
+        <v>46186.27264118587</v>
       </c>
       <c r="Z380" s="4" t="inlineStr"/>
     </row>
@@ -24451,7 +24743,7 @@
       <c r="W381" s="4" t="inlineStr"/>
       <c r="X381" s="4" t="inlineStr"/>
       <c r="Y381" s="5" t="n">
-        <v>46186.23724720294</v>
+        <v>46186.27264118609</v>
       </c>
       <c r="Z381" s="4" t="inlineStr"/>
     </row>
@@ -24519,7 +24811,7 @@
       <c r="W382" s="4" t="inlineStr"/>
       <c r="X382" s="4" t="inlineStr"/>
       <c r="Y382" s="5" t="n">
-        <v>46186.23724720317</v>
+        <v>46186.27264118631</v>
       </c>
       <c r="Z382" s="4" t="inlineStr"/>
     </row>
@@ -24533,7 +24825,11 @@
       <c r="C383" s="5" t="n">
         <v>46182</v>
       </c>
-      <c r="D383" s="4" t="inlineStr"/>
+      <c r="D383" s="4" t="inlineStr">
+        <is>
+          <t>DE.UGS.RE01.STR.S7</t>
+        </is>
+      </c>
       <c r="E383" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BR09 - Structure Ancillary 01 Dwall Reinforcements Details : DE.UGS.RE01.STR.S7.D3_Rev.C02</t>
@@ -24575,7 +24871,7 @@
       <c r="W383" s="4" t="inlineStr"/>
       <c r="X383" s="4" t="inlineStr"/>
       <c r="Y383" s="5" t="n">
-        <v>46186.23724720335</v>
+        <v>46186.27264118651</v>
       </c>
       <c r="Z383" s="4" t="inlineStr"/>
     </row>
@@ -24589,7 +24885,11 @@
       <c r="C384" s="5" t="n">
         <v>46182</v>
       </c>
-      <c r="D384" s="4" t="inlineStr"/>
+      <c r="D384" s="4" t="inlineStr">
+        <is>
+          <t>DE.ZNE.ZN05.ARD.R0</t>
+        </is>
+      </c>
       <c r="E384" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Z0045 Road Package : DE.ZNE.ZN05.ARD.R0.D2_Rev.C01(RCS Submission)</t>
@@ -24631,7 +24931,7 @@
       <c r="W384" s="4" t="inlineStr"/>
       <c r="X384" s="4" t="inlineStr"/>
       <c r="Y384" s="5" t="n">
-        <v>46186.23724720352</v>
+        <v>46186.27264118671</v>
       </c>
       <c r="Z384" s="4" t="inlineStr"/>
     </row>
@@ -24687,7 +24987,7 @@
       <c r="W385" s="4" t="inlineStr"/>
       <c r="X385" s="4" t="inlineStr"/>
       <c r="Y385" s="5" t="n">
-        <v>46186.23724720368</v>
+        <v>46186.27264118691</v>
       </c>
       <c r="Z385" s="4" t="inlineStr"/>
     </row>
@@ -24755,7 +25055,7 @@
       <c r="W386" s="4" t="inlineStr"/>
       <c r="X386" s="4" t="inlineStr"/>
       <c r="Y386" s="5" t="n">
-        <v>46186.23724720388</v>
+        <v>46186.27264118712</v>
       </c>
       <c r="Z386" s="4" t="inlineStr"/>
     </row>
@@ -24823,7 +25123,7 @@
       <c r="W387" s="4" t="inlineStr"/>
       <c r="X387" s="4" t="inlineStr"/>
       <c r="Y387" s="5" t="n">
-        <v>46186.23724720409</v>
+        <v>46186.27264118794</v>
       </c>
       <c r="Z387" s="4" t="inlineStr"/>
     </row>
@@ -24891,7 +25191,7 @@
       <c r="W388" s="4" t="inlineStr"/>
       <c r="X388" s="4" t="inlineStr"/>
       <c r="Y388" s="5" t="n">
-        <v>46186.23724720427</v>
+        <v>46186.27264118828</v>
       </c>
       <c r="Z388" s="4" t="inlineStr"/>
     </row>
@@ -24959,7 +25259,7 @@
       <c r="W389" s="4" t="inlineStr"/>
       <c r="X389" s="4" t="inlineStr"/>
       <c r="Y389" s="5" t="n">
-        <v>46186.23724720446</v>
+        <v>46186.27264118851</v>
       </c>
       <c r="Z389" s="4" t="inlineStr"/>
     </row>
@@ -25027,7 +25327,7 @@
       <c r="W390" s="4" t="inlineStr"/>
       <c r="X390" s="4" t="inlineStr"/>
       <c r="Y390" s="5" t="n">
-        <v>46186.23724720464</v>
+        <v>46186.27264118871</v>
       </c>
       <c r="Z390" s="4" t="inlineStr"/>
     </row>
@@ -25095,7 +25395,7 @@
       <c r="W391" s="4" t="inlineStr"/>
       <c r="X391" s="4" t="inlineStr"/>
       <c r="Y391" s="5" t="n">
-        <v>46186.23724720514</v>
+        <v>46186.27264118891</v>
       </c>
       <c r="Z391" s="4" t="inlineStr"/>
     </row>
@@ -25163,7 +25463,7 @@
       <c r="W392" s="4" t="inlineStr"/>
       <c r="X392" s="4" t="inlineStr"/>
       <c r="Y392" s="5" t="n">
-        <v>46186.23724720548</v>
+        <v>46186.27264118911</v>
       </c>
       <c r="Z392" s="4" t="inlineStr"/>
     </row>
@@ -25231,7 +25531,7 @@
       <c r="W393" s="4" t="inlineStr"/>
       <c r="X393" s="4" t="inlineStr"/>
       <c r="Y393" s="5" t="n">
-        <v>46186.2372472057</v>
+        <v>46186.27264118931</v>
       </c>
       <c r="Z393" s="4" t="inlineStr"/>
     </row>
@@ -25299,7 +25599,7 @@
       <c r="W394" s="8" t="inlineStr"/>
       <c r="X394" s="8" t="inlineStr"/>
       <c r="Y394" s="9" t="n">
-        <v>46186.23724720593</v>
+        <v>46186.27264118951</v>
       </c>
       <c r="Z394" s="8" t="inlineStr"/>
     </row>
@@ -25351,7 +25651,7 @@
       <c r="W395" s="4" t="inlineStr"/>
       <c r="X395" s="4" t="inlineStr"/>
       <c r="Y395" s="5" t="n">
-        <v>46186.23724720615</v>
+        <v>46186.27264118975</v>
       </c>
       <c r="Z395" s="4" t="inlineStr"/>
     </row>
@@ -25419,7 +25719,7 @@
       <c r="W396" s="8" t="inlineStr"/>
       <c r="X396" s="8" t="inlineStr"/>
       <c r="Y396" s="9" t="n">
-        <v>46186.23724720635</v>
+        <v>46186.27264118994</v>
       </c>
       <c r="Z396" s="8" t="inlineStr"/>
     </row>
@@ -25487,7 +25787,7 @@
       <c r="W397" s="8" t="inlineStr"/>
       <c r="X397" s="8" t="inlineStr"/>
       <c r="Y397" s="9" t="n">
-        <v>46186.23724720655</v>
+        <v>46186.27264119014</v>
       </c>
       <c r="Z397" s="8" t="inlineStr"/>
     </row>
@@ -25501,7 +25801,11 @@
       <c r="C398" s="9" t="n">
         <v>46182</v>
       </c>
-      <c r="D398" s="8" t="inlineStr"/>
+      <c r="D398" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST03.STR.V3</t>
+        </is>
+      </c>
       <c r="E398" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Stretch-03 - Viaduct Structure Superstructure 2SP : DE.VDT.ST03.STR.V3.D3_Rev.C02</t>
@@ -25539,7 +25843,7 @@
       <c r="W398" s="8" t="inlineStr"/>
       <c r="X398" s="8" t="inlineStr"/>
       <c r="Y398" s="9" t="n">
-        <v>46186.23724720672</v>
+        <v>46186.27264119033</v>
       </c>
       <c r="Z398" s="8" t="inlineStr"/>
     </row>
@@ -25607,7 +25911,7 @@
       <c r="W399" s="4" t="inlineStr"/>
       <c r="X399" s="4" t="inlineStr"/>
       <c r="Y399" s="5" t="n">
-        <v>46186.23724720701</v>
+        <v>46186.27264119055</v>
       </c>
       <c r="Z399" s="4" t="inlineStr"/>
     </row>
@@ -25675,7 +25979,7 @@
       <c r="W400" s="8" t="inlineStr"/>
       <c r="X400" s="8" t="inlineStr"/>
       <c r="Y400" s="9" t="n">
-        <v>46186.23724720721</v>
+        <v>46186.27264119074</v>
       </c>
       <c r="Z400" s="8" t="inlineStr"/>
     </row>
@@ -25727,7 +26031,7 @@
       <c r="W401" s="8" t="inlineStr"/>
       <c r="X401" s="8" t="inlineStr"/>
       <c r="Y401" s="9" t="n">
-        <v>46186.23724720738</v>
+        <v>46186.27264119094</v>
       </c>
       <c r="Z401" s="8" t="inlineStr"/>
     </row>
@@ -25795,7 +26099,7 @@
       <c r="W402" s="8" t="inlineStr"/>
       <c r="X402" s="8" t="inlineStr"/>
       <c r="Y402" s="9" t="n">
-        <v>46186.23724720762</v>
+        <v>46186.27264119117</v>
       </c>
       <c r="Z402" s="8" t="inlineStr"/>
     </row>
@@ -25859,7 +26163,7 @@
       <c r="W403" s="8" t="inlineStr"/>
       <c r="X403" s="8" t="inlineStr"/>
       <c r="Y403" s="9" t="n">
-        <v>46186.23724720789</v>
+        <v>46186.27264119139</v>
       </c>
       <c r="Z403" s="8" t="inlineStr"/>
     </row>
@@ -25923,7 +26227,7 @@
       <c r="W404" s="8" t="inlineStr"/>
       <c r="X404" s="8" t="inlineStr"/>
       <c r="Y404" s="9" t="n">
-        <v>46186.23724720811</v>
+        <v>46186.27264119159</v>
       </c>
       <c r="Z404" s="8" t="inlineStr"/>
     </row>
@@ -25937,7 +26241,11 @@
       <c r="C405" s="9" t="n">
         <v>46182</v>
       </c>
-      <c r="D405" s="8" t="inlineStr"/>
+      <c r="D405" s="8" t="inlineStr">
+        <is>
+          <t>DE.ANX.AX17.STR.S0</t>
+        </is>
+      </c>
       <c r="E405" s="10" t="inlineStr">
         <is>
           <t>Re: NOC Drawing Submission - NOC Drawing Submission - ANNEX 08_NOC Drawings : DE.ANX.AX17.STR.S0.NC_Rev.C02</t>
@@ -25971,7 +26279,7 @@
       <c r="W405" s="8" t="inlineStr"/>
       <c r="X405" s="8" t="inlineStr"/>
       <c r="Y405" s="9" t="n">
-        <v>46186.23724720829</v>
+        <v>46186.2726411918</v>
       </c>
       <c r="Z405" s="8" t="inlineStr"/>
     </row>
@@ -25985,7 +26293,11 @@
       <c r="C406" s="9" t="n">
         <v>46182</v>
       </c>
-      <c r="D406" s="8" t="inlineStr"/>
+      <c r="D406" s="8" t="inlineStr">
+        <is>
+          <t>DE.ANX.AX16.STR.S0</t>
+        </is>
+      </c>
       <c r="E406" s="10" t="inlineStr">
         <is>
           <t>Re: NOC Drawing Submission - Annex-BL-EES-07 - Structure NOC : DE.ANX.AX16.STR.S0.NC_Rev.C03</t>
@@ -26019,7 +26331,7 @@
       <c r="W406" s="8" t="inlineStr"/>
       <c r="X406" s="8" t="inlineStr"/>
       <c r="Y406" s="9" t="n">
-        <v>46186.23724720846</v>
+        <v>46186.272641192</v>
       </c>
       <c r="Z406" s="8" t="inlineStr"/>
     </row>
@@ -26071,7 +26383,7 @@
       <c r="W407" s="8" t="inlineStr"/>
       <c r="X407" s="8" t="inlineStr"/>
       <c r="Y407" s="9" t="n">
-        <v>46186.23724720864</v>
+        <v>46186.2726411922</v>
       </c>
       <c r="Z407" s="8" t="inlineStr"/>
     </row>
@@ -26085,7 +26397,11 @@
       <c r="C408" s="9" t="n">
         <v>46182</v>
       </c>
-      <c r="D408" s="8" t="inlineStr"/>
+      <c r="D408" s="8" t="inlineStr">
+        <is>
+          <t>DE.ZNE.ZN01.UTI.U2</t>
+        </is>
+      </c>
       <c r="E408" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Zone 01 Utility Z0039 : DE.ZNE.ZN01.UTI.U2.D2_Rev.C02</t>
@@ -26123,7 +26439,7 @@
       <c r="W408" s="8" t="inlineStr"/>
       <c r="X408" s="8" t="inlineStr"/>
       <c r="Y408" s="9" t="n">
-        <v>46186.23724720879</v>
+        <v>46186.27264119239</v>
       </c>
       <c r="Z408" s="8" t="inlineStr"/>
     </row>
@@ -26175,7 +26491,7 @@
       <c r="W409" s="8" t="inlineStr"/>
       <c r="X409" s="8" t="inlineStr"/>
       <c r="Y409" s="9" t="n">
-        <v>46186.23724720893</v>
+        <v>46186.27264119258</v>
       </c>
       <c r="Z409" s="8" t="inlineStr"/>
     </row>
@@ -26239,7 +26555,7 @@
       <c r="W410" s="8" t="inlineStr"/>
       <c r="X410" s="8" t="inlineStr"/>
       <c r="Y410" s="9" t="n">
-        <v>46186.23724720914</v>
+        <v>46186.27264119279</v>
       </c>
       <c r="Z410" s="8" t="inlineStr"/>
     </row>
@@ -26303,7 +26619,7 @@
       <c r="W411" s="8" t="inlineStr"/>
       <c r="X411" s="8" t="inlineStr"/>
       <c r="Y411" s="9" t="n">
-        <v>46186.23724720933</v>
+        <v>46186.27264119298</v>
       </c>
       <c r="Z411" s="8" t="inlineStr"/>
     </row>
@@ -26371,7 +26687,7 @@
       <c r="W412" s="8" t="inlineStr"/>
       <c r="X412" s="8" t="inlineStr"/>
       <c r="Y412" s="9" t="n">
-        <v>46186.23724720952</v>
+        <v>46186.27264119318</v>
       </c>
       <c r="Z412" s="8" t="inlineStr"/>
     </row>
@@ -26439,7 +26755,7 @@
       <c r="W413" s="4" t="inlineStr"/>
       <c r="X413" s="4" t="inlineStr"/>
       <c r="Y413" s="5" t="n">
-        <v>46186.23724720972</v>
+        <v>46186.27264119338</v>
       </c>
       <c r="Z413" s="4" t="inlineStr"/>
     </row>
@@ -26453,7 +26769,11 @@
       <c r="C414" s="9" t="n">
         <v>46182</v>
       </c>
-      <c r="D414" s="8" t="inlineStr"/>
+      <c r="D414" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST07.STR.V2</t>
+        </is>
+      </c>
       <c r="E414" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Stretch 07 - Viaduct Structure Bearing Schedule -BC-3SP-72-10A : DE.VDT.ST07.STR.V2.D3_Rev.C01</t>
@@ -26491,7 +26811,7 @@
       <c r="W414" s="8" t="inlineStr"/>
       <c r="X414" s="8" t="inlineStr"/>
       <c r="Y414" s="9" t="n">
-        <v>46186.23724720989</v>
+        <v>46186.27264119359</v>
       </c>
       <c r="Z414" s="8" t="inlineStr"/>
     </row>
@@ -26555,7 +26875,7 @@
       <c r="W415" s="8" t="inlineStr"/>
       <c r="X415" s="8" t="inlineStr"/>
       <c r="Y415" s="9" t="n">
-        <v>46186.23724721009</v>
+        <v>46186.27264119378</v>
       </c>
       <c r="Z415" s="8" t="inlineStr"/>
     </row>
@@ -26619,7 +26939,7 @@
       <c r="W416" s="8" t="inlineStr"/>
       <c r="X416" s="8" t="inlineStr"/>
       <c r="Y416" s="9" t="n">
-        <v>46186.23724721032</v>
+        <v>46186.27264119445</v>
       </c>
       <c r="Z416" s="8" t="inlineStr"/>
     </row>
@@ -26633,7 +26953,11 @@
       <c r="C417" s="9" t="n">
         <v>46182</v>
       </c>
-      <c r="D417" s="8" t="inlineStr"/>
+      <c r="D417" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE11.STR.S0</t>
+        </is>
+      </c>
       <c r="E417" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Station BB03 Structural Package : DE.ELS.GE11.STR.S0.D2_Rev.00 (RCS Resubmission)</t>
@@ -26671,7 +26995,7 @@
       <c r="W417" s="8" t="inlineStr"/>
       <c r="X417" s="8" t="inlineStr"/>
       <c r="Y417" s="9" t="n">
-        <v>46186.23724721048</v>
+        <v>46186.27264119478</v>
       </c>
       <c r="Z417" s="8" t="inlineStr"/>
     </row>
@@ -26739,7 +27063,7 @@
       <c r="W418" s="4" t="inlineStr"/>
       <c r="X418" s="4" t="inlineStr"/>
       <c r="Y418" s="5" t="n">
-        <v>46186.23724721066</v>
+        <v>46186.27264119502</v>
       </c>
       <c r="Z418" s="4" t="inlineStr"/>
     </row>
@@ -26807,7 +27131,7 @@
       <c r="W419" s="4" t="inlineStr"/>
       <c r="X419" s="4" t="inlineStr"/>
       <c r="Y419" s="5" t="n">
-        <v>46186.23724721091</v>
+        <v>46186.27264119525</v>
       </c>
       <c r="Z419" s="4" t="inlineStr"/>
     </row>
@@ -26875,7 +27199,7 @@
       <c r="W420" s="4" t="inlineStr"/>
       <c r="X420" s="4" t="inlineStr"/>
       <c r="Y420" s="5" t="n">
-        <v>46186.23724721153</v>
+        <v>46186.27264119544</v>
       </c>
       <c r="Z420" s="4" t="inlineStr"/>
     </row>
@@ -26943,7 +27267,7 @@
       <c r="W421" s="4" t="inlineStr"/>
       <c r="X421" s="4" t="inlineStr"/>
       <c r="Y421" s="5" t="n">
-        <v>46186.23724721177</v>
+        <v>46186.27264119564</v>
       </c>
       <c r="Z421" s="4" t="inlineStr"/>
     </row>
@@ -27011,7 +27335,7 @@
       <c r="W422" s="4" t="inlineStr"/>
       <c r="X422" s="4" t="inlineStr"/>
       <c r="Y422" s="5" t="n">
-        <v>46186.23724721197</v>
+        <v>46186.27264119581</v>
       </c>
       <c r="Z422" s="4" t="inlineStr"/>
     </row>
@@ -27025,7 +27349,11 @@
       <c r="C423" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="D423" s="4" t="inlineStr"/>
+      <c r="D423" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.GN00.STR.04</t>
+        </is>
+      </c>
       <c r="E423" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 Station Superstructure-Global 3SPAN PKG-1 : DE.VDT.GN00.STR.04.D3_Rev.C03</t>
@@ -27067,7 +27395,7 @@
       <c r="W423" s="4" t="inlineStr"/>
       <c r="X423" s="4" t="inlineStr"/>
       <c r="Y423" s="5" t="n">
-        <v>46186.23724721214</v>
+        <v>46186.27264119602</v>
       </c>
       <c r="Z423" s="4" t="inlineStr"/>
     </row>
@@ -27081,7 +27409,11 @@
       <c r="C424" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="D424" s="4" t="inlineStr"/>
+      <c r="D424" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.GE11.STR.V3</t>
+        </is>
+      </c>
       <c r="E424" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3_Station BB03 - Viaduct Structure Three Span Setting Out Superstructure: DE.VDT.GE11.STR.V3.D3_Rev.C01</t>
@@ -27119,7 +27451,7 @@
       <c r="W424" s="4" t="inlineStr"/>
       <c r="X424" s="4" t="inlineStr"/>
       <c r="Y424" s="5" t="n">
-        <v>46186.23724721234</v>
+        <v>46186.27264119623</v>
       </c>
       <c r="Z424" s="4" t="inlineStr"/>
     </row>
@@ -27179,7 +27511,7 @@
       <c r="W425" s="8" t="inlineStr"/>
       <c r="X425" s="8" t="inlineStr"/>
       <c r="Y425" s="9" t="n">
-        <v>46186.23724721255</v>
+        <v>46186.27264119642</v>
       </c>
       <c r="Z425" s="8" t="inlineStr"/>
     </row>
@@ -27251,7 +27583,7 @@
       <c r="W426" s="8" t="inlineStr"/>
       <c r="X426" s="8" t="inlineStr"/>
       <c r="Y426" s="9" t="n">
-        <v>46186.23724721275</v>
+        <v>46186.27264119661</v>
       </c>
       <c r="Z426" s="8" t="inlineStr"/>
     </row>
@@ -27315,7 +27647,7 @@
       <c r="W427" s="8" t="inlineStr"/>
       <c r="X427" s="8" t="inlineStr"/>
       <c r="Y427" s="9" t="n">
-        <v>46186.23724721297</v>
+        <v>46186.27264119682</v>
       </c>
       <c r="Z427" s="8" t="inlineStr"/>
     </row>
@@ -27379,7 +27711,7 @@
       <c r="W428" s="8" t="inlineStr"/>
       <c r="X428" s="8" t="inlineStr"/>
       <c r="Y428" s="9" t="n">
-        <v>46186.2372472132</v>
+        <v>46186.27264119706</v>
       </c>
       <c r="Z428" s="8" t="inlineStr"/>
     </row>
@@ -27447,7 +27779,7 @@
       <c r="W429" s="8" t="inlineStr"/>
       <c r="X429" s="8" t="inlineStr"/>
       <c r="Y429" s="9" t="n">
-        <v>46186.23724721339</v>
+        <v>46186.27264119725</v>
       </c>
       <c r="Z429" s="8" t="inlineStr"/>
     </row>
@@ -27511,7 +27843,7 @@
       <c r="W430" s="8" t="inlineStr"/>
       <c r="X430" s="8" t="inlineStr"/>
       <c r="Y430" s="9" t="n">
-        <v>46186.23724721409</v>
+        <v>46186.27264119747</v>
       </c>
       <c r="Z430" s="8" t="inlineStr"/>
     </row>
@@ -27575,7 +27907,7 @@
       <c r="W431" s="8" t="inlineStr"/>
       <c r="X431" s="8" t="inlineStr"/>
       <c r="Y431" s="9" t="n">
-        <v>46186.23724721432</v>
+        <v>46186.27264119765</v>
       </c>
       <c r="Z431" s="8" t="inlineStr"/>
     </row>
@@ -27589,7 +27921,11 @@
       <c r="C432" s="9" t="n">
         <v>46181</v>
       </c>
-      <c r="D432" s="8" t="inlineStr"/>
+      <c r="D432" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST04.GEO.G1</t>
+        </is>
+      </c>
       <c r="E432" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 -Technical Note-Working Pile load Test Viaduct Stretch 4 (PM-101-04): DE.VDT.ST04.GEO.G1.D3_Rev.C01</t>
@@ -27627,7 +27963,7 @@
       <c r="W432" s="8" t="inlineStr"/>
       <c r="X432" s="8" t="inlineStr"/>
       <c r="Y432" s="9" t="n">
-        <v>46186.23724721451</v>
+        <v>46186.27264119784</v>
       </c>
       <c r="Z432" s="8" t="inlineStr"/>
     </row>
@@ -27691,7 +28027,7 @@
       <c r="W433" s="8" t="inlineStr"/>
       <c r="X433" s="8" t="inlineStr"/>
       <c r="Y433" s="9" t="n">
-        <v>46186.23724721473</v>
+        <v>46186.27264119805</v>
       </c>
       <c r="Z433" s="8" t="inlineStr"/>
     </row>
@@ -27755,7 +28091,7 @@
       <c r="W434" s="8" t="inlineStr"/>
       <c r="X434" s="8" t="inlineStr"/>
       <c r="Y434" s="9" t="n">
-        <v>46186.23724721493</v>
+        <v>46186.27264119825</v>
       </c>
       <c r="Z434" s="8" t="inlineStr"/>
     </row>
@@ -27769,7 +28105,11 @@
       <c r="C435" s="9" t="n">
         <v>46181</v>
       </c>
-      <c r="D435" s="8" t="inlineStr"/>
+      <c r="D435" s="8" t="inlineStr">
+        <is>
+          <t>DE.DPT.TBG2.ARC.A0</t>
+        </is>
+      </c>
       <c r="E435" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Depot BDR11 - Architecture Chiller Compound-2 : DE.DPT.TBG2.ARC.A0.D2_Rev.C02</t>
@@ -27807,7 +28147,7 @@
       <c r="W435" s="8" t="inlineStr"/>
       <c r="X435" s="8" t="inlineStr"/>
       <c r="Y435" s="9" t="n">
-        <v>46186.23724721509</v>
+        <v>46186.27264119844</v>
       </c>
       <c r="Z435" s="8" t="inlineStr"/>
     </row>
@@ -27875,7 +28215,7 @@
       <c r="W436" s="8" t="inlineStr"/>
       <c r="X436" s="8" t="inlineStr"/>
       <c r="Y436" s="9" t="n">
-        <v>46186.2372472153</v>
+        <v>46186.27264119864</v>
       </c>
       <c r="Z436" s="8" t="inlineStr"/>
     </row>
@@ -27943,7 +28283,7 @@
       <c r="W437" s="8" t="inlineStr"/>
       <c r="X437" s="8" t="inlineStr"/>
       <c r="Y437" s="9" t="n">
-        <v>46186.23724721549</v>
+        <v>46186.27264119933</v>
       </c>
       <c r="Z437" s="8" t="inlineStr"/>
     </row>
@@ -28011,7 +28351,7 @@
       <c r="W438" s="8" t="inlineStr"/>
       <c r="X438" s="8" t="inlineStr"/>
       <c r="Y438" s="9" t="n">
-        <v>46186.23724721606</v>
+        <v>46186.27264119962</v>
       </c>
       <c r="Z438" s="8" t="inlineStr"/>
     </row>
@@ -28079,7 +28419,7 @@
       <c r="W439" s="8" t="inlineStr"/>
       <c r="X439" s="8" t="inlineStr"/>
       <c r="Y439" s="9" t="n">
-        <v>46186.23724721636</v>
+        <v>46186.27264119982</v>
       </c>
       <c r="Z439" s="8" t="inlineStr"/>
     </row>
@@ -28147,7 +28487,7 @@
       <c r="W440" s="4" t="inlineStr"/>
       <c r="X440" s="4" t="inlineStr"/>
       <c r="Y440" s="5" t="n">
-        <v>46186.23724721659</v>
+        <v>46186.27264120005</v>
       </c>
       <c r="Z440" s="4" t="inlineStr"/>
     </row>
@@ -28215,7 +28555,7 @@
       <c r="W441" s="4" t="inlineStr"/>
       <c r="X441" s="4" t="inlineStr"/>
       <c r="Y441" s="5" t="n">
-        <v>46186.23724721677</v>
+        <v>46186.27264120024</v>
       </c>
       <c r="Z441" s="4" t="inlineStr"/>
     </row>
@@ -28283,7 +28623,7 @@
       <c r="W442" s="4" t="inlineStr"/>
       <c r="X442" s="4" t="inlineStr"/>
       <c r="Y442" s="5" t="n">
-        <v>46186.23724721697</v>
+        <v>46186.27264120045</v>
       </c>
       <c r="Z442" s="4" t="inlineStr"/>
     </row>
@@ -28351,7 +28691,7 @@
       <c r="W443" s="4" t="inlineStr"/>
       <c r="X443" s="4" t="inlineStr"/>
       <c r="Y443" s="5" t="n">
-        <v>46186.23724721716</v>
+        <v>46186.27264120064</v>
       </c>
       <c r="Z443" s="4" t="inlineStr"/>
     </row>
@@ -28419,7 +28759,7 @@
       <c r="W444" s="4" t="inlineStr"/>
       <c r="X444" s="4" t="inlineStr"/>
       <c r="Y444" s="5" t="n">
-        <v>46186.23724721735</v>
+        <v>46186.27264120161</v>
       </c>
       <c r="Z444" s="4" t="inlineStr"/>
     </row>
@@ -28487,7 +28827,7 @@
       <c r="W445" s="4" t="inlineStr"/>
       <c r="X445" s="4" t="inlineStr"/>
       <c r="Y445" s="5" t="n">
-        <v>46186.23724721764</v>
+        <v>46186.27264120197</v>
       </c>
       <c r="Z445" s="4" t="inlineStr"/>
     </row>
@@ -28555,7 +28895,7 @@
       <c r="W446" s="4" t="inlineStr"/>
       <c r="X446" s="4" t="inlineStr"/>
       <c r="Y446" s="5" t="n">
-        <v>46186.23724721794</v>
+        <v>46186.27264120226</v>
       </c>
       <c r="Z446" s="4" t="inlineStr"/>
     </row>
@@ -28623,7 +28963,7 @@
       <c r="W447" s="4" t="inlineStr"/>
       <c r="X447" s="4" t="inlineStr"/>
       <c r="Y447" s="5" t="n">
-        <v>46186.23724721814</v>
+        <v>46186.27264120246</v>
       </c>
       <c r="Z447" s="4" t="inlineStr"/>
     </row>
@@ -28691,7 +29031,7 @@
       <c r="W448" s="4" t="inlineStr"/>
       <c r="X448" s="4" t="inlineStr"/>
       <c r="Y448" s="5" t="n">
-        <v>46186.23724721873</v>
+        <v>46186.27264120266</v>
       </c>
       <c r="Z448" s="4" t="inlineStr"/>
     </row>
@@ -28759,7 +29099,7 @@
       <c r="W449" s="4" t="inlineStr"/>
       <c r="X449" s="4" t="inlineStr"/>
       <c r="Y449" s="5" t="n">
-        <v>46186.237247219</v>
+        <v>46186.27264120285</v>
       </c>
       <c r="Z449" s="4" t="inlineStr"/>
     </row>
@@ -28823,7 +29163,7 @@
       <c r="W450" s="8" t="inlineStr"/>
       <c r="X450" s="8" t="inlineStr"/>
       <c r="Y450" s="9" t="n">
-        <v>46186.23724721921</v>
+        <v>46186.27264120305</v>
       </c>
       <c r="Z450" s="8" t="inlineStr"/>
     </row>
@@ -28891,7 +29231,7 @@
       <c r="W451" s="8" t="inlineStr"/>
       <c r="X451" s="8" t="inlineStr"/>
       <c r="Y451" s="9" t="n">
-        <v>46186.23724721951</v>
+        <v>46186.27264120325</v>
       </c>
       <c r="Z451" s="8" t="inlineStr"/>
     </row>
@@ -28959,7 +29299,7 @@
       <c r="W452" s="8" t="inlineStr"/>
       <c r="X452" s="8" t="inlineStr"/>
       <c r="Y452" s="9" t="n">
-        <v>46186.23724721978</v>
+        <v>46186.2726412035</v>
       </c>
       <c r="Z452" s="8" t="inlineStr"/>
     </row>
@@ -29023,7 +29363,7 @@
       <c r="W453" s="8" t="inlineStr"/>
       <c r="X453" s="8" t="inlineStr"/>
       <c r="Y453" s="9" t="n">
-        <v>46186.23724722001</v>
+        <v>46186.27264120373</v>
       </c>
       <c r="Z453" s="8" t="inlineStr"/>
     </row>
@@ -29091,7 +29431,7 @@
       <c r="W454" s="8" t="inlineStr"/>
       <c r="X454" s="8" t="inlineStr"/>
       <c r="Y454" s="9" t="n">
-        <v>46186.23724722023</v>
+        <v>46186.27264120393</v>
       </c>
       <c r="Z454" s="8" t="inlineStr"/>
     </row>
@@ -29159,7 +29499,7 @@
       <c r="W455" s="8" t="inlineStr"/>
       <c r="X455" s="8" t="inlineStr"/>
       <c r="Y455" s="9" t="n">
-        <v>46186.23724722044</v>
+        <v>46186.27264120414</v>
       </c>
       <c r="Z455" s="8" t="inlineStr"/>
     </row>
@@ -29227,7 +29567,7 @@
       <c r="W456" s="8" t="inlineStr"/>
       <c r="X456" s="8" t="inlineStr"/>
       <c r="Y456" s="9" t="n">
-        <v>46186.23724722067</v>
+        <v>46186.27264120438</v>
       </c>
       <c r="Z456" s="8" t="inlineStr"/>
     </row>
@@ -29295,7 +29635,7 @@
       <c r="W457" s="8" t="inlineStr"/>
       <c r="X457" s="8" t="inlineStr"/>
       <c r="Y457" s="9" t="n">
-        <v>46186.2372472209</v>
+        <v>46186.27264120462</v>
       </c>
       <c r="Z457" s="8" t="inlineStr"/>
     </row>
@@ -29363,7 +29703,7 @@
       <c r="W458" s="8" t="inlineStr"/>
       <c r="X458" s="8" t="inlineStr"/>
       <c r="Y458" s="9" t="n">
-        <v>46186.2372472211</v>
+        <v>46186.27264120481</v>
       </c>
       <c r="Z458" s="8" t="inlineStr"/>
     </row>
@@ -29431,7 +29771,7 @@
       <c r="W459" s="8" t="inlineStr"/>
       <c r="X459" s="8" t="inlineStr"/>
       <c r="Y459" s="9" t="n">
-        <v>46186.2372472213</v>
+        <v>46186.272641205</v>
       </c>
       <c r="Z459" s="8" t="inlineStr"/>
     </row>
@@ -29499,7 +29839,7 @@
       <c r="W460" s="8" t="inlineStr"/>
       <c r="X460" s="8" t="inlineStr"/>
       <c r="Y460" s="9" t="n">
-        <v>46186.23724722148</v>
+        <v>46186.27264120519</v>
       </c>
       <c r="Z460" s="8" t="inlineStr"/>
     </row>
@@ -29567,7 +29907,7 @@
       <c r="W461" s="8" t="inlineStr"/>
       <c r="X461" s="8" t="inlineStr"/>
       <c r="Y461" s="9" t="n">
-        <v>46186.23724722167</v>
+        <v>46186.27264120536</v>
       </c>
       <c r="Z461" s="8" t="inlineStr"/>
     </row>
@@ -29581,7 +29921,11 @@
       <c r="C462" s="9" t="n">
         <v>46181</v>
       </c>
-      <c r="D462" s="8" t="inlineStr"/>
+      <c r="D462" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.RE00.MEP.M2</t>
+        </is>
+      </c>
       <c r="E462" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - BR10 Stations MEP - DAW &amp;WTS : DE.ELS.RE00.MEP.M2.D2_Rev.C01</t>
@@ -29619,7 +29963,7 @@
       <c r="W462" s="8" t="inlineStr"/>
       <c r="X462" s="8" t="inlineStr"/>
       <c r="Y462" s="9" t="n">
-        <v>46186.23724722184</v>
+        <v>46186.27264120556</v>
       </c>
       <c r="Z462" s="8" t="inlineStr"/>
     </row>
@@ -29683,7 +30027,7 @@
       <c r="W463" s="8" t="inlineStr"/>
       <c r="X463" s="8" t="inlineStr"/>
       <c r="Y463" s="9" t="n">
-        <v>46186.23724722202</v>
+        <v>46186.27264120575</v>
       </c>
       <c r="Z463" s="8" t="inlineStr"/>
     </row>
@@ -29747,7 +30091,7 @@
       <c r="W464" s="8" t="inlineStr"/>
       <c r="X464" s="8" t="inlineStr"/>
       <c r="Y464" s="9" t="n">
-        <v>46186.23724722221</v>
+        <v>46186.27264120595</v>
       </c>
       <c r="Z464" s="8" t="inlineStr"/>
     </row>
@@ -29811,7 +30155,7 @@
       <c r="W465" s="8" t="inlineStr"/>
       <c r="X465" s="8" t="inlineStr"/>
       <c r="Y465" s="9" t="n">
-        <v>46186.23724722242</v>
+        <v>46186.27264120616</v>
       </c>
       <c r="Z465" s="8" t="inlineStr"/>
     </row>
@@ -29875,7 +30219,7 @@
       <c r="W466" s="8" t="inlineStr"/>
       <c r="X466" s="8" t="inlineStr"/>
       <c r="Y466" s="9" t="n">
-        <v>46186.23724722266</v>
+        <v>46186.27264120647</v>
       </c>
       <c r="Z466" s="8" t="inlineStr"/>
     </row>
@@ -29939,7 +30283,7 @@
       <c r="W467" s="8" t="inlineStr"/>
       <c r="X467" s="8" t="inlineStr"/>
       <c r="Y467" s="9" t="n">
-        <v>46186.23724722288</v>
+        <v>46186.27264120668</v>
       </c>
       <c r="Z467" s="8" t="inlineStr"/>
     </row>
@@ -30003,7 +30347,7 @@
       <c r="W468" s="8" t="inlineStr"/>
       <c r="X468" s="8" t="inlineStr"/>
       <c r="Y468" s="9" t="n">
-        <v>46186.2372472231</v>
+        <v>46186.2726412069</v>
       </c>
       <c r="Z468" s="8" t="inlineStr"/>
     </row>
@@ -30067,7 +30411,7 @@
       <c r="W469" s="8" t="inlineStr"/>
       <c r="X469" s="8" t="inlineStr"/>
       <c r="Y469" s="9" t="n">
-        <v>46186.2372472233</v>
+        <v>46186.27264120711</v>
       </c>
       <c r="Z469" s="8" t="inlineStr"/>
     </row>
@@ -30131,7 +30475,7 @@
       <c r="W470" s="8" t="inlineStr"/>
       <c r="X470" s="8" t="inlineStr"/>
       <c r="Y470" s="9" t="n">
-        <v>46186.23724722349</v>
+        <v>46186.27264120732</v>
       </c>
       <c r="Z470" s="8" t="inlineStr"/>
     </row>
@@ -30195,7 +30539,7 @@
       <c r="W471" s="8" t="inlineStr"/>
       <c r="X471" s="8" t="inlineStr"/>
       <c r="Y471" s="9" t="n">
-        <v>46186.2372472237</v>
+        <v>46186.27264120754</v>
       </c>
       <c r="Z471" s="8" t="inlineStr"/>
     </row>
@@ -30259,7 +30603,7 @@
       <c r="W472" s="8" t="inlineStr"/>
       <c r="X472" s="8" t="inlineStr"/>
       <c r="Y472" s="9" t="n">
-        <v>46186.23724722391</v>
+        <v>46186.27264120809</v>
       </c>
       <c r="Z472" s="8" t="inlineStr"/>
     </row>
@@ -30323,7 +30667,7 @@
       <c r="W473" s="8" t="inlineStr"/>
       <c r="X473" s="8" t="inlineStr"/>
       <c r="Y473" s="9" t="n">
-        <v>46186.23724722413</v>
+        <v>46186.27264120846</v>
       </c>
       <c r="Z473" s="8" t="inlineStr"/>
     </row>
@@ -30387,7 +30731,7 @@
       <c r="W474" s="8" t="inlineStr"/>
       <c r="X474" s="8" t="inlineStr"/>
       <c r="Y474" s="9" t="n">
-        <v>46186.23724722433</v>
+        <v>46186.27264120871</v>
       </c>
       <c r="Z474" s="8" t="inlineStr"/>
     </row>
@@ -30451,7 +30795,7 @@
       <c r="W475" s="8" t="inlineStr"/>
       <c r="X475" s="8" t="inlineStr"/>
       <c r="Y475" s="9" t="n">
-        <v>46186.23724722451</v>
+        <v>46186.27264120893</v>
       </c>
       <c r="Z475" s="8" t="inlineStr"/>
     </row>
@@ -30515,7 +30859,7 @@
       <c r="W476" s="8" t="inlineStr"/>
       <c r="X476" s="8" t="inlineStr"/>
       <c r="Y476" s="9" t="n">
-        <v>46186.23724722533</v>
+        <v>46186.27264120914</v>
       </c>
       <c r="Z476" s="8" t="inlineStr"/>
     </row>
@@ -30529,7 +30873,11 @@
       <c r="C477" s="9" t="n">
         <v>46181</v>
       </c>
-      <c r="D477" s="8" t="inlineStr"/>
+      <c r="D477" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST06.STR.V1</t>
+        </is>
+      </c>
       <c r="E477" s="10" t="inlineStr">
         <is>
           <t>Re: Shop Drawing Submission - 	Stretch-06.2 - Viaduct Structure Pier Shop Drawing - PM159 &amp; PM160 : DE.VDT.ST06.STR.V1.D5_Rev.C01</t>
@@ -30563,7 +30911,7 @@
       <c r="W477" s="8" t="inlineStr"/>
       <c r="X477" s="8" t="inlineStr"/>
       <c r="Y477" s="9" t="n">
-        <v>46186.23724722565</v>
+        <v>46186.27264120936</v>
       </c>
       <c r="Z477" s="8" t="inlineStr"/>
     </row>
@@ -30627,7 +30975,7 @@
       <c r="W478" s="8" t="inlineStr"/>
       <c r="X478" s="8" t="inlineStr"/>
       <c r="Y478" s="9" t="n">
-        <v>46186.23724722589</v>
+        <v>46186.27264120956</v>
       </c>
       <c r="Z478" s="8" t="inlineStr"/>
     </row>
@@ -30691,7 +31039,7 @@
       <c r="W479" s="8" t="inlineStr"/>
       <c r="X479" s="8" t="inlineStr"/>
       <c r="Y479" s="9" t="n">
-        <v>46186.23724722612</v>
+        <v>46186.27264120977</v>
       </c>
       <c r="Z479" s="8" t="inlineStr"/>
     </row>
@@ -30755,7 +31103,7 @@
       <c r="W480" s="8" t="inlineStr"/>
       <c r="X480" s="8" t="inlineStr"/>
       <c r="Y480" s="9" t="n">
-        <v>46186.23724722633</v>
+        <v>46186.27264120997</v>
       </c>
       <c r="Z480" s="8" t="inlineStr"/>
     </row>
@@ -30823,7 +31171,7 @@
       <c r="W481" s="8" t="inlineStr"/>
       <c r="X481" s="8" t="inlineStr"/>
       <c r="Y481" s="9" t="n">
-        <v>46186.23724722655</v>
+        <v>46186.27264121079</v>
       </c>
       <c r="Z481" s="8" t="inlineStr"/>
     </row>
@@ -30891,7 +31239,7 @@
       <c r="W482" s="4" t="inlineStr"/>
       <c r="X482" s="4" t="inlineStr"/>
       <c r="Y482" s="5" t="n">
-        <v>46186.23724722715</v>
+        <v>46186.27264121112</v>
       </c>
       <c r="Z482" s="4" t="inlineStr"/>
     </row>
@@ -30905,7 +31253,11 @@
       <c r="C483" s="9" t="n">
         <v>46181</v>
       </c>
-      <c r="D483" s="8" t="inlineStr"/>
+      <c r="D483" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST04.STR.V2</t>
+        </is>
+      </c>
       <c r="E483" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Stretch-04.1 - Viaduct Structure Bearing Schedule (Part 1) : DE.VDT.ST04.STR.V2.D3_Rev.C01</t>
@@ -30943,7 +31295,7 @@
       <c r="W483" s="8" t="inlineStr"/>
       <c r="X483" s="8" t="inlineStr"/>
       <c r="Y483" s="9" t="n">
-        <v>46186.23724722742</v>
+        <v>46186.27264121136</v>
       </c>
       <c r="Z483" s="8" t="inlineStr"/>
     </row>
@@ -30957,7 +31309,11 @@
       <c r="C484" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="D484" s="4" t="inlineStr"/>
+      <c r="D484" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST00.STR.V2</t>
+        </is>
+      </c>
       <c r="E484" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Stretch 00 - Viaduct Structure Pier Head ISO &amp; 2SP:  DE.VDT.ST00.STR.V2.D3_Rev.C01</t>
@@ -30999,7 +31355,7 @@
       <c r="W484" s="4" t="inlineStr"/>
       <c r="X484" s="4" t="inlineStr"/>
       <c r="Y484" s="5" t="n">
-        <v>46186.23724722762</v>
+        <v>46186.27264121156</v>
       </c>
       <c r="Z484" s="4" t="inlineStr"/>
     </row>
@@ -31067,7 +31423,7 @@
       <c r="W485" s="8" t="inlineStr"/>
       <c r="X485" s="8" t="inlineStr"/>
       <c r="Y485" s="9" t="n">
-        <v>46186.23724722784</v>
+        <v>46186.27264121177</v>
       </c>
       <c r="Z485" s="8" t="inlineStr"/>
     </row>
@@ -31131,7 +31487,7 @@
       <c r="W486" s="8" t="inlineStr"/>
       <c r="X486" s="8" t="inlineStr"/>
       <c r="Y486" s="9" t="n">
-        <v>46186.23724722813</v>
+        <v>46186.27264121206</v>
       </c>
       <c r="Z486" s="8" t="inlineStr"/>
     </row>
@@ -31195,7 +31551,7 @@
       <c r="W487" s="8" t="inlineStr"/>
       <c r="X487" s="8" t="inlineStr"/>
       <c r="Y487" s="9" t="n">
-        <v>46186.23724722838</v>
+        <v>46186.27264121229</v>
       </c>
       <c r="Z487" s="8" t="inlineStr"/>
     </row>
@@ -31263,7 +31619,7 @@
       <c r="W488" s="4" t="inlineStr"/>
       <c r="X488" s="4" t="inlineStr"/>
       <c r="Y488" s="5" t="n">
-        <v>46186.23724722867</v>
+        <v>46186.27264121259</v>
       </c>
       <c r="Z488" s="4" t="inlineStr"/>
     </row>
@@ -31331,7 +31687,7 @@
       <c r="W489" s="4" t="inlineStr"/>
       <c r="X489" s="4" t="inlineStr"/>
       <c r="Y489" s="5" t="n">
-        <v>46186.23724722886</v>
+        <v>46186.27264121279</v>
       </c>
       <c r="Z489" s="4" t="inlineStr"/>
     </row>
@@ -31395,7 +31751,7 @@
       <c r="W490" s="4" t="inlineStr"/>
       <c r="X490" s="4" t="inlineStr"/>
       <c r="Y490" s="5" t="n">
-        <v>46186.23724722907</v>
+        <v>46186.27264121299</v>
       </c>
       <c r="Z490" s="4" t="inlineStr"/>
     </row>
@@ -31463,7 +31819,7 @@
       <c r="W491" s="4" t="inlineStr"/>
       <c r="X491" s="4" t="inlineStr"/>
       <c r="Y491" s="5" t="n">
-        <v>46186.23724722927</v>
+        <v>46186.27264121317</v>
       </c>
       <c r="Z491" s="4" t="inlineStr"/>
     </row>
@@ -31477,7 +31833,11 @@
       <c r="C492" s="9" t="n">
         <v>46181</v>
       </c>
-      <c r="D492" s="8" t="inlineStr"/>
+      <c r="D492" s="8" t="inlineStr">
+        <is>
+          <t>DE.UGS.GE08.STR.S4</t>
+        </is>
+      </c>
       <c r="E492" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BB06 Base slab (TBM SHAFT AREA) : DE.UGS.GE08.STR.S4.D3_Rev.C03 (Partial Submission)</t>
@@ -31515,7 +31875,7 @@
       <c r="W492" s="8" t="inlineStr"/>
       <c r="X492" s="8" t="inlineStr"/>
       <c r="Y492" s="9" t="n">
-        <v>46186.23724722944</v>
+        <v>46186.27264121338</v>
       </c>
       <c r="Z492" s="8" t="inlineStr"/>
     </row>
@@ -31583,7 +31943,7 @@
       <c r="W493" s="4" t="inlineStr"/>
       <c r="X493" s="4" t="inlineStr"/>
       <c r="Y493" s="5" t="n">
-        <v>46186.23724722963</v>
+        <v>46186.27264121357</v>
       </c>
       <c r="Z493" s="4" t="inlineStr"/>
     </row>
@@ -31651,7 +32011,7 @@
       <c r="W494" s="4" t="inlineStr"/>
       <c r="X494" s="4" t="inlineStr"/>
       <c r="Y494" s="5" t="n">
-        <v>46186.23724722982</v>
+        <v>46186.27264121374</v>
       </c>
       <c r="Z494" s="4" t="inlineStr"/>
     </row>
@@ -31665,7 +32025,11 @@
       <c r="C495" s="9" t="n">
         <v>46181</v>
       </c>
-      <c r="D495" s="8" t="inlineStr"/>
+      <c r="D495" s="8" t="inlineStr">
+        <is>
+          <t>DE.DPT.TBG1.STR.S0</t>
+        </is>
+      </c>
       <c r="E495" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Depot BDR10 Chiller Compound 1 - Structural (DM Submission):  DE.DPT.TBG1.STR.S0.D3_Rev.C01</t>
@@ -31703,7 +32067,7 @@
       <c r="W495" s="8" t="inlineStr"/>
       <c r="X495" s="8" t="inlineStr"/>
       <c r="Y495" s="9" t="n">
-        <v>46186.23724723</v>
+        <v>46186.27264121394</v>
       </c>
       <c r="Z495" s="8" t="inlineStr"/>
     </row>
@@ -31771,7 +32135,7 @@
       <c r="W496" s="4" t="inlineStr"/>
       <c r="X496" s="4" t="inlineStr"/>
       <c r="Y496" s="5" t="n">
-        <v>46186.23724723019</v>
+        <v>46186.27264121413</v>
       </c>
       <c r="Z496" s="4" t="inlineStr"/>
     </row>
@@ -31839,7 +32203,7 @@
       <c r="W497" s="8" t="inlineStr"/>
       <c r="X497" s="8" t="inlineStr"/>
       <c r="Y497" s="9" t="n">
-        <v>46186.23724723037</v>
+        <v>46186.27264121432</v>
       </c>
       <c r="Z497" s="8" t="inlineStr"/>
     </row>
@@ -31907,7 +32271,7 @@
       <c r="W498" s="8" t="inlineStr"/>
       <c r="X498" s="8" t="inlineStr"/>
       <c r="Y498" s="9" t="n">
-        <v>46186.2372472307</v>
+        <v>46186.27264121453</v>
       </c>
       <c r="Z498" s="8" t="inlineStr"/>
     </row>
@@ -31921,7 +32285,11 @@
       <c r="C499" s="9" t="n">
         <v>46181</v>
       </c>
-      <c r="D499" s="8" t="inlineStr"/>
+      <c r="D499" s="8" t="inlineStr">
+        <is>
+          <t>DE.UGS.GE09.STR.S1</t>
+        </is>
+      </c>
       <c r="E499" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BB05 - Earthing and Bonding Below Base Slab Design: DE.UGS.GE09.STR.S1.D3_Rev C02</t>
@@ -31959,7 +32327,7 @@
       <c r="W499" s="8" t="inlineStr"/>
       <c r="X499" s="8" t="inlineStr"/>
       <c r="Y499" s="9" t="n">
-        <v>46186.23724723104</v>
+        <v>46186.27264121475</v>
       </c>
       <c r="Z499" s="8" t="inlineStr"/>
     </row>
@@ -31973,7 +32341,11 @@
       <c r="C500" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="D500" s="4" t="inlineStr"/>
+      <c r="D500" s="4" t="inlineStr">
+        <is>
+          <t>DE.ZNE.ZN06.UTI.U2</t>
+        </is>
+      </c>
       <c r="E500" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Utility Station Tie-in, SL and SWD - Z0046 Package: DE.ZNE.ZN06.UTI.U2.D2_Rev.C02</t>
@@ -32015,7 +32387,7 @@
       <c r="W500" s="4" t="inlineStr"/>
       <c r="X500" s="4" t="inlineStr"/>
       <c r="Y500" s="5" t="n">
-        <v>46186.23724723124</v>
+        <v>46186.27264121493</v>
       </c>
       <c r="Z500" s="4" t="inlineStr"/>
     </row>
@@ -32071,7 +32443,7 @@
       <c r="W501" s="4" t="inlineStr"/>
       <c r="X501" s="4" t="inlineStr"/>
       <c r="Y501" s="5" t="n">
-        <v>46186.2372472314</v>
+        <v>46186.27264121555</v>
       </c>
       <c r="Z501" s="4" t="inlineStr"/>
     </row>
@@ -32135,7 +32507,7 @@
       <c r="W502" s="8" t="inlineStr"/>
       <c r="X502" s="8" t="inlineStr"/>
       <c r="Y502" s="9" t="n">
-        <v>46186.23724723162</v>
+        <v>46186.27264121596</v>
       </c>
       <c r="Z502" s="8" t="inlineStr"/>
     </row>
@@ -32199,7 +32571,7 @@
       <c r="W503" s="8" t="inlineStr"/>
       <c r="X503" s="8" t="inlineStr"/>
       <c r="Y503" s="9" t="n">
-        <v>46186.23724723182</v>
+        <v>46186.27264121622</v>
       </c>
       <c r="Z503" s="8" t="inlineStr"/>
     </row>
@@ -32263,7 +32635,7 @@
       <c r="W504" s="8" t="inlineStr"/>
       <c r="X504" s="8" t="inlineStr"/>
       <c r="Y504" s="9" t="n">
-        <v>46186.23724723201</v>
+        <v>46186.27264121643</v>
       </c>
       <c r="Z504" s="8" t="inlineStr"/>
     </row>
@@ -32277,7 +32649,11 @@
       <c r="C505" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="D505" s="4" t="inlineStr"/>
+      <c r="D505" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST08.STR.V2</t>
+        </is>
+      </c>
       <c r="E505" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Stretch 08.1 - Viaduct Structure Pierhead - 2SP Part 2 (PM246) : DE.VDT.ST08.STR.V2.D3_Rev.C01</t>
@@ -32319,7 +32695,7 @@
       <c r="W505" s="4" t="inlineStr"/>
       <c r="X505" s="4" t="inlineStr"/>
       <c r="Y505" s="5" t="n">
-        <v>46186.23724723324</v>
+        <v>46186.27264121664</v>
       </c>
       <c r="Z505" s="4" t="inlineStr"/>
     </row>
@@ -32387,7 +32763,7 @@
       <c r="W506" s="4" t="inlineStr"/>
       <c r="X506" s="4" t="inlineStr"/>
       <c r="Y506" s="5" t="n">
-        <v>46186.23724723353</v>
+        <v>46186.27264121686</v>
       </c>
       <c r="Z506" s="4" t="inlineStr"/>
     </row>
@@ -32401,7 +32777,11 @@
       <c r="C507" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="D507" s="4" t="inlineStr"/>
+      <c r="D507" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST09.STR.V1</t>
+        </is>
+      </c>
       <c r="E507" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Stretch 09.2 - Viaduct Structure Substructure - Transition Ramps-4 Concrete Out Line : DE.VDT.ST09.STR.V1.D3_Rev.C01</t>
@@ -32443,7 +32823,7 @@
       <c r="W507" s="4" t="inlineStr"/>
       <c r="X507" s="4" t="inlineStr"/>
       <c r="Y507" s="5" t="n">
-        <v>46186.23724723375</v>
+        <v>46186.2726412171</v>
       </c>
       <c r="Z507" s="4" t="inlineStr"/>
     </row>
@@ -32511,7 +32891,7 @@
       <c r="W508" s="4" t="inlineStr"/>
       <c r="X508" s="4" t="inlineStr"/>
       <c r="Y508" s="5" t="n">
-        <v>46186.23724723401</v>
+        <v>46186.2726412179</v>
       </c>
       <c r="Z508" s="4" t="inlineStr"/>
     </row>
@@ -32579,7 +32959,7 @@
       <c r="W509" s="4" t="inlineStr"/>
       <c r="X509" s="4" t="inlineStr"/>
       <c r="Y509" s="5" t="n">
-        <v>46186.23724723424</v>
+        <v>46186.27264121821</v>
       </c>
       <c r="Z509" s="4" t="inlineStr"/>
     </row>
@@ -32593,7 +32973,11 @@
       <c r="C510" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="D510" s="4" t="inlineStr"/>
+      <c r="D510" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST03.STR.V2</t>
+        </is>
+      </c>
       <c r="E510" s="6" t="inlineStr">
         <is>
           <t>Shop Drawing Submission - Stretch-03 - Viaduct Structure Pierhead -PM74, Inserts, Coordinates &amp; Bearing BBS : DE.VDT.ST03.STR.V2.D5_Rev.C01</t>
@@ -32631,7 +33015,7 @@
       <c r="W510" s="4" t="inlineStr"/>
       <c r="X510" s="4" t="inlineStr"/>
       <c r="Y510" s="5" t="n">
-        <v>46186.23724723444</v>
+        <v>46186.27264121846</v>
       </c>
       <c r="Z510" s="4" t="inlineStr"/>
     </row>
@@ -32645,7 +33029,11 @@
       <c r="C511" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="D511" s="4" t="inlineStr"/>
+      <c r="D511" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.GN00.STR.01</t>
+        </is>
+      </c>
       <c r="E511" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 -Global - Viaduct Structure ISO Span Superstructure-Global ISO Pkg : DE.VDT.GN00.STR.01.D3_Rev.C01</t>
@@ -32687,7 +33075,7 @@
       <c r="W511" s="4" t="inlineStr"/>
       <c r="X511" s="4" t="inlineStr"/>
       <c r="Y511" s="5" t="n">
-        <v>46186.23724723458</v>
+        <v>46186.27264121878</v>
       </c>
       <c r="Z511" s="4" t="inlineStr"/>
     </row>
@@ -32755,7 +33143,7 @@
       <c r="W512" s="4" t="inlineStr"/>
       <c r="X512" s="4" t="inlineStr"/>
       <c r="Y512" s="5" t="n">
-        <v>46186.23724723481</v>
+        <v>46186.27264121914</v>
       </c>
       <c r="Z512" s="4" t="inlineStr"/>
     </row>
@@ -32823,7 +33211,7 @@
       <c r="W513" s="4" t="inlineStr"/>
       <c r="X513" s="4" t="inlineStr"/>
       <c r="Y513" s="5" t="n">
-        <v>46186.23724723508</v>
+        <v>46186.27264121948</v>
       </c>
       <c r="Z513" s="4" t="inlineStr"/>
     </row>
@@ -32891,7 +33279,7 @@
       <c r="W514" s="4" t="inlineStr"/>
       <c r="X514" s="4" t="inlineStr"/>
       <c r="Y514" s="5" t="n">
-        <v>46186.23724723534</v>
+        <v>46186.27264121982</v>
       </c>
       <c r="Z514" s="4" t="inlineStr"/>
     </row>
@@ -32959,7 +33347,7 @@
       <c r="W515" s="4" t="inlineStr"/>
       <c r="X515" s="4" t="inlineStr"/>
       <c r="Y515" s="5" t="n">
-        <v>46186.23724723556</v>
+        <v>46186.27264122004</v>
       </c>
       <c r="Z515" s="4" t="inlineStr"/>
     </row>
@@ -33027,7 +33415,7 @@
       <c r="W516" s="4" t="inlineStr"/>
       <c r="X516" s="4" t="inlineStr"/>
       <c r="Y516" s="5" t="n">
-        <v>46186.2372472358</v>
+        <v>46186.2726412203</v>
       </c>
       <c r="Z516" s="4" t="inlineStr"/>
     </row>
@@ -33099,7 +33487,7 @@
       <c r="W517" s="4" t="inlineStr"/>
       <c r="X517" s="4" t="inlineStr"/>
       <c r="Y517" s="5" t="n">
-        <v>46186.23724723601</v>
+        <v>46186.27264122051</v>
       </c>
       <c r="Z517" s="4" t="inlineStr"/>
     </row>
@@ -33171,7 +33559,7 @@
       <c r="W518" s="4" t="inlineStr"/>
       <c r="X518" s="4" t="inlineStr"/>
       <c r="Y518" s="5" t="n">
-        <v>46186.23724723622</v>
+        <v>46186.27264122073</v>
       </c>
       <c r="Z518" s="4" t="inlineStr"/>
     </row>
@@ -33243,7 +33631,7 @@
       <c r="W519" s="4" t="inlineStr"/>
       <c r="X519" s="4" t="inlineStr"/>
       <c r="Y519" s="5" t="n">
-        <v>46186.23724723641</v>
+        <v>46186.27264122092</v>
       </c>
       <c r="Z519" s="4" t="inlineStr"/>
     </row>
@@ -33315,7 +33703,7 @@
       <c r="W520" s="4" t="inlineStr"/>
       <c r="X520" s="4" t="inlineStr"/>
       <c r="Y520" s="5" t="n">
-        <v>46186.2372472369</v>
+        <v>46186.2726412211</v>
       </c>
       <c r="Z520" s="4" t="inlineStr"/>
     </row>
@@ -33387,7 +33775,7 @@
       <c r="W521" s="4" t="inlineStr"/>
       <c r="X521" s="4" t="inlineStr"/>
       <c r="Y521" s="5" t="n">
-        <v>46186.23724723719</v>
+        <v>46186.27264122127</v>
       </c>
       <c r="Z521" s="4" t="inlineStr"/>
     </row>
@@ -33455,7 +33843,7 @@
       <c r="W522" s="4" t="inlineStr"/>
       <c r="X522" s="4" t="inlineStr"/>
       <c r="Y522" s="5" t="n">
-        <v>46186.23724723959</v>
+        <v>46186.27264122431</v>
       </c>
       <c r="Z522" s="4" t="inlineStr"/>
     </row>
@@ -33469,7 +33857,11 @@
       <c r="C523" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="D523" s="4" t="inlineStr"/>
+      <c r="D523" s="4" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE10.ARC.A2</t>
+        </is>
+      </c>
       <c r="E523" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP2 - Elevated Station – BB04 Architecture: DE.ELS.GE10.ARC.A2.D2_Rev.C01</t>
@@ -33511,7 +33903,7 @@
       <c r="W523" s="4" t="inlineStr"/>
       <c r="X523" s="4" t="inlineStr"/>
       <c r="Y523" s="5" t="n">
-        <v>46186.23724723983</v>
+        <v>46186.27264122463</v>
       </c>
       <c r="Z523" s="4" t="inlineStr"/>
     </row>
@@ -33579,7 +33971,7 @@
       <c r="W524" s="4" t="inlineStr"/>
       <c r="X524" s="4" t="inlineStr"/>
       <c r="Y524" s="5" t="n">
-        <v>46186.23724724008</v>
+        <v>46186.27264122487</v>
       </c>
       <c r="Z524" s="4" t="inlineStr"/>
     </row>
@@ -33593,7 +33985,11 @@
       <c r="C525" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="D525" s="4" t="inlineStr"/>
+      <c r="D525" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST09.STR.V2</t>
+        </is>
+      </c>
       <c r="E525" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Stretch-09.1 - Viaduct Structure Pierhead ISO &amp; 2SP Span : DE.VDT.ST09.STR.V2.D3_Rev.C01</t>
@@ -33635,7 +34031,7 @@
       <c r="W525" s="4" t="inlineStr"/>
       <c r="X525" s="4" t="inlineStr"/>
       <c r="Y525" s="5" t="n">
-        <v>46186.23724724026</v>
+        <v>46186.27264122508</v>
       </c>
       <c r="Z525" s="4" t="inlineStr"/>
     </row>
@@ -33703,7 +34099,7 @@
       <c r="W526" s="4" t="inlineStr"/>
       <c r="X526" s="4" t="inlineStr"/>
       <c r="Y526" s="5" t="n">
-        <v>46186.23724724047</v>
+        <v>46186.27264122529</v>
       </c>
       <c r="Z526" s="4" t="inlineStr"/>
     </row>
@@ -33771,7 +34167,7 @@
       <c r="W527" s="4" t="inlineStr"/>
       <c r="X527" s="4" t="inlineStr"/>
       <c r="Y527" s="5" t="n">
-        <v>46186.23724724067</v>
+        <v>46186.2726412255</v>
       </c>
       <c r="Z527" s="4" t="inlineStr"/>
     </row>
@@ -33839,7 +34235,7 @@
       <c r="W528" s="4" t="inlineStr"/>
       <c r="X528" s="4" t="inlineStr"/>
       <c r="Y528" s="5" t="n">
-        <v>46186.23724724088</v>
+        <v>46186.2726412257</v>
       </c>
       <c r="Z528" s="4" t="inlineStr"/>
     </row>
@@ -33907,7 +34303,7 @@
       <c r="W529" s="4" t="inlineStr"/>
       <c r="X529" s="4" t="inlineStr"/>
       <c r="Y529" s="5" t="n">
-        <v>46186.2372472411</v>
+        <v>46186.2726412265</v>
       </c>
       <c r="Z529" s="4" t="inlineStr"/>
     </row>
@@ -33975,7 +34371,7 @@
       <c r="W530" s="4" t="inlineStr"/>
       <c r="X530" s="4" t="inlineStr"/>
       <c r="Y530" s="5" t="n">
-        <v>46186.23724724133</v>
+        <v>46186.27264122689</v>
       </c>
       <c r="Z530" s="4" t="inlineStr"/>
     </row>
@@ -34043,7 +34439,7 @@
       <c r="W531" s="4" t="inlineStr"/>
       <c r="X531" s="4" t="inlineStr"/>
       <c r="Y531" s="5" t="n">
-        <v>46186.23724724153</v>
+        <v>46186.27264122711</v>
       </c>
       <c r="Z531" s="4" t="inlineStr"/>
     </row>
@@ -34111,7 +34507,7 @@
       <c r="W532" s="4" t="inlineStr"/>
       <c r="X532" s="4" t="inlineStr"/>
       <c r="Y532" s="5" t="n">
-        <v>46186.23724724173</v>
+        <v>46186.27264122735</v>
       </c>
       <c r="Z532" s="4" t="inlineStr"/>
     </row>
@@ -34125,7 +34521,11 @@
       <c r="C533" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="D533" s="4" t="inlineStr"/>
+      <c r="D533" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.GN00.STR.05</t>
+        </is>
+      </c>
       <c r="E533" s="6" t="inlineStr">
         <is>
           <t>Re: Shop Drawing Submission - Global - Viaduct Structure Pierhead - Balanced Cantilever PHR-BC-11:  DE.VDT.GN00.STR.05.D5_Rev.C01</t>
@@ -34163,7 +34563,7 @@
       <c r="W533" s="4" t="inlineStr"/>
       <c r="X533" s="4" t="inlineStr"/>
       <c r="Y533" s="5" t="n">
-        <v>46186.23724724238</v>
+        <v>46186.27264122758</v>
       </c>
       <c r="Z533" s="4" t="inlineStr"/>
     </row>
@@ -34231,7 +34631,7 @@
       <c r="W534" s="4" t="inlineStr"/>
       <c r="X534" s="4" t="inlineStr"/>
       <c r="Y534" s="5" t="n">
-        <v>46186.23724724283</v>
+        <v>46186.27264122779</v>
       </c>
       <c r="Z534" s="4" t="inlineStr"/>
     </row>
@@ -34299,7 +34699,7 @@
       <c r="W535" s="4" t="inlineStr"/>
       <c r="X535" s="4" t="inlineStr"/>
       <c r="Y535" s="5" t="n">
-        <v>46186.23724724309</v>
+        <v>46186.27264122802</v>
       </c>
       <c r="Z535" s="4" t="inlineStr"/>
     </row>
@@ -34313,7 +34713,11 @@
       <c r="C536" s="9" t="n">
         <v>46181</v>
       </c>
-      <c r="D536" s="8" t="inlineStr"/>
+      <c r="D536" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE00.ARC.A2</t>
+        </is>
+      </c>
       <c r="E536" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - BG31 Creek Interchange Station Architectural : DE.ELS.GE00.ARC.A2.D2_Rev.C02</t>
@@ -34351,7 +34755,7 @@
       <c r="W536" s="8" t="inlineStr"/>
       <c r="X536" s="8" t="inlineStr"/>
       <c r="Y536" s="9" t="n">
-        <v>46186.23724724328</v>
+        <v>46186.27264122824</v>
       </c>
       <c r="Z536" s="8" t="inlineStr"/>
     </row>
@@ -34419,7 +34823,7 @@
       <c r="W537" s="4" t="inlineStr"/>
       <c r="X537" s="4" t="inlineStr"/>
       <c r="Y537" s="5" t="n">
-        <v>46186.23724724349</v>
+        <v>46186.27264122844</v>
       </c>
       <c r="Z537" s="4" t="inlineStr"/>
     </row>
@@ -34487,7 +34891,7 @@
       <c r="W538" s="4" t="inlineStr"/>
       <c r="X538" s="4" t="inlineStr"/>
       <c r="Y538" s="5" t="n">
-        <v>46186.23724724371</v>
+        <v>46186.27264122864</v>
       </c>
       <c r="Z538" s="4" t="inlineStr"/>
     </row>
@@ -34539,7 +34943,7 @@
       <c r="W539" s="4" t="inlineStr"/>
       <c r="X539" s="4" t="inlineStr"/>
       <c r="Y539" s="5" t="n">
-        <v>46186.23724724391</v>
+        <v>46186.27264122888</v>
       </c>
       <c r="Z539" s="4" t="inlineStr"/>
     </row>
@@ -34607,7 +35011,7 @@
       <c r="W540" s="4" t="inlineStr"/>
       <c r="X540" s="4" t="inlineStr"/>
       <c r="Y540" s="5" t="n">
-        <v>46186.23724724412</v>
+        <v>46186.27264122952</v>
       </c>
       <c r="Z540" s="4" t="inlineStr"/>
     </row>
@@ -34675,7 +35079,7 @@
       <c r="W541" s="4" t="inlineStr"/>
       <c r="X541" s="4" t="inlineStr"/>
       <c r="Y541" s="5" t="n">
-        <v>46186.23724724471</v>
+        <v>46186.27264122984</v>
       </c>
       <c r="Z541" s="4" t="inlineStr"/>
     </row>
@@ -34743,7 +35147,7 @@
       <c r="W542" s="4" t="inlineStr"/>
       <c r="X542" s="4" t="inlineStr"/>
       <c r="Y542" s="5" t="n">
-        <v>46186.23724724502</v>
+        <v>46186.27264123007</v>
       </c>
       <c r="Z542" s="4" t="inlineStr"/>
     </row>
@@ -34807,7 +35211,7 @@
       <c r="W543" s="4" t="inlineStr"/>
       <c r="X543" s="4" t="inlineStr"/>
       <c r="Y543" s="5" t="n">
-        <v>46186.23724724527</v>
+        <v>46186.27264123028</v>
       </c>
       <c r="Z543" s="4" t="inlineStr"/>
     </row>
@@ -34875,7 +35279,7 @@
       <c r="W544" s="4" t="inlineStr"/>
       <c r="X544" s="4" t="inlineStr"/>
       <c r="Y544" s="5" t="n">
-        <v>46186.23724724547</v>
+        <v>46186.27264123048</v>
       </c>
       <c r="Z544" s="4" t="inlineStr"/>
     </row>
@@ -34943,7 +35347,7 @@
       <c r="W545" s="4" t="inlineStr"/>
       <c r="X545" s="4" t="inlineStr"/>
       <c r="Y545" s="5" t="n">
-        <v>46186.23724724568</v>
+        <v>46186.27264123067</v>
       </c>
       <c r="Z545" s="4" t="inlineStr"/>
     </row>
@@ -35011,7 +35415,7 @@
       <c r="W546" s="4" t="inlineStr"/>
       <c r="X546" s="4" t="inlineStr"/>
       <c r="Y546" s="5" t="n">
-        <v>46186.23724724587</v>
+        <v>46186.27264123085</v>
       </c>
       <c r="Z546" s="4" t="inlineStr"/>
     </row>
@@ -35079,7 +35483,7 @@
       <c r="W547" s="4" t="inlineStr"/>
       <c r="X547" s="4" t="inlineStr"/>
       <c r="Y547" s="5" t="n">
-        <v>46186.23724724604</v>
+        <v>46186.27264123102</v>
       </c>
       <c r="Z547" s="4" t="inlineStr"/>
     </row>
@@ -35147,7 +35551,7 @@
       <c r="W548" s="4" t="inlineStr"/>
       <c r="X548" s="4" t="inlineStr"/>
       <c r="Y548" s="5" t="n">
-        <v>46186.23724724623</v>
+        <v>46186.27264123118</v>
       </c>
       <c r="Z548" s="4" t="inlineStr"/>
     </row>
@@ -35219,7 +35623,7 @@
       <c r="W549" s="4" t="inlineStr"/>
       <c r="X549" s="4" t="inlineStr"/>
       <c r="Y549" s="5" t="n">
-        <v>46186.2372472464</v>
+        <v>46186.27264123134</v>
       </c>
       <c r="Z549" s="4" t="inlineStr"/>
     </row>
@@ -35287,7 +35691,7 @@
       <c r="W550" s="4" t="inlineStr"/>
       <c r="X550" s="4" t="inlineStr"/>
       <c r="Y550" s="5" t="n">
-        <v>46186.23724724661</v>
+        <v>46186.27264123155</v>
       </c>
       <c r="Z550" s="4" t="inlineStr"/>
     </row>
@@ -35355,7 +35759,7 @@
       <c r="W551" s="4" t="inlineStr"/>
       <c r="X551" s="4" t="inlineStr"/>
       <c r="Y551" s="5" t="n">
-        <v>46186.23724724681</v>
+        <v>46186.27264123174</v>
       </c>
       <c r="Z551" s="4" t="inlineStr"/>
     </row>
@@ -35423,7 +35827,7 @@
       <c r="W552" s="4" t="inlineStr"/>
       <c r="X552" s="4" t="inlineStr"/>
       <c r="Y552" s="5" t="n">
-        <v>46186.23724724699</v>
+        <v>46186.27264123192</v>
       </c>
       <c r="Z552" s="4" t="inlineStr"/>
     </row>
@@ -35437,7 +35841,11 @@
       <c r="C553" s="5" t="n">
         <v>46179</v>
       </c>
-      <c r="D553" s="4" t="inlineStr"/>
+      <c r="D553" s="4" t="inlineStr">
+        <is>
+          <t>DE.ANX.AX06.STR.S0</t>
+        </is>
+      </c>
       <c r="E553" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP2 - Annex Structure - BL-EES14 Structure : DE.ANX.AX06.STR.S0.D2_Rev.C01</t>
@@ -35479,7 +35887,7 @@
       <c r="W553" s="4" t="inlineStr"/>
       <c r="X553" s="4" t="inlineStr"/>
       <c r="Y553" s="5" t="n">
-        <v>46186.23724724715</v>
+        <v>46186.27264123211</v>
       </c>
       <c r="Z553" s="4" t="inlineStr"/>
     </row>
@@ -35547,7 +35955,7 @@
       <c r="W554" s="4" t="inlineStr"/>
       <c r="X554" s="4" t="inlineStr"/>
       <c r="Y554" s="5" t="n">
-        <v>46186.23724724737</v>
+        <v>46186.27264123234</v>
       </c>
       <c r="Z554" s="4" t="inlineStr"/>
     </row>
@@ -35619,7 +36027,7 @@
       <c r="W555" s="4" t="inlineStr"/>
       <c r="X555" s="4" t="inlineStr"/>
       <c r="Y555" s="5" t="n">
-        <v>46186.23724724755</v>
+        <v>46186.27264123252</v>
       </c>
       <c r="Z555" s="4" t="inlineStr"/>
     </row>
@@ -35687,7 +36095,7 @@
       <c r="W556" s="4" t="inlineStr"/>
       <c r="X556" s="4" t="inlineStr"/>
       <c r="Y556" s="5" t="n">
-        <v>46186.23724724774</v>
+        <v>46186.27264123271</v>
       </c>
       <c r="Z556" s="4" t="inlineStr"/>
     </row>
@@ -35701,7 +36109,11 @@
       <c r="C557" s="5" t="n">
         <v>46179</v>
       </c>
-      <c r="D557" s="4" t="inlineStr"/>
+      <c r="D557" s="4" t="inlineStr">
+        <is>
+          <t>DE.ANX.AX09.STR.S1</t>
+        </is>
+      </c>
       <c r="E557" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Annex Structure - BL-EES17 Structure D-Wall -: DE.ANX.AX09.STR.S1.D3_Rev.C01</t>
@@ -35743,7 +36155,7 @@
       <c r="W557" s="4" t="inlineStr"/>
       <c r="X557" s="4" t="inlineStr"/>
       <c r="Y557" s="5" t="n">
-        <v>46186.2372472479</v>
+        <v>46186.27264123324</v>
       </c>
       <c r="Z557" s="4" t="inlineStr"/>
     </row>
@@ -35757,7 +36169,11 @@
       <c r="C558" s="5" t="n">
         <v>46179</v>
       </c>
-      <c r="D558" s="4" t="inlineStr"/>
+      <c r="D558" s="4" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE03.ARC.A2</t>
+        </is>
+      </c>
       <c r="E558" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - BG34 Station - Architecture Package : DE.ELS.GE03.ARC.A2.D2_Rev.C03 (Part 2 Submission)</t>
@@ -35795,7 +36211,7 @@
       <c r="W558" s="4" t="inlineStr"/>
       <c r="X558" s="4" t="inlineStr"/>
       <c r="Y558" s="5" t="n">
-        <v>46186.23724724806</v>
+        <v>46186.27264123385</v>
       </c>
       <c r="Z558" s="4" t="inlineStr"/>
     </row>
@@ -35863,7 +36279,7 @@
       <c r="W559" s="4" t="inlineStr"/>
       <c r="X559" s="4" t="inlineStr"/>
       <c r="Y559" s="5" t="n">
-        <v>46186.23724724863</v>
+        <v>46186.27264123418</v>
       </c>
       <c r="Z559" s="4" t="inlineStr"/>
     </row>
@@ -35931,7 +36347,7 @@
       <c r="W560" s="4" t="inlineStr"/>
       <c r="X560" s="4" t="inlineStr"/>
       <c r="Y560" s="5" t="n">
-        <v>46186.23724724892</v>
+        <v>46186.27264123442</v>
       </c>
       <c r="Z560" s="4" t="inlineStr"/>
     </row>
@@ -35995,7 +36411,7 @@
       <c r="W561" s="4" t="inlineStr"/>
       <c r="X561" s="4" t="inlineStr"/>
       <c r="Y561" s="5" t="n">
-        <v>46186.23724724947</v>
+        <v>46186.27264123464</v>
       </c>
       <c r="Z561" s="4" t="inlineStr"/>
     </row>
@@ -36063,7 +36479,7 @@
       <c r="W562" s="4" t="inlineStr"/>
       <c r="X562" s="4" t="inlineStr"/>
       <c r="Y562" s="5" t="n">
-        <v>46186.23724724986</v>
+        <v>46186.27264123492</v>
       </c>
       <c r="Z562" s="4" t="inlineStr"/>
     </row>
@@ -36131,7 +36547,7 @@
       <c r="W563" s="4" t="inlineStr"/>
       <c r="X563" s="4" t="inlineStr"/>
       <c r="Y563" s="5" t="n">
-        <v>46186.23724725017</v>
+        <v>46186.2726412352</v>
       </c>
       <c r="Z563" s="4" t="inlineStr"/>
     </row>
@@ -36145,7 +36561,11 @@
       <c r="C564" s="5" t="n">
         <v>46179</v>
       </c>
-      <c r="D564" s="4" t="inlineStr"/>
+      <c r="D564" s="4" t="inlineStr">
+        <is>
+          <t>DE.DPT.GN00.LDS.L0</t>
+        </is>
+      </c>
       <c r="E564" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP2 - Al Ruwayyah Depot Landscape Design: DE.DPT.GN00.LDS.L0.D2_Rev C01</t>
@@ -36187,7 +36607,7 @@
       <c r="W564" s="4" t="inlineStr"/>
       <c r="X564" s="4" t="inlineStr"/>
       <c r="Y564" s="5" t="n">
-        <v>46186.23724725037</v>
+        <v>46186.2726412354</v>
       </c>
       <c r="Z564" s="4" t="inlineStr"/>
     </row>
@@ -36255,7 +36675,7 @@
       <c r="W565" s="4" t="inlineStr"/>
       <c r="X565" s="4" t="inlineStr"/>
       <c r="Y565" s="5" t="n">
-        <v>46186.2372472506</v>
+        <v>46186.27264123559</v>
       </c>
       <c r="Z565" s="4" t="inlineStr"/>
     </row>
@@ -36323,7 +36743,7 @@
       <c r="W566" s="4" t="inlineStr"/>
       <c r="X566" s="4" t="inlineStr"/>
       <c r="Y566" s="5" t="n">
-        <v>46186.23724725081</v>
+        <v>46186.27264123577</v>
       </c>
       <c r="Z566" s="4" t="inlineStr"/>
     </row>
@@ -36391,7 +36811,7 @@
       <c r="W567" s="4" t="inlineStr"/>
       <c r="X567" s="4" t="inlineStr"/>
       <c r="Y567" s="5" t="n">
-        <v>46186.237247251</v>
+        <v>46186.27264123596</v>
       </c>
       <c r="Z567" s="4" t="inlineStr"/>
     </row>
@@ -36405,7 +36825,11 @@
       <c r="C568" s="5" t="n">
         <v>46179</v>
       </c>
-      <c r="D568" s="4" t="inlineStr"/>
+      <c r="D568" s="4" t="inlineStr">
+        <is>
+          <t>DE.ZNE.ZN03.UTI.U2</t>
+        </is>
+      </c>
       <c r="E568" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP2 - Z0042 (Creek Mainline) Utility Package : DE.ZNE.ZN03.UTI.U2.D2_Rev.C01</t>
@@ -36447,7 +36871,7 @@
       <c r="W568" s="4" t="inlineStr"/>
       <c r="X568" s="4" t="inlineStr"/>
       <c r="Y568" s="5" t="n">
-        <v>46186.23724725116</v>
+        <v>46186.27264123614</v>
       </c>
       <c r="Z568" s="4" t="inlineStr"/>
     </row>
@@ -36519,7 +36943,7 @@
       <c r="W569" s="4" t="inlineStr"/>
       <c r="X569" s="4" t="inlineStr"/>
       <c r="Y569" s="5" t="n">
-        <v>46186.23724725135</v>
+        <v>46186.27264123634</v>
       </c>
       <c r="Z569" s="4" t="inlineStr"/>
     </row>
@@ -36571,7 +36995,7 @@
       <c r="W570" s="4" t="inlineStr"/>
       <c r="X570" s="4" t="inlineStr"/>
       <c r="Y570" s="5" t="n">
-        <v>46186.23724725154</v>
+        <v>46186.27264123655</v>
       </c>
       <c r="Z570" s="4" t="inlineStr"/>
     </row>
@@ -36627,7 +37051,7 @@
       <c r="W571" s="4" t="inlineStr"/>
       <c r="X571" s="4" t="inlineStr"/>
       <c r="Y571" s="5" t="n">
-        <v>46186.2372472517</v>
+        <v>46186.27264123676</v>
       </c>
       <c r="Z571" s="4" t="inlineStr"/>
     </row>
@@ -36683,7 +37107,7 @@
       <c r="W572" s="4" t="inlineStr"/>
       <c r="X572" s="4" t="inlineStr"/>
       <c r="Y572" s="5" t="n">
-        <v>46186.23724725185</v>
+        <v>46186.27264123694</v>
       </c>
       <c r="Z572" s="4" t="inlineStr"/>
     </row>
@@ -36751,7 +37175,7 @@
       <c r="W573" s="4" t="inlineStr"/>
       <c r="X573" s="4" t="inlineStr"/>
       <c r="Y573" s="5" t="n">
-        <v>46186.23724725202</v>
+        <v>46186.27264123714</v>
       </c>
       <c r="Z573" s="4" t="inlineStr"/>
     </row>
@@ -36819,7 +37243,7 @@
       <c r="W574" s="4" t="inlineStr"/>
       <c r="X574" s="4" t="inlineStr"/>
       <c r="Y574" s="5" t="n">
-        <v>46186.23724725223</v>
+        <v>46186.27264123735</v>
       </c>
       <c r="Z574" s="4" t="inlineStr"/>
     </row>
@@ -36887,7 +37311,7 @@
       <c r="W575" s="4" t="inlineStr"/>
       <c r="X575" s="4" t="inlineStr"/>
       <c r="Y575" s="5" t="n">
-        <v>46186.23724725243</v>
+        <v>46186.27264123755</v>
       </c>
       <c r="Z575" s="4" t="inlineStr"/>
     </row>
@@ -36959,7 +37383,7 @@
       <c r="W576" s="4" t="inlineStr"/>
       <c r="X576" s="4" t="inlineStr"/>
       <c r="Y576" s="5" t="n">
-        <v>46186.23724725262</v>
+        <v>46186.27264123773</v>
       </c>
       <c r="Z576" s="4" t="inlineStr"/>
     </row>
@@ -37027,7 +37451,7 @@
       <c r="W577" s="4" t="inlineStr"/>
       <c r="X577" s="4" t="inlineStr"/>
       <c r="Y577" s="5" t="n">
-        <v>46186.23724725284</v>
+        <v>46186.27264123794</v>
       </c>
       <c r="Z577" s="4" t="inlineStr"/>
     </row>
@@ -37095,7 +37519,7 @@
       <c r="W578" s="4" t="inlineStr"/>
       <c r="X578" s="4" t="inlineStr"/>
       <c r="Y578" s="5" t="n">
-        <v>46186.23724725303</v>
+        <v>46186.27264123815</v>
       </c>
       <c r="Z578" s="4" t="inlineStr"/>
     </row>
@@ -37163,7 +37587,7 @@
       <c r="W579" s="4" t="inlineStr"/>
       <c r="X579" s="4" t="inlineStr"/>
       <c r="Y579" s="5" t="n">
-        <v>46186.23724725322</v>
+        <v>46186.27264123836</v>
       </c>
       <c r="Z579" s="4" t="inlineStr"/>
     </row>
@@ -37231,7 +37655,7 @@
       <c r="W580" s="4" t="inlineStr"/>
       <c r="X580" s="4" t="inlineStr"/>
       <c r="Y580" s="5" t="n">
-        <v>46186.23724725341</v>
+        <v>46186.27264123854</v>
       </c>
       <c r="Z580" s="4" t="inlineStr"/>
     </row>
@@ -37299,7 +37723,7 @@
       <c r="W581" s="4" t="inlineStr"/>
       <c r="X581" s="4" t="inlineStr"/>
       <c r="Y581" s="5" t="n">
-        <v>46186.23724725359</v>
+        <v>46186.27264123873</v>
       </c>
       <c r="Z581" s="4" t="inlineStr"/>
     </row>
@@ -37367,7 +37791,7 @@
       <c r="W582" s="4" t="inlineStr"/>
       <c r="X582" s="4" t="inlineStr"/>
       <c r="Y582" s="5" t="n">
-        <v>46186.23724725376</v>
+        <v>46186.2726412389</v>
       </c>
       <c r="Z582" s="4" t="inlineStr"/>
     </row>
@@ -37431,7 +37855,7 @@
       <c r="W583" s="8" t="inlineStr"/>
       <c r="X583" s="8" t="inlineStr"/>
       <c r="Y583" s="9" t="n">
-        <v>46186.23724725396</v>
+        <v>46186.27264123912</v>
       </c>
       <c r="Z583" s="8" t="inlineStr"/>
     </row>
@@ -37495,7 +37919,7 @@
       <c r="W584" s="8" t="inlineStr"/>
       <c r="X584" s="8" t="inlineStr"/>
       <c r="Y584" s="9" t="n">
-        <v>46186.23724725427</v>
+        <v>46186.27264123936</v>
       </c>
       <c r="Z584" s="8" t="inlineStr"/>
     </row>
@@ -37559,7 +37983,7 @@
       <c r="W585" s="8" t="inlineStr"/>
       <c r="X585" s="8" t="inlineStr"/>
       <c r="Y585" s="9" t="n">
-        <v>46186.23724725447</v>
+        <v>46186.27264123955</v>
       </c>
       <c r="Z585" s="8" t="inlineStr"/>
     </row>
@@ -37627,7 +38051,7 @@
       <c r="W586" s="8" t="inlineStr"/>
       <c r="X586" s="8" t="inlineStr"/>
       <c r="Y586" s="9" t="n">
-        <v>46186.2372472547</v>
+        <v>46186.27264124022</v>
       </c>
       <c r="Z586" s="8" t="inlineStr"/>
     </row>
@@ -37695,7 +38119,7 @@
       <c r="W587" s="4" t="inlineStr"/>
       <c r="X587" s="4" t="inlineStr"/>
       <c r="Y587" s="5" t="n">
-        <v>46186.23724725488</v>
+        <v>46186.27264124049</v>
       </c>
       <c r="Z587" s="4" t="inlineStr"/>
     </row>
@@ -37763,7 +38187,7 @@
       <c r="W588" s="8" t="inlineStr"/>
       <c r="X588" s="8" t="inlineStr"/>
       <c r="Y588" s="9" t="n">
-        <v>46186.23724725507</v>
+        <v>46186.27264124071</v>
       </c>
       <c r="Z588" s="8" t="inlineStr"/>
     </row>
@@ -37831,7 +38255,7 @@
       <c r="W589" s="8" t="inlineStr"/>
       <c r="X589" s="8" t="inlineStr"/>
       <c r="Y589" s="9" t="n">
-        <v>46186.23724725525</v>
+        <v>46186.27264124102</v>
       </c>
       <c r="Z589" s="8" t="inlineStr"/>
     </row>
@@ -37899,7 +38323,7 @@
       <c r="W590" s="4" t="inlineStr"/>
       <c r="X590" s="4" t="inlineStr"/>
       <c r="Y590" s="5" t="n">
-        <v>46186.23724725621</v>
+        <v>46186.27264124157</v>
       </c>
       <c r="Z590" s="4" t="inlineStr"/>
     </row>
@@ -37967,7 +38391,7 @@
       <c r="W591" s="8" t="inlineStr"/>
       <c r="X591" s="8" t="inlineStr"/>
       <c r="Y591" s="9" t="n">
-        <v>46186.23724725653</v>
+        <v>46186.27264124189</v>
       </c>
       <c r="Z591" s="8" t="inlineStr"/>
     </row>
@@ -38035,7 +38459,7 @@
       <c r="W592" s="4" t="inlineStr"/>
       <c r="X592" s="4" t="inlineStr"/>
       <c r="Y592" s="5" t="n">
-        <v>46186.23724725677</v>
+        <v>46186.27264124213</v>
       </c>
       <c r="Z592" s="4" t="inlineStr"/>
     </row>
@@ -38099,7 +38523,7 @@
       <c r="W593" s="8" t="inlineStr"/>
       <c r="X593" s="8" t="inlineStr"/>
       <c r="Y593" s="9" t="n">
-        <v>46186.23724725699</v>
+        <v>46186.27264124234</v>
       </c>
       <c r="Z593" s="8" t="inlineStr"/>
     </row>
@@ -38167,7 +38591,7 @@
       <c r="W594" s="8" t="inlineStr"/>
       <c r="X594" s="8" t="inlineStr"/>
       <c r="Y594" s="9" t="n">
-        <v>46186.23724725719</v>
+        <v>46186.27264124253</v>
       </c>
       <c r="Z594" s="8" t="inlineStr"/>
     </row>
@@ -38235,7 +38659,7 @@
       <c r="W595" s="8" t="inlineStr"/>
       <c r="X595" s="8" t="inlineStr"/>
       <c r="Y595" s="9" t="n">
-        <v>46186.23724725738</v>
+        <v>46186.27264124272</v>
       </c>
       <c r="Z595" s="8" t="inlineStr"/>
     </row>
@@ -38303,7 +38727,7 @@
       <c r="W596" s="8" t="inlineStr"/>
       <c r="X596" s="8" t="inlineStr"/>
       <c r="Y596" s="9" t="n">
-        <v>46186.2372472576</v>
+        <v>46186.2726412429</v>
       </c>
       <c r="Z596" s="8" t="inlineStr"/>
     </row>
@@ -38371,7 +38795,7 @@
       <c r="W597" s="8" t="inlineStr"/>
       <c r="X597" s="8" t="inlineStr"/>
       <c r="Y597" s="9" t="n">
-        <v>46186.23724725784</v>
+        <v>46186.27264124314</v>
       </c>
       <c r="Z597" s="8" t="inlineStr"/>
     </row>
@@ -38439,7 +38863,7 @@
       <c r="W598" s="8" t="inlineStr"/>
       <c r="X598" s="8" t="inlineStr"/>
       <c r="Y598" s="9" t="n">
-        <v>46186.23724725805</v>
+        <v>46186.27264124335</v>
       </c>
       <c r="Z598" s="8" t="inlineStr"/>
     </row>
@@ -38507,7 +38931,7 @@
       <c r="W599" s="8" t="inlineStr"/>
       <c r="X599" s="8" t="inlineStr"/>
       <c r="Y599" s="9" t="n">
-        <v>46186.23724725825</v>
+        <v>46186.27264124353</v>
       </c>
       <c r="Z599" s="8" t="inlineStr"/>
     </row>
@@ -38571,7 +38995,7 @@
       <c r="W600" s="8" t="inlineStr"/>
       <c r="X600" s="8" t="inlineStr"/>
       <c r="Y600" s="9" t="n">
-        <v>46186.23724725845</v>
+        <v>46186.27264124373</v>
       </c>
       <c r="Z600" s="8" t="inlineStr"/>
     </row>
@@ -38639,7 +39063,7 @@
       <c r="W601" s="8" t="inlineStr"/>
       <c r="X601" s="8" t="inlineStr"/>
       <c r="Y601" s="9" t="n">
-        <v>46186.23724725867</v>
+        <v>46186.27264124394</v>
       </c>
       <c r="Z601" s="8" t="inlineStr"/>
     </row>
@@ -38703,7 +39127,7 @@
       <c r="W602" s="8" t="inlineStr"/>
       <c r="X602" s="8" t="inlineStr"/>
       <c r="Y602" s="9" t="n">
-        <v>46186.23724725887</v>
+        <v>46186.27264124414</v>
       </c>
       <c r="Z602" s="8" t="inlineStr"/>
     </row>
@@ -38717,7 +39141,11 @@
       <c r="C603" s="9" t="n">
         <v>46179</v>
       </c>
-      <c r="D603" s="8" t="inlineStr"/>
+      <c r="D603" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.GE11.ARC.A2</t>
+        </is>
+      </c>
       <c r="E603" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - BB03 - Academic City Station (GLE-11) Architecture Design Package: DE.ELS.GE11.ARC.A2.D2_Rev C04</t>
@@ -38755,7 +39183,7 @@
       <c r="W603" s="8" t="inlineStr"/>
       <c r="X603" s="8" t="inlineStr"/>
       <c r="Y603" s="9" t="n">
-        <v>46186.23724725905</v>
+        <v>46186.27264124435</v>
       </c>
       <c r="Z603" s="8" t="inlineStr"/>
     </row>
@@ -38823,7 +39251,7 @@
       <c r="W604" s="8" t="inlineStr"/>
       <c r="X604" s="8" t="inlineStr"/>
       <c r="Y604" s="9" t="n">
-        <v>46186.23724725927</v>
+        <v>46186.27264124457</v>
       </c>
       <c r="Z604" s="8" t="inlineStr"/>
     </row>
@@ -38891,7 +39319,7 @@
       <c r="W605" s="8" t="inlineStr"/>
       <c r="X605" s="8" t="inlineStr"/>
       <c r="Y605" s="9" t="n">
-        <v>46186.23724725947</v>
+        <v>46186.27264124477</v>
       </c>
       <c r="Z605" s="8" t="inlineStr"/>
     </row>
@@ -38963,7 +39391,7 @@
       <c r="W606" s="8" t="inlineStr"/>
       <c r="X606" s="8" t="inlineStr"/>
       <c r="Y606" s="9" t="n">
-        <v>46186.23724725969</v>
+        <v>46186.27264124499</v>
       </c>
       <c r="Z606" s="8" t="inlineStr"/>
     </row>
@@ -39031,7 +39459,7 @@
       <c r="W607" s="8" t="inlineStr"/>
       <c r="X607" s="8" t="inlineStr"/>
       <c r="Y607" s="9" t="n">
-        <v>46186.23724726027</v>
+        <v>46186.27264124547</v>
       </c>
       <c r="Z607" s="8" t="inlineStr"/>
     </row>
@@ -39045,7 +39473,11 @@
       <c r="C608" s="9" t="n">
         <v>46179</v>
       </c>
-      <c r="D608" s="8" t="inlineStr"/>
+      <c r="D608" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST06.GEO.G1</t>
+        </is>
+      </c>
       <c r="E608" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Technical Note - Working Pile Load Test Viaduct Stretch 6 (PM-172-01) : DE.VDT.ST06.GEO.G1.D3_Rev.C02</t>
@@ -39083,7 +39515,7 @@
       <c r="W608" s="8" t="inlineStr"/>
       <c r="X608" s="8" t="inlineStr"/>
       <c r="Y608" s="9" t="n">
-        <v>46186.23724726046</v>
+        <v>46186.27264124579</v>
       </c>
       <c r="Z608" s="8" t="inlineStr"/>
     </row>
@@ -39151,7 +39583,7 @@
       <c r="W609" s="4" t="inlineStr"/>
       <c r="X609" s="4" t="inlineStr"/>
       <c r="Y609" s="5" t="n">
-        <v>46186.23724726068</v>
+        <v>46186.27264124602</v>
       </c>
       <c r="Z609" s="4" t="inlineStr"/>
     </row>
@@ -39165,7 +39597,11 @@
       <c r="C610" s="9" t="n">
         <v>46179</v>
       </c>
-      <c r="D610" s="8" t="inlineStr"/>
+      <c r="D610" s="8" t="inlineStr">
+        <is>
+          <t>DE.UGS.GE09.STR.S5</t>
+        </is>
+      </c>
       <c r="E610" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Station BB05 - Structure Base Slab : DE.UGS.GE09.STR.S5.D3_Rev.C02</t>
@@ -39203,7 +39639,7 @@
       <c r="W610" s="8" t="inlineStr"/>
       <c r="X610" s="8" t="inlineStr"/>
       <c r="Y610" s="9" t="n">
-        <v>46186.23724726085</v>
+        <v>46186.27264124624</v>
       </c>
       <c r="Z610" s="8" t="inlineStr"/>
     </row>
@@ -39217,7 +39653,11 @@
       <c r="C611" s="9" t="n">
         <v>46179</v>
       </c>
-      <c r="D611" s="8" t="inlineStr"/>
+      <c r="D611" s="8" t="inlineStr">
+        <is>
+          <t>DE.UGS.SB01.STR.S6</t>
+        </is>
+      </c>
       <c r="E611" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Switchbox-Structure Top Slab Design : DE.UGS.SB01.STR.S6.D3_Rev.C01</t>
@@ -39255,7 +39695,7 @@
       <c r="W611" s="8" t="inlineStr"/>
       <c r="X611" s="8" t="inlineStr"/>
       <c r="Y611" s="9" t="n">
-        <v>46186.23724726103</v>
+        <v>46186.27264124688</v>
       </c>
       <c r="Z611" s="8" t="inlineStr"/>
     </row>
@@ -39269,7 +39709,11 @@
       <c r="C612" s="9" t="n">
         <v>46179</v>
       </c>
-      <c r="D612" s="8" t="inlineStr"/>
+      <c r="D612" s="8" t="inlineStr">
+        <is>
+          <t>DE.ELS.RE00.GEO.G1</t>
+        </is>
+      </c>
       <c r="E612" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Technical Note-Working Pile Load test at BR10 (SOP42) : DE.ELS.RE00.GEO.G1.D3_Rev.C01</t>
@@ -39307,7 +39751,7 @@
       <c r="W612" s="8" t="inlineStr"/>
       <c r="X612" s="8" t="inlineStr"/>
       <c r="Y612" s="9" t="n">
-        <v>46186.23724726119</v>
+        <v>46186.27264124715</v>
       </c>
       <c r="Z612" s="8" t="inlineStr"/>
     </row>
@@ -39359,7 +39803,7 @@
       <c r="W613" s="8" t="inlineStr"/>
       <c r="X613" s="8" t="inlineStr"/>
       <c r="Y613" s="9" t="n">
-        <v>46186.23724726134</v>
+        <v>46186.27264124891</v>
       </c>
       <c r="Z613" s="8" t="inlineStr"/>
     </row>
@@ -39423,7 +39867,7 @@
       <c r="W614" s="8" t="inlineStr"/>
       <c r="X614" s="8" t="inlineStr"/>
       <c r="Y614" s="9" t="n">
-        <v>46186.23724726154</v>
+        <v>46186.27264124991</v>
       </c>
       <c r="Z614" s="8" t="inlineStr"/>
     </row>
@@ -39437,7 +39881,11 @@
       <c r="C615" s="9" t="n">
         <v>46179</v>
       </c>
-      <c r="D615" s="8" t="inlineStr"/>
+      <c r="D615" s="8" t="inlineStr">
+        <is>
+          <t>DE.UGS.GE09.STR.S1</t>
+        </is>
+      </c>
       <c r="E615" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - Station BB05 Instrumentation and Monitoring Drawings : DE.UGS.GE09.STR.S1.D3_Rev.C02</t>
@@ -39471,7 +39919,7 @@
       <c r="W615" s="8" t="inlineStr"/>
       <c r="X615" s="8" t="inlineStr"/>
       <c r="Y615" s="9" t="n">
-        <v>46186.23724726173</v>
+        <v>46186.27264125019</v>
       </c>
       <c r="Z615" s="8" t="inlineStr"/>
     </row>
@@ -39535,7 +39983,7 @@
       <c r="W616" s="8" t="inlineStr"/>
       <c r="X616" s="8" t="inlineStr"/>
       <c r="Y616" s="9" t="n">
-        <v>46186.23724726191</v>
+        <v>46186.27264125043</v>
       </c>
       <c r="Z616" s="8" t="inlineStr"/>
     </row>
@@ -39549,7 +39997,11 @@
       <c r="C617" s="9" t="n">
         <v>46179</v>
       </c>
-      <c r="D617" s="8" t="inlineStr"/>
+      <c r="D617" s="8" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST02.STR.V1</t>
+        </is>
+      </c>
       <c r="E617" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission -  DCP3 - Viaduct Foundation &amp; Substructure - Stretch 02-Balance Cantilever 3SP-72-01 : DE.VDT.ST02.STR.V1.D3_Rev.C03</t>
@@ -39587,7 +40039,7 @@
       <c r="W617" s="8" t="inlineStr"/>
       <c r="X617" s="8" t="inlineStr"/>
       <c r="Y617" s="9" t="n">
-        <v>46186.23724726208</v>
+        <v>46186.27264125066</v>
       </c>
       <c r="Z617" s="8" t="inlineStr"/>
     </row>
@@ -39651,7 +40103,7 @@
       <c r="W618" s="8" t="inlineStr"/>
       <c r="X618" s="8" t="inlineStr"/>
       <c r="Y618" s="9" t="n">
-        <v>46186.23724726273</v>
+        <v>46186.27264125091</v>
       </c>
       <c r="Z618" s="8" t="inlineStr"/>
     </row>
@@ -39665,7 +40117,11 @@
       <c r="C619" s="9" t="n">
         <v>46179</v>
       </c>
-      <c r="D619" s="8" t="inlineStr"/>
+      <c r="D619" s="8" t="inlineStr">
+        <is>
+          <t>DE.TNL.GN00.MEP.T1</t>
+        </is>
+      </c>
       <c r="E619" s="10" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP2 - Tunnel 01 Drainage Package (S0702 &amp; S0704): DE.TNL.GN00.MEP.T1.D2_Rev.C01</t>
@@ -39703,7 +40159,7 @@
       <c r="W619" s="8" t="inlineStr"/>
       <c r="X619" s="8" t="inlineStr"/>
       <c r="Y619" s="9" t="n">
-        <v>46186.23724726296</v>
+        <v>46186.27264125113</v>
       </c>
       <c r="Z619" s="8" t="inlineStr"/>
     </row>
@@ -39771,7 +40227,7 @@
       <c r="W620" s="8" t="inlineStr"/>
       <c r="X620" s="8" t="inlineStr"/>
       <c r="Y620" s="9" t="n">
-        <v>46186.2372472632</v>
+        <v>46186.27264125133</v>
       </c>
       <c r="Z620" s="8" t="inlineStr"/>
     </row>
@@ -39835,7 +40291,7 @@
       <c r="W621" s="8" t="inlineStr"/>
       <c r="X621" s="8" t="inlineStr"/>
       <c r="Y621" s="9" t="n">
-        <v>46186.23724726339</v>
+        <v>46186.27264125154</v>
       </c>
       <c r="Z621" s="8" t="inlineStr"/>
     </row>
@@ -39899,7 +40355,7 @@
       <c r="W622" s="8" t="inlineStr"/>
       <c r="X622" s="8" t="inlineStr"/>
       <c r="Y622" s="9" t="n">
-        <v>46186.23724726404</v>
+        <v>46186.27264125178</v>
       </c>
       <c r="Z622" s="8" t="inlineStr"/>
     </row>
@@ -39963,7 +40419,7 @@
       <c r="W623" s="8" t="inlineStr"/>
       <c r="X623" s="8" t="inlineStr"/>
       <c r="Y623" s="9" t="n">
-        <v>46186.2372472643</v>
+        <v>46186.27264125198</v>
       </c>
       <c r="Z623" s="8" t="inlineStr"/>
     </row>
@@ -39977,7 +40433,11 @@
       <c r="C624" s="5" t="n">
         <v>46179</v>
       </c>
-      <c r="D624" s="4" t="inlineStr"/>
+      <c r="D624" s="4" t="inlineStr">
+        <is>
+          <t>DE.ANX.AX17.ARC.A0</t>
+        </is>
+      </c>
       <c r="E624" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP2 -  Annex Structure - BL-EES08 Architecture : DE.ANX.AX17.ARC.A0.D2_Rev.C01</t>
@@ -40015,7 +40475,7 @@
       <c r="W624" s="4" t="inlineStr"/>
       <c r="X624" s="4" t="inlineStr"/>
       <c r="Y624" s="5" t="n">
-        <v>46186.23724726449</v>
+        <v>46186.27264125219</v>
       </c>
       <c r="Z624" s="4" t="inlineStr"/>
     </row>
@@ -40029,7 +40489,11 @@
       <c r="C625" s="5" t="n">
         <v>46179</v>
       </c>
-      <c r="D625" s="4" t="inlineStr"/>
+      <c r="D625" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.GN00.STR.01</t>
+        </is>
+      </c>
       <c r="E625" s="6" t="inlineStr">
         <is>
           <t>Re: Package Submission - DCP3 - Global - Viaduct Structure Superstructure Global 2SP PKG4 : DE.VDT.GN00.STR.01.D3_Rev.C03</t>
@@ -40071,7 +40535,7 @@
       <c r="W625" s="4" t="inlineStr"/>
       <c r="X625" s="4" t="inlineStr"/>
       <c r="Y625" s="5" t="n">
-        <v>46186.23724726467</v>
+        <v>46186.27264125238</v>
       </c>
       <c r="Z625" s="4" t="inlineStr"/>
     </row>
@@ -40139,7 +40603,7 @@
       <c r="W626" s="4" t="inlineStr"/>
       <c r="X626" s="4" t="inlineStr"/>
       <c r="Y626" s="5" t="n">
-        <v>46186.23724726489</v>
+        <v>46186.27264125266</v>
       </c>
       <c r="Z626" s="4" t="inlineStr"/>
     </row>
@@ -40207,7 +40671,7 @@
       <c r="W627" s="4" t="inlineStr"/>
       <c r="X627" s="4" t="inlineStr"/>
       <c r="Y627" s="5" t="n">
-        <v>46186.23724726548</v>
+        <v>46186.27264125287</v>
       </c>
       <c r="Z627" s="4" t="inlineStr"/>
     </row>
@@ -40279,7 +40743,7 @@
       <c r="W628" s="4" t="inlineStr"/>
       <c r="X628" s="4" t="inlineStr"/>
       <c r="Y628" s="5" t="n">
-        <v>46186.2372472658</v>
+        <v>46186.27264125307</v>
       </c>
       <c r="Z628" s="4" t="inlineStr"/>
     </row>
@@ -40293,7 +40757,11 @@
       <c r="C629" s="5" t="n">
         <v>46179</v>
       </c>
-      <c r="D629" s="4" t="inlineStr"/>
+      <c r="D629" s="4" t="inlineStr">
+        <is>
+          <t>DE.VDT.ST07.STR.V2</t>
+        </is>
+      </c>
       <c r="E629" s="6" t="inlineStr">
         <is>
           <t>Package Submission - DCP3 - Stretch-07 - Viaduct Structure Pierhead 2SP Span : DE.VDT.ST07.STR.V2.D3_Rev.C01</t>
@@ -40335,7 +40803,7 @@
       <c r="W629" s="4" t="inlineStr"/>
       <c r="X629" s="4" t="inlineStr"/>
       <c r="Y629" s="5" t="n">
-        <v>46186.23724726597</v>
+        <v>46186.27264125326</v>
       </c>
       <c r="Z629" s="4" t="inlineStr"/>
     </row>
@@ -40416,7 +40884,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13/06/2026 05:41</t>
+          <t>13/06/2026 06:32</t>
         </is>
       </c>
     </row>

--- a/output_transmittal_register.xlsx
+++ b/output_transmittal_register.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 13/06/2026 06:32</t>
+          <t>Generated: 13/06/2026 06:33</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
       <c r="Y9" s="5" t="n">
-        <v>46186.27264108857</v>
+        <v>46186.27342835638</v>
       </c>
       <c r="Z9" s="4" t="inlineStr"/>
     </row>
@@ -947,7 +947,7 @@
       <c r="W10" s="4" t="inlineStr"/>
       <c r="X10" s="4" t="inlineStr"/>
       <c r="Y10" s="5" t="n">
-        <v>46186.27264108917</v>
+        <v>46186.273428357</v>
       </c>
       <c r="Z10" s="4" t="inlineStr"/>
     </row>
@@ -1015,7 +1015,7 @@
       <c r="W11" s="8" t="inlineStr"/>
       <c r="X11" s="8" t="inlineStr"/>
       <c r="Y11" s="9" t="n">
-        <v>46186.2726410895</v>
+        <v>46186.27342835737</v>
       </c>
       <c r="Z11" s="8" t="inlineStr"/>
     </row>
@@ -1083,7 +1083,7 @@
       <c r="W12" s="8" t="inlineStr"/>
       <c r="X12" s="8" t="inlineStr"/>
       <c r="Y12" s="9" t="n">
-        <v>46186.2726410898</v>
+        <v>46186.27342835767</v>
       </c>
       <c r="Z12" s="8" t="inlineStr"/>
     </row>
@@ -1155,7 +1155,7 @@
       <c r="W13" s="8" t="inlineStr"/>
       <c r="X13" s="8" t="inlineStr"/>
       <c r="Y13" s="9" t="n">
-        <v>46186.27264109007</v>
+        <v>46186.27342835796</v>
       </c>
       <c r="Z13" s="8" t="inlineStr"/>
     </row>
@@ -1223,7 +1223,7 @@
       <c r="W14" s="8" t="inlineStr"/>
       <c r="X14" s="8" t="inlineStr"/>
       <c r="Y14" s="9" t="n">
-        <v>46186.27264109039</v>
+        <v>46186.27342835826</v>
       </c>
       <c r="Z14" s="8" t="inlineStr"/>
     </row>
@@ -1291,7 +1291,7 @@
       <c r="W15" s="8" t="inlineStr"/>
       <c r="X15" s="8" t="inlineStr"/>
       <c r="Y15" s="9" t="n">
-        <v>46186.27264109098</v>
+        <v>46186.27342835875</v>
       </c>
       <c r="Z15" s="8" t="inlineStr"/>
     </row>
@@ -1355,7 +1355,7 @@
       <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="5" t="n">
-        <v>46186.27264109131</v>
+        <v>46186.27342835906</v>
       </c>
       <c r="Z16" s="4" t="inlineStr"/>
     </row>
@@ -1419,7 +1419,7 @@
       <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="5" t="n">
-        <v>46186.27264109156</v>
+        <v>46186.27342835929</v>
       </c>
       <c r="Z17" s="4" t="inlineStr"/>
     </row>
@@ -1483,7 +1483,7 @@
       <c r="W18" s="4" t="inlineStr"/>
       <c r="X18" s="4" t="inlineStr"/>
       <c r="Y18" s="5" t="n">
-        <v>46186.27264109178</v>
+        <v>46186.27342835951</v>
       </c>
       <c r="Z18" s="4" t="inlineStr"/>
     </row>
@@ -1547,7 +1547,7 @@
       <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="5" t="n">
-        <v>46186.2726410925</v>
+        <v>46186.27342835972</v>
       </c>
       <c r="Z19" s="4" t="inlineStr"/>
     </row>
@@ -1611,7 +1611,7 @@
       <c r="W20" s="8" t="inlineStr"/>
       <c r="X20" s="8" t="inlineStr"/>
       <c r="Y20" s="9" t="n">
-        <v>46186.27264109282</v>
+        <v>46186.27342835996</v>
       </c>
       <c r="Z20" s="8" t="inlineStr"/>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="W21" s="8" t="inlineStr"/>
       <c r="X21" s="8" t="inlineStr"/>
       <c r="Y21" s="9" t="n">
-        <v>46186.27264109306</v>
+        <v>46186.27342836017</v>
       </c>
       <c r="Z21" s="8" t="inlineStr"/>
     </row>
@@ -1727,7 +1727,7 @@
       <c r="W22" s="8" t="inlineStr"/>
       <c r="X22" s="8" t="inlineStr"/>
       <c r="Y22" s="9" t="n">
-        <v>46186.2726410933</v>
+        <v>46186.27342836039</v>
       </c>
       <c r="Z22" s="8" t="inlineStr"/>
     </row>
@@ -1795,7 +1795,7 @@
       <c r="W23" s="8" t="inlineStr"/>
       <c r="X23" s="8" t="inlineStr"/>
       <c r="Y23" s="9" t="n">
-        <v>46186.27264109354</v>
+        <v>46186.27342836063</v>
       </c>
       <c r="Z23" s="8" t="inlineStr"/>
     </row>
@@ -1859,7 +1859,7 @@
       <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="5" t="n">
-        <v>46186.27264109375</v>
+        <v>46186.27342836122</v>
       </c>
       <c r="Z24" s="4" t="inlineStr"/>
     </row>
@@ -1927,7 +1927,7 @@
       <c r="W25" s="8" t="inlineStr"/>
       <c r="X25" s="8" t="inlineStr"/>
       <c r="Y25" s="9" t="n">
-        <v>46186.27264109406</v>
+        <v>46186.27342836159</v>
       </c>
       <c r="Z25" s="8" t="inlineStr"/>
     </row>
@@ -1995,7 +1995,7 @@
       <c r="W26" s="8" t="inlineStr"/>
       <c r="X26" s="8" t="inlineStr"/>
       <c r="Y26" s="9" t="n">
-        <v>46186.27264109429</v>
+        <v>46186.27342836184</v>
       </c>
       <c r="Z26" s="8" t="inlineStr"/>
     </row>
@@ -2059,7 +2059,7 @@
       <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="5" t="n">
-        <v>46186.2726410945</v>
+        <v>46186.27342836207</v>
       </c>
       <c r="Z27" s="4" t="inlineStr"/>
     </row>
@@ -2123,7 +2123,7 @@
       <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="5" t="n">
-        <v>46186.27264109499</v>
+        <v>46186.27342836231</v>
       </c>
       <c r="Z28" s="4" t="inlineStr"/>
     </row>
@@ -2187,7 +2187,7 @@
       <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="5" t="n">
-        <v>46186.27264109537</v>
+        <v>46186.27342836258</v>
       </c>
       <c r="Z29" s="4" t="inlineStr"/>
     </row>
@@ -2251,7 +2251,7 @@
       <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="5" t="n">
-        <v>46186.27264109598</v>
+        <v>46186.27342836324</v>
       </c>
       <c r="Z30" s="4" t="inlineStr"/>
     </row>
@@ -2315,7 +2315,7 @@
       <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="5" t="n">
-        <v>46186.27264109633</v>
+        <v>46186.27342836358</v>
       </c>
       <c r="Z31" s="4" t="inlineStr"/>
     </row>
@@ -2371,7 +2371,7 @@
       <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="5" t="n">
-        <v>46186.2726410966</v>
+        <v>46186.27342836381</v>
       </c>
       <c r="Z32" s="4" t="inlineStr"/>
     </row>
@@ -2435,7 +2435,7 @@
       <c r="W33" s="4" t="inlineStr"/>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="5" t="n">
-        <v>46186.27264109686</v>
+        <v>46186.27342836406</v>
       </c>
       <c r="Z33" s="4" t="inlineStr"/>
     </row>
@@ -2503,7 +2503,7 @@
       <c r="W34" s="4" t="inlineStr"/>
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="5" t="n">
-        <v>46186.27264109707</v>
+        <v>46186.27342836427</v>
       </c>
       <c r="Z34" s="4" t="inlineStr"/>
     </row>
@@ -2567,7 +2567,7 @@
       <c r="W35" s="4" t="inlineStr"/>
       <c r="X35" s="4" t="inlineStr"/>
       <c r="Y35" s="5" t="n">
-        <v>46186.27264109728</v>
+        <v>46186.27342836447</v>
       </c>
       <c r="Z35" s="4" t="inlineStr"/>
     </row>
@@ -2635,7 +2635,7 @@
       <c r="W36" s="8" t="inlineStr"/>
       <c r="X36" s="8" t="inlineStr"/>
       <c r="Y36" s="9" t="n">
-        <v>46186.27264109749</v>
+        <v>46186.27342836469</v>
       </c>
       <c r="Z36" s="8" t="inlineStr"/>
     </row>
@@ -2699,7 +2699,7 @@
       <c r="W37" s="8" t="inlineStr"/>
       <c r="X37" s="8" t="inlineStr"/>
       <c r="Y37" s="9" t="n">
-        <v>46186.2726410977</v>
+        <v>46186.27342836492</v>
       </c>
       <c r="Z37" s="8" t="inlineStr"/>
     </row>
@@ -2747,7 +2747,7 @@
       <c r="W38" s="4" t="inlineStr"/>
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="5" t="n">
-        <v>46186.27264109794</v>
+        <v>46186.27342836515</v>
       </c>
       <c r="Z38" s="4" t="inlineStr"/>
     </row>
@@ -2811,7 +2811,7 @@
       <c r="W39" s="8" t="inlineStr"/>
       <c r="X39" s="8" t="inlineStr"/>
       <c r="Y39" s="9" t="n">
-        <v>46186.27264109817</v>
+        <v>46186.27342836538</v>
       </c>
       <c r="Z39" s="8" t="inlineStr"/>
     </row>
@@ -2875,7 +2875,7 @@
       <c r="W40" s="8" t="inlineStr"/>
       <c r="X40" s="8" t="inlineStr"/>
       <c r="Y40" s="9" t="n">
-        <v>46186.2726410984</v>
+        <v>46186.27342836568</v>
       </c>
       <c r="Z40" s="8" t="inlineStr"/>
     </row>
@@ -2939,7 +2939,7 @@
       <c r="W41" s="8" t="inlineStr"/>
       <c r="X41" s="8" t="inlineStr"/>
       <c r="Y41" s="9" t="n">
-        <v>46186.27264109862</v>
+        <v>46186.27342836589</v>
       </c>
       <c r="Z41" s="8" t="inlineStr"/>
     </row>
@@ -3007,7 +3007,7 @@
       <c r="W42" s="8" t="inlineStr"/>
       <c r="X42" s="8" t="inlineStr"/>
       <c r="Y42" s="9" t="n">
-        <v>46186.27264109884</v>
+        <v>46186.27342836611</v>
       </c>
       <c r="Z42" s="8" t="inlineStr"/>
     </row>
@@ -3071,7 +3071,7 @@
       <c r="W43" s="8" t="inlineStr"/>
       <c r="X43" s="8" t="inlineStr"/>
       <c r="Y43" s="9" t="n">
-        <v>46186.27264109904</v>
+        <v>46186.27342836631</v>
       </c>
       <c r="Z43" s="8" t="inlineStr"/>
     </row>
@@ -3127,7 +3127,7 @@
       <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="8" t="inlineStr"/>
       <c r="Y44" s="9" t="n">
-        <v>46186.27264109925</v>
+        <v>46186.27342836693</v>
       </c>
       <c r="Z44" s="8" t="inlineStr"/>
     </row>
@@ -3191,7 +3191,7 @@
       <c r="W45" s="8" t="inlineStr"/>
       <c r="X45" s="8" t="inlineStr"/>
       <c r="Y45" s="9" t="n">
-        <v>46186.27264109946</v>
+        <v>46186.2734283672</v>
       </c>
       <c r="Z45" s="8" t="inlineStr"/>
     </row>
@@ -3247,7 +3247,7 @@
       <c r="W46" s="8" t="inlineStr"/>
       <c r="X46" s="8" t="inlineStr"/>
       <c r="Y46" s="9" t="n">
-        <v>46186.27264109969</v>
+        <v>46186.27342836743</v>
       </c>
       <c r="Z46" s="8" t="inlineStr"/>
     </row>
@@ -3303,7 +3303,7 @@
       <c r="W47" s="8" t="inlineStr"/>
       <c r="X47" s="8" t="inlineStr"/>
       <c r="Y47" s="9" t="n">
-        <v>46186.27264110021</v>
+        <v>46186.27342836766</v>
       </c>
       <c r="Z47" s="8" t="inlineStr"/>
     </row>
@@ -3371,7 +3371,7 @@
       <c r="W48" s="8" t="inlineStr"/>
       <c r="X48" s="8" t="inlineStr"/>
       <c r="Y48" s="9" t="n">
-        <v>46186.27264110056</v>
+        <v>46186.27342836789</v>
       </c>
       <c r="Z48" s="8" t="inlineStr"/>
     </row>
@@ -3427,7 +3427,7 @@
       <c r="W49" s="8" t="inlineStr"/>
       <c r="X49" s="8" t="inlineStr"/>
       <c r="Y49" s="9" t="n">
-        <v>46186.27264110082</v>
+        <v>46186.27342836809</v>
       </c>
       <c r="Z49" s="8" t="inlineStr"/>
     </row>
@@ -3495,7 +3495,7 @@
       <c r="W50" s="8" t="inlineStr"/>
       <c r="X50" s="8" t="inlineStr"/>
       <c r="Y50" s="9" t="n">
-        <v>46186.27264110146</v>
+        <v>46186.27342836831</v>
       </c>
       <c r="Z50" s="8" t="inlineStr"/>
     </row>
@@ -3563,7 +3563,7 @@
       <c r="W51" s="8" t="inlineStr"/>
       <c r="X51" s="8" t="inlineStr"/>
       <c r="Y51" s="9" t="n">
-        <v>46186.27264110182</v>
+        <v>46186.27342836853</v>
       </c>
       <c r="Z51" s="8" t="inlineStr"/>
     </row>
@@ -3619,7 +3619,7 @@
       <c r="W52" s="8" t="inlineStr"/>
       <c r="X52" s="8" t="inlineStr"/>
       <c r="Y52" s="9" t="n">
-        <v>46186.27264110227</v>
+        <v>46186.27342836875</v>
       </c>
       <c r="Z52" s="8" t="inlineStr"/>
     </row>
@@ -3671,7 +3671,7 @@
       <c r="W53" s="4" t="inlineStr"/>
       <c r="X53" s="4" t="inlineStr"/>
       <c r="Y53" s="5" t="n">
-        <v>46186.27264110262</v>
+        <v>46186.27342836896</v>
       </c>
       <c r="Z53" s="4" t="inlineStr"/>
     </row>
@@ -3735,7 +3735,7 @@
       <c r="W54" s="8" t="inlineStr"/>
       <c r="X54" s="8" t="inlineStr"/>
       <c r="Y54" s="9" t="n">
-        <v>46186.27264110287</v>
+        <v>46186.27342836918</v>
       </c>
       <c r="Z54" s="8" t="inlineStr"/>
     </row>
@@ -3799,7 +3799,7 @@
       <c r="W55" s="4" t="inlineStr"/>
       <c r="X55" s="4" t="inlineStr"/>
       <c r="Y55" s="5" t="n">
-        <v>46186.27264110308</v>
+        <v>46186.27342836937</v>
       </c>
       <c r="Z55" s="4" t="inlineStr"/>
     </row>
@@ -3855,7 +3855,7 @@
       <c r="W56" s="4" t="inlineStr"/>
       <c r="X56" s="4" t="inlineStr"/>
       <c r="Y56" s="5" t="n">
-        <v>46186.27264110329</v>
+        <v>46186.27342836957</v>
       </c>
       <c r="Z56" s="4" t="inlineStr"/>
     </row>
@@ -3919,7 +3919,7 @@
       <c r="W57" s="8" t="inlineStr"/>
       <c r="X57" s="8" t="inlineStr"/>
       <c r="Y57" s="9" t="n">
-        <v>46186.2726411035</v>
+        <v>46186.27342836978</v>
       </c>
       <c r="Z57" s="8" t="inlineStr"/>
     </row>
@@ -3975,7 +3975,7 @@
       <c r="W58" s="4" t="inlineStr"/>
       <c r="X58" s="4" t="inlineStr"/>
       <c r="Y58" s="5" t="n">
-        <v>46186.27264110373</v>
+        <v>46186.27342836999</v>
       </c>
       <c r="Z58" s="4" t="inlineStr"/>
     </row>
@@ -4031,7 +4031,7 @@
       <c r="W59" s="4" t="inlineStr"/>
       <c r="X59" s="4" t="inlineStr"/>
       <c r="Y59" s="5" t="n">
-        <v>46186.27264110399</v>
+        <v>46186.27342837019</v>
       </c>
       <c r="Z59" s="4" t="inlineStr"/>
     </row>
@@ -4095,7 +4095,7 @@
       <c r="W60" s="4" t="inlineStr"/>
       <c r="X60" s="4" t="inlineStr"/>
       <c r="Y60" s="5" t="n">
-        <v>46186.27264110421</v>
+        <v>46186.27342837044</v>
       </c>
       <c r="Z60" s="4" t="inlineStr"/>
     </row>
@@ -4159,7 +4159,7 @@
       <c r="W61" s="8" t="inlineStr"/>
       <c r="X61" s="8" t="inlineStr"/>
       <c r="Y61" s="9" t="n">
-        <v>46186.27264110441</v>
+        <v>46186.27342837064</v>
       </c>
       <c r="Z61" s="8" t="inlineStr"/>
     </row>
@@ -4223,7 +4223,7 @@
       <c r="W62" s="4" t="inlineStr"/>
       <c r="X62" s="4" t="inlineStr"/>
       <c r="Y62" s="5" t="n">
-        <v>46186.27264110465</v>
+        <v>46186.27342837088</v>
       </c>
       <c r="Z62" s="4" t="inlineStr"/>
     </row>
@@ -4287,7 +4287,7 @@
       <c r="W63" s="4" t="inlineStr"/>
       <c r="X63" s="4" t="inlineStr"/>
       <c r="Y63" s="5" t="n">
-        <v>46186.27264110485</v>
+        <v>46186.27342837105</v>
       </c>
       <c r="Z63" s="4" t="inlineStr"/>
     </row>
@@ -4343,7 +4343,7 @@
       <c r="W64" s="4" t="inlineStr"/>
       <c r="X64" s="4" t="inlineStr"/>
       <c r="Y64" s="5" t="n">
-        <v>46186.27264110507</v>
+        <v>46186.27342837125</v>
       </c>
       <c r="Z64" s="4" t="inlineStr"/>
     </row>
@@ -4407,7 +4407,7 @@
       <c r="W65" s="4" t="inlineStr"/>
       <c r="X65" s="4" t="inlineStr"/>
       <c r="Y65" s="5" t="n">
-        <v>46186.27264110526</v>
+        <v>46186.27342837147</v>
       </c>
       <c r="Z65" s="4" t="inlineStr"/>
     </row>
@@ -4471,7 +4471,7 @@
       <c r="W66" s="4" t="inlineStr"/>
       <c r="X66" s="4" t="inlineStr"/>
       <c r="Y66" s="5" t="n">
-        <v>46186.27264110546</v>
+        <v>46186.27342837168</v>
       </c>
       <c r="Z66" s="4" t="inlineStr"/>
     </row>
@@ -4523,7 +4523,7 @@
       <c r="W67" s="4" t="inlineStr"/>
       <c r="X67" s="4" t="inlineStr"/>
       <c r="Y67" s="5" t="n">
-        <v>46186.27264110566</v>
+        <v>46186.27342837199</v>
       </c>
       <c r="Z67" s="4" t="inlineStr"/>
     </row>
@@ -4587,7 +4587,7 @@
       <c r="W68" s="4" t="inlineStr"/>
       <c r="X68" s="4" t="inlineStr"/>
       <c r="Y68" s="5" t="n">
-        <v>46186.27264110587</v>
+        <v>46186.27342837259</v>
       </c>
       <c r="Z68" s="4" t="inlineStr"/>
     </row>
@@ -4639,7 +4639,7 @@
       <c r="W69" s="4" t="inlineStr"/>
       <c r="X69" s="4" t="inlineStr"/>
       <c r="Y69" s="5" t="n">
-        <v>46186.27264110606</v>
+        <v>46186.27342837308</v>
       </c>
       <c r="Z69" s="4" t="inlineStr"/>
     </row>
@@ -4703,7 +4703,7 @@
       <c r="W70" s="4" t="inlineStr"/>
       <c r="X70" s="4" t="inlineStr"/>
       <c r="Y70" s="5" t="n">
-        <v>46186.27264110673</v>
+        <v>46186.2734283735</v>
       </c>
       <c r="Z70" s="4" t="inlineStr"/>
     </row>
@@ -4767,7 +4767,7 @@
       <c r="W71" s="4" t="inlineStr"/>
       <c r="X71" s="4" t="inlineStr"/>
       <c r="Y71" s="5" t="n">
-        <v>46186.27264110708</v>
+        <v>46186.27342837389</v>
       </c>
       <c r="Z71" s="4" t="inlineStr"/>
     </row>
@@ -4835,7 +4835,7 @@
       <c r="W72" s="4" t="inlineStr"/>
       <c r="X72" s="4" t="inlineStr"/>
       <c r="Y72" s="5" t="n">
-        <v>46186.27264110732</v>
+        <v>46186.27342837455</v>
       </c>
       <c r="Z72" s="4" t="inlineStr"/>
     </row>
@@ -4899,7 +4899,7 @@
       <c r="W73" s="4" t="inlineStr"/>
       <c r="X73" s="4" t="inlineStr"/>
       <c r="Y73" s="5" t="n">
-        <v>46186.27264110753</v>
+        <v>46186.27342837491</v>
       </c>
       <c r="Z73" s="4" t="inlineStr"/>
     </row>
@@ -4963,7 +4963,7 @@
       <c r="W74" s="4" t="inlineStr"/>
       <c r="X74" s="4" t="inlineStr"/>
       <c r="Y74" s="5" t="n">
-        <v>46186.27264110773</v>
+        <v>46186.27342837516</v>
       </c>
       <c r="Z74" s="4" t="inlineStr"/>
     </row>
@@ -5027,7 +5027,7 @@
       <c r="W75" s="4" t="inlineStr"/>
       <c r="X75" s="4" t="inlineStr"/>
       <c r="Y75" s="5" t="n">
-        <v>46186.27264110792</v>
+        <v>46186.27342837537</v>
       </c>
       <c r="Z75" s="4" t="inlineStr"/>
     </row>
@@ -5095,7 +5095,7 @@
       <c r="W76" s="4" t="inlineStr"/>
       <c r="X76" s="4" t="inlineStr"/>
       <c r="Y76" s="5" t="n">
-        <v>46186.27264110938</v>
+        <v>46186.27342837559</v>
       </c>
       <c r="Z76" s="4" t="inlineStr"/>
     </row>
@@ -5163,7 +5163,7 @@
       <c r="W77" s="8" t="inlineStr"/>
       <c r="X77" s="8" t="inlineStr"/>
       <c r="Y77" s="9" t="n">
-        <v>46186.2726411098</v>
+        <v>46186.27342837587</v>
       </c>
       <c r="Z77" s="8" t="inlineStr"/>
     </row>
@@ -5227,7 +5227,7 @@
       <c r="W78" s="8" t="inlineStr"/>
       <c r="X78" s="8" t="inlineStr"/>
       <c r="Y78" s="9" t="n">
-        <v>46186.27264111004</v>
+        <v>46186.2734283761</v>
       </c>
       <c r="Z78" s="8" t="inlineStr"/>
     </row>
@@ -5283,7 +5283,7 @@
       <c r="W79" s="8" t="inlineStr"/>
       <c r="X79" s="8" t="inlineStr"/>
       <c r="Y79" s="9" t="n">
-        <v>46186.27264111028</v>
+        <v>46186.27342837631</v>
       </c>
       <c r="Z79" s="8" t="inlineStr"/>
     </row>
@@ -5351,7 +5351,7 @@
       <c r="W80" s="8" t="inlineStr"/>
       <c r="X80" s="8" t="inlineStr"/>
       <c r="Y80" s="9" t="n">
-        <v>46186.27264111049</v>
+        <v>46186.27342837652</v>
       </c>
       <c r="Z80" s="8" t="inlineStr"/>
     </row>
@@ -5419,7 +5419,7 @@
       <c r="W81" s="8" t="inlineStr"/>
       <c r="X81" s="8" t="inlineStr"/>
       <c r="Y81" s="9" t="n">
-        <v>46186.27264111069</v>
+        <v>46186.27342837673</v>
       </c>
       <c r="Z81" s="8" t="inlineStr"/>
     </row>
@@ -5487,7 +5487,7 @@
       <c r="W82" s="8" t="inlineStr"/>
       <c r="X82" s="8" t="inlineStr"/>
       <c r="Y82" s="9" t="n">
-        <v>46186.27264111087</v>
+        <v>46186.2734283774</v>
       </c>
       <c r="Z82" s="8" t="inlineStr"/>
     </row>
@@ -5551,7 +5551,7 @@
       <c r="W83" s="4" t="inlineStr"/>
       <c r="X83" s="4" t="inlineStr"/>
       <c r="Y83" s="5" t="n">
-        <v>46186.27264111106</v>
+        <v>46186.27342837771</v>
       </c>
       <c r="Z83" s="4" t="inlineStr"/>
     </row>
@@ -5603,7 +5603,7 @@
       <c r="W84" s="8" t="inlineStr"/>
       <c r="X84" s="8" t="inlineStr"/>
       <c r="Y84" s="9" t="n">
-        <v>46186.27264111125</v>
+        <v>46186.27342837794</v>
       </c>
       <c r="Z84" s="8" t="inlineStr"/>
     </row>
@@ -5659,7 +5659,7 @@
       <c r="W85" s="4" t="inlineStr"/>
       <c r="X85" s="4" t="inlineStr"/>
       <c r="Y85" s="5" t="n">
-        <v>46186.27264111146</v>
+        <v>46186.27342837816</v>
       </c>
       <c r="Z85" s="4" t="inlineStr"/>
     </row>
@@ -5723,7 +5723,7 @@
       <c r="W86" s="8" t="inlineStr"/>
       <c r="X86" s="8" t="inlineStr"/>
       <c r="Y86" s="9" t="n">
-        <v>46186.27264111169</v>
+        <v>46186.27342837838</v>
       </c>
       <c r="Z86" s="8" t="inlineStr"/>
     </row>
@@ -5787,7 +5787,7 @@
       <c r="W87" s="8" t="inlineStr"/>
       <c r="X87" s="8" t="inlineStr"/>
       <c r="Y87" s="9" t="n">
-        <v>46186.2726411119</v>
+        <v>46186.27342837861</v>
       </c>
       <c r="Z87" s="8" t="inlineStr"/>
     </row>
@@ -5855,7 +5855,7 @@
       <c r="W88" s="8" t="inlineStr"/>
       <c r="X88" s="8" t="inlineStr"/>
       <c r="Y88" s="9" t="n">
-        <v>46186.2726411121</v>
+        <v>46186.27342837881</v>
       </c>
       <c r="Z88" s="8" t="inlineStr"/>
     </row>
@@ -5919,7 +5919,7 @@
       <c r="W89" s="4" t="inlineStr"/>
       <c r="X89" s="4" t="inlineStr"/>
       <c r="Y89" s="5" t="n">
-        <v>46186.27264111228</v>
+        <v>46186.27342837898</v>
       </c>
       <c r="Z89" s="4" t="inlineStr"/>
     </row>
@@ -5987,7 +5987,7 @@
       <c r="W90" s="8" t="inlineStr"/>
       <c r="X90" s="8" t="inlineStr"/>
       <c r="Y90" s="9" t="n">
-        <v>46186.27264111298</v>
+        <v>46186.27342837918</v>
       </c>
       <c r="Z90" s="8" t="inlineStr"/>
     </row>
@@ -6047,7 +6047,7 @@
       <c r="W91" s="8" t="inlineStr"/>
       <c r="X91" s="8" t="inlineStr"/>
       <c r="Y91" s="9" t="n">
-        <v>46186.27264111337</v>
+        <v>46186.27342837947</v>
       </c>
       <c r="Z91" s="8" t="inlineStr"/>
     </row>
@@ -6115,7 +6115,7 @@
       <c r="W92" s="8" t="inlineStr"/>
       <c r="X92" s="8" t="inlineStr"/>
       <c r="Y92" s="9" t="n">
-        <v>46186.27264111369</v>
+        <v>46186.27342838007</v>
       </c>
       <c r="Z92" s="8" t="inlineStr"/>
     </row>
@@ -6179,7 +6179,7 @@
       <c r="W93" s="8" t="inlineStr"/>
       <c r="X93" s="8" t="inlineStr"/>
       <c r="Y93" s="9" t="n">
-        <v>46186.27264111392</v>
+        <v>46186.27342838039</v>
       </c>
       <c r="Z93" s="8" t="inlineStr"/>
     </row>
@@ -6243,7 +6243,7 @@
       <c r="W94" s="8" t="inlineStr"/>
       <c r="X94" s="8" t="inlineStr"/>
       <c r="Y94" s="9" t="n">
-        <v>46186.27264111416</v>
+        <v>46186.27342838063</v>
       </c>
       <c r="Z94" s="8" t="inlineStr"/>
     </row>
@@ -6299,7 +6299,7 @@
       <c r="W95" s="8" t="inlineStr"/>
       <c r="X95" s="8" t="inlineStr"/>
       <c r="Y95" s="9" t="n">
-        <v>46186.27264111437</v>
+        <v>46186.27342838085</v>
       </c>
       <c r="Z95" s="8" t="inlineStr"/>
     </row>
@@ -6355,7 +6355,7 @@
       <c r="W96" s="4" t="inlineStr"/>
       <c r="X96" s="4" t="inlineStr"/>
       <c r="Y96" s="5" t="n">
-        <v>46186.27264111459</v>
+        <v>46186.27342838108</v>
       </c>
       <c r="Z96" s="4" t="inlineStr"/>
     </row>
@@ -6411,7 +6411,7 @@
       <c r="W97" s="4" t="inlineStr"/>
       <c r="X97" s="4" t="inlineStr"/>
       <c r="Y97" s="5" t="n">
-        <v>46186.27264111482</v>
+        <v>46186.27342838128</v>
       </c>
       <c r="Z97" s="4" t="inlineStr"/>
     </row>
@@ -6479,7 +6479,7 @@
       <c r="W98" s="4" t="inlineStr"/>
       <c r="X98" s="4" t="inlineStr"/>
       <c r="Y98" s="5" t="n">
-        <v>46186.27264111502</v>
+        <v>46186.27342838151</v>
       </c>
       <c r="Z98" s="4" t="inlineStr"/>
     </row>
@@ -6539,7 +6539,7 @@
       <c r="W99" s="4" t="inlineStr"/>
       <c r="X99" s="4" t="inlineStr"/>
       <c r="Y99" s="5" t="n">
-        <v>46186.27264111523</v>
+        <v>46186.27342838171</v>
       </c>
       <c r="Z99" s="4" t="inlineStr"/>
     </row>
@@ -6599,7 +6599,7 @@
       <c r="W100" s="4" t="inlineStr"/>
       <c r="X100" s="4" t="inlineStr"/>
       <c r="Y100" s="5" t="n">
-        <v>46186.27264111543</v>
+        <v>46186.27342838221</v>
       </c>
       <c r="Z100" s="4" t="inlineStr"/>
     </row>
@@ -6667,7 +6667,7 @@
       <c r="W101" s="4" t="inlineStr"/>
       <c r="X101" s="4" t="inlineStr"/>
       <c r="Y101" s="5" t="n">
-        <v>46186.27264111567</v>
+        <v>46186.27342838259</v>
       </c>
       <c r="Z101" s="4" t="inlineStr"/>
     </row>
@@ -6739,7 +6739,7 @@
       <c r="W102" s="4" t="inlineStr"/>
       <c r="X102" s="4" t="inlineStr"/>
       <c r="Y102" s="5" t="n">
-        <v>46186.27264111589</v>
+        <v>46186.27342838285</v>
       </c>
       <c r="Z102" s="4" t="inlineStr"/>
     </row>
@@ -6807,7 +6807,7 @@
       <c r="W103" s="4" t="inlineStr"/>
       <c r="X103" s="4" t="inlineStr"/>
       <c r="Y103" s="5" t="n">
-        <v>46186.27264111608</v>
+        <v>46186.27342838306</v>
       </c>
       <c r="Z103" s="4" t="inlineStr"/>
     </row>
@@ -6875,7 +6875,7 @@
       <c r="W104" s="4" t="inlineStr"/>
       <c r="X104" s="4" t="inlineStr"/>
       <c r="Y104" s="5" t="n">
-        <v>46186.27264111669</v>
+        <v>46186.27342838325</v>
       </c>
       <c r="Z104" s="4" t="inlineStr"/>
     </row>
@@ -6943,7 +6943,7 @@
       <c r="W105" s="4" t="inlineStr"/>
       <c r="X105" s="4" t="inlineStr"/>
       <c r="Y105" s="5" t="n">
-        <v>46186.27264111694</v>
+        <v>46186.27342838344</v>
       </c>
       <c r="Z105" s="4" t="inlineStr"/>
     </row>
@@ -7015,7 +7015,7 @@
       <c r="W106" s="4" t="inlineStr"/>
       <c r="X106" s="4" t="inlineStr"/>
       <c r="Y106" s="5" t="n">
-        <v>46186.27264111714</v>
+        <v>46186.27342838363</v>
       </c>
       <c r="Z106" s="4" t="inlineStr"/>
     </row>
@@ -7083,7 +7083,7 @@
       <c r="W107" s="4" t="inlineStr"/>
       <c r="X107" s="4" t="inlineStr"/>
       <c r="Y107" s="5" t="n">
-        <v>46186.27264111735</v>
+        <v>46186.27342838382</v>
       </c>
       <c r="Z107" s="4" t="inlineStr"/>
     </row>
@@ -7151,7 +7151,7 @@
       <c r="W108" s="4" t="inlineStr"/>
       <c r="X108" s="4" t="inlineStr"/>
       <c r="Y108" s="5" t="n">
-        <v>46186.27264111756</v>
+        <v>46186.27342838441</v>
       </c>
       <c r="Z108" s="4" t="inlineStr"/>
     </row>
@@ -7219,7 +7219,7 @@
       <c r="W109" s="4" t="inlineStr"/>
       <c r="X109" s="4" t="inlineStr"/>
       <c r="Y109" s="5" t="n">
-        <v>46186.27264111774</v>
+        <v>46186.27342838465</v>
       </c>
       <c r="Z109" s="4" t="inlineStr"/>
     </row>
@@ -7287,7 +7287,7 @@
       <c r="W110" s="4" t="inlineStr"/>
       <c r="X110" s="4" t="inlineStr"/>
       <c r="Y110" s="5" t="n">
-        <v>46186.27264111827</v>
+        <v>46186.27342838487</v>
       </c>
       <c r="Z110" s="4" t="inlineStr"/>
     </row>
@@ -7351,7 +7351,7 @@
       <c r="W111" s="4" t="inlineStr"/>
       <c r="X111" s="4" t="inlineStr"/>
       <c r="Y111" s="5" t="n">
-        <v>46186.27264111856</v>
+        <v>46186.2734283851</v>
       </c>
       <c r="Z111" s="4" t="inlineStr"/>
     </row>
@@ -7407,7 +7407,7 @@
       <c r="W112" s="4" t="inlineStr"/>
       <c r="X112" s="4" t="inlineStr"/>
       <c r="Y112" s="5" t="n">
-        <v>46186.27264111884</v>
+        <v>46186.27342838537</v>
       </c>
       <c r="Z112" s="4" t="inlineStr"/>
     </row>
@@ -7475,7 +7475,7 @@
       <c r="W113" s="4" t="inlineStr"/>
       <c r="X113" s="4" t="inlineStr"/>
       <c r="Y113" s="5" t="n">
-        <v>46186.2726411191</v>
+        <v>46186.27342838563</v>
       </c>
       <c r="Z113" s="4" t="inlineStr"/>
     </row>
@@ -7543,7 +7543,7 @@
       <c r="W114" s="4" t="inlineStr"/>
       <c r="X114" s="4" t="inlineStr"/>
       <c r="Y114" s="5" t="n">
-        <v>46186.27264111931</v>
+        <v>46186.27342838584</v>
       </c>
       <c r="Z114" s="4" t="inlineStr"/>
     </row>
@@ -7591,7 +7591,7 @@
       <c r="W115" s="4" t="inlineStr"/>
       <c r="X115" s="4" t="inlineStr"/>
       <c r="Y115" s="5" t="n">
-        <v>46186.27264111954</v>
+        <v>46186.27342838606</v>
       </c>
       <c r="Z115" s="4" t="inlineStr"/>
     </row>
@@ -7639,7 +7639,7 @@
       <c r="W116" s="4" t="inlineStr"/>
       <c r="X116" s="4" t="inlineStr"/>
       <c r="Y116" s="5" t="n">
-        <v>46186.27264111974</v>
+        <v>46186.27342838627</v>
       </c>
       <c r="Z116" s="4" t="inlineStr"/>
     </row>
@@ -7707,7 +7707,7 @@
       <c r="W117" s="4" t="inlineStr"/>
       <c r="X117" s="4" t="inlineStr"/>
       <c r="Y117" s="5" t="n">
-        <v>46186.27264111995</v>
+        <v>46186.27342838647</v>
       </c>
       <c r="Z117" s="4" t="inlineStr"/>
     </row>
@@ -7771,7 +7771,7 @@
       <c r="W118" s="8" t="inlineStr"/>
       <c r="X118" s="8" t="inlineStr"/>
       <c r="Y118" s="9" t="n">
-        <v>46186.27264112017</v>
+        <v>46186.27342838669</v>
       </c>
       <c r="Z118" s="8" t="inlineStr"/>
     </row>
@@ -7839,7 +7839,7 @@
       <c r="W119" s="4" t="inlineStr"/>
       <c r="X119" s="4" t="inlineStr"/>
       <c r="Y119" s="5" t="n">
-        <v>46186.27264112037</v>
+        <v>46186.27342838688</v>
       </c>
       <c r="Z119" s="4" t="inlineStr"/>
     </row>
@@ -7907,7 +7907,7 @@
       <c r="W120" s="8" t="inlineStr"/>
       <c r="X120" s="8" t="inlineStr"/>
       <c r="Y120" s="9" t="n">
-        <v>46186.27264112066</v>
+        <v>46186.27342838716</v>
       </c>
       <c r="Z120" s="8" t="inlineStr"/>
     </row>
@@ -7971,7 +7971,7 @@
       <c r="W121" s="8" t="inlineStr"/>
       <c r="X121" s="8" t="inlineStr"/>
       <c r="Y121" s="9" t="n">
-        <v>46186.27264112096</v>
+        <v>46186.27342838737</v>
       </c>
       <c r="Z121" s="8" t="inlineStr"/>
     </row>
@@ -8039,7 +8039,7 @@
       <c r="W122" s="8" t="inlineStr"/>
       <c r="X122" s="8" t="inlineStr"/>
       <c r="Y122" s="9" t="n">
-        <v>46186.27264112127</v>
+        <v>46186.27342838763</v>
       </c>
       <c r="Z122" s="8" t="inlineStr"/>
     </row>
@@ -8107,7 +8107,7 @@
       <c r="W123" s="4" t="inlineStr"/>
       <c r="X123" s="4" t="inlineStr"/>
       <c r="Y123" s="5" t="n">
-        <v>46186.27264112152</v>
+        <v>46186.27342838787</v>
       </c>
       <c r="Z123" s="4" t="inlineStr"/>
     </row>
@@ -8175,7 +8175,7 @@
       <c r="W124" s="4" t="inlineStr"/>
       <c r="X124" s="4" t="inlineStr"/>
       <c r="Y124" s="5" t="n">
-        <v>46186.27264112172</v>
+        <v>46186.27342838806</v>
       </c>
       <c r="Z124" s="4" t="inlineStr"/>
     </row>
@@ -8243,7 +8243,7 @@
       <c r="W125" s="4" t="inlineStr"/>
       <c r="X125" s="4" t="inlineStr"/>
       <c r="Y125" s="5" t="n">
-        <v>46186.27264112194</v>
+        <v>46186.27342838827</v>
       </c>
       <c r="Z125" s="4" t="inlineStr"/>
     </row>
@@ -8311,7 +8311,7 @@
       <c r="W126" s="4" t="inlineStr"/>
       <c r="X126" s="4" t="inlineStr"/>
       <c r="Y126" s="5" t="n">
-        <v>46186.27264112215</v>
+        <v>46186.27342838849</v>
       </c>
       <c r="Z126" s="4" t="inlineStr"/>
     </row>
@@ -8379,7 +8379,7 @@
       <c r="W127" s="4" t="inlineStr"/>
       <c r="X127" s="4" t="inlineStr"/>
       <c r="Y127" s="5" t="n">
-        <v>46186.27264112235</v>
+        <v>46186.27342838874</v>
       </c>
       <c r="Z127" s="4" t="inlineStr"/>
     </row>
@@ -8447,7 +8447,7 @@
       <c r="W128" s="4" t="inlineStr"/>
       <c r="X128" s="4" t="inlineStr"/>
       <c r="Y128" s="5" t="n">
-        <v>46186.27264112252</v>
+        <v>46186.27342838892</v>
       </c>
       <c r="Z128" s="4" t="inlineStr"/>
     </row>
@@ -8515,7 +8515,7 @@
       <c r="W129" s="4" t="inlineStr"/>
       <c r="X129" s="4" t="inlineStr"/>
       <c r="Y129" s="5" t="n">
-        <v>46186.27264112272</v>
+        <v>46186.27342838955</v>
       </c>
       <c r="Z129" s="4" t="inlineStr"/>
     </row>
@@ -8583,7 +8583,7 @@
       <c r="W130" s="4" t="inlineStr"/>
       <c r="X130" s="4" t="inlineStr"/>
       <c r="Y130" s="5" t="n">
-        <v>46186.27264112291</v>
+        <v>46186.27342838982</v>
       </c>
       <c r="Z130" s="4" t="inlineStr"/>
     </row>
@@ -8651,7 +8651,7 @@
       <c r="W131" s="4" t="inlineStr"/>
       <c r="X131" s="4" t="inlineStr"/>
       <c r="Y131" s="5" t="n">
-        <v>46186.27264112311</v>
+        <v>46186.27342839004</v>
       </c>
       <c r="Z131" s="4" t="inlineStr"/>
     </row>
@@ -8711,7 +8711,7 @@
       <c r="W132" s="4" t="inlineStr"/>
       <c r="X132" s="4" t="inlineStr"/>
       <c r="Y132" s="5" t="n">
-        <v>46186.2726411237</v>
+        <v>46186.27342839025</v>
       </c>
       <c r="Z132" s="4" t="inlineStr"/>
     </row>
@@ -8779,7 +8779,7 @@
       <c r="W133" s="4" t="inlineStr"/>
       <c r="X133" s="4" t="inlineStr"/>
       <c r="Y133" s="5" t="n">
-        <v>46186.27264112404</v>
+        <v>46186.27342839044</v>
       </c>
       <c r="Z133" s="4" t="inlineStr"/>
     </row>
@@ -8847,7 +8847,7 @@
       <c r="W134" s="4" t="inlineStr"/>
       <c r="X134" s="4" t="inlineStr"/>
       <c r="Y134" s="5" t="n">
-        <v>46186.27264112428</v>
+        <v>46186.27342839064</v>
       </c>
       <c r="Z134" s="4" t="inlineStr"/>
     </row>
@@ -8915,7 +8915,7 @@
       <c r="W135" s="4" t="inlineStr"/>
       <c r="X135" s="4" t="inlineStr"/>
       <c r="Y135" s="5" t="n">
-        <v>46186.27264112454</v>
+        <v>46186.27342839086</v>
       </c>
       <c r="Z135" s="4" t="inlineStr"/>
     </row>
@@ -8975,7 +8975,7 @@
       <c r="W136" s="4" t="inlineStr"/>
       <c r="X136" s="4" t="inlineStr"/>
       <c r="Y136" s="5" t="n">
-        <v>46186.27264112476</v>
+        <v>46186.27342839108</v>
       </c>
       <c r="Z136" s="4" t="inlineStr"/>
     </row>
@@ -9035,7 +9035,7 @@
       <c r="W137" s="4" t="inlineStr"/>
       <c r="X137" s="4" t="inlineStr"/>
       <c r="Y137" s="5" t="n">
-        <v>46186.27264112498</v>
+        <v>46186.27342839129</v>
       </c>
       <c r="Z137" s="4" t="inlineStr"/>
     </row>
@@ -9103,7 +9103,7 @@
       <c r="W138" s="4" t="inlineStr"/>
       <c r="X138" s="4" t="inlineStr"/>
       <c r="Y138" s="5" t="n">
-        <v>46186.27264112527</v>
+        <v>46186.27342839152</v>
       </c>
       <c r="Z138" s="4" t="inlineStr"/>
     </row>
@@ -9171,7 +9171,7 @@
       <c r="W139" s="4" t="inlineStr"/>
       <c r="X139" s="4" t="inlineStr"/>
       <c r="Y139" s="5" t="n">
-        <v>46186.27264112548</v>
+        <v>46186.27342839172</v>
       </c>
       <c r="Z139" s="4" t="inlineStr"/>
     </row>
@@ -9239,7 +9239,7 @@
       <c r="W140" s="4" t="inlineStr"/>
       <c r="X140" s="4" t="inlineStr"/>
       <c r="Y140" s="5" t="n">
-        <v>46186.2726411257</v>
+        <v>46186.27342839193</v>
       </c>
       <c r="Z140" s="4" t="inlineStr"/>
     </row>
@@ -9307,7 +9307,7 @@
       <c r="W141" s="4" t="inlineStr"/>
       <c r="X141" s="4" t="inlineStr"/>
       <c r="Y141" s="5" t="n">
-        <v>46186.27264112591</v>
+        <v>46186.27342839212</v>
       </c>
       <c r="Z141" s="4" t="inlineStr"/>
     </row>
@@ -9375,7 +9375,7 @@
       <c r="W142" s="4" t="inlineStr"/>
       <c r="X142" s="4" t="inlineStr"/>
       <c r="Y142" s="5" t="n">
-        <v>46186.27264112647</v>
+        <v>46186.27342839233</v>
       </c>
       <c r="Z142" s="4" t="inlineStr"/>
     </row>
@@ -9443,7 +9443,7 @@
       <c r="W143" s="4" t="inlineStr"/>
       <c r="X143" s="4" t="inlineStr"/>
       <c r="Y143" s="5" t="n">
-        <v>46186.27264112682</v>
+        <v>46186.27342839257</v>
       </c>
       <c r="Z143" s="4" t="inlineStr"/>
     </row>
@@ -9511,7 +9511,7 @@
       <c r="W144" s="4" t="inlineStr"/>
       <c r="X144" s="4" t="inlineStr"/>
       <c r="Y144" s="5" t="n">
-        <v>46186.27264112705</v>
+        <v>46186.27342839316</v>
       </c>
       <c r="Z144" s="4" t="inlineStr"/>
     </row>
@@ -9579,7 +9579,7 @@
       <c r="W145" s="4" t="inlineStr"/>
       <c r="X145" s="4" t="inlineStr"/>
       <c r="Y145" s="5" t="n">
-        <v>46186.27264112727</v>
+        <v>46186.27342839347</v>
       </c>
       <c r="Z145" s="4" t="inlineStr"/>
     </row>
@@ -9647,7 +9647,7 @@
       <c r="W146" s="4" t="inlineStr"/>
       <c r="X146" s="4" t="inlineStr"/>
       <c r="Y146" s="5" t="n">
-        <v>46186.27264112749</v>
+        <v>46186.2734283937</v>
       </c>
       <c r="Z146" s="4" t="inlineStr"/>
     </row>
@@ -9711,7 +9711,7 @@
       <c r="W147" s="8" t="inlineStr"/>
       <c r="X147" s="8" t="inlineStr"/>
       <c r="Y147" s="9" t="n">
-        <v>46186.27264112767</v>
+        <v>46186.27342839391</v>
       </c>
       <c r="Z147" s="8" t="inlineStr"/>
     </row>
@@ -9775,7 +9775,7 @@
       <c r="W148" s="8" t="inlineStr"/>
       <c r="X148" s="8" t="inlineStr"/>
       <c r="Y148" s="9" t="n">
-        <v>46186.27264112789</v>
+        <v>46186.27342839413</v>
       </c>
       <c r="Z148" s="8" t="inlineStr"/>
     </row>
@@ -9839,7 +9839,7 @@
       <c r="W149" s="8" t="inlineStr"/>
       <c r="X149" s="8" t="inlineStr"/>
       <c r="Y149" s="9" t="n">
-        <v>46186.27264112805</v>
+        <v>46186.27342839434</v>
       </c>
       <c r="Z149" s="8" t="inlineStr"/>
     </row>
@@ -9903,7 +9903,7 @@
       <c r="W150" s="8" t="inlineStr"/>
       <c r="X150" s="8" t="inlineStr"/>
       <c r="Y150" s="9" t="n">
-        <v>46186.27264112823</v>
+        <v>46186.27342839452</v>
       </c>
       <c r="Z150" s="8" t="inlineStr"/>
     </row>
@@ -9971,7 +9971,7 @@
       <c r="W151" s="4" t="inlineStr"/>
       <c r="X151" s="4" t="inlineStr"/>
       <c r="Y151" s="5" t="n">
-        <v>46186.2726411284</v>
+        <v>46186.27342839471</v>
       </c>
       <c r="Z151" s="4" t="inlineStr"/>
     </row>
@@ -10035,7 +10035,7 @@
       <c r="W152" s="8" t="inlineStr"/>
       <c r="X152" s="8" t="inlineStr"/>
       <c r="Y152" s="9" t="n">
-        <v>46186.27264112859</v>
+        <v>46186.27342839492</v>
       </c>
       <c r="Z152" s="8" t="inlineStr"/>
     </row>
@@ -10083,7 +10083,7 @@
       <c r="W153" s="8" t="inlineStr"/>
       <c r="X153" s="8" t="inlineStr"/>
       <c r="Y153" s="9" t="n">
-        <v>46186.27264112885</v>
+        <v>46186.27342839519</v>
       </c>
       <c r="Z153" s="8" t="inlineStr"/>
     </row>
@@ -10151,7 +10151,7 @@
       <c r="W154" s="8" t="inlineStr"/>
       <c r="X154" s="8" t="inlineStr"/>
       <c r="Y154" s="9" t="n">
-        <v>46186.27264112907</v>
+        <v>46186.27342839541</v>
       </c>
       <c r="Z154" s="8" t="inlineStr"/>
     </row>
@@ -10219,7 +10219,7 @@
       <c r="W155" s="8" t="inlineStr"/>
       <c r="X155" s="8" t="inlineStr"/>
       <c r="Y155" s="9" t="n">
-        <v>46186.27264112932</v>
+        <v>46186.27342839599</v>
       </c>
       <c r="Z155" s="8" t="inlineStr"/>
     </row>
@@ -10279,7 +10279,7 @@
       <c r="W156" s="4" t="inlineStr"/>
       <c r="X156" s="4" t="inlineStr"/>
       <c r="Y156" s="5" t="n">
-        <v>46186.27264112984</v>
+        <v>46186.27342839626</v>
       </c>
       <c r="Z156" s="4" t="inlineStr"/>
     </row>
@@ -10339,7 +10339,7 @@
       <c r="W157" s="4" t="inlineStr"/>
       <c r="X157" s="4" t="inlineStr"/>
       <c r="Y157" s="5" t="n">
-        <v>46186.27264113009</v>
+        <v>46186.27342839693</v>
       </c>
       <c r="Z157" s="4" t="inlineStr"/>
     </row>
@@ -10399,7 +10399,7 @@
       <c r="W158" s="4" t="inlineStr"/>
       <c r="X158" s="4" t="inlineStr"/>
       <c r="Y158" s="5" t="n">
-        <v>46186.2726411303</v>
+        <v>46186.2734283972</v>
       </c>
       <c r="Z158" s="4" t="inlineStr"/>
     </row>
@@ -10463,7 +10463,7 @@
       <c r="W159" s="8" t="inlineStr"/>
       <c r="X159" s="8" t="inlineStr"/>
       <c r="Y159" s="9" t="n">
-        <v>46186.27264113054</v>
+        <v>46186.27342839748</v>
       </c>
       <c r="Z159" s="8" t="inlineStr"/>
     </row>
@@ -10519,7 +10519,7 @@
       <c r="W160" s="8" t="inlineStr"/>
       <c r="X160" s="8" t="inlineStr"/>
       <c r="Y160" s="9" t="n">
-        <v>46186.27264113077</v>
+        <v>46186.27342839771</v>
       </c>
       <c r="Z160" s="8" t="inlineStr"/>
     </row>
@@ -10575,7 +10575,7 @@
       <c r="W161" s="8" t="inlineStr"/>
       <c r="X161" s="8" t="inlineStr"/>
       <c r="Y161" s="9" t="n">
-        <v>46186.27264113138</v>
+        <v>46186.27342839792</v>
       </c>
       <c r="Z161" s="8" t="inlineStr"/>
     </row>
@@ -10631,7 +10631,7 @@
       <c r="W162" s="8" t="inlineStr"/>
       <c r="X162" s="8" t="inlineStr"/>
       <c r="Y162" s="9" t="n">
-        <v>46186.27264113163</v>
+        <v>46186.27342839811</v>
       </c>
       <c r="Z162" s="8" t="inlineStr"/>
     </row>
@@ -10687,7 +10687,7 @@
       <c r="W163" s="8" t="inlineStr"/>
       <c r="X163" s="8" t="inlineStr"/>
       <c r="Y163" s="9" t="n">
-        <v>46186.27264113185</v>
+        <v>46186.27342839831</v>
       </c>
       <c r="Z163" s="8" t="inlineStr"/>
     </row>
@@ -10751,7 +10751,7 @@
       <c r="W164" s="8" t="inlineStr"/>
       <c r="X164" s="8" t="inlineStr"/>
       <c r="Y164" s="9" t="n">
-        <v>46186.27264113207</v>
+        <v>46186.27342839852</v>
       </c>
       <c r="Z164" s="8" t="inlineStr"/>
     </row>
@@ -10815,7 +10815,7 @@
       <c r="W165" s="8" t="inlineStr"/>
       <c r="X165" s="8" t="inlineStr"/>
       <c r="Y165" s="9" t="n">
-        <v>46186.27264113228</v>
+        <v>46186.27342839874</v>
       </c>
       <c r="Z165" s="8" t="inlineStr"/>
     </row>
@@ -10883,7 +10883,7 @@
       <c r="W166" s="8" t="inlineStr"/>
       <c r="X166" s="8" t="inlineStr"/>
       <c r="Y166" s="9" t="n">
-        <v>46186.27264113249</v>
+        <v>46186.27342839893</v>
       </c>
       <c r="Z166" s="8" t="inlineStr"/>
     </row>
@@ -10951,7 +10951,7 @@
       <c r="W167" s="8" t="inlineStr"/>
       <c r="X167" s="8" t="inlineStr"/>
       <c r="Y167" s="9" t="n">
-        <v>46186.27264113272</v>
+        <v>46186.27342839919</v>
       </c>
       <c r="Z167" s="8" t="inlineStr"/>
     </row>
@@ -11019,7 +11019,7 @@
       <c r="W168" s="8" t="inlineStr"/>
       <c r="X168" s="8" t="inlineStr"/>
       <c r="Y168" s="9" t="n">
-        <v>46186.27264113295</v>
+        <v>46186.27342839942</v>
       </c>
       <c r="Z168" s="8" t="inlineStr"/>
     </row>
@@ -11075,7 +11075,7 @@
       <c r="W169" s="8" t="inlineStr"/>
       <c r="X169" s="8" t="inlineStr"/>
       <c r="Y169" s="9" t="n">
-        <v>46186.27264113316</v>
+        <v>46186.27342839963</v>
       </c>
       <c r="Z169" s="8" t="inlineStr"/>
     </row>
@@ -11131,7 +11131,7 @@
       <c r="W170" s="8" t="inlineStr"/>
       <c r="X170" s="8" t="inlineStr"/>
       <c r="Y170" s="9" t="n">
-        <v>46186.27264113334</v>
+        <v>46186.27342839984</v>
       </c>
       <c r="Z170" s="8" t="inlineStr"/>
     </row>
@@ -11195,7 +11195,7 @@
       <c r="W171" s="8" t="inlineStr"/>
       <c r="X171" s="8" t="inlineStr"/>
       <c r="Y171" s="9" t="n">
-        <v>46186.27264113357</v>
+        <v>46186.27342840005</v>
       </c>
       <c r="Z171" s="8" t="inlineStr"/>
     </row>
@@ -11259,7 +11259,7 @@
       <c r="W172" s="8" t="inlineStr"/>
       <c r="X172" s="8" t="inlineStr"/>
       <c r="Y172" s="9" t="n">
-        <v>46186.27264113377</v>
+        <v>46186.27342840035</v>
       </c>
       <c r="Z172" s="8" t="inlineStr"/>
     </row>
@@ -11323,7 +11323,7 @@
       <c r="W173" s="8" t="inlineStr"/>
       <c r="X173" s="8" t="inlineStr"/>
       <c r="Y173" s="9" t="n">
-        <v>46186.27264113396</v>
+        <v>46186.27342840054</v>
       </c>
       <c r="Z173" s="8" t="inlineStr"/>
     </row>
@@ -11387,7 +11387,7 @@
       <c r="W174" s="8" t="inlineStr"/>
       <c r="X174" s="8" t="inlineStr"/>
       <c r="Y174" s="9" t="n">
-        <v>46186.27264113414</v>
+        <v>46186.27342840073</v>
       </c>
       <c r="Z174" s="8" t="inlineStr"/>
     </row>
@@ -11451,7 +11451,7 @@
       <c r="W175" s="8" t="inlineStr"/>
       <c r="X175" s="8" t="inlineStr"/>
       <c r="Y175" s="9" t="n">
-        <v>46186.27264113438</v>
+        <v>46186.27342840099</v>
       </c>
       <c r="Z175" s="8" t="inlineStr"/>
     </row>
@@ -11519,7 +11519,7 @@
       <c r="W176" s="8" t="inlineStr"/>
       <c r="X176" s="8" t="inlineStr"/>
       <c r="Y176" s="9" t="n">
-        <v>46186.27264113459</v>
+        <v>46186.2734284012</v>
       </c>
       <c r="Z176" s="8" t="inlineStr"/>
     </row>
@@ -11583,7 +11583,7 @@
       <c r="W177" s="8" t="inlineStr"/>
       <c r="X177" s="8" t="inlineStr"/>
       <c r="Y177" s="9" t="n">
-        <v>46186.27264113479</v>
+        <v>46186.2734284014</v>
       </c>
       <c r="Z177" s="8" t="inlineStr"/>
     </row>
@@ -11647,7 +11647,7 @@
       <c r="W178" s="8" t="inlineStr"/>
       <c r="X178" s="8" t="inlineStr"/>
       <c r="Y178" s="9" t="n">
-        <v>46186.27264113498</v>
+        <v>46186.2734284016</v>
       </c>
       <c r="Z178" s="8" t="inlineStr"/>
     </row>
@@ -11711,7 +11711,7 @@
       <c r="W179" s="8" t="inlineStr"/>
       <c r="X179" s="8" t="inlineStr"/>
       <c r="Y179" s="9" t="n">
-        <v>46186.27264113516</v>
+        <v>46186.27342840178</v>
       </c>
       <c r="Z179" s="8" t="inlineStr"/>
     </row>
@@ -11771,7 +11771,7 @@
       <c r="W180" s="4" t="inlineStr"/>
       <c r="X180" s="4" t="inlineStr"/>
       <c r="Y180" s="5" t="n">
-        <v>46186.27264113535</v>
+        <v>46186.27342840197</v>
       </c>
       <c r="Z180" s="4" t="inlineStr"/>
     </row>
@@ -11827,7 +11827,7 @@
       <c r="W181" s="8" t="inlineStr"/>
       <c r="X181" s="8" t="inlineStr"/>
       <c r="Y181" s="9" t="n">
-        <v>46186.27264113558</v>
+        <v>46186.2734284022</v>
       </c>
       <c r="Z181" s="8" t="inlineStr"/>
     </row>
@@ -11895,7 +11895,7 @@
       <c r="W182" s="8" t="inlineStr"/>
       <c r="X182" s="8" t="inlineStr"/>
       <c r="Y182" s="9" t="n">
-        <v>46186.27264113585</v>
+        <v>46186.27342840246</v>
       </c>
       <c r="Z182" s="8" t="inlineStr"/>
     </row>
@@ -11959,7 +11959,7 @@
       <c r="W183" s="8" t="inlineStr"/>
       <c r="X183" s="8" t="inlineStr"/>
       <c r="Y183" s="9" t="n">
-        <v>46186.27264113604</v>
+        <v>46186.27342840267</v>
       </c>
       <c r="Z183" s="8" t="inlineStr"/>
     </row>
@@ -12027,7 +12027,7 @@
       <c r="W184" s="4" t="inlineStr"/>
       <c r="X184" s="4" t="inlineStr"/>
       <c r="Y184" s="5" t="n">
-        <v>46186.27264113624</v>
+        <v>46186.27342840287</v>
       </c>
       <c r="Z184" s="4" t="inlineStr"/>
     </row>
@@ -12095,7 +12095,7 @@
       <c r="W185" s="4" t="inlineStr"/>
       <c r="X185" s="4" t="inlineStr"/>
       <c r="Y185" s="5" t="n">
-        <v>46186.27264113641</v>
+        <v>46186.27342840308</v>
       </c>
       <c r="Z185" s="4" t="inlineStr"/>
     </row>
@@ -12163,7 +12163,7 @@
       <c r="W186" s="4" t="inlineStr"/>
       <c r="X186" s="4" t="inlineStr"/>
       <c r="Y186" s="5" t="n">
-        <v>46186.27264113659</v>
+        <v>46186.27342840538</v>
       </c>
       <c r="Z186" s="4" t="inlineStr"/>
     </row>
@@ -12223,7 +12223,7 @@
       <c r="W187" s="4" t="inlineStr"/>
       <c r="X187" s="4" t="inlineStr"/>
       <c r="Y187" s="5" t="n">
-        <v>46186.2726411369</v>
+        <v>46186.27342840594</v>
       </c>
       <c r="Z187" s="4" t="inlineStr"/>
     </row>
@@ -12291,7 +12291,7 @@
       <c r="W188" s="4" t="inlineStr"/>
       <c r="X188" s="4" t="inlineStr"/>
       <c r="Y188" s="5" t="n">
-        <v>46186.2726411371</v>
+        <v>46186.27342840622</v>
       </c>
       <c r="Z188" s="4" t="inlineStr"/>
     </row>
@@ -12359,7 +12359,7 @@
       <c r="W189" s="4" t="inlineStr"/>
       <c r="X189" s="4" t="inlineStr"/>
       <c r="Y189" s="5" t="n">
-        <v>46186.27264113761</v>
+        <v>46186.27342840651</v>
       </c>
       <c r="Z189" s="4" t="inlineStr"/>
     </row>
@@ -12427,7 +12427,7 @@
       <c r="W190" s="4" t="inlineStr"/>
       <c r="X190" s="4" t="inlineStr"/>
       <c r="Y190" s="5" t="n">
-        <v>46186.27264113795</v>
+        <v>46186.27342840671</v>
       </c>
       <c r="Z190" s="4" t="inlineStr"/>
     </row>
@@ -12495,7 +12495,7 @@
       <c r="W191" s="4" t="inlineStr"/>
       <c r="X191" s="4" t="inlineStr"/>
       <c r="Y191" s="5" t="n">
-        <v>46186.2726411382</v>
+        <v>46186.27342840691</v>
       </c>
       <c r="Z191" s="4" t="inlineStr"/>
     </row>
@@ -12563,7 +12563,7 @@
       <c r="W192" s="4" t="inlineStr"/>
       <c r="X192" s="4" t="inlineStr"/>
       <c r="Y192" s="5" t="n">
-        <v>46186.2726411384</v>
+        <v>46186.27342840767</v>
       </c>
       <c r="Z192" s="4" t="inlineStr"/>
     </row>
@@ -12627,7 +12627,7 @@
       <c r="W193" s="8" t="inlineStr"/>
       <c r="X193" s="8" t="inlineStr"/>
       <c r="Y193" s="9" t="n">
-        <v>46186.27264113862</v>
+        <v>46186.27342840801</v>
       </c>
       <c r="Z193" s="8" t="inlineStr"/>
     </row>
@@ -12695,7 +12695,7 @@
       <c r="W194" s="8" t="inlineStr"/>
       <c r="X194" s="8" t="inlineStr"/>
       <c r="Y194" s="9" t="n">
-        <v>46186.27264113886</v>
+        <v>46186.27342840833</v>
       </c>
       <c r="Z194" s="8" t="inlineStr"/>
     </row>
@@ -12759,7 +12759,7 @@
       <c r="W195" s="8" t="inlineStr"/>
       <c r="X195" s="8" t="inlineStr"/>
       <c r="Y195" s="9" t="n">
-        <v>46186.27264113908</v>
+        <v>46186.27342840857</v>
       </c>
       <c r="Z195" s="8" t="inlineStr"/>
     </row>
@@ -12815,7 +12815,7 @@
       <c r="W196" s="8" t="inlineStr"/>
       <c r="X196" s="8" t="inlineStr"/>
       <c r="Y196" s="9" t="n">
-        <v>46186.27264113929</v>
+        <v>46186.27342840879</v>
       </c>
       <c r="Z196" s="8" t="inlineStr"/>
     </row>
@@ -12871,7 +12871,7 @@
       <c r="W197" s="8" t="inlineStr"/>
       <c r="X197" s="8" t="inlineStr"/>
       <c r="Y197" s="9" t="n">
-        <v>46186.27264113951</v>
+        <v>46186.27342840902</v>
       </c>
       <c r="Z197" s="8" t="inlineStr"/>
     </row>
@@ -12923,7 +12923,7 @@
       <c r="W198" s="8" t="inlineStr"/>
       <c r="X198" s="8" t="inlineStr"/>
       <c r="Y198" s="9" t="n">
-        <v>46186.27264113971</v>
+        <v>46186.27342840921</v>
       </c>
       <c r="Z198" s="8" t="inlineStr"/>
     </row>
@@ -12987,7 +12987,7 @@
       <c r="W199" s="8" t="inlineStr"/>
       <c r="X199" s="8" t="inlineStr"/>
       <c r="Y199" s="9" t="n">
-        <v>46186.27264113992</v>
+        <v>46186.27342840945</v>
       </c>
       <c r="Z199" s="8" t="inlineStr"/>
     </row>
@@ -13043,7 +13043,7 @@
       <c r="W200" s="8" t="inlineStr"/>
       <c r="X200" s="8" t="inlineStr"/>
       <c r="Y200" s="9" t="n">
-        <v>46186.27264114014</v>
+        <v>46186.27342840967</v>
       </c>
       <c r="Z200" s="8" t="inlineStr"/>
     </row>
@@ -13099,7 +13099,7 @@
       <c r="W201" s="8" t="inlineStr"/>
       <c r="X201" s="8" t="inlineStr"/>
       <c r="Y201" s="9" t="n">
-        <v>46186.27264114035</v>
+        <v>46186.27342840986</v>
       </c>
       <c r="Z201" s="8" t="inlineStr"/>
     </row>
@@ -13167,7 +13167,7 @@
       <c r="W202" s="4" t="inlineStr"/>
       <c r="X202" s="4" t="inlineStr"/>
       <c r="Y202" s="5" t="n">
-        <v>46186.27264114058</v>
+        <v>46186.27342841012</v>
       </c>
       <c r="Z202" s="4" t="inlineStr"/>
     </row>
@@ -13227,7 +13227,7 @@
       <c r="W203" s="4" t="inlineStr"/>
       <c r="X203" s="4" t="inlineStr"/>
       <c r="Y203" s="5" t="n">
-        <v>46186.2726411408</v>
+        <v>46186.27342841032</v>
       </c>
       <c r="Z203" s="4" t="inlineStr"/>
     </row>
@@ -13295,7 +13295,7 @@
       <c r="W204" s="4" t="inlineStr"/>
       <c r="X204" s="4" t="inlineStr"/>
       <c r="Y204" s="5" t="n">
-        <v>46186.2726411413</v>
+        <v>46186.27342841053</v>
       </c>
       <c r="Z204" s="4" t="inlineStr"/>
     </row>
@@ -13359,7 +13359,7 @@
       <c r="W205" s="4" t="inlineStr"/>
       <c r="X205" s="4" t="inlineStr"/>
       <c r="Y205" s="5" t="n">
-        <v>46186.27264114165</v>
+        <v>46186.27342841079</v>
       </c>
       <c r="Z205" s="4" t="inlineStr"/>
     </row>
@@ -13427,7 +13427,7 @@
       <c r="W206" s="4" t="inlineStr"/>
       <c r="X206" s="4" t="inlineStr"/>
       <c r="Y206" s="5" t="n">
-        <v>46186.27264114228</v>
+        <v>46186.27342841164</v>
       </c>
       <c r="Z206" s="4" t="inlineStr"/>
     </row>
@@ -13487,7 +13487,7 @@
       <c r="W207" s="4" t="inlineStr"/>
       <c r="X207" s="4" t="inlineStr"/>
       <c r="Y207" s="5" t="n">
-        <v>46186.2726411426</v>
+        <v>46186.27342841197</v>
       </c>
       <c r="Z207" s="4" t="inlineStr"/>
     </row>
@@ -13547,7 +13547,7 @@
       <c r="W208" s="4" t="inlineStr"/>
       <c r="X208" s="4" t="inlineStr"/>
       <c r="Y208" s="5" t="n">
-        <v>46186.2726411429</v>
+        <v>46186.27342841227</v>
       </c>
       <c r="Z208" s="4" t="inlineStr"/>
     </row>
@@ -13603,7 +13603,7 @@
       <c r="W209" s="4" t="inlineStr"/>
       <c r="X209" s="4" t="inlineStr"/>
       <c r="Y209" s="5" t="n">
-        <v>46186.27264114311</v>
+        <v>46186.27342841247</v>
       </c>
       <c r="Z209" s="4" t="inlineStr"/>
     </row>
@@ -13671,7 +13671,7 @@
       <c r="W210" s="4" t="inlineStr"/>
       <c r="X210" s="4" t="inlineStr"/>
       <c r="Y210" s="5" t="n">
-        <v>46186.27264114335</v>
+        <v>46186.27342841274</v>
       </c>
       <c r="Z210" s="4" t="inlineStr"/>
     </row>
@@ -13739,7 +13739,7 @@
       <c r="W211" s="4" t="inlineStr"/>
       <c r="X211" s="4" t="inlineStr"/>
       <c r="Y211" s="5" t="n">
-        <v>46186.27264114358</v>
+        <v>46186.273428413</v>
       </c>
       <c r="Z211" s="4" t="inlineStr"/>
     </row>
@@ -13807,7 +13807,7 @@
       <c r="W212" s="4" t="inlineStr"/>
       <c r="X212" s="4" t="inlineStr"/>
       <c r="Y212" s="5" t="n">
-        <v>46186.27264114378</v>
+        <v>46186.27342841322</v>
       </c>
       <c r="Z212" s="4" t="inlineStr"/>
     </row>
@@ -13875,7 +13875,7 @@
       <c r="W213" s="4" t="inlineStr"/>
       <c r="X213" s="4" t="inlineStr"/>
       <c r="Y213" s="5" t="n">
-        <v>46186.27264114399</v>
+        <v>46186.27342841343</v>
       </c>
       <c r="Z213" s="4" t="inlineStr"/>
     </row>
@@ -13943,7 +13943,7 @@
       <c r="W214" s="4" t="inlineStr"/>
       <c r="X214" s="4" t="inlineStr"/>
       <c r="Y214" s="5" t="n">
-        <v>46186.2726411442</v>
+        <v>46186.27342841412</v>
       </c>
       <c r="Z214" s="4" t="inlineStr"/>
     </row>
@@ -14011,7 +14011,7 @@
       <c r="W215" s="4" t="inlineStr"/>
       <c r="X215" s="4" t="inlineStr"/>
       <c r="Y215" s="5" t="n">
-        <v>46186.27264114442</v>
+        <v>46186.2734284144</v>
       </c>
       <c r="Z215" s="4" t="inlineStr"/>
     </row>
@@ -14067,7 +14067,7 @@
       <c r="W216" s="4" t="inlineStr"/>
       <c r="X216" s="4" t="inlineStr"/>
       <c r="Y216" s="5" t="n">
-        <v>46186.27264114461</v>
+        <v>46186.27342841463</v>
       </c>
       <c r="Z216" s="4" t="inlineStr"/>
     </row>
@@ -14123,7 +14123,7 @@
       <c r="W217" s="4" t="inlineStr"/>
       <c r="X217" s="4" t="inlineStr"/>
       <c r="Y217" s="5" t="n">
-        <v>46186.27264114511</v>
+        <v>46186.27342841484</v>
       </c>
       <c r="Z217" s="4" t="inlineStr"/>
     </row>
@@ -14179,7 +14179,7 @@
       <c r="W218" s="4" t="inlineStr"/>
       <c r="X218" s="4" t="inlineStr"/>
       <c r="Y218" s="5" t="n">
-        <v>46186.27264114544</v>
+        <v>46186.27342841504</v>
       </c>
       <c r="Z218" s="4" t="inlineStr"/>
     </row>
@@ -14235,7 +14235,7 @@
       <c r="W219" s="4" t="inlineStr"/>
       <c r="X219" s="4" t="inlineStr"/>
       <c r="Y219" s="5" t="n">
-        <v>46186.27264114566</v>
+        <v>46186.27342841522</v>
       </c>
       <c r="Z219" s="4" t="inlineStr"/>
     </row>
@@ -14303,7 +14303,7 @@
       <c r="W220" s="4" t="inlineStr"/>
       <c r="X220" s="4" t="inlineStr"/>
       <c r="Y220" s="5" t="n">
-        <v>46186.2726411459</v>
+        <v>46186.27342841545</v>
       </c>
       <c r="Z220" s="4" t="inlineStr"/>
     </row>
@@ -14371,7 +14371,7 @@
       <c r="W221" s="4" t="inlineStr"/>
       <c r="X221" s="4" t="inlineStr"/>
       <c r="Y221" s="5" t="n">
-        <v>46186.27264114613</v>
+        <v>46186.27342841565</v>
       </c>
       <c r="Z221" s="4" t="inlineStr"/>
     </row>
@@ -14439,7 +14439,7 @@
       <c r="W222" s="4" t="inlineStr"/>
       <c r="X222" s="4" t="inlineStr"/>
       <c r="Y222" s="5" t="n">
-        <v>46186.27264114637</v>
+        <v>46186.27342841589</v>
       </c>
       <c r="Z222" s="4" t="inlineStr"/>
     </row>
@@ -14507,7 +14507,7 @@
       <c r="W223" s="4" t="inlineStr"/>
       <c r="X223" s="4" t="inlineStr"/>
       <c r="Y223" s="5" t="n">
-        <v>46186.27264114658</v>
+        <v>46186.27342841611</v>
       </c>
       <c r="Z223" s="4" t="inlineStr"/>
     </row>
@@ -14575,7 +14575,7 @@
       <c r="W224" s="4" t="inlineStr"/>
       <c r="X224" s="4" t="inlineStr"/>
       <c r="Y224" s="5" t="n">
-        <v>46186.27264114682</v>
+        <v>46186.27342841635</v>
       </c>
       <c r="Z224" s="4" t="inlineStr"/>
     </row>
@@ -14643,7 +14643,7 @@
       <c r="W225" s="4" t="inlineStr"/>
       <c r="X225" s="4" t="inlineStr"/>
       <c r="Y225" s="5" t="n">
-        <v>46186.27264114703</v>
+        <v>46186.27342841655</v>
       </c>
       <c r="Z225" s="4" t="inlineStr"/>
     </row>
@@ -14711,7 +14711,7 @@
       <c r="W226" s="4" t="inlineStr"/>
       <c r="X226" s="4" t="inlineStr"/>
       <c r="Y226" s="5" t="n">
-        <v>46186.27264114723</v>
+        <v>46186.27342841676</v>
       </c>
       <c r="Z226" s="4" t="inlineStr"/>
     </row>
@@ -14779,7 +14779,7 @@
       <c r="W227" s="4" t="inlineStr"/>
       <c r="X227" s="4" t="inlineStr"/>
       <c r="Y227" s="5" t="n">
-        <v>46186.27264114741</v>
+        <v>46186.27342841693</v>
       </c>
       <c r="Z227" s="4" t="inlineStr"/>
     </row>
@@ -14847,7 +14847,7 @@
       <c r="W228" s="4" t="inlineStr"/>
       <c r="X228" s="4" t="inlineStr"/>
       <c r="Y228" s="5" t="n">
-        <v>46186.2726411476</v>
+        <v>46186.27342841712</v>
       </c>
       <c r="Z228" s="4" t="inlineStr"/>
     </row>
@@ -14903,7 +14903,7 @@
       <c r="W229" s="4" t="inlineStr"/>
       <c r="X229" s="4" t="inlineStr"/>
       <c r="Y229" s="5" t="n">
-        <v>46186.27264114784</v>
+        <v>46186.27342841745</v>
       </c>
       <c r="Z229" s="4" t="inlineStr"/>
     </row>
@@ -14971,7 +14971,7 @@
       <c r="W230" s="4" t="inlineStr"/>
       <c r="X230" s="4" t="inlineStr"/>
       <c r="Y230" s="5" t="n">
-        <v>46186.27264114805</v>
+        <v>46186.27342841766</v>
       </c>
       <c r="Z230" s="4" t="inlineStr"/>
     </row>
@@ -15043,7 +15043,7 @@
       <c r="W231" s="4" t="inlineStr"/>
       <c r="X231" s="4" t="inlineStr"/>
       <c r="Y231" s="5" t="n">
-        <v>46186.27264114827</v>
+        <v>46186.27342841795</v>
       </c>
       <c r="Z231" s="4" t="inlineStr"/>
     </row>
@@ -15111,7 +15111,7 @@
       <c r="W232" s="4" t="inlineStr"/>
       <c r="X232" s="4" t="inlineStr"/>
       <c r="Y232" s="5" t="n">
-        <v>46186.27264114853</v>
+        <v>46186.27342841816</v>
       </c>
       <c r="Z232" s="4" t="inlineStr"/>
     </row>
@@ -15171,7 +15171,7 @@
       <c r="W233" s="4" t="inlineStr"/>
       <c r="X233" s="4" t="inlineStr"/>
       <c r="Y233" s="5" t="n">
-        <v>46186.27264114874</v>
+        <v>46186.27342841835</v>
       </c>
       <c r="Z233" s="4" t="inlineStr"/>
     </row>
@@ -15239,7 +15239,7 @@
       <c r="W234" s="4" t="inlineStr"/>
       <c r="X234" s="4" t="inlineStr"/>
       <c r="Y234" s="5" t="n">
-        <v>46186.27264114895</v>
+        <v>46186.27342841888</v>
       </c>
       <c r="Z234" s="4" t="inlineStr"/>
     </row>
@@ -15307,7 +15307,7 @@
       <c r="W235" s="4" t="inlineStr"/>
       <c r="X235" s="4" t="inlineStr"/>
       <c r="Y235" s="5" t="n">
-        <v>46186.2726411492</v>
+        <v>46186.27342841929</v>
       </c>
       <c r="Z235" s="4" t="inlineStr"/>
     </row>
@@ -15375,7 +15375,7 @@
       <c r="W236" s="4" t="inlineStr"/>
       <c r="X236" s="4" t="inlineStr"/>
       <c r="Y236" s="5" t="n">
-        <v>46186.27264114948</v>
+        <v>46186.2734284196</v>
       </c>
       <c r="Z236" s="4" t="inlineStr"/>
     </row>
@@ -15443,7 +15443,7 @@
       <c r="W237" s="4" t="inlineStr"/>
       <c r="X237" s="4" t="inlineStr"/>
       <c r="Y237" s="5" t="n">
-        <v>46186.27264114966</v>
+        <v>46186.27342841982</v>
       </c>
       <c r="Z237" s="4" t="inlineStr"/>
     </row>
@@ -15511,7 +15511,7 @@
       <c r="W238" s="4" t="inlineStr"/>
       <c r="X238" s="4" t="inlineStr"/>
       <c r="Y238" s="5" t="n">
-        <v>46186.27264114986</v>
+        <v>46186.27342842005</v>
       </c>
       <c r="Z238" s="4" t="inlineStr"/>
     </row>
@@ -15579,7 +15579,7 @@
       <c r="W239" s="4" t="inlineStr"/>
       <c r="X239" s="4" t="inlineStr"/>
       <c r="Y239" s="5" t="n">
-        <v>46186.27264115006</v>
+        <v>46186.27342842025</v>
       </c>
       <c r="Z239" s="4" t="inlineStr"/>
     </row>
@@ -15647,7 +15647,7 @@
       <c r="W240" s="4" t="inlineStr"/>
       <c r="X240" s="4" t="inlineStr"/>
       <c r="Y240" s="5" t="n">
-        <v>46186.27264115027</v>
+        <v>46186.27342842046</v>
       </c>
       <c r="Z240" s="4" t="inlineStr"/>
     </row>
@@ -15715,7 +15715,7 @@
       <c r="W241" s="4" t="inlineStr"/>
       <c r="X241" s="4" t="inlineStr"/>
       <c r="Y241" s="5" t="n">
-        <v>46186.27264115048</v>
+        <v>46186.27342842068</v>
       </c>
       <c r="Z241" s="4" t="inlineStr"/>
     </row>
@@ -15779,7 +15779,7 @@
       <c r="W242" s="8" t="inlineStr"/>
       <c r="X242" s="8" t="inlineStr"/>
       <c r="Y242" s="9" t="n">
-        <v>46186.27264115067</v>
+        <v>46186.27342842137</v>
       </c>
       <c r="Z242" s="8" t="inlineStr"/>
     </row>
@@ -15847,7 +15847,7 @@
       <c r="W243" s="8" t="inlineStr"/>
       <c r="X243" s="8" t="inlineStr"/>
       <c r="Y243" s="9" t="n">
-        <v>46186.27264115087</v>
+        <v>46186.27342842164</v>
       </c>
       <c r="Z243" s="8" t="inlineStr"/>
     </row>
@@ -15915,7 +15915,7 @@
       <c r="W244" s="8" t="inlineStr"/>
       <c r="X244" s="8" t="inlineStr"/>
       <c r="Y244" s="9" t="n">
-        <v>46186.27264115107</v>
+        <v>46186.27342842186</v>
       </c>
       <c r="Z244" s="8" t="inlineStr"/>
     </row>
@@ -15983,7 +15983,7 @@
       <c r="W245" s="4" t="inlineStr"/>
       <c r="X245" s="4" t="inlineStr"/>
       <c r="Y245" s="5" t="n">
-        <v>46186.27264115126</v>
+        <v>46186.27342842209</v>
       </c>
       <c r="Z245" s="4" t="inlineStr"/>
     </row>
@@ -16047,7 +16047,7 @@
       <c r="W246" s="8" t="inlineStr"/>
       <c r="X246" s="8" t="inlineStr"/>
       <c r="Y246" s="9" t="n">
-        <v>46186.2726411519</v>
+        <v>46186.27342842231</v>
       </c>
       <c r="Z246" s="8" t="inlineStr"/>
     </row>
@@ -16115,7 +16115,7 @@
       <c r="W247" s="4" t="inlineStr"/>
       <c r="X247" s="4" t="inlineStr"/>
       <c r="Y247" s="5" t="n">
-        <v>46186.27264115213</v>
+        <v>46186.27342842251</v>
       </c>
       <c r="Z247" s="4" t="inlineStr"/>
     </row>
@@ -16171,7 +16171,7 @@
       <c r="W248" s="8" t="inlineStr"/>
       <c r="X248" s="8" t="inlineStr"/>
       <c r="Y248" s="9" t="n">
-        <v>46186.27264115235</v>
+        <v>46186.27342842273</v>
       </c>
       <c r="Z248" s="8" t="inlineStr"/>
     </row>
@@ -16235,7 +16235,7 @@
       <c r="W249" s="8" t="inlineStr"/>
       <c r="X249" s="8" t="inlineStr"/>
       <c r="Y249" s="9" t="n">
-        <v>46186.27264115286</v>
+        <v>46186.27342842297</v>
       </c>
       <c r="Z249" s="8" t="inlineStr"/>
     </row>
@@ -16291,7 +16291,7 @@
       <c r="W250" s="8" t="inlineStr"/>
       <c r="X250" s="8" t="inlineStr"/>
       <c r="Y250" s="9" t="n">
-        <v>46186.27264115316</v>
+        <v>46186.27342842364</v>
       </c>
       <c r="Z250" s="8" t="inlineStr"/>
     </row>
@@ -16359,7 +16359,7 @@
       <c r="W251" s="8" t="inlineStr"/>
       <c r="X251" s="8" t="inlineStr"/>
       <c r="Y251" s="9" t="n">
-        <v>46186.27264115338</v>
+        <v>46186.27342842396</v>
       </c>
       <c r="Z251" s="8" t="inlineStr"/>
     </row>
@@ -16427,7 +16427,7 @@
       <c r="W252" s="4" t="inlineStr"/>
       <c r="X252" s="4" t="inlineStr"/>
       <c r="Y252" s="5" t="n">
-        <v>46186.27264115366</v>
+        <v>46186.27342842425</v>
       </c>
       <c r="Z252" s="4" t="inlineStr"/>
     </row>
@@ -16491,7 +16491,7 @@
       <c r="W253" s="8" t="inlineStr"/>
       <c r="X253" s="8" t="inlineStr"/>
       <c r="Y253" s="9" t="n">
-        <v>46186.27264115389</v>
+        <v>46186.27342842447</v>
       </c>
       <c r="Z253" s="8" t="inlineStr"/>
     </row>
@@ -16559,7 +16559,7 @@
       <c r="W254" s="4" t="inlineStr"/>
       <c r="X254" s="4" t="inlineStr"/>
       <c r="Y254" s="5" t="n">
-        <v>46186.27264115407</v>
+        <v>46186.27342842468</v>
       </c>
       <c r="Z254" s="4" t="inlineStr"/>
     </row>
@@ -16627,7 +16627,7 @@
       <c r="W255" s="8" t="inlineStr"/>
       <c r="X255" s="8" t="inlineStr"/>
       <c r="Y255" s="9" t="n">
-        <v>46186.27264115427</v>
+        <v>46186.27342842489</v>
       </c>
       <c r="Z255" s="8" t="inlineStr"/>
     </row>
@@ -16691,7 +16691,7 @@
       <c r="W256" s="8" t="inlineStr"/>
       <c r="X256" s="8" t="inlineStr"/>
       <c r="Y256" s="9" t="n">
-        <v>46186.2726411545</v>
+        <v>46186.27342842511</v>
       </c>
       <c r="Z256" s="8" t="inlineStr"/>
     </row>
@@ -16763,7 +16763,7 @@
       <c r="W257" s="4" t="inlineStr"/>
       <c r="X257" s="4" t="inlineStr"/>
       <c r="Y257" s="5" t="n">
-        <v>46186.27264115517</v>
+        <v>46186.27342842531</v>
       </c>
       <c r="Z257" s="4" t="inlineStr"/>
     </row>
@@ -16819,7 +16819,7 @@
       <c r="W258" s="8" t="inlineStr"/>
       <c r="X258" s="8" t="inlineStr"/>
       <c r="Y258" s="9" t="n">
-        <v>46186.27264115548</v>
+        <v>46186.27342842552</v>
       </c>
       <c r="Z258" s="8" t="inlineStr"/>
     </row>
@@ -16883,7 +16883,7 @@
       <c r="W259" s="8" t="inlineStr"/>
       <c r="X259" s="8" t="inlineStr"/>
       <c r="Y259" s="9" t="n">
-        <v>46186.27264115573</v>
+        <v>46186.27342842574</v>
       </c>
       <c r="Z259" s="8" t="inlineStr"/>
     </row>
@@ -16951,7 +16951,7 @@
       <c r="W260" s="8" t="inlineStr"/>
       <c r="X260" s="8" t="inlineStr"/>
       <c r="Y260" s="9" t="n">
-        <v>46186.27264115632</v>
+        <v>46186.27342842593</v>
       </c>
       <c r="Z260" s="8" t="inlineStr"/>
     </row>
@@ -17003,7 +17003,7 @@
       <c r="W261" s="8" t="inlineStr"/>
       <c r="X261" s="8" t="inlineStr"/>
       <c r="Y261" s="9" t="n">
-        <v>46186.27264115661</v>
+        <v>46186.27342842612</v>
       </c>
       <c r="Z261" s="8" t="inlineStr"/>
     </row>
@@ -17075,7 +17075,7 @@
       <c r="W262" s="8" t="inlineStr"/>
       <c r="X262" s="8" t="inlineStr"/>
       <c r="Y262" s="9" t="n">
-        <v>46186.27264115684</v>
+        <v>46186.27342842677</v>
       </c>
       <c r="Z262" s="8" t="inlineStr"/>
     </row>
@@ -17131,7 +17131,7 @@
       <c r="W263" s="8" t="inlineStr"/>
       <c r="X263" s="8" t="inlineStr"/>
       <c r="Y263" s="9" t="n">
-        <v>46186.27264115705</v>
+        <v>46186.27342842708</v>
       </c>
       <c r="Z263" s="8" t="inlineStr"/>
     </row>
@@ -17187,7 +17187,7 @@
       <c r="W264" s="8" t="inlineStr"/>
       <c r="X264" s="8" t="inlineStr"/>
       <c r="Y264" s="9" t="n">
-        <v>46186.27264115726</v>
+        <v>46186.27342842732</v>
       </c>
       <c r="Z264" s="8" t="inlineStr"/>
     </row>
@@ -17251,7 +17251,7 @@
       <c r="W265" s="8" t="inlineStr"/>
       <c r="X265" s="8" t="inlineStr"/>
       <c r="Y265" s="9" t="n">
-        <v>46186.27264115745</v>
+        <v>46186.27342842795</v>
       </c>
       <c r="Z265" s="8" t="inlineStr"/>
     </row>
@@ -17315,7 +17315,7 @@
       <c r="W266" s="8" t="inlineStr"/>
       <c r="X266" s="8" t="inlineStr"/>
       <c r="Y266" s="9" t="n">
-        <v>46186.27264115766</v>
+        <v>46186.27342842824</v>
       </c>
       <c r="Z266" s="8" t="inlineStr"/>
     </row>
@@ -17379,7 +17379,7 @@
       <c r="W267" s="8" t="inlineStr"/>
       <c r="X267" s="8" t="inlineStr"/>
       <c r="Y267" s="9" t="n">
-        <v>46186.27264115785</v>
+        <v>46186.27342842846</v>
       </c>
       <c r="Z267" s="8" t="inlineStr"/>
     </row>
@@ -17443,7 +17443,7 @@
       <c r="W268" s="8" t="inlineStr"/>
       <c r="X268" s="8" t="inlineStr"/>
       <c r="Y268" s="9" t="n">
-        <v>46186.27264115804</v>
+        <v>46186.27342842868</v>
       </c>
       <c r="Z268" s="8" t="inlineStr"/>
     </row>
@@ -17511,7 +17511,7 @@
       <c r="W269" s="4" t="inlineStr"/>
       <c r="X269" s="4" t="inlineStr"/>
       <c r="Y269" s="5" t="n">
-        <v>46186.27264115823</v>
+        <v>46186.27342842895</v>
       </c>
       <c r="Z269" s="4" t="inlineStr"/>
     </row>
@@ -17579,7 +17579,7 @@
       <c r="W270" s="4" t="inlineStr"/>
       <c r="X270" s="4" t="inlineStr"/>
       <c r="Y270" s="5" t="n">
-        <v>46186.27264115842</v>
+        <v>46186.27342842946</v>
       </c>
       <c r="Z270" s="4" t="inlineStr"/>
     </row>
@@ -17647,7 +17647,7 @@
       <c r="W271" s="4" t="inlineStr"/>
       <c r="X271" s="4" t="inlineStr"/>
       <c r="Y271" s="5" t="n">
-        <v>46186.2726411586</v>
+        <v>46186.27342842979</v>
       </c>
       <c r="Z271" s="4" t="inlineStr"/>
     </row>
@@ -17711,7 +17711,7 @@
       <c r="W272" s="8" t="inlineStr"/>
       <c r="X272" s="8" t="inlineStr"/>
       <c r="Y272" s="9" t="n">
-        <v>46186.27264115879</v>
+        <v>46186.27342843002</v>
       </c>
       <c r="Z272" s="8" t="inlineStr"/>
     </row>
@@ -17767,7 +17767,7 @@
       <c r="W273" s="8" t="inlineStr"/>
       <c r="X273" s="8" t="inlineStr"/>
       <c r="Y273" s="9" t="n">
-        <v>46186.27264115906</v>
+        <v>46186.27342843065</v>
       </c>
       <c r="Z273" s="8" t="inlineStr"/>
     </row>
@@ -17839,7 +17839,7 @@
       <c r="W274" s="4" t="inlineStr"/>
       <c r="X274" s="4" t="inlineStr"/>
       <c r="Y274" s="5" t="n">
-        <v>46186.2726411597</v>
+        <v>46186.27342843097</v>
       </c>
       <c r="Z274" s="4" t="inlineStr"/>
     </row>
@@ -17907,7 +17907,7 @@
       <c r="W275" s="4" t="inlineStr"/>
       <c r="X275" s="4" t="inlineStr"/>
       <c r="Y275" s="5" t="n">
-        <v>46186.27264116001</v>
+        <v>46186.2734284312</v>
       </c>
       <c r="Z275" s="4" t="inlineStr"/>
     </row>
@@ -17975,7 +17975,7 @@
       <c r="W276" s="4" t="inlineStr"/>
       <c r="X276" s="4" t="inlineStr"/>
       <c r="Y276" s="5" t="n">
-        <v>46186.27264116023</v>
+        <v>46186.27342843141</v>
       </c>
       <c r="Z276" s="4" t="inlineStr"/>
     </row>
@@ -18035,7 +18035,7 @@
       <c r="W277" s="4" t="inlineStr"/>
       <c r="X277" s="4" t="inlineStr"/>
       <c r="Y277" s="5" t="n">
-        <v>46186.27264116044</v>
+        <v>46186.27342843162</v>
       </c>
       <c r="Z277" s="4" t="inlineStr"/>
     </row>
@@ -18103,7 +18103,7 @@
       <c r="W278" s="4" t="inlineStr"/>
       <c r="X278" s="4" t="inlineStr"/>
       <c r="Y278" s="5" t="n">
-        <v>46186.27264116063</v>
+        <v>46186.27342843183</v>
       </c>
       <c r="Z278" s="4" t="inlineStr"/>
     </row>
@@ -18175,7 +18175,7 @@
       <c r="W279" s="4" t="inlineStr"/>
       <c r="X279" s="4" t="inlineStr"/>
       <c r="Y279" s="5" t="n">
-        <v>46186.27264116083</v>
+        <v>46186.27342843202</v>
       </c>
       <c r="Z279" s="4" t="inlineStr"/>
     </row>
@@ -18247,7 +18247,7 @@
       <c r="W280" s="4" t="inlineStr"/>
       <c r="X280" s="4" t="inlineStr"/>
       <c r="Y280" s="5" t="n">
-        <v>46186.27264116102</v>
+        <v>46186.2734284322</v>
       </c>
       <c r="Z280" s="4" t="inlineStr"/>
     </row>
@@ -18315,7 +18315,7 @@
       <c r="W281" s="4" t="inlineStr"/>
       <c r="X281" s="4" t="inlineStr"/>
       <c r="Y281" s="5" t="n">
-        <v>46186.27264116122</v>
+        <v>46186.27342843241</v>
       </c>
       <c r="Z281" s="4" t="inlineStr"/>
     </row>
@@ -18371,7 +18371,7 @@
       <c r="W282" s="4" t="inlineStr"/>
       <c r="X282" s="4" t="inlineStr"/>
       <c r="Y282" s="5" t="n">
-        <v>46186.2726411614</v>
+        <v>46186.27342843259</v>
       </c>
       <c r="Z282" s="4" t="inlineStr"/>
     </row>
@@ -18427,7 +18427,7 @@
       <c r="W283" s="4" t="inlineStr"/>
       <c r="X283" s="4" t="inlineStr"/>
       <c r="Y283" s="5" t="n">
-        <v>46186.27264116161</v>
+        <v>46186.27342843281</v>
       </c>
       <c r="Z283" s="4" t="inlineStr"/>
     </row>
@@ -18495,7 +18495,7 @@
       <c r="W284" s="4" t="inlineStr"/>
       <c r="X284" s="4" t="inlineStr"/>
       <c r="Y284" s="5" t="n">
-        <v>46186.27264116182</v>
+        <v>46186.27342843301</v>
       </c>
       <c r="Z284" s="4" t="inlineStr"/>
     </row>
@@ -18563,7 +18563,7 @@
       <c r="W285" s="4" t="inlineStr"/>
       <c r="X285" s="4" t="inlineStr"/>
       <c r="Y285" s="5" t="n">
-        <v>46186.27264116199</v>
+        <v>46186.2734284332</v>
       </c>
       <c r="Z285" s="4" t="inlineStr"/>
     </row>
@@ -18635,7 +18635,7 @@
       <c r="W286" s="4" t="inlineStr"/>
       <c r="X286" s="4" t="inlineStr"/>
       <c r="Y286" s="5" t="n">
-        <v>46186.27264116218</v>
+        <v>46186.27342843339</v>
       </c>
       <c r="Z286" s="4" t="inlineStr"/>
     </row>
@@ -18703,7 +18703,7 @@
       <c r="W287" s="4" t="inlineStr"/>
       <c r="X287" s="4" t="inlineStr"/>
       <c r="Y287" s="5" t="n">
-        <v>46186.27264116242</v>
+        <v>46186.27342843363</v>
       </c>
       <c r="Z287" s="4" t="inlineStr"/>
     </row>
@@ -18771,7 +18771,7 @@
       <c r="W288" s="4" t="inlineStr"/>
       <c r="X288" s="4" t="inlineStr"/>
       <c r="Y288" s="5" t="n">
-        <v>46186.27264116264</v>
+        <v>46186.27342843384</v>
       </c>
       <c r="Z288" s="4" t="inlineStr"/>
     </row>
@@ -18835,7 +18835,7 @@
       <c r="W289" s="8" t="inlineStr"/>
       <c r="X289" s="8" t="inlineStr"/>
       <c r="Y289" s="9" t="n">
-        <v>46186.27264116282</v>
+        <v>46186.27342843402</v>
       </c>
       <c r="Z289" s="8" t="inlineStr"/>
     </row>
@@ -18899,7 +18899,7 @@
       <c r="W290" s="8" t="inlineStr"/>
       <c r="X290" s="8" t="inlineStr"/>
       <c r="Y290" s="9" t="n">
-        <v>46186.27264116309</v>
+        <v>46186.27342843428</v>
       </c>
       <c r="Z290" s="8" t="inlineStr"/>
     </row>
@@ -18963,7 +18963,7 @@
       <c r="W291" s="8" t="inlineStr"/>
       <c r="X291" s="8" t="inlineStr"/>
       <c r="Y291" s="9" t="n">
-        <v>46186.27264116329</v>
+        <v>46186.2734284345</v>
       </c>
       <c r="Z291" s="8" t="inlineStr"/>
     </row>
@@ -19019,7 +19019,7 @@
       <c r="W292" s="8" t="inlineStr"/>
       <c r="X292" s="8" t="inlineStr"/>
       <c r="Y292" s="9" t="n">
-        <v>46186.27264116349</v>
+        <v>46186.27342843473</v>
       </c>
       <c r="Z292" s="8" t="inlineStr"/>
     </row>
@@ -19071,7 +19071,7 @@
       <c r="W293" s="8" t="inlineStr"/>
       <c r="X293" s="8" t="inlineStr"/>
       <c r="Y293" s="9" t="n">
-        <v>46186.27264116369</v>
+        <v>46186.27342843492</v>
       </c>
       <c r="Z293" s="8" t="inlineStr"/>
     </row>
@@ -19127,7 +19127,7 @@
       <c r="W294" s="8" t="inlineStr"/>
       <c r="X294" s="8" t="inlineStr"/>
       <c r="Y294" s="9" t="n">
-        <v>46186.27264116389</v>
+        <v>46186.27342843512</v>
       </c>
       <c r="Z294" s="8" t="inlineStr"/>
     </row>
@@ -19183,7 +19183,7 @@
       <c r="W295" s="8" t="inlineStr"/>
       <c r="X295" s="8" t="inlineStr"/>
       <c r="Y295" s="9" t="n">
-        <v>46186.27264116478</v>
+        <v>46186.27342843529</v>
       </c>
       <c r="Z295" s="8" t="inlineStr"/>
     </row>
@@ -19239,7 +19239,7 @@
       <c r="W296" s="8" t="inlineStr"/>
       <c r="X296" s="8" t="inlineStr"/>
       <c r="Y296" s="9" t="n">
-        <v>46186.27264116506</v>
+        <v>46186.27342843547</v>
       </c>
       <c r="Z296" s="8" t="inlineStr"/>
     </row>
@@ -19303,7 +19303,7 @@
       <c r="W297" s="8" t="inlineStr"/>
       <c r="X297" s="8" t="inlineStr"/>
       <c r="Y297" s="9" t="n">
-        <v>46186.27264116529</v>
+        <v>46186.27342843566</v>
       </c>
       <c r="Z297" s="8" t="inlineStr"/>
     </row>
@@ -19367,7 +19367,7 @@
       <c r="W298" s="8" t="inlineStr"/>
       <c r="X298" s="8" t="inlineStr"/>
       <c r="Y298" s="9" t="n">
-        <v>46186.27264116552</v>
+        <v>46186.27342843587</v>
       </c>
       <c r="Z298" s="8" t="inlineStr"/>
     </row>
@@ -19431,7 +19431,7 @@
       <c r="W299" s="8" t="inlineStr"/>
       <c r="X299" s="8" t="inlineStr"/>
       <c r="Y299" s="9" t="n">
-        <v>46186.27264116574</v>
+        <v>46186.27342843655</v>
       </c>
       <c r="Z299" s="8" t="inlineStr"/>
     </row>
@@ -19495,7 +19495,7 @@
       <c r="W300" s="8" t="inlineStr"/>
       <c r="X300" s="8" t="inlineStr"/>
       <c r="Y300" s="9" t="n">
-        <v>46186.27264116594</v>
+        <v>46186.27342843682</v>
       </c>
       <c r="Z300" s="8" t="inlineStr"/>
     </row>
@@ -19551,7 +19551,7 @@
       <c r="W301" s="8" t="inlineStr"/>
       <c r="X301" s="8" t="inlineStr"/>
       <c r="Y301" s="9" t="n">
-        <v>46186.27264116616</v>
+        <v>46186.27342843704</v>
       </c>
       <c r="Z301" s="8" t="inlineStr"/>
     </row>
@@ -19607,7 +19607,7 @@
       <c r="W302" s="8" t="inlineStr"/>
       <c r="X302" s="8" t="inlineStr"/>
       <c r="Y302" s="9" t="n">
-        <v>46186.27264116635</v>
+        <v>46186.27342843724</v>
       </c>
       <c r="Z302" s="8" t="inlineStr"/>
     </row>
@@ -19663,7 +19663,7 @@
       <c r="W303" s="8" t="inlineStr"/>
       <c r="X303" s="8" t="inlineStr"/>
       <c r="Y303" s="9" t="n">
-        <v>46186.27264116696</v>
+        <v>46186.27342843745</v>
       </c>
       <c r="Z303" s="8" t="inlineStr"/>
     </row>
@@ -19731,7 +19731,7 @@
       <c r="W304" s="8" t="inlineStr"/>
       <c r="X304" s="8" t="inlineStr"/>
       <c r="Y304" s="9" t="n">
-        <v>46186.27264116726</v>
+        <v>46186.2734284377</v>
       </c>
       <c r="Z304" s="8" t="inlineStr"/>
     </row>
@@ -19799,7 +19799,7 @@
       <c r="W305" s="8" t="inlineStr"/>
       <c r="X305" s="8" t="inlineStr"/>
       <c r="Y305" s="9" t="n">
-        <v>46186.2726411675</v>
+        <v>46186.27342843795</v>
       </c>
       <c r="Z305" s="8" t="inlineStr"/>
     </row>
@@ -19867,7 +19867,7 @@
       <c r="W306" s="8" t="inlineStr"/>
       <c r="X306" s="8" t="inlineStr"/>
       <c r="Y306" s="9" t="n">
-        <v>46186.27264116771</v>
+        <v>46186.27342843815</v>
       </c>
       <c r="Z306" s="8" t="inlineStr"/>
     </row>
@@ -19935,7 +19935,7 @@
       <c r="W307" s="8" t="inlineStr"/>
       <c r="X307" s="8" t="inlineStr"/>
       <c r="Y307" s="9" t="n">
-        <v>46186.27264116792</v>
+        <v>46186.27342843835</v>
       </c>
       <c r="Z307" s="8" t="inlineStr"/>
     </row>
@@ -20003,7 +20003,7 @@
       <c r="W308" s="8" t="inlineStr"/>
       <c r="X308" s="8" t="inlineStr"/>
       <c r="Y308" s="9" t="n">
-        <v>46186.27264116812</v>
+        <v>46186.27342843854</v>
       </c>
       <c r="Z308" s="8" t="inlineStr"/>
     </row>
@@ -20067,7 +20067,7 @@
       <c r="W309" s="8" t="inlineStr"/>
       <c r="X309" s="8" t="inlineStr"/>
       <c r="Y309" s="9" t="n">
-        <v>46186.27264116833</v>
+        <v>46186.27342843875</v>
       </c>
       <c r="Z309" s="8" t="inlineStr"/>
     </row>
@@ -20123,7 +20123,7 @@
       <c r="W310" s="8" t="inlineStr"/>
       <c r="X310" s="8" t="inlineStr"/>
       <c r="Y310" s="9" t="n">
-        <v>46186.27264116852</v>
+        <v>46186.27342843894</v>
       </c>
       <c r="Z310" s="8" t="inlineStr"/>
     </row>
@@ -20179,7 +20179,7 @@
       <c r="W311" s="8" t="inlineStr"/>
       <c r="X311" s="8" t="inlineStr"/>
       <c r="Y311" s="9" t="n">
-        <v>46186.27264116876</v>
+        <v>46186.27342843918</v>
       </c>
       <c r="Z311" s="8" t="inlineStr"/>
     </row>
@@ -20247,7 +20247,7 @@
       <c r="W312" s="4" t="inlineStr"/>
       <c r="X312" s="4" t="inlineStr"/>
       <c r="Y312" s="5" t="n">
-        <v>46186.27264116898</v>
+        <v>46186.27342843941</v>
       </c>
       <c r="Z312" s="4" t="inlineStr"/>
     </row>
@@ -20315,7 +20315,7 @@
       <c r="W313" s="4" t="inlineStr"/>
       <c r="X313" s="4" t="inlineStr"/>
       <c r="Y313" s="5" t="n">
-        <v>46186.27264116923</v>
+        <v>46186.27342843966</v>
       </c>
       <c r="Z313" s="4" t="inlineStr"/>
     </row>
@@ -20375,7 +20375,7 @@
       <c r="W314" s="4" t="inlineStr"/>
       <c r="X314" s="4" t="inlineStr"/>
       <c r="Y314" s="5" t="n">
-        <v>46186.27264116941</v>
+        <v>46186.27342843988</v>
       </c>
       <c r="Z314" s="4" t="inlineStr"/>
     </row>
@@ -20443,7 +20443,7 @@
       <c r="W315" s="8" t="inlineStr"/>
       <c r="X315" s="8" t="inlineStr"/>
       <c r="Y315" s="9" t="n">
-        <v>46186.27264116961</v>
+        <v>46186.27342844006</v>
       </c>
       <c r="Z315" s="8" t="inlineStr"/>
     </row>
@@ -20511,7 +20511,7 @@
       <c r="W316" s="12" t="inlineStr"/>
       <c r="X316" s="12" t="inlineStr"/>
       <c r="Y316" s="13" t="n">
-        <v>46186.27264116979</v>
+        <v>46186.27342844025</v>
       </c>
       <c r="Z316" s="12" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
       <c r="W317" s="8" t="inlineStr"/>
       <c r="X317" s="8" t="inlineStr"/>
       <c r="Y317" s="9" t="n">
-        <v>46186.27264117002</v>
+        <v>46186.27342844055</v>
       </c>
       <c r="Z317" s="8" t="inlineStr"/>
     </row>
@@ -20647,7 +20647,7 @@
       <c r="W318" s="4" t="inlineStr"/>
       <c r="X318" s="4" t="inlineStr"/>
       <c r="Y318" s="5" t="n">
-        <v>46186.27264117025</v>
+        <v>46186.27342844079</v>
       </c>
       <c r="Z318" s="4" t="inlineStr"/>
     </row>
@@ -20715,7 +20715,7 @@
       <c r="W319" s="4" t="inlineStr"/>
       <c r="X319" s="4" t="inlineStr"/>
       <c r="Y319" s="5" t="n">
-        <v>46186.27264117046</v>
+        <v>46186.273428441</v>
       </c>
       <c r="Z319" s="4" t="inlineStr"/>
     </row>
@@ -20787,7 +20787,7 @@
       <c r="W320" s="4" t="inlineStr"/>
       <c r="X320" s="4" t="inlineStr"/>
       <c r="Y320" s="5" t="n">
-        <v>46186.27264117067</v>
+        <v>46186.27342844123</v>
       </c>
       <c r="Z320" s="4" t="inlineStr"/>
     </row>
@@ -20855,7 +20855,7 @@
       <c r="W321" s="4" t="inlineStr"/>
       <c r="X321" s="4" t="inlineStr"/>
       <c r="Y321" s="5" t="n">
-        <v>46186.27264117123</v>
+        <v>46186.27342844145</v>
       </c>
       <c r="Z321" s="4" t="inlineStr"/>
     </row>
@@ -20927,7 +20927,7 @@
       <c r="W322" s="4" t="inlineStr"/>
       <c r="X322" s="4" t="inlineStr"/>
       <c r="Y322" s="5" t="n">
-        <v>46186.27264117158</v>
+        <v>46186.27342844225</v>
       </c>
       <c r="Z322" s="4" t="inlineStr"/>
     </row>
@@ -20995,7 +20995,7 @@
       <c r="W323" s="4" t="inlineStr"/>
       <c r="X323" s="4" t="inlineStr"/>
       <c r="Y323" s="5" t="n">
-        <v>46186.27264117186</v>
+        <v>46186.27342844262</v>
       </c>
       <c r="Z323" s="4" t="inlineStr"/>
     </row>
@@ -21063,7 +21063,7 @@
       <c r="W324" s="4" t="inlineStr"/>
       <c r="X324" s="4" t="inlineStr"/>
       <c r="Y324" s="5" t="n">
-        <v>46186.27264117209</v>
+        <v>46186.27342844286</v>
       </c>
       <c r="Z324" s="4" t="inlineStr"/>
     </row>
@@ -21131,7 +21131,7 @@
       <c r="W325" s="4" t="inlineStr"/>
       <c r="X325" s="4" t="inlineStr"/>
       <c r="Y325" s="5" t="n">
-        <v>46186.27264117228</v>
+        <v>46186.27342844307</v>
       </c>
       <c r="Z325" s="4" t="inlineStr"/>
     </row>
@@ -21191,7 +21191,7 @@
       <c r="W326" s="4" t="inlineStr"/>
       <c r="X326" s="4" t="inlineStr"/>
       <c r="Y326" s="5" t="n">
-        <v>46186.27264117255</v>
+        <v>46186.27342844332</v>
       </c>
       <c r="Z326" s="4" t="inlineStr"/>
     </row>
@@ -21255,7 +21255,7 @@
       <c r="W327" s="8" t="inlineStr"/>
       <c r="X327" s="8" t="inlineStr"/>
       <c r="Y327" s="9" t="n">
-        <v>46186.27264117278</v>
+        <v>46186.27342844395</v>
       </c>
       <c r="Z327" s="8" t="inlineStr"/>
     </row>
@@ -21323,7 +21323,7 @@
       <c r="W328" s="8" t="inlineStr"/>
       <c r="X328" s="8" t="inlineStr"/>
       <c r="Y328" s="9" t="n">
-        <v>46186.27264117299</v>
+        <v>46186.2734284442</v>
       </c>
       <c r="Z328" s="8" t="inlineStr"/>
     </row>
@@ -21391,7 +21391,7 @@
       <c r="W329" s="8" t="inlineStr"/>
       <c r="X329" s="8" t="inlineStr"/>
       <c r="Y329" s="9" t="n">
-        <v>46186.27264117321</v>
+        <v>46186.27342844447</v>
       </c>
       <c r="Z329" s="8" t="inlineStr"/>
     </row>
@@ -21455,7 +21455,7 @@
       <c r="W330" s="8" t="inlineStr"/>
       <c r="X330" s="8" t="inlineStr"/>
       <c r="Y330" s="9" t="n">
-        <v>46186.27264117343</v>
+        <v>46186.27342844468</v>
       </c>
       <c r="Z330" s="8" t="inlineStr"/>
     </row>
@@ -21523,7 +21523,7 @@
       <c r="W331" s="8" t="inlineStr"/>
       <c r="X331" s="8" t="inlineStr"/>
       <c r="Y331" s="9" t="n">
-        <v>46186.27264117405</v>
+        <v>46186.27342844491</v>
       </c>
       <c r="Z331" s="8" t="inlineStr"/>
     </row>
@@ -21591,7 +21591,7 @@
       <c r="W332" s="8" t="inlineStr"/>
       <c r="X332" s="8" t="inlineStr"/>
       <c r="Y332" s="9" t="n">
-        <v>46186.27264117434</v>
+        <v>46186.27342844513</v>
       </c>
       <c r="Z332" s="8" t="inlineStr"/>
     </row>
@@ -21655,7 +21655,7 @@
       <c r="W333" s="8" t="inlineStr"/>
       <c r="X333" s="8" t="inlineStr"/>
       <c r="Y333" s="9" t="n">
-        <v>46186.27264117456</v>
+        <v>46186.27342844533</v>
       </c>
       <c r="Z333" s="8" t="inlineStr"/>
     </row>
@@ -21723,7 +21723,7 @@
       <c r="W334" s="8" t="inlineStr"/>
       <c r="X334" s="8" t="inlineStr"/>
       <c r="Y334" s="9" t="n">
-        <v>46186.2726411748</v>
+        <v>46186.27342844557</v>
       </c>
       <c r="Z334" s="8" t="inlineStr"/>
     </row>
@@ -21791,7 +21791,7 @@
       <c r="W335" s="4" t="inlineStr"/>
       <c r="X335" s="4" t="inlineStr"/>
       <c r="Y335" s="5" t="n">
-        <v>46186.27264117501</v>
+        <v>46186.27342844578</v>
       </c>
       <c r="Z335" s="4" t="inlineStr"/>
     </row>
@@ -21855,7 +21855,7 @@
       <c r="W336" s="8" t="inlineStr"/>
       <c r="X336" s="8" t="inlineStr"/>
       <c r="Y336" s="9" t="n">
-        <v>46186.27264117523</v>
+        <v>46186.27342844598</v>
       </c>
       <c r="Z336" s="8" t="inlineStr"/>
     </row>
@@ -21923,7 +21923,7 @@
       <c r="W337" s="4" t="inlineStr"/>
       <c r="X337" s="4" t="inlineStr"/>
       <c r="Y337" s="5" t="n">
-        <v>46186.27264117543</v>
+        <v>46186.27342844618</v>
       </c>
       <c r="Z337" s="4" t="inlineStr"/>
     </row>
@@ -21987,7 +21987,7 @@
       <c r="W338" s="8" t="inlineStr"/>
       <c r="X338" s="8" t="inlineStr"/>
       <c r="Y338" s="9" t="n">
-        <v>46186.27264117562</v>
+        <v>46186.27342844638</v>
       </c>
       <c r="Z338" s="8" t="inlineStr"/>
     </row>
@@ -22051,7 +22051,7 @@
       <c r="W339" s="8" t="inlineStr"/>
       <c r="X339" s="8" t="inlineStr"/>
       <c r="Y339" s="9" t="n">
-        <v>46186.27264117613</v>
+        <v>46186.27342844656</v>
       </c>
       <c r="Z339" s="8" t="inlineStr"/>
     </row>
@@ -22119,7 +22119,7 @@
       <c r="W340" s="4" t="inlineStr"/>
       <c r="X340" s="4" t="inlineStr"/>
       <c r="Y340" s="5" t="n">
-        <v>46186.2726411764</v>
+        <v>46186.27342844674</v>
       </c>
       <c r="Z340" s="4" t="inlineStr"/>
     </row>
@@ -22187,7 +22187,7 @@
       <c r="W341" s="4" t="inlineStr"/>
       <c r="X341" s="4" t="inlineStr"/>
       <c r="Y341" s="5" t="n">
-        <v>46186.27264117666</v>
+        <v>46186.27342844697</v>
       </c>
       <c r="Z341" s="4" t="inlineStr"/>
     </row>
@@ -22247,7 +22247,7 @@
       <c r="W342" s="4" t="inlineStr"/>
       <c r="X342" s="4" t="inlineStr"/>
       <c r="Y342" s="5" t="n">
-        <v>46186.27264117686</v>
+        <v>46186.27342844715</v>
       </c>
       <c r="Z342" s="4" t="inlineStr"/>
     </row>
@@ -22311,7 +22311,7 @@
       <c r="W343" s="8" t="inlineStr"/>
       <c r="X343" s="8" t="inlineStr"/>
       <c r="Y343" s="9" t="n">
-        <v>46186.27264117707</v>
+        <v>46186.27342844736</v>
       </c>
       <c r="Z343" s="8" t="inlineStr"/>
     </row>
@@ -22383,7 +22383,7 @@
       <c r="W344" s="4" t="inlineStr"/>
       <c r="X344" s="4" t="inlineStr"/>
       <c r="Y344" s="5" t="n">
-        <v>46186.27264117727</v>
+        <v>46186.27342844756</v>
       </c>
       <c r="Z344" s="4" t="inlineStr"/>
     </row>
@@ -22443,7 +22443,7 @@
       <c r="W345" s="4" t="inlineStr"/>
       <c r="X345" s="4" t="inlineStr"/>
       <c r="Y345" s="5" t="n">
-        <v>46186.27264117748</v>
+        <v>46186.27342844774</v>
       </c>
       <c r="Z345" s="4" t="inlineStr"/>
     </row>
@@ -22515,7 +22515,7 @@
       <c r="W346" s="4" t="inlineStr"/>
       <c r="X346" s="4" t="inlineStr"/>
       <c r="Y346" s="5" t="n">
-        <v>46186.27264117767</v>
+        <v>46186.27342844795</v>
       </c>
       <c r="Z346" s="4" t="inlineStr"/>
     </row>
@@ -22583,7 +22583,7 @@
       <c r="W347" s="8" t="inlineStr"/>
       <c r="X347" s="8" t="inlineStr"/>
       <c r="Y347" s="9" t="n">
-        <v>46186.27264117787</v>
+        <v>46186.27342844813</v>
       </c>
       <c r="Z347" s="8" t="inlineStr"/>
     </row>
@@ -22651,7 +22651,7 @@
       <c r="W348" s="4" t="inlineStr"/>
       <c r="X348" s="4" t="inlineStr"/>
       <c r="Y348" s="5" t="n">
-        <v>46186.27264117809</v>
+        <v>46186.27342844834</v>
       </c>
       <c r="Z348" s="4" t="inlineStr"/>
     </row>
@@ -22719,7 +22719,7 @@
       <c r="W349" s="4" t="inlineStr"/>
       <c r="X349" s="4" t="inlineStr"/>
       <c r="Y349" s="5" t="n">
-        <v>46186.27264117829</v>
+        <v>46186.27342844854</v>
       </c>
       <c r="Z349" s="4" t="inlineStr"/>
     </row>
@@ -22779,7 +22779,7 @@
       <c r="W350" s="4" t="inlineStr"/>
       <c r="X350" s="4" t="inlineStr"/>
       <c r="Y350" s="5" t="n">
-        <v>46186.27264117848</v>
+        <v>46186.27342844872</v>
       </c>
       <c r="Z350" s="4" t="inlineStr"/>
     </row>
@@ -22835,7 +22835,7 @@
       <c r="W351" s="8" t="inlineStr"/>
       <c r="X351" s="8" t="inlineStr"/>
       <c r="Y351" s="9" t="n">
-        <v>46186.27264117869</v>
+        <v>46186.27342844891</v>
       </c>
       <c r="Z351" s="8" t="inlineStr"/>
     </row>
@@ -22895,7 +22895,7 @@
       <c r="W352" s="4" t="inlineStr"/>
       <c r="X352" s="4" t="inlineStr"/>
       <c r="Y352" s="5" t="n">
-        <v>46186.27264117889</v>
+        <v>46186.27342844911</v>
       </c>
       <c r="Z352" s="4" t="inlineStr"/>
     </row>
@@ -22963,7 +22963,7 @@
       <c r="W353" s="4" t="inlineStr"/>
       <c r="X353" s="4" t="inlineStr"/>
       <c r="Y353" s="5" t="n">
-        <v>46186.27264117907</v>
+        <v>46186.27342844929</v>
       </c>
       <c r="Z353" s="4" t="inlineStr"/>
     </row>
@@ -23019,7 +23019,7 @@
       <c r="W354" s="4" t="inlineStr"/>
       <c r="X354" s="4" t="inlineStr"/>
       <c r="Y354" s="5" t="n">
-        <v>46186.27264117925</v>
+        <v>46186.27342844948</v>
       </c>
       <c r="Z354" s="4" t="inlineStr"/>
     </row>
@@ -23071,7 +23071,7 @@
       <c r="W355" s="8" t="inlineStr"/>
       <c r="X355" s="8" t="inlineStr"/>
       <c r="Y355" s="9" t="n">
-        <v>46186.27264117946</v>
+        <v>46186.27342845005</v>
       </c>
       <c r="Z355" s="8" t="inlineStr"/>
     </row>
@@ -23139,7 +23139,7 @@
       <c r="W356" s="4" t="inlineStr"/>
       <c r="X356" s="4" t="inlineStr"/>
       <c r="Y356" s="5" t="n">
-        <v>46186.27264117966</v>
+        <v>46186.2734284504</v>
       </c>
       <c r="Z356" s="4" t="inlineStr"/>
     </row>
@@ -23191,7 +23191,7 @@
       <c r="W357" s="8" t="inlineStr"/>
       <c r="X357" s="8" t="inlineStr"/>
       <c r="Y357" s="9" t="n">
-        <v>46186.27264117986</v>
+        <v>46186.27342845066</v>
       </c>
       <c r="Z357" s="8" t="inlineStr"/>
     </row>
@@ -23259,7 +23259,7 @@
       <c r="W358" s="8" t="inlineStr"/>
       <c r="X358" s="8" t="inlineStr"/>
       <c r="Y358" s="9" t="n">
-        <v>46186.2726411801</v>
+        <v>46186.27342845093</v>
       </c>
       <c r="Z358" s="8" t="inlineStr"/>
     </row>
@@ -23311,7 +23311,7 @@
       <c r="W359" s="8" t="inlineStr"/>
       <c r="X359" s="8" t="inlineStr"/>
       <c r="Y359" s="9" t="n">
-        <v>46186.27264118071</v>
+        <v>46186.27342845113</v>
       </c>
       <c r="Z359" s="8" t="inlineStr"/>
     </row>
@@ -23363,7 +23363,7 @@
       <c r="W360" s="8" t="inlineStr"/>
       <c r="X360" s="8" t="inlineStr"/>
       <c r="Y360" s="9" t="n">
-        <v>46186.27264118095</v>
+        <v>46186.27342845133</v>
       </c>
       <c r="Z360" s="8" t="inlineStr"/>
     </row>
@@ -23415,7 +23415,7 @@
       <c r="W361" s="8" t="inlineStr"/>
       <c r="X361" s="8" t="inlineStr"/>
       <c r="Y361" s="9" t="n">
-        <v>46186.27264118116</v>
+        <v>46186.2734284515</v>
       </c>
       <c r="Z361" s="8" t="inlineStr"/>
     </row>
@@ -23483,7 +23483,7 @@
       <c r="W362" s="8" t="inlineStr"/>
       <c r="X362" s="8" t="inlineStr"/>
       <c r="Y362" s="9" t="n">
-        <v>46186.2726411814</v>
+        <v>46186.27342845182</v>
       </c>
       <c r="Z362" s="8" t="inlineStr"/>
     </row>
@@ -23539,7 +23539,7 @@
       <c r="W363" s="8" t="inlineStr"/>
       <c r="X363" s="8" t="inlineStr"/>
       <c r="Y363" s="9" t="n">
-        <v>46186.27264118161</v>
+        <v>46186.27342845209</v>
       </c>
       <c r="Z363" s="8" t="inlineStr"/>
     </row>
@@ -23595,7 +23595,7 @@
       <c r="W364" s="8" t="inlineStr"/>
       <c r="X364" s="8" t="inlineStr"/>
       <c r="Y364" s="9" t="n">
-        <v>46186.27264118181</v>
+        <v>46186.2734284523</v>
       </c>
       <c r="Z364" s="8" t="inlineStr"/>
     </row>
@@ -23659,7 +23659,7 @@
       <c r="W365" s="8" t="inlineStr"/>
       <c r="X365" s="8" t="inlineStr"/>
       <c r="Y365" s="9" t="n">
-        <v>46186.27264118208</v>
+        <v>46186.27342845274</v>
       </c>
       <c r="Z365" s="8" t="inlineStr"/>
     </row>
@@ -23723,7 +23723,7 @@
       <c r="W366" s="8" t="inlineStr"/>
       <c r="X366" s="8" t="inlineStr"/>
       <c r="Y366" s="9" t="n">
-        <v>46186.27264118234</v>
+        <v>46186.27342845314</v>
       </c>
       <c r="Z366" s="8" t="inlineStr"/>
     </row>
@@ -23791,7 +23791,7 @@
       <c r="W367" s="4" t="inlineStr"/>
       <c r="X367" s="4" t="inlineStr"/>
       <c r="Y367" s="5" t="n">
-        <v>46186.27264118254</v>
+        <v>46186.27342845385</v>
       </c>
       <c r="Z367" s="4" t="inlineStr"/>
     </row>
@@ -23859,7 +23859,7 @@
       <c r="W368" s="4" t="inlineStr"/>
       <c r="X368" s="4" t="inlineStr"/>
       <c r="Y368" s="5" t="n">
-        <v>46186.27264118277</v>
+        <v>46186.27342845416</v>
       </c>
       <c r="Z368" s="4" t="inlineStr"/>
     </row>
@@ -23923,7 +23923,7 @@
       <c r="W369" s="8" t="inlineStr"/>
       <c r="X369" s="8" t="inlineStr"/>
       <c r="Y369" s="9" t="n">
-        <v>46186.27264118295</v>
+        <v>46186.27342845438</v>
       </c>
       <c r="Z369" s="8" t="inlineStr"/>
     </row>
@@ -23991,7 +23991,7 @@
       <c r="W370" s="4" t="inlineStr"/>
       <c r="X370" s="4" t="inlineStr"/>
       <c r="Y370" s="5" t="n">
-        <v>46186.27264118322</v>
+        <v>46186.27342845462</v>
       </c>
       <c r="Z370" s="4" t="inlineStr"/>
     </row>
@@ -24059,7 +24059,7 @@
       <c r="W371" s="8" t="inlineStr"/>
       <c r="X371" s="8" t="inlineStr"/>
       <c r="Y371" s="9" t="n">
-        <v>46186.27264118347</v>
+        <v>46186.27342845491</v>
       </c>
       <c r="Z371" s="8" t="inlineStr"/>
     </row>
@@ -24123,7 +24123,7 @@
       <c r="W372" s="8" t="inlineStr"/>
       <c r="X372" s="8" t="inlineStr"/>
       <c r="Y372" s="9" t="n">
-        <v>46186.27264118366</v>
+        <v>46186.27342845522</v>
       </c>
       <c r="Z372" s="8" t="inlineStr"/>
     </row>
@@ -24191,7 +24191,7 @@
       <c r="W373" s="4" t="inlineStr"/>
       <c r="X373" s="4" t="inlineStr"/>
       <c r="Y373" s="5" t="n">
-        <v>46186.27264118385</v>
+        <v>46186.27342845551</v>
       </c>
       <c r="Z373" s="4" t="inlineStr"/>
     </row>
@@ -24259,7 +24259,7 @@
       <c r="W374" s="4" t="inlineStr"/>
       <c r="X374" s="4" t="inlineStr"/>
       <c r="Y374" s="5" t="n">
-        <v>46186.27264118402</v>
+        <v>46186.27342845583</v>
       </c>
       <c r="Z374" s="4" t="inlineStr"/>
     </row>
@@ -24327,7 +24327,7 @@
       <c r="W375" s="4" t="inlineStr"/>
       <c r="X375" s="4" t="inlineStr"/>
       <c r="Y375" s="5" t="n">
-        <v>46186.27264118436</v>
+        <v>46186.27342845628</v>
       </c>
       <c r="Z375" s="4" t="inlineStr"/>
     </row>
@@ -24395,7 +24395,7 @@
       <c r="W376" s="4" t="inlineStr"/>
       <c r="X376" s="4" t="inlineStr"/>
       <c r="Y376" s="5" t="n">
-        <v>46186.27264118455</v>
+        <v>46186.27342845665</v>
       </c>
       <c r="Z376" s="4" t="inlineStr"/>
     </row>
@@ -24463,7 +24463,7 @@
       <c r="W377" s="4" t="inlineStr"/>
       <c r="X377" s="4" t="inlineStr"/>
       <c r="Y377" s="5" t="n">
-        <v>46186.27264118475</v>
+        <v>46186.273428457</v>
       </c>
       <c r="Z377" s="4" t="inlineStr"/>
     </row>
@@ -24531,7 +24531,7 @@
       <c r="W378" s="4" t="inlineStr"/>
       <c r="X378" s="4" t="inlineStr"/>
       <c r="Y378" s="5" t="n">
-        <v>46186.27264118532</v>
+        <v>46186.27342845722</v>
       </c>
       <c r="Z378" s="4" t="inlineStr"/>
     </row>
@@ -24599,7 +24599,7 @@
       <c r="W379" s="4" t="inlineStr"/>
       <c r="X379" s="4" t="inlineStr"/>
       <c r="Y379" s="5" t="n">
-        <v>46186.27264118563</v>
+        <v>46186.27342845789</v>
       </c>
       <c r="Z379" s="4" t="inlineStr"/>
     </row>
@@ -24671,7 +24671,7 @@
       <c r="W380" s="4" t="inlineStr"/>
       <c r="X380" s="4" t="inlineStr"/>
       <c r="Y380" s="5" t="n">
-        <v>46186.27264118587</v>
+        <v>46186.27342845823</v>
       </c>
       <c r="Z380" s="4" t="inlineStr"/>
     </row>
@@ -24743,7 +24743,7 @@
       <c r="W381" s="4" t="inlineStr"/>
       <c r="X381" s="4" t="inlineStr"/>
       <c r="Y381" s="5" t="n">
-        <v>46186.27264118609</v>
+        <v>46186.27342845846</v>
       </c>
       <c r="Z381" s="4" t="inlineStr"/>
     </row>
@@ -24811,7 +24811,7 @@
       <c r="W382" s="4" t="inlineStr"/>
       <c r="X382" s="4" t="inlineStr"/>
       <c r="Y382" s="5" t="n">
-        <v>46186.27264118631</v>
+        <v>46186.27342845868</v>
       </c>
       <c r="Z382" s="4" t="inlineStr"/>
     </row>
@@ -24871,7 +24871,7 @@
       <c r="W383" s="4" t="inlineStr"/>
       <c r="X383" s="4" t="inlineStr"/>
       <c r="Y383" s="5" t="n">
-        <v>46186.27264118651</v>
+        <v>46186.27342845889</v>
       </c>
       <c r="Z383" s="4" t="inlineStr"/>
     </row>
@@ -24931,7 +24931,7 @@
       <c r="W384" s="4" t="inlineStr"/>
       <c r="X384" s="4" t="inlineStr"/>
       <c r="Y384" s="5" t="n">
-        <v>46186.27264118671</v>
+        <v>46186.27342845953</v>
       </c>
       <c r="Z384" s="4" t="inlineStr"/>
     </row>
@@ -24987,7 +24987,7 @@
       <c r="W385" s="4" t="inlineStr"/>
       <c r="X385" s="4" t="inlineStr"/>
       <c r="Y385" s="5" t="n">
-        <v>46186.27264118691</v>
+        <v>46186.27342845979</v>
       </c>
       <c r="Z385" s="4" t="inlineStr"/>
     </row>
@@ -25055,7 +25055,7 @@
       <c r="W386" s="4" t="inlineStr"/>
       <c r="X386" s="4" t="inlineStr"/>
       <c r="Y386" s="5" t="n">
-        <v>46186.27264118712</v>
+        <v>46186.27342846002</v>
       </c>
       <c r="Z386" s="4" t="inlineStr"/>
     </row>
@@ -25123,7 +25123,7 @@
       <c r="W387" s="4" t="inlineStr"/>
       <c r="X387" s="4" t="inlineStr"/>
       <c r="Y387" s="5" t="n">
-        <v>46186.27264118794</v>
+        <v>46186.27342846023</v>
       </c>
       <c r="Z387" s="4" t="inlineStr"/>
     </row>
@@ -25191,7 +25191,7 @@
       <c r="W388" s="4" t="inlineStr"/>
       <c r="X388" s="4" t="inlineStr"/>
       <c r="Y388" s="5" t="n">
-        <v>46186.27264118828</v>
+        <v>46186.27342846044</v>
       </c>
       <c r="Z388" s="4" t="inlineStr"/>
     </row>
@@ -25259,7 +25259,7 @@
       <c r="W389" s="4" t="inlineStr"/>
       <c r="X389" s="4" t="inlineStr"/>
       <c r="Y389" s="5" t="n">
-        <v>46186.27264118851</v>
+        <v>46186.27342846063</v>
       </c>
       <c r="Z389" s="4" t="inlineStr"/>
     </row>
@@ -25327,7 +25327,7 @@
       <c r="W390" s="4" t="inlineStr"/>
       <c r="X390" s="4" t="inlineStr"/>
       <c r="Y390" s="5" t="n">
-        <v>46186.27264118871</v>
+        <v>46186.27342846081</v>
       </c>
       <c r="Z390" s="4" t="inlineStr"/>
     </row>
@@ -25395,7 +25395,7 @@
       <c r="W391" s="4" t="inlineStr"/>
       <c r="X391" s="4" t="inlineStr"/>
       <c r="Y391" s="5" t="n">
-        <v>46186.27264118891</v>
+        <v>46186.27342846101</v>
       </c>
       <c r="Z391" s="4" t="inlineStr"/>
     </row>
@@ -25463,7 +25463,7 @@
       <c r="W392" s="4" t="inlineStr"/>
       <c r="X392" s="4" t="inlineStr"/>
       <c r="Y392" s="5" t="n">
-        <v>46186.27264118911</v>
+        <v>46186.2734284612</v>
       </c>
       <c r="Z392" s="4" t="inlineStr"/>
     </row>
@@ -25531,7 +25531,7 @@
       <c r="W393" s="4" t="inlineStr"/>
       <c r="X393" s="4" t="inlineStr"/>
       <c r="Y393" s="5" t="n">
-        <v>46186.27264118931</v>
+        <v>46186.27342846138</v>
       </c>
       <c r="Z393" s="4" t="inlineStr"/>
     </row>
@@ -25599,7 +25599,7 @@
       <c r="W394" s="8" t="inlineStr"/>
       <c r="X394" s="8" t="inlineStr"/>
       <c r="Y394" s="9" t="n">
-        <v>46186.27264118951</v>
+        <v>46186.27342846157</v>
       </c>
       <c r="Z394" s="8" t="inlineStr"/>
     </row>
@@ -25651,7 +25651,7 @@
       <c r="W395" s="4" t="inlineStr"/>
       <c r="X395" s="4" t="inlineStr"/>
       <c r="Y395" s="5" t="n">
-        <v>46186.27264118975</v>
+        <v>46186.27342846181</v>
       </c>
       <c r="Z395" s="4" t="inlineStr"/>
     </row>
@@ -25719,7 +25719,7 @@
       <c r="W396" s="8" t="inlineStr"/>
       <c r="X396" s="8" t="inlineStr"/>
       <c r="Y396" s="9" t="n">
-        <v>46186.27264118994</v>
+        <v>46186.27342846202</v>
       </c>
       <c r="Z396" s="8" t="inlineStr"/>
     </row>
@@ -25787,7 +25787,7 @@
       <c r="W397" s="8" t="inlineStr"/>
       <c r="X397" s="8" t="inlineStr"/>
       <c r="Y397" s="9" t="n">
-        <v>46186.27264119014</v>
+        <v>46186.27342846221</v>
       </c>
       <c r="Z397" s="8" t="inlineStr"/>
     </row>
@@ -25843,7 +25843,7 @@
       <c r="W398" s="8" t="inlineStr"/>
       <c r="X398" s="8" t="inlineStr"/>
       <c r="Y398" s="9" t="n">
-        <v>46186.27264119033</v>
+        <v>46186.27342846241</v>
       </c>
       <c r="Z398" s="8" t="inlineStr"/>
     </row>
@@ -25911,7 +25911,7 @@
       <c r="W399" s="4" t="inlineStr"/>
       <c r="X399" s="4" t="inlineStr"/>
       <c r="Y399" s="5" t="n">
-        <v>46186.27264119055</v>
+        <v>46186.27342846261</v>
       </c>
       <c r="Z399" s="4" t="inlineStr"/>
     </row>
@@ -25979,7 +25979,7 @@
       <c r="W400" s="8" t="inlineStr"/>
       <c r="X400" s="8" t="inlineStr"/>
       <c r="Y400" s="9" t="n">
-        <v>46186.27264119074</v>
+        <v>46186.27342846281</v>
       </c>
       <c r="Z400" s="8" t="inlineStr"/>
     </row>
@@ -26031,7 +26031,7 @@
       <c r="W401" s="8" t="inlineStr"/>
       <c r="X401" s="8" t="inlineStr"/>
       <c r="Y401" s="9" t="n">
-        <v>46186.27264119094</v>
+        <v>46186.27342846301</v>
       </c>
       <c r="Z401" s="8" t="inlineStr"/>
     </row>
@@ -26099,7 +26099,7 @@
       <c r="W402" s="8" t="inlineStr"/>
       <c r="X402" s="8" t="inlineStr"/>
       <c r="Y402" s="9" t="n">
-        <v>46186.27264119117</v>
+        <v>46186.27342846325</v>
       </c>
       <c r="Z402" s="8" t="inlineStr"/>
     </row>
@@ -26163,7 +26163,7 @@
       <c r="W403" s="8" t="inlineStr"/>
       <c r="X403" s="8" t="inlineStr"/>
       <c r="Y403" s="9" t="n">
-        <v>46186.27264119139</v>
+        <v>46186.27342846347</v>
       </c>
       <c r="Z403" s="8" t="inlineStr"/>
     </row>
@@ -26227,7 +26227,7 @@
       <c r="W404" s="8" t="inlineStr"/>
       <c r="X404" s="8" t="inlineStr"/>
       <c r="Y404" s="9" t="n">
-        <v>46186.27264119159</v>
+        <v>46186.27342846374</v>
       </c>
       <c r="Z404" s="8" t="inlineStr"/>
     </row>
@@ -26279,7 +26279,7 @@
       <c r="W405" s="8" t="inlineStr"/>
       <c r="X405" s="8" t="inlineStr"/>
       <c r="Y405" s="9" t="n">
-        <v>46186.2726411918</v>
+        <v>46186.27342846392</v>
       </c>
       <c r="Z405" s="8" t="inlineStr"/>
     </row>
@@ -26331,7 +26331,7 @@
       <c r="W406" s="8" t="inlineStr"/>
       <c r="X406" s="8" t="inlineStr"/>
       <c r="Y406" s="9" t="n">
-        <v>46186.272641192</v>
+        <v>46186.27342846412</v>
       </c>
       <c r="Z406" s="8" t="inlineStr"/>
     </row>
@@ -26383,7 +26383,7 @@
       <c r="W407" s="8" t="inlineStr"/>
       <c r="X407" s="8" t="inlineStr"/>
       <c r="Y407" s="9" t="n">
-        <v>46186.2726411922</v>
+        <v>46186.27342846431</v>
       </c>
       <c r="Z407" s="8" t="inlineStr"/>
     </row>
@@ -26439,7 +26439,7 @@
       <c r="W408" s="8" t="inlineStr"/>
       <c r="X408" s="8" t="inlineStr"/>
       <c r="Y408" s="9" t="n">
-        <v>46186.27264119239</v>
+        <v>46186.27342846448</v>
       </c>
       <c r="Z408" s="8" t="inlineStr"/>
     </row>
@@ -26491,7 +26491,7 @@
       <c r="W409" s="8" t="inlineStr"/>
       <c r="X409" s="8" t="inlineStr"/>
       <c r="Y409" s="9" t="n">
-        <v>46186.27264119258</v>
+        <v>46186.27342846471</v>
       </c>
       <c r="Z409" s="8" t="inlineStr"/>
     </row>
@@ -26555,7 +26555,7 @@
       <c r="W410" s="8" t="inlineStr"/>
       <c r="X410" s="8" t="inlineStr"/>
       <c r="Y410" s="9" t="n">
-        <v>46186.27264119279</v>
+        <v>46186.27342846527</v>
       </c>
       <c r="Z410" s="8" t="inlineStr"/>
     </row>
@@ -26619,7 +26619,7 @@
       <c r="W411" s="8" t="inlineStr"/>
       <c r="X411" s="8" t="inlineStr"/>
       <c r="Y411" s="9" t="n">
-        <v>46186.27264119298</v>
+        <v>46186.27342846555</v>
       </c>
       <c r="Z411" s="8" t="inlineStr"/>
     </row>
@@ -26687,7 +26687,7 @@
       <c r="W412" s="8" t="inlineStr"/>
       <c r="X412" s="8" t="inlineStr"/>
       <c r="Y412" s="9" t="n">
-        <v>46186.27264119318</v>
+        <v>46186.2734284661</v>
       </c>
       <c r="Z412" s="8" t="inlineStr"/>
     </row>
@@ -26755,7 +26755,7 @@
       <c r="W413" s="4" t="inlineStr"/>
       <c r="X413" s="4" t="inlineStr"/>
       <c r="Y413" s="5" t="n">
-        <v>46186.27264119338</v>
+        <v>46186.27342846647</v>
       </c>
       <c r="Z413" s="4" t="inlineStr"/>
     </row>
@@ -26811,7 +26811,7 @@
       <c r="W414" s="8" t="inlineStr"/>
       <c r="X414" s="8" t="inlineStr"/>
       <c r="Y414" s="9" t="n">
-        <v>46186.27264119359</v>
+        <v>46186.27342846672</v>
       </c>
       <c r="Z414" s="8" t="inlineStr"/>
     </row>
@@ -26875,7 +26875,7 @@
       <c r="W415" s="8" t="inlineStr"/>
       <c r="X415" s="8" t="inlineStr"/>
       <c r="Y415" s="9" t="n">
-        <v>46186.27264119378</v>
+        <v>46186.27342846694</v>
       </c>
       <c r="Z415" s="8" t="inlineStr"/>
     </row>
@@ -26939,7 +26939,7 @@
       <c r="W416" s="8" t="inlineStr"/>
       <c r="X416" s="8" t="inlineStr"/>
       <c r="Y416" s="9" t="n">
-        <v>46186.27264119445</v>
+        <v>46186.27342846719</v>
       </c>
       <c r="Z416" s="8" t="inlineStr"/>
     </row>
@@ -26995,7 +26995,7 @@
       <c r="W417" s="8" t="inlineStr"/>
       <c r="X417" s="8" t="inlineStr"/>
       <c r="Y417" s="9" t="n">
-        <v>46186.27264119478</v>
+        <v>46186.27342846739</v>
       </c>
       <c r="Z417" s="8" t="inlineStr"/>
     </row>
@@ -27063,7 +27063,7 @@
       <c r="W418" s="4" t="inlineStr"/>
       <c r="X418" s="4" t="inlineStr"/>
       <c r="Y418" s="5" t="n">
-        <v>46186.27264119502</v>
+        <v>46186.27342846759</v>
       </c>
       <c r="Z418" s="4" t="inlineStr"/>
     </row>
@@ -27131,7 +27131,7 @@
       <c r="W419" s="4" t="inlineStr"/>
       <c r="X419" s="4" t="inlineStr"/>
       <c r="Y419" s="5" t="n">
-        <v>46186.27264119525</v>
+        <v>46186.27342846779</v>
       </c>
       <c r="Z419" s="4" t="inlineStr"/>
     </row>
@@ -27199,7 +27199,7 @@
       <c r="W420" s="4" t="inlineStr"/>
       <c r="X420" s="4" t="inlineStr"/>
       <c r="Y420" s="5" t="n">
-        <v>46186.27264119544</v>
+        <v>46186.27342846798</v>
       </c>
       <c r="Z420" s="4" t="inlineStr"/>
     </row>
@@ -27267,7 +27267,7 @@
       <c r="W421" s="4" t="inlineStr"/>
       <c r="X421" s="4" t="inlineStr"/>
       <c r="Y421" s="5" t="n">
-        <v>46186.27264119564</v>
+        <v>46186.27342846816</v>
       </c>
       <c r="Z421" s="4" t="inlineStr"/>
     </row>
@@ -27335,7 +27335,7 @@
       <c r="W422" s="4" t="inlineStr"/>
       <c r="X422" s="4" t="inlineStr"/>
       <c r="Y422" s="5" t="n">
-        <v>46186.27264119581</v>
+        <v>46186.27342846832</v>
       </c>
       <c r="Z422" s="4" t="inlineStr"/>
     </row>
@@ -27395,7 +27395,7 @@
       <c r="W423" s="4" t="inlineStr"/>
       <c r="X423" s="4" t="inlineStr"/>
       <c r="Y423" s="5" t="n">
-        <v>46186.27264119602</v>
+        <v>46186.27342846851</v>
       </c>
       <c r="Z423" s="4" t="inlineStr"/>
     </row>
@@ -27451,7 +27451,7 @@
       <c r="W424" s="4" t="inlineStr"/>
       <c r="X424" s="4" t="inlineStr"/>
       <c r="Y424" s="5" t="n">
-        <v>46186.27264119623</v>
+        <v>46186.27342846872</v>
       </c>
       <c r="Z424" s="4" t="inlineStr"/>
     </row>
@@ -27511,7 +27511,7 @@
       <c r="W425" s="8" t="inlineStr"/>
       <c r="X425" s="8" t="inlineStr"/>
       <c r="Y425" s="9" t="n">
-        <v>46186.27264119642</v>
+        <v>46186.27342846892</v>
       </c>
       <c r="Z425" s="8" t="inlineStr"/>
     </row>
@@ -27583,7 +27583,7 @@
       <c r="W426" s="8" t="inlineStr"/>
       <c r="X426" s="8" t="inlineStr"/>
       <c r="Y426" s="9" t="n">
-        <v>46186.27264119661</v>
+        <v>46186.27342846911</v>
       </c>
       <c r="Z426" s="8" t="inlineStr"/>
     </row>
@@ -27647,7 +27647,7 @@
       <c r="W427" s="8" t="inlineStr"/>
       <c r="X427" s="8" t="inlineStr"/>
       <c r="Y427" s="9" t="n">
-        <v>46186.27264119682</v>
+        <v>46186.27342846933</v>
       </c>
       <c r="Z427" s="8" t="inlineStr"/>
     </row>
@@ -27711,7 +27711,7 @@
       <c r="W428" s="8" t="inlineStr"/>
       <c r="X428" s="8" t="inlineStr"/>
       <c r="Y428" s="9" t="n">
-        <v>46186.27264119706</v>
+        <v>46186.27342847002</v>
       </c>
       <c r="Z428" s="8" t="inlineStr"/>
     </row>
@@ -27779,7 +27779,7 @@
       <c r="W429" s="8" t="inlineStr"/>
       <c r="X429" s="8" t="inlineStr"/>
       <c r="Y429" s="9" t="n">
-        <v>46186.27264119725</v>
+        <v>46186.27342847031</v>
       </c>
       <c r="Z429" s="8" t="inlineStr"/>
     </row>
@@ -27843,7 +27843,7 @@
       <c r="W430" s="8" t="inlineStr"/>
       <c r="X430" s="8" t="inlineStr"/>
       <c r="Y430" s="9" t="n">
-        <v>46186.27264119747</v>
+        <v>46186.27342847056</v>
       </c>
       <c r="Z430" s="8" t="inlineStr"/>
     </row>
@@ -27907,7 +27907,7 @@
       <c r="W431" s="8" t="inlineStr"/>
       <c r="X431" s="8" t="inlineStr"/>
       <c r="Y431" s="9" t="n">
-        <v>46186.27264119765</v>
+        <v>46186.27342847075</v>
       </c>
       <c r="Z431" s="8" t="inlineStr"/>
     </row>
@@ -27963,7 +27963,7 @@
       <c r="W432" s="8" t="inlineStr"/>
       <c r="X432" s="8" t="inlineStr"/>
       <c r="Y432" s="9" t="n">
-        <v>46186.27264119784</v>
+        <v>46186.27342847096</v>
       </c>
       <c r="Z432" s="8" t="inlineStr"/>
     </row>
@@ -28027,7 +28027,7 @@
       <c r="W433" s="8" t="inlineStr"/>
       <c r="X433" s="8" t="inlineStr"/>
       <c r="Y433" s="9" t="n">
-        <v>46186.27264119805</v>
+        <v>46186.27342847116</v>
       </c>
       <c r="Z433" s="8" t="inlineStr"/>
     </row>
@@ -28091,7 +28091,7 @@
       <c r="W434" s="8" t="inlineStr"/>
       <c r="X434" s="8" t="inlineStr"/>
       <c r="Y434" s="9" t="n">
-        <v>46186.27264119825</v>
+        <v>46186.27342847135</v>
       </c>
       <c r="Z434" s="8" t="inlineStr"/>
     </row>
@@ -28147,7 +28147,7 @@
       <c r="W435" s="8" t="inlineStr"/>
       <c r="X435" s="8" t="inlineStr"/>
       <c r="Y435" s="9" t="n">
-        <v>46186.27264119844</v>
+        <v>46186.27342847155</v>
       </c>
       <c r="Z435" s="8" t="inlineStr"/>
     </row>
@@ -28215,7 +28215,7 @@
       <c r="W436" s="8" t="inlineStr"/>
       <c r="X436" s="8" t="inlineStr"/>
       <c r="Y436" s="9" t="n">
-        <v>46186.27264119864</v>
+        <v>46186.27342847174</v>
       </c>
       <c r="Z436" s="8" t="inlineStr"/>
     </row>
@@ -28283,7 +28283,7 @@
       <c r="W437" s="8" t="inlineStr"/>
       <c r="X437" s="8" t="inlineStr"/>
       <c r="Y437" s="9" t="n">
-        <v>46186.27264119933</v>
+        <v>46186.27342847194</v>
       </c>
       <c r="Z437" s="8" t="inlineStr"/>
     </row>
@@ -28351,7 +28351,7 @@
       <c r="W438" s="8" t="inlineStr"/>
       <c r="X438" s="8" t="inlineStr"/>
       <c r="Y438" s="9" t="n">
-        <v>46186.27264119962</v>
+        <v>46186.27342847256</v>
       </c>
       <c r="Z438" s="8" t="inlineStr"/>
     </row>
@@ -28419,7 +28419,7 @@
       <c r="W439" s="8" t="inlineStr"/>
       <c r="X439" s="8" t="inlineStr"/>
       <c r="Y439" s="9" t="n">
-        <v>46186.27264119982</v>
+        <v>46186.27342847286</v>
       </c>
       <c r="Z439" s="8" t="inlineStr"/>
     </row>
@@ -28487,7 +28487,7 @@
       <c r="W440" s="4" t="inlineStr"/>
       <c r="X440" s="4" t="inlineStr"/>
       <c r="Y440" s="5" t="n">
-        <v>46186.27264120005</v>
+        <v>46186.27342847338</v>
       </c>
       <c r="Z440" s="4" t="inlineStr"/>
     </row>
@@ -28555,7 +28555,7 @@
       <c r="W441" s="4" t="inlineStr"/>
       <c r="X441" s="4" t="inlineStr"/>
       <c r="Y441" s="5" t="n">
-        <v>46186.27264120024</v>
+        <v>46186.27342847372</v>
       </c>
       <c r="Z441" s="4" t="inlineStr"/>
     </row>
@@ -28623,7 +28623,7 @@
       <c r="W442" s="4" t="inlineStr"/>
       <c r="X442" s="4" t="inlineStr"/>
       <c r="Y442" s="5" t="n">
-        <v>46186.27264120045</v>
+        <v>46186.27342847397</v>
       </c>
       <c r="Z442" s="4" t="inlineStr"/>
     </row>
@@ -28691,7 +28691,7 @@
       <c r="W443" s="4" t="inlineStr"/>
       <c r="X443" s="4" t="inlineStr"/>
       <c r="Y443" s="5" t="n">
-        <v>46186.27264120064</v>
+        <v>46186.27342847417</v>
       </c>
       <c r="Z443" s="4" t="inlineStr"/>
     </row>
@@ -28759,7 +28759,7 @@
       <c r="W444" s="4" t="inlineStr"/>
       <c r="X444" s="4" t="inlineStr"/>
       <c r="Y444" s="5" t="n">
-        <v>46186.27264120161</v>
+        <v>46186.27342847438</v>
       </c>
       <c r="Z444" s="4" t="inlineStr"/>
     </row>
@@ -28827,7 +28827,7 @@
       <c r="W445" s="4" t="inlineStr"/>
       <c r="X445" s="4" t="inlineStr"/>
       <c r="Y445" s="5" t="n">
-        <v>46186.27264120197</v>
+        <v>46186.27342847466</v>
       </c>
       <c r="Z445" s="4" t="inlineStr"/>
     </row>
@@ -28895,7 +28895,7 @@
       <c r="W446" s="4" t="inlineStr"/>
       <c r="X446" s="4" t="inlineStr"/>
       <c r="Y446" s="5" t="n">
-        <v>46186.27264120226</v>
+        <v>46186.27342847493</v>
       </c>
       <c r="Z446" s="4" t="inlineStr"/>
     </row>
@@ -28963,7 +28963,7 @@
       <c r="W447" s="4" t="inlineStr"/>
       <c r="X447" s="4" t="inlineStr"/>
       <c r="Y447" s="5" t="n">
-        <v>46186.27264120246</v>
+        <v>46186.27342847519</v>
       </c>
       <c r="Z447" s="4" t="inlineStr"/>
     </row>
@@ -29031,7 +29031,7 @@
       <c r="W448" s="4" t="inlineStr"/>
       <c r="X448" s="4" t="inlineStr"/>
       <c r="Y448" s="5" t="n">
-        <v>46186.27264120266</v>
+        <v>46186.27342847538</v>
       </c>
       <c r="Z448" s="4" t="inlineStr"/>
     </row>
@@ -29099,7 +29099,7 @@
       <c r="W449" s="4" t="inlineStr"/>
       <c r="X449" s="4" t="inlineStr"/>
       <c r="Y449" s="5" t="n">
-        <v>46186.27264120285</v>
+        <v>46186.27342847556</v>
       </c>
       <c r="Z449" s="4" t="inlineStr"/>
     </row>
@@ -29163,7 +29163,7 @@
       <c r="W450" s="8" t="inlineStr"/>
       <c r="X450" s="8" t="inlineStr"/>
       <c r="Y450" s="9" t="n">
-        <v>46186.27264120305</v>
+        <v>46186.27342847576</v>
       </c>
       <c r="Z450" s="8" t="inlineStr"/>
     </row>
@@ -29231,7 +29231,7 @@
       <c r="W451" s="8" t="inlineStr"/>
       <c r="X451" s="8" t="inlineStr"/>
       <c r="Y451" s="9" t="n">
-        <v>46186.27264120325</v>
+        <v>46186.27342847599</v>
       </c>
       <c r="Z451" s="8" t="inlineStr"/>
     </row>
@@ -29299,7 +29299,7 @@
       <c r="W452" s="8" t="inlineStr"/>
       <c r="X452" s="8" t="inlineStr"/>
       <c r="Y452" s="9" t="n">
-        <v>46186.2726412035</v>
+        <v>46186.27342847624</v>
       </c>
       <c r="Z452" s="8" t="inlineStr"/>
     </row>
@@ -29363,7 +29363,7 @@
       <c r="W453" s="8" t="inlineStr"/>
       <c r="X453" s="8" t="inlineStr"/>
       <c r="Y453" s="9" t="n">
-        <v>46186.27264120373</v>
+        <v>46186.27342847674</v>
       </c>
       <c r="Z453" s="8" t="inlineStr"/>
     </row>
@@ -29431,7 +29431,7 @@
       <c r="W454" s="8" t="inlineStr"/>
       <c r="X454" s="8" t="inlineStr"/>
       <c r="Y454" s="9" t="n">
-        <v>46186.27264120393</v>
+        <v>46186.27342847709</v>
       </c>
       <c r="Z454" s="8" t="inlineStr"/>
     </row>
@@ -29499,7 +29499,7 @@
       <c r="W455" s="8" t="inlineStr"/>
       <c r="X455" s="8" t="inlineStr"/>
       <c r="Y455" s="9" t="n">
-        <v>46186.27264120414</v>
+        <v>46186.27342847734</v>
       </c>
       <c r="Z455" s="8" t="inlineStr"/>
     </row>
@@ -29567,7 +29567,7 @@
       <c r="W456" s="8" t="inlineStr"/>
       <c r="X456" s="8" t="inlineStr"/>
       <c r="Y456" s="9" t="n">
-        <v>46186.27264120438</v>
+        <v>46186.27342847759</v>
       </c>
       <c r="Z456" s="8" t="inlineStr"/>
     </row>
@@ -29635,7 +29635,7 @@
       <c r="W457" s="8" t="inlineStr"/>
       <c r="X457" s="8" t="inlineStr"/>
       <c r="Y457" s="9" t="n">
-        <v>46186.27264120462</v>
+        <v>46186.27342847783</v>
       </c>
       <c r="Z457" s="8" t="inlineStr"/>
     </row>
@@ -29703,7 +29703,7 @@
       <c r="W458" s="8" t="inlineStr"/>
       <c r="X458" s="8" t="inlineStr"/>
       <c r="Y458" s="9" t="n">
-        <v>46186.27264120481</v>
+        <v>46186.27342847803</v>
       </c>
       <c r="Z458" s="8" t="inlineStr"/>
     </row>
@@ -29771,7 +29771,7 @@
       <c r="W459" s="8" t="inlineStr"/>
       <c r="X459" s="8" t="inlineStr"/>
       <c r="Y459" s="9" t="n">
-        <v>46186.272641205</v>
+        <v>46186.27342847824</v>
       </c>
       <c r="Z459" s="8" t="inlineStr"/>
     </row>
@@ -29839,7 +29839,7 @@
       <c r="W460" s="8" t="inlineStr"/>
       <c r="X460" s="8" t="inlineStr"/>
       <c r="Y460" s="9" t="n">
-        <v>46186.27264120519</v>
+        <v>46186.27342847842</v>
       </c>
       <c r="Z460" s="8" t="inlineStr"/>
     </row>
@@ -29907,7 +29907,7 @@
       <c r="W461" s="8" t="inlineStr"/>
       <c r="X461" s="8" t="inlineStr"/>
       <c r="Y461" s="9" t="n">
-        <v>46186.27264120536</v>
+        <v>46186.27342847861</v>
       </c>
       <c r="Z461" s="8" t="inlineStr"/>
     </row>
@@ -29963,7 +29963,7 @@
       <c r="W462" s="8" t="inlineStr"/>
       <c r="X462" s="8" t="inlineStr"/>
       <c r="Y462" s="9" t="n">
-        <v>46186.27264120556</v>
+        <v>46186.27342847879</v>
       </c>
       <c r="Z462" s="8" t="inlineStr"/>
     </row>
@@ -30027,7 +30027,7 @@
       <c r="W463" s="8" t="inlineStr"/>
       <c r="X463" s="8" t="inlineStr"/>
       <c r="Y463" s="9" t="n">
-        <v>46186.27264120575</v>
+        <v>46186.27342847898</v>
       </c>
       <c r="Z463" s="8" t="inlineStr"/>
     </row>
@@ -30091,7 +30091,7 @@
       <c r="W464" s="8" t="inlineStr"/>
       <c r="X464" s="8" t="inlineStr"/>
       <c r="Y464" s="9" t="n">
-        <v>46186.27264120595</v>
+        <v>46186.27342847917</v>
       </c>
       <c r="Z464" s="8" t="inlineStr"/>
     </row>
@@ -30155,7 +30155,7 @@
       <c r="W465" s="8" t="inlineStr"/>
       <c r="X465" s="8" t="inlineStr"/>
       <c r="Y465" s="9" t="n">
-        <v>46186.27264120616</v>
+        <v>46186.27342847938</v>
       </c>
       <c r="Z465" s="8" t="inlineStr"/>
     </row>
@@ -30219,7 +30219,7 @@
       <c r="W466" s="8" t="inlineStr"/>
       <c r="X466" s="8" t="inlineStr"/>
       <c r="Y466" s="9" t="n">
-        <v>46186.27264120647</v>
+        <v>46186.27342847962</v>
       </c>
       <c r="Z466" s="8" t="inlineStr"/>
     </row>
@@ -30283,7 +30283,7 @@
       <c r="W467" s="8" t="inlineStr"/>
       <c r="X467" s="8" t="inlineStr"/>
       <c r="Y467" s="9" t="n">
-        <v>46186.27264120668</v>
+        <v>46186.27342847983</v>
       </c>
       <c r="Z467" s="8" t="inlineStr"/>
     </row>
@@ -30347,7 +30347,7 @@
       <c r="W468" s="8" t="inlineStr"/>
       <c r="X468" s="8" t="inlineStr"/>
       <c r="Y468" s="9" t="n">
-        <v>46186.2726412069</v>
+        <v>46186.27342848005</v>
       </c>
       <c r="Z468" s="8" t="inlineStr"/>
     </row>
@@ -30411,7 +30411,7 @@
       <c r="W469" s="8" t="inlineStr"/>
       <c r="X469" s="8" t="inlineStr"/>
       <c r="Y469" s="9" t="n">
-        <v>46186.27264120711</v>
+        <v>46186.27342848071</v>
       </c>
       <c r="Z469" s="8" t="inlineStr"/>
     </row>
@@ -30475,7 +30475,7 @@
       <c r="W470" s="8" t="inlineStr"/>
       <c r="X470" s="8" t="inlineStr"/>
       <c r="Y470" s="9" t="n">
-        <v>46186.27264120732</v>
+        <v>46186.27342848096</v>
       </c>
       <c r="Z470" s="8" t="inlineStr"/>
     </row>
@@ -30539,7 +30539,7 @@
       <c r="W471" s="8" t="inlineStr"/>
       <c r="X471" s="8" t="inlineStr"/>
       <c r="Y471" s="9" t="n">
-        <v>46186.27264120754</v>
+        <v>46186.2734284812</v>
       </c>
       <c r="Z471" s="8" t="inlineStr"/>
     </row>
@@ -30603,7 +30603,7 @@
       <c r="W472" s="8" t="inlineStr"/>
       <c r="X472" s="8" t="inlineStr"/>
       <c r="Y472" s="9" t="n">
-        <v>46186.27264120809</v>
+        <v>46186.27342848142</v>
       </c>
       <c r="Z472" s="8" t="inlineStr"/>
     </row>
@@ -30667,7 +30667,7 @@
       <c r="W473" s="8" t="inlineStr"/>
       <c r="X473" s="8" t="inlineStr"/>
       <c r="Y473" s="9" t="n">
-        <v>46186.27264120846</v>
+        <v>46186.27342848165</v>
       </c>
       <c r="Z473" s="8" t="inlineStr"/>
     </row>
@@ -30731,7 +30731,7 @@
       <c r="W474" s="8" t="inlineStr"/>
       <c r="X474" s="8" t="inlineStr"/>
       <c r="Y474" s="9" t="n">
-        <v>46186.27264120871</v>
+        <v>46186.27342848184</v>
       </c>
       <c r="Z474" s="8" t="inlineStr"/>
     </row>
@@ -30795,7 +30795,7 @@
       <c r="W475" s="8" t="inlineStr"/>
       <c r="X475" s="8" t="inlineStr"/>
       <c r="Y475" s="9" t="n">
-        <v>46186.27264120893</v>
+        <v>46186.27342848205</v>
       </c>
       <c r="Z475" s="8" t="inlineStr"/>
     </row>
@@ -30859,7 +30859,7 @@
       <c r="W476" s="8" t="inlineStr"/>
       <c r="X476" s="8" t="inlineStr"/>
       <c r="Y476" s="9" t="n">
-        <v>46186.27264120914</v>
+        <v>46186.27342848226</v>
       </c>
       <c r="Z476" s="8" t="inlineStr"/>
     </row>
@@ -30911,7 +30911,7 @@
       <c r="W477" s="8" t="inlineStr"/>
       <c r="X477" s="8" t="inlineStr"/>
       <c r="Y477" s="9" t="n">
-        <v>46186.27264120936</v>
+        <v>46186.27342848245</v>
       </c>
       <c r="Z477" s="8" t="inlineStr"/>
     </row>
@@ -30975,7 +30975,7 @@
       <c r="W478" s="8" t="inlineStr"/>
       <c r="X478" s="8" t="inlineStr"/>
       <c r="Y478" s="9" t="n">
-        <v>46186.27264120956</v>
+        <v>46186.27342848263</v>
       </c>
       <c r="Z478" s="8" t="inlineStr"/>
     </row>
@@ -31039,7 +31039,7 @@
       <c r="W479" s="8" t="inlineStr"/>
       <c r="X479" s="8" t="inlineStr"/>
       <c r="Y479" s="9" t="n">
-        <v>46186.27264120977</v>
+        <v>46186.27342848283</v>
       </c>
       <c r="Z479" s="8" t="inlineStr"/>
     </row>
@@ -31103,7 +31103,7 @@
       <c r="W480" s="8" t="inlineStr"/>
       <c r="X480" s="8" t="inlineStr"/>
       <c r="Y480" s="9" t="n">
-        <v>46186.27264120997</v>
+        <v>46186.27342848302</v>
       </c>
       <c r="Z480" s="8" t="inlineStr"/>
     </row>
@@ -31171,7 +31171,7 @@
       <c r="W481" s="8" t="inlineStr"/>
       <c r="X481" s="8" t="inlineStr"/>
       <c r="Y481" s="9" t="n">
-        <v>46186.27264121079</v>
+        <v>46186.27342848324</v>
       </c>
       <c r="Z481" s="8" t="inlineStr"/>
     </row>
@@ -31239,7 +31239,7 @@
       <c r="W482" s="4" t="inlineStr"/>
       <c r="X482" s="4" t="inlineStr"/>
       <c r="Y482" s="5" t="n">
-        <v>46186.27264121112</v>
+        <v>46186.27342848382</v>
       </c>
       <c r="Z482" s="4" t="inlineStr"/>
     </row>
@@ -31295,7 +31295,7 @@
       <c r="W483" s="8" t="inlineStr"/>
       <c r="X483" s="8" t="inlineStr"/>
       <c r="Y483" s="9" t="n">
-        <v>46186.27264121136</v>
+        <v>46186.27342848411</v>
       </c>
       <c r="Z483" s="8" t="inlineStr"/>
     </row>
@@ -31355,7 +31355,7 @@
       <c r="W484" s="4" t="inlineStr"/>
       <c r="X484" s="4" t="inlineStr"/>
       <c r="Y484" s="5" t="n">
-        <v>46186.27264121156</v>
+        <v>46186.27342848432</v>
       </c>
       <c r="Z484" s="4" t="inlineStr"/>
     </row>
@@ -31423,7 +31423,7 @@
       <c r="W485" s="8" t="inlineStr"/>
       <c r="X485" s="8" t="inlineStr"/>
       <c r="Y485" s="9" t="n">
-        <v>46186.27264121177</v>
+        <v>46186.27342848455</v>
       </c>
       <c r="Z485" s="8" t="inlineStr"/>
     </row>
@@ -31487,7 +31487,7 @@
       <c r="W486" s="8" t="inlineStr"/>
       <c r="X486" s="8" t="inlineStr"/>
       <c r="Y486" s="9" t="n">
-        <v>46186.27264121206</v>
+        <v>46186.27342848484</v>
       </c>
       <c r="Z486" s="8" t="inlineStr"/>
     </row>
@@ -31551,7 +31551,7 @@
       <c r="W487" s="8" t="inlineStr"/>
       <c r="X487" s="8" t="inlineStr"/>
       <c r="Y487" s="9" t="n">
-        <v>46186.27264121229</v>
+        <v>46186.27342848508</v>
       </c>
       <c r="Z487" s="8" t="inlineStr"/>
     </row>
@@ -31619,7 +31619,7 @@
       <c r="W488" s="4" t="inlineStr"/>
       <c r="X488" s="4" t="inlineStr"/>
       <c r="Y488" s="5" t="n">
-        <v>46186.27264121259</v>
+        <v>46186.27342848538</v>
       </c>
       <c r="Z488" s="4" t="inlineStr"/>
     </row>
@@ -31687,7 +31687,7 @@
       <c r="W489" s="4" t="inlineStr"/>
       <c r="X489" s="4" t="inlineStr"/>
       <c r="Y489" s="5" t="n">
-        <v>46186.27264121279</v>
+        <v>46186.27342848559</v>
       </c>
       <c r="Z489" s="4" t="inlineStr"/>
     </row>
@@ -31751,7 +31751,7 @@
       <c r="W490" s="4" t="inlineStr"/>
       <c r="X490" s="4" t="inlineStr"/>
       <c r="Y490" s="5" t="n">
-        <v>46186.27264121299</v>
+        <v>46186.27342848579</v>
       </c>
       <c r="Z490" s="4" t="inlineStr"/>
     </row>
@@ -31819,7 +31819,7 @@
       <c r="W491" s="4" t="inlineStr"/>
       <c r="X491" s="4" t="inlineStr"/>
       <c r="Y491" s="5" t="n">
-        <v>46186.27264121317</v>
+        <v>46186.27342848597</v>
       </c>
       <c r="Z491" s="4" t="inlineStr"/>
     </row>
@@ -31875,7 +31875,7 @@
       <c r="W492" s="8" t="inlineStr"/>
       <c r="X492" s="8" t="inlineStr"/>
       <c r="Y492" s="9" t="n">
-        <v>46186.27264121338</v>
+        <v>46186.27342848618</v>
       </c>
       <c r="Z492" s="8" t="inlineStr"/>
     </row>
@@ -31943,7 +31943,7 @@
       <c r="W493" s="4" t="inlineStr"/>
       <c r="X493" s="4" t="inlineStr"/>
       <c r="Y493" s="5" t="n">
-        <v>46186.27264121357</v>
+        <v>46186.27342848637</v>
       </c>
       <c r="Z493" s="4" t="inlineStr"/>
     </row>
@@ -32011,7 +32011,7 @@
       <c r="W494" s="4" t="inlineStr"/>
       <c r="X494" s="4" t="inlineStr"/>
       <c r="Y494" s="5" t="n">
-        <v>46186.27264121374</v>
+        <v>46186.27342848657</v>
       </c>
       <c r="Z494" s="4" t="inlineStr"/>
     </row>
@@ -32067,7 +32067,7 @@
       <c r="W495" s="8" t="inlineStr"/>
       <c r="X495" s="8" t="inlineStr"/>
       <c r="Y495" s="9" t="n">
-        <v>46186.27264121394</v>
+        <v>46186.27342848684</v>
       </c>
       <c r="Z495" s="8" t="inlineStr"/>
     </row>
@@ -32135,7 +32135,7 @@
       <c r="W496" s="4" t="inlineStr"/>
       <c r="X496" s="4" t="inlineStr"/>
       <c r="Y496" s="5" t="n">
-        <v>46186.27264121413</v>
+        <v>46186.27342848706</v>
       </c>
       <c r="Z496" s="4" t="inlineStr"/>
     </row>
@@ -32203,7 +32203,7 @@
       <c r="W497" s="8" t="inlineStr"/>
       <c r="X497" s="8" t="inlineStr"/>
       <c r="Y497" s="9" t="n">
-        <v>46186.27264121432</v>
+        <v>46186.27342848769</v>
       </c>
       <c r="Z497" s="8" t="inlineStr"/>
     </row>
@@ -32271,7 +32271,7 @@
       <c r="W498" s="8" t="inlineStr"/>
       <c r="X498" s="8" t="inlineStr"/>
       <c r="Y498" s="9" t="n">
-        <v>46186.27264121453</v>
+        <v>46186.273428488</v>
       </c>
       <c r="Z498" s="8" t="inlineStr"/>
     </row>
@@ -32327,7 +32327,7 @@
       <c r="W499" s="8" t="inlineStr"/>
       <c r="X499" s="8" t="inlineStr"/>
       <c r="Y499" s="9" t="n">
-        <v>46186.27264121475</v>
+        <v>46186.27342848857</v>
       </c>
       <c r="Z499" s="8" t="inlineStr"/>
     </row>
@@ -32387,7 +32387,7 @@
       <c r="W500" s="4" t="inlineStr"/>
       <c r="X500" s="4" t="inlineStr"/>
       <c r="Y500" s="5" t="n">
-        <v>46186.27264121493</v>
+        <v>46186.27342848883</v>
       </c>
       <c r="Z500" s="4" t="inlineStr"/>
     </row>
@@ -32443,7 +32443,7 @@
       <c r="W501" s="4" t="inlineStr"/>
       <c r="X501" s="4" t="inlineStr"/>
       <c r="Y501" s="5" t="n">
-        <v>46186.27264121555</v>
+        <v>46186.27342848904</v>
       </c>
       <c r="Z501" s="4" t="inlineStr"/>
     </row>
@@ -32507,7 +32507,7 @@
       <c r="W502" s="8" t="inlineStr"/>
       <c r="X502" s="8" t="inlineStr"/>
       <c r="Y502" s="9" t="n">
-        <v>46186.27264121596</v>
+        <v>46186.27342848927</v>
       </c>
       <c r="Z502" s="8" t="inlineStr"/>
     </row>
@@ -32571,7 +32571,7 @@
       <c r="W503" s="8" t="inlineStr"/>
       <c r="X503" s="8" t="inlineStr"/>
       <c r="Y503" s="9" t="n">
-        <v>46186.27264121622</v>
+        <v>46186.27342848949</v>
       </c>
       <c r="Z503" s="8" t="inlineStr"/>
     </row>
@@ -32635,7 +32635,7 @@
       <c r="W504" s="8" t="inlineStr"/>
       <c r="X504" s="8" t="inlineStr"/>
       <c r="Y504" s="9" t="n">
-        <v>46186.27264121643</v>
+        <v>46186.27342848969</v>
       </c>
       <c r="Z504" s="8" t="inlineStr"/>
     </row>
@@ -32695,7 +32695,7 @@
       <c r="W505" s="4" t="inlineStr"/>
       <c r="X505" s="4" t="inlineStr"/>
       <c r="Y505" s="5" t="n">
-        <v>46186.27264121664</v>
+        <v>46186.27342848988</v>
       </c>
       <c r="Z505" s="4" t="inlineStr"/>
     </row>
@@ -32763,7 +32763,7 @@
       <c r="W506" s="4" t="inlineStr"/>
       <c r="X506" s="4" t="inlineStr"/>
       <c r="Y506" s="5" t="n">
-        <v>46186.27264121686</v>
+        <v>46186.27342849009</v>
       </c>
       <c r="Z506" s="4" t="inlineStr"/>
     </row>
@@ -32823,7 +32823,7 @@
       <c r="W507" s="4" t="inlineStr"/>
       <c r="X507" s="4" t="inlineStr"/>
       <c r="Y507" s="5" t="n">
-        <v>46186.2726412171</v>
+        <v>46186.27342849033</v>
       </c>
       <c r="Z507" s="4" t="inlineStr"/>
     </row>
@@ -32891,7 +32891,7 @@
       <c r="W508" s="4" t="inlineStr"/>
       <c r="X508" s="4" t="inlineStr"/>
       <c r="Y508" s="5" t="n">
-        <v>46186.2726412179</v>
+        <v>46186.27342849055</v>
       </c>
       <c r="Z508" s="4" t="inlineStr"/>
     </row>
@@ -32959,7 +32959,7 @@
       <c r="W509" s="4" t="inlineStr"/>
       <c r="X509" s="4" t="inlineStr"/>
       <c r="Y509" s="5" t="n">
-        <v>46186.27264121821</v>
+        <v>46186.27342849078</v>
       </c>
       <c r="Z509" s="4" t="inlineStr"/>
     </row>
@@ -33015,7 +33015,7 @@
       <c r="W510" s="4" t="inlineStr"/>
       <c r="X510" s="4" t="inlineStr"/>
       <c r="Y510" s="5" t="n">
-        <v>46186.27264121846</v>
+        <v>46186.27342849098</v>
       </c>
       <c r="Z510" s="4" t="inlineStr"/>
     </row>
@@ -33075,7 +33075,7 @@
       <c r="W511" s="4" t="inlineStr"/>
       <c r="X511" s="4" t="inlineStr"/>
       <c r="Y511" s="5" t="n">
-        <v>46186.27264121878</v>
+        <v>46186.27342849116</v>
       </c>
       <c r="Z511" s="4" t="inlineStr"/>
     </row>
@@ -33143,7 +33143,7 @@
       <c r="W512" s="4" t="inlineStr"/>
       <c r="X512" s="4" t="inlineStr"/>
       <c r="Y512" s="5" t="n">
-        <v>46186.27264121914</v>
+        <v>46186.27342849137</v>
       </c>
       <c r="Z512" s="4" t="inlineStr"/>
     </row>
@@ -33211,7 +33211,7 @@
       <c r="W513" s="4" t="inlineStr"/>
       <c r="X513" s="4" t="inlineStr"/>
       <c r="Y513" s="5" t="n">
-        <v>46186.27264121948</v>
+        <v>46186.27342849166</v>
       </c>
       <c r="Z513" s="4" t="inlineStr"/>
     </row>
@@ -33279,7 +33279,7 @@
       <c r="W514" s="4" t="inlineStr"/>
       <c r="X514" s="4" t="inlineStr"/>
       <c r="Y514" s="5" t="n">
-        <v>46186.27264121982</v>
+        <v>46186.27342849192</v>
       </c>
       <c r="Z514" s="4" t="inlineStr"/>
     </row>
@@ -33347,7 +33347,7 @@
       <c r="W515" s="4" t="inlineStr"/>
       <c r="X515" s="4" t="inlineStr"/>
       <c r="Y515" s="5" t="n">
-        <v>46186.27264122004</v>
+        <v>46186.27342849216</v>
       </c>
       <c r="Z515" s="4" t="inlineStr"/>
     </row>
@@ -33415,7 +33415,7 @@
       <c r="W516" s="4" t="inlineStr"/>
       <c r="X516" s="4" t="inlineStr"/>
       <c r="Y516" s="5" t="n">
-        <v>46186.2726412203</v>
+        <v>46186.27342849239</v>
       </c>
       <c r="Z516" s="4" t="inlineStr"/>
     </row>
@@ -33487,7 +33487,7 @@
       <c r="W517" s="4" t="inlineStr"/>
       <c r="X517" s="4" t="inlineStr"/>
       <c r="Y517" s="5" t="n">
-        <v>46186.27264122051</v>
+        <v>46186.27342849262</v>
       </c>
       <c r="Z517" s="4" t="inlineStr"/>
     </row>
@@ -33559,7 +33559,7 @@
       <c r="W518" s="4" t="inlineStr"/>
       <c r="X518" s="4" t="inlineStr"/>
       <c r="Y518" s="5" t="n">
-        <v>46186.27264122073</v>
+        <v>46186.27342849284</v>
       </c>
       <c r="Z518" s="4" t="inlineStr"/>
     </row>
@@ -33631,7 +33631,7 @@
       <c r="W519" s="4" t="inlineStr"/>
       <c r="X519" s="4" t="inlineStr"/>
       <c r="Y519" s="5" t="n">
-        <v>46186.27264122092</v>
+        <v>46186.27342849303</v>
       </c>
       <c r="Z519" s="4" t="inlineStr"/>
     </row>
@@ -33703,7 +33703,7 @@
       <c r="W520" s="4" t="inlineStr"/>
       <c r="X520" s="4" t="inlineStr"/>
       <c r="Y520" s="5" t="n">
-        <v>46186.2726412211</v>
+        <v>46186.27342849321</v>
       </c>
       <c r="Z520" s="4" t="inlineStr"/>
     </row>
@@ -33775,7 +33775,7 @@
       <c r="W521" s="4" t="inlineStr"/>
       <c r="X521" s="4" t="inlineStr"/>
       <c r="Y521" s="5" t="n">
-        <v>46186.27264122127</v>
+        <v>46186.27342849339</v>
       </c>
       <c r="Z521" s="4" t="inlineStr"/>
     </row>
@@ -33843,7 +33843,7 @@
       <c r="W522" s="4" t="inlineStr"/>
       <c r="X522" s="4" t="inlineStr"/>
       <c r="Y522" s="5" t="n">
-        <v>46186.27264122431</v>
+        <v>46186.27342849545</v>
       </c>
       <c r="Z522" s="4" t="inlineStr"/>
     </row>
@@ -33903,7 +33903,7 @@
       <c r="W523" s="4" t="inlineStr"/>
       <c r="X523" s="4" t="inlineStr"/>
       <c r="Y523" s="5" t="n">
-        <v>46186.27264122463</v>
+        <v>46186.27342849572</v>
       </c>
       <c r="Z523" s="4" t="inlineStr"/>
     </row>
@@ -33971,7 +33971,7 @@
       <c r="W524" s="4" t="inlineStr"/>
       <c r="X524" s="4" t="inlineStr"/>
       <c r="Y524" s="5" t="n">
-        <v>46186.27264122487</v>
+        <v>46186.27342849595</v>
       </c>
       <c r="Z524" s="4" t="inlineStr"/>
     </row>
@@ -34031,7 +34031,7 @@
       <c r="W525" s="4" t="inlineStr"/>
       <c r="X525" s="4" t="inlineStr"/>
       <c r="Y525" s="5" t="n">
-        <v>46186.27264122508</v>
+        <v>46186.27342849616</v>
       </c>
       <c r="Z525" s="4" t="inlineStr"/>
     </row>
@@ -34099,7 +34099,7 @@
       <c r="W526" s="4" t="inlineStr"/>
       <c r="X526" s="4" t="inlineStr"/>
       <c r="Y526" s="5" t="n">
-        <v>46186.27264122529</v>
+        <v>46186.27342849697</v>
       </c>
       <c r="Z526" s="4" t="inlineStr"/>
     </row>
@@ -34167,7 +34167,7 @@
       <c r="W527" s="4" t="inlineStr"/>
       <c r="X527" s="4" t="inlineStr"/>
       <c r="Y527" s="5" t="n">
-        <v>46186.2726412255</v>
+        <v>46186.27342849723</v>
       </c>
       <c r="Z527" s="4" t="inlineStr"/>
     </row>
@@ -34235,7 +34235,7 @@
       <c r="W528" s="4" t="inlineStr"/>
       <c r="X528" s="4" t="inlineStr"/>
       <c r="Y528" s="5" t="n">
-        <v>46186.2726412257</v>
+        <v>46186.27342849746</v>
       </c>
       <c r="Z528" s="4" t="inlineStr"/>
     </row>
@@ -34303,7 +34303,7 @@
       <c r="W529" s="4" t="inlineStr"/>
       <c r="X529" s="4" t="inlineStr"/>
       <c r="Y529" s="5" t="n">
-        <v>46186.2726412265</v>
+        <v>46186.27342849768</v>
       </c>
       <c r="Z529" s="4" t="inlineStr"/>
     </row>
@@ -34371,7 +34371,7 @@
       <c r="W530" s="4" t="inlineStr"/>
       <c r="X530" s="4" t="inlineStr"/>
       <c r="Y530" s="5" t="n">
-        <v>46186.27264122689</v>
+        <v>46186.27342849793</v>
       </c>
       <c r="Z530" s="4" t="inlineStr"/>
     </row>
@@ -34439,7 +34439,7 @@
       <c r="W531" s="4" t="inlineStr"/>
       <c r="X531" s="4" t="inlineStr"/>
       <c r="Y531" s="5" t="n">
-        <v>46186.27264122711</v>
+        <v>46186.27342849813</v>
       </c>
       <c r="Z531" s="4" t="inlineStr"/>
     </row>
@@ -34507,7 +34507,7 @@
       <c r="W532" s="4" t="inlineStr"/>
       <c r="X532" s="4" t="inlineStr"/>
       <c r="Y532" s="5" t="n">
-        <v>46186.27264122735</v>
+        <v>46186.27342849843</v>
       </c>
       <c r="Z532" s="4" t="inlineStr"/>
     </row>
@@ -34563,7 +34563,7 @@
       <c r="W533" s="4" t="inlineStr"/>
       <c r="X533" s="4" t="inlineStr"/>
       <c r="Y533" s="5" t="n">
-        <v>46186.27264122758</v>
+        <v>46186.27342849864</v>
       </c>
       <c r="Z533" s="4" t="inlineStr"/>
     </row>
@@ -34631,7 +34631,7 @@
       <c r="W534" s="4" t="inlineStr"/>
       <c r="X534" s="4" t="inlineStr"/>
       <c r="Y534" s="5" t="n">
-        <v>46186.27264122779</v>
+        <v>46186.27342849887</v>
       </c>
       <c r="Z534" s="4" t="inlineStr"/>
     </row>
@@ -34699,7 +34699,7 @@
       <c r="W535" s="4" t="inlineStr"/>
       <c r="X535" s="4" t="inlineStr"/>
       <c r="Y535" s="5" t="n">
-        <v>46186.27264122802</v>
+        <v>46186.27342849911</v>
       </c>
       <c r="Z535" s="4" t="inlineStr"/>
     </row>
@@ -34755,7 +34755,7 @@
       <c r="W536" s="8" t="inlineStr"/>
       <c r="X536" s="8" t="inlineStr"/>
       <c r="Y536" s="9" t="n">
-        <v>46186.27264122824</v>
+        <v>46186.27342849932</v>
       </c>
       <c r="Z536" s="8" t="inlineStr"/>
     </row>
@@ -34823,7 +34823,7 @@
       <c r="W537" s="4" t="inlineStr"/>
       <c r="X537" s="4" t="inlineStr"/>
       <c r="Y537" s="5" t="n">
-        <v>46186.27264122844</v>
+        <v>46186.27342849952</v>
       </c>
       <c r="Z537" s="4" t="inlineStr"/>
     </row>
@@ -34891,7 +34891,7 @@
       <c r="W538" s="4" t="inlineStr"/>
       <c r="X538" s="4" t="inlineStr"/>
       <c r="Y538" s="5" t="n">
-        <v>46186.27264122864</v>
+        <v>46186.27342850009</v>
       </c>
       <c r="Z538" s="4" t="inlineStr"/>
     </row>
@@ -34943,7 +34943,7 @@
       <c r="W539" s="4" t="inlineStr"/>
       <c r="X539" s="4" t="inlineStr"/>
       <c r="Y539" s="5" t="n">
-        <v>46186.27264122888</v>
+        <v>46186.2734285004</v>
       </c>
       <c r="Z539" s="4" t="inlineStr"/>
     </row>
@@ -35011,7 +35011,7 @@
       <c r="W540" s="4" t="inlineStr"/>
       <c r="X540" s="4" t="inlineStr"/>
       <c r="Y540" s="5" t="n">
-        <v>46186.27264122952</v>
+        <v>46186.27342850064</v>
       </c>
       <c r="Z540" s="4" t="inlineStr"/>
     </row>
@@ -35079,7 +35079,7 @@
       <c r="W541" s="4" t="inlineStr"/>
       <c r="X541" s="4" t="inlineStr"/>
       <c r="Y541" s="5" t="n">
-        <v>46186.27264122984</v>
+        <v>46186.27342850126</v>
       </c>
       <c r="Z541" s="4" t="inlineStr"/>
     </row>
@@ -35147,7 +35147,7 @@
       <c r="W542" s="4" t="inlineStr"/>
       <c r="X542" s="4" t="inlineStr"/>
       <c r="Y542" s="5" t="n">
-        <v>46186.27264123007</v>
+        <v>46186.27342850158</v>
       </c>
       <c r="Z542" s="4" t="inlineStr"/>
     </row>
@@ -35211,7 +35211,7 @@
       <c r="W543" s="4" t="inlineStr"/>
       <c r="X543" s="4" t="inlineStr"/>
       <c r="Y543" s="5" t="n">
-        <v>46186.27264123028</v>
+        <v>46186.27342850181</v>
       </c>
       <c r="Z543" s="4" t="inlineStr"/>
     </row>
@@ -35279,7 +35279,7 @@
       <c r="W544" s="4" t="inlineStr"/>
       <c r="X544" s="4" t="inlineStr"/>
       <c r="Y544" s="5" t="n">
-        <v>46186.27264123048</v>
+        <v>46186.27342850203</v>
       </c>
       <c r="Z544" s="4" t="inlineStr"/>
     </row>
@@ -35347,7 +35347,7 @@
       <c r="W545" s="4" t="inlineStr"/>
       <c r="X545" s="4" t="inlineStr"/>
       <c r="Y545" s="5" t="n">
-        <v>46186.27264123067</v>
+        <v>46186.27342850222</v>
       </c>
       <c r="Z545" s="4" t="inlineStr"/>
     </row>
@@ -35415,7 +35415,7 @@
       <c r="W546" s="4" t="inlineStr"/>
       <c r="X546" s="4" t="inlineStr"/>
       <c r="Y546" s="5" t="n">
-        <v>46186.27264123085</v>
+        <v>46186.27342850241</v>
       </c>
       <c r="Z546" s="4" t="inlineStr"/>
     </row>
@@ -35483,7 +35483,7 @@
       <c r="W547" s="4" t="inlineStr"/>
       <c r="X547" s="4" t="inlineStr"/>
       <c r="Y547" s="5" t="n">
-        <v>46186.27264123102</v>
+        <v>46186.27342850258</v>
       </c>
       <c r="Z547" s="4" t="inlineStr"/>
     </row>
@@ -35551,7 +35551,7 @@
       <c r="W548" s="4" t="inlineStr"/>
       <c r="X548" s="4" t="inlineStr"/>
       <c r="Y548" s="5" t="n">
-        <v>46186.27264123118</v>
+        <v>46186.27342850277</v>
       </c>
       <c r="Z548" s="4" t="inlineStr"/>
     </row>
@@ -35623,7 +35623,7 @@
       <c r="W549" s="4" t="inlineStr"/>
       <c r="X549" s="4" t="inlineStr"/>
       <c r="Y549" s="5" t="n">
-        <v>46186.27264123134</v>
+        <v>46186.27342850297</v>
       </c>
       <c r="Z549" s="4" t="inlineStr"/>
     </row>
@@ -35691,7 +35691,7 @@
       <c r="W550" s="4" t="inlineStr"/>
       <c r="X550" s="4" t="inlineStr"/>
       <c r="Y550" s="5" t="n">
-        <v>46186.27264123155</v>
+        <v>46186.27342850317</v>
       </c>
       <c r="Z550" s="4" t="inlineStr"/>
     </row>
@@ -35759,7 +35759,7 @@
       <c r="W551" s="4" t="inlineStr"/>
       <c r="X551" s="4" t="inlineStr"/>
       <c r="Y551" s="5" t="n">
-        <v>46186.27264123174</v>
+        <v>46186.27342850337</v>
       </c>
       <c r="Z551" s="4" t="inlineStr"/>
     </row>
@@ -35827,7 +35827,7 @@
       <c r="W552" s="4" t="inlineStr"/>
       <c r="X552" s="4" t="inlineStr"/>
       <c r="Y552" s="5" t="n">
-        <v>46186.27264123192</v>
+        <v>46186.27342850355</v>
       </c>
       <c r="Z552" s="4" t="inlineStr"/>
     </row>
@@ -35887,7 +35887,7 @@
       <c r="W553" s="4" t="inlineStr"/>
       <c r="X553" s="4" t="inlineStr"/>
       <c r="Y553" s="5" t="n">
-        <v>46186.27264123211</v>
+        <v>46186.27342850375</v>
       </c>
       <c r="Z553" s="4" t="inlineStr"/>
     </row>
@@ -35955,7 +35955,7 @@
       <c r="W554" s="4" t="inlineStr"/>
       <c r="X554" s="4" t="inlineStr"/>
       <c r="Y554" s="5" t="n">
-        <v>46186.27264123234</v>
+        <v>46186.27342850444</v>
       </c>
       <c r="Z554" s="4" t="inlineStr"/>
     </row>
@@ -36027,7 +36027,7 @@
       <c r="W555" s="4" t="inlineStr"/>
       <c r="X555" s="4" t="inlineStr"/>
       <c r="Y555" s="5" t="n">
-        <v>46186.27264123252</v>
+        <v>46186.27342850471</v>
       </c>
       <c r="Z555" s="4" t="inlineStr"/>
     </row>
@@ -36095,7 +36095,7 @@
       <c r="W556" s="4" t="inlineStr"/>
       <c r="X556" s="4" t="inlineStr"/>
       <c r="Y556" s="5" t="n">
-        <v>46186.27264123271</v>
+        <v>46186.27342850493</v>
       </c>
       <c r="Z556" s="4" t="inlineStr"/>
     </row>
@@ -36155,7 +36155,7 @@
       <c r="W557" s="4" t="inlineStr"/>
       <c r="X557" s="4" t="inlineStr"/>
       <c r="Y557" s="5" t="n">
-        <v>46186.27264123324</v>
+        <v>46186.27342850514</v>
       </c>
       <c r="Z557" s="4" t="inlineStr"/>
     </row>
@@ -36211,7 +36211,7 @@
       <c r="W558" s="4" t="inlineStr"/>
       <c r="X558" s="4" t="inlineStr"/>
       <c r="Y558" s="5" t="n">
-        <v>46186.27264123385</v>
+        <v>46186.27342850574</v>
       </c>
       <c r="Z558" s="4" t="inlineStr"/>
     </row>
@@ -36279,7 +36279,7 @@
       <c r="W559" s="4" t="inlineStr"/>
       <c r="X559" s="4" t="inlineStr"/>
       <c r="Y559" s="5" t="n">
-        <v>46186.27264123418</v>
+        <v>46186.27342850601</v>
       </c>
       <c r="Z559" s="4" t="inlineStr"/>
     </row>
@@ -36347,7 +36347,7 @@
       <c r="W560" s="4" t="inlineStr"/>
       <c r="X560" s="4" t="inlineStr"/>
       <c r="Y560" s="5" t="n">
-        <v>46186.27264123442</v>
+        <v>46186.27342850624</v>
       </c>
       <c r="Z560" s="4" t="inlineStr"/>
     </row>
@@ -36411,7 +36411,7 @@
       <c r="W561" s="4" t="inlineStr"/>
       <c r="X561" s="4" t="inlineStr"/>
       <c r="Y561" s="5" t="n">
-        <v>46186.27264123464</v>
+        <v>46186.27342850644</v>
       </c>
       <c r="Z561" s="4" t="inlineStr"/>
     </row>
@@ -36479,7 +36479,7 @@
       <c r="W562" s="4" t="inlineStr"/>
       <c r="X562" s="4" t="inlineStr"/>
       <c r="Y562" s="5" t="n">
-        <v>46186.27264123492</v>
+        <v>46186.27342850671</v>
       </c>
       <c r="Z562" s="4" t="inlineStr"/>
     </row>
@@ -36547,7 +36547,7 @@
       <c r="W563" s="4" t="inlineStr"/>
       <c r="X563" s="4" t="inlineStr"/>
       <c r="Y563" s="5" t="n">
-        <v>46186.2726412352</v>
+        <v>46186.27342850698</v>
       </c>
       <c r="Z563" s="4" t="inlineStr"/>
     </row>
@@ -36607,7 +36607,7 @@
       <c r="W564" s="4" t="inlineStr"/>
       <c r="X564" s="4" t="inlineStr"/>
       <c r="Y564" s="5" t="n">
-        <v>46186.2726412354</v>
+        <v>46186.27342850718</v>
       </c>
       <c r="Z564" s="4" t="inlineStr"/>
     </row>
@@ -36675,7 +36675,7 @@
       <c r="W565" s="4" t="inlineStr"/>
       <c r="X565" s="4" t="inlineStr"/>
       <c r="Y565" s="5" t="n">
-        <v>46186.27264123559</v>
+        <v>46186.27342850738</v>
       </c>
       <c r="Z565" s="4" t="inlineStr"/>
     </row>
@@ -36743,7 +36743,7 @@
       <c r="W566" s="4" t="inlineStr"/>
       <c r="X566" s="4" t="inlineStr"/>
       <c r="Y566" s="5" t="n">
-        <v>46186.27264123577</v>
+        <v>46186.27342850757</v>
       </c>
       <c r="Z566" s="4" t="inlineStr"/>
     </row>
@@ -36811,7 +36811,7 @@
       <c r="W567" s="4" t="inlineStr"/>
       <c r="X567" s="4" t="inlineStr"/>
       <c r="Y567" s="5" t="n">
-        <v>46186.27264123596</v>
+        <v>46186.27342850775</v>
       </c>
       <c r="Z567" s="4" t="inlineStr"/>
     </row>
@@ -36871,7 +36871,7 @@
       <c r="W568" s="4" t="inlineStr"/>
       <c r="X568" s="4" t="inlineStr"/>
       <c r="Y568" s="5" t="n">
-        <v>46186.27264123614</v>
+        <v>46186.27342850794</v>
       </c>
       <c r="Z568" s="4" t="inlineStr"/>
     </row>
@@ -36943,7 +36943,7 @@
       <c r="W569" s="4" t="inlineStr"/>
       <c r="X569" s="4" t="inlineStr"/>
       <c r="Y569" s="5" t="n">
-        <v>46186.27264123634</v>
+        <v>46186.27342850814</v>
       </c>
       <c r="Z569" s="4" t="inlineStr"/>
     </row>
@@ -36995,7 +36995,7 @@
       <c r="W570" s="4" t="inlineStr"/>
       <c r="X570" s="4" t="inlineStr"/>
       <c r="Y570" s="5" t="n">
-        <v>46186.27264123655</v>
+        <v>46186.27342850836</v>
       </c>
       <c r="Z570" s="4" t="inlineStr"/>
     </row>
@@ -37051,7 +37051,7 @@
       <c r="W571" s="4" t="inlineStr"/>
       <c r="X571" s="4" t="inlineStr"/>
       <c r="Y571" s="5" t="n">
-        <v>46186.27264123676</v>
+        <v>46186.27342850854</v>
       </c>
       <c r="Z571" s="4" t="inlineStr"/>
     </row>
@@ -37107,7 +37107,7 @@
       <c r="W572" s="4" t="inlineStr"/>
       <c r="X572" s="4" t="inlineStr"/>
       <c r="Y572" s="5" t="n">
-        <v>46186.27264123694</v>
+        <v>46186.27342850871</v>
       </c>
       <c r="Z572" s="4" t="inlineStr"/>
     </row>
@@ -37175,7 +37175,7 @@
       <c r="W573" s="4" t="inlineStr"/>
       <c r="X573" s="4" t="inlineStr"/>
       <c r="Y573" s="5" t="n">
-        <v>46186.27264123714</v>
+        <v>46186.27342850891</v>
       </c>
       <c r="Z573" s="4" t="inlineStr"/>
     </row>
@@ -37243,7 +37243,7 @@
       <c r="W574" s="4" t="inlineStr"/>
       <c r="X574" s="4" t="inlineStr"/>
       <c r="Y574" s="5" t="n">
-        <v>46186.27264123735</v>
+        <v>46186.27342850911</v>
       </c>
       <c r="Z574" s="4" t="inlineStr"/>
     </row>
@@ -37311,7 +37311,7 @@
       <c r="W575" s="4" t="inlineStr"/>
       <c r="X575" s="4" t="inlineStr"/>
       <c r="Y575" s="5" t="n">
-        <v>46186.27264123755</v>
+        <v>46186.2734285093</v>
       </c>
       <c r="Z575" s="4" t="inlineStr"/>
     </row>
@@ -37383,7 +37383,7 @@
       <c r="W576" s="4" t="inlineStr"/>
       <c r="X576" s="4" t="inlineStr"/>
       <c r="Y576" s="5" t="n">
-        <v>46186.27264123773</v>
+        <v>46186.27342850948</v>
       </c>
       <c r="Z576" s="4" t="inlineStr"/>
     </row>
@@ -37451,7 +37451,7 @@
       <c r="W577" s="4" t="inlineStr"/>
       <c r="X577" s="4" t="inlineStr"/>
       <c r="Y577" s="5" t="n">
-        <v>46186.27264123794</v>
+        <v>46186.27342850967</v>
       </c>
       <c r="Z577" s="4" t="inlineStr"/>
     </row>
@@ -37519,7 +37519,7 @@
       <c r="W578" s="4" t="inlineStr"/>
       <c r="X578" s="4" t="inlineStr"/>
       <c r="Y578" s="5" t="n">
-        <v>46186.27264123815</v>
+        <v>46186.27342850994</v>
       </c>
       <c r="Z578" s="4" t="inlineStr"/>
     </row>
@@ -37587,7 +37587,7 @@
       <c r="W579" s="4" t="inlineStr"/>
       <c r="X579" s="4" t="inlineStr"/>
       <c r="Y579" s="5" t="n">
-        <v>46186.27264123836</v>
+        <v>46186.27342851015</v>
       </c>
       <c r="Z579" s="4" t="inlineStr"/>
     </row>
@@ -37655,7 +37655,7 @@
       <c r="W580" s="4" t="inlineStr"/>
       <c r="X580" s="4" t="inlineStr"/>
       <c r="Y580" s="5" t="n">
-        <v>46186.27264123854</v>
+        <v>46186.27342851034</v>
       </c>
       <c r="Z580" s="4" t="inlineStr"/>
     </row>
@@ -37723,7 +37723,7 @@
       <c r="W581" s="4" t="inlineStr"/>
       <c r="X581" s="4" t="inlineStr"/>
       <c r="Y581" s="5" t="n">
-        <v>46186.27264123873</v>
+        <v>46186.27342851051</v>
       </c>
       <c r="Z581" s="4" t="inlineStr"/>
     </row>
@@ -37791,7 +37791,7 @@
       <c r="W582" s="4" t="inlineStr"/>
       <c r="X582" s="4" t="inlineStr"/>
       <c r="Y582" s="5" t="n">
-        <v>46186.2726412389</v>
+        <v>46186.27342851114</v>
       </c>
       <c r="Z582" s="4" t="inlineStr"/>
     </row>
@@ -37855,7 +37855,7 @@
       <c r="W583" s="8" t="inlineStr"/>
       <c r="X583" s="8" t="inlineStr"/>
       <c r="Y583" s="9" t="n">
-        <v>46186.27264123912</v>
+        <v>46186.27342851181</v>
       </c>
       <c r="Z583" s="8" t="inlineStr"/>
     </row>
@@ -37919,7 +37919,7 @@
       <c r="W584" s="8" t="inlineStr"/>
       <c r="X584" s="8" t="inlineStr"/>
       <c r="Y584" s="9" t="n">
-        <v>46186.27264123936</v>
+        <v>46186.27342851212</v>
       </c>
       <c r="Z584" s="8" t="inlineStr"/>
     </row>
@@ -37983,7 +37983,7 @@
       <c r="W585" s="8" t="inlineStr"/>
       <c r="X585" s="8" t="inlineStr"/>
       <c r="Y585" s="9" t="n">
-        <v>46186.27264123955</v>
+        <v>46186.27342851233</v>
       </c>
       <c r="Z585" s="8" t="inlineStr"/>
     </row>
@@ -38051,7 +38051,7 @@
       <c r="W586" s="8" t="inlineStr"/>
       <c r="X586" s="8" t="inlineStr"/>
       <c r="Y586" s="9" t="n">
-        <v>46186.27264124022</v>
+        <v>46186.27342851257</v>
       </c>
       <c r="Z586" s="8" t="inlineStr"/>
     </row>
@@ -38119,7 +38119,7 @@
       <c r="W587" s="4" t="inlineStr"/>
       <c r="X587" s="4" t="inlineStr"/>
       <c r="Y587" s="5" t="n">
-        <v>46186.27264124049</v>
+        <v>46186.27342851278</v>
       </c>
       <c r="Z587" s="4" t="inlineStr"/>
     </row>
@@ -38187,7 +38187,7 @@
       <c r="W588" s="8" t="inlineStr"/>
       <c r="X588" s="8" t="inlineStr"/>
       <c r="Y588" s="9" t="n">
-        <v>46186.27264124071</v>
+        <v>46186.27342851298</v>
       </c>
       <c r="Z588" s="8" t="inlineStr"/>
     </row>
@@ -38255,7 +38255,7 @@
       <c r="W589" s="8" t="inlineStr"/>
       <c r="X589" s="8" t="inlineStr"/>
       <c r="Y589" s="9" t="n">
-        <v>46186.27264124102</v>
+        <v>46186.27342851317</v>
       </c>
       <c r="Z589" s="8" t="inlineStr"/>
     </row>
@@ -38323,7 +38323,7 @@
       <c r="W590" s="4" t="inlineStr"/>
       <c r="X590" s="4" t="inlineStr"/>
       <c r="Y590" s="5" t="n">
-        <v>46186.27264124157</v>
+        <v>46186.27342851374</v>
       </c>
       <c r="Z590" s="4" t="inlineStr"/>
     </row>
@@ -38391,7 +38391,7 @@
       <c r="W591" s="8" t="inlineStr"/>
       <c r="X591" s="8" t="inlineStr"/>
       <c r="Y591" s="9" t="n">
-        <v>46186.27264124189</v>
+        <v>46186.27342851405</v>
       </c>
       <c r="Z591" s="8" t="inlineStr"/>
     </row>
@@ -38459,7 +38459,7 @@
       <c r="W592" s="4" t="inlineStr"/>
       <c r="X592" s="4" t="inlineStr"/>
       <c r="Y592" s="5" t="n">
-        <v>46186.27264124213</v>
+        <v>46186.27342851429</v>
       </c>
       <c r="Z592" s="4" t="inlineStr"/>
     </row>
@@ -38523,7 +38523,7 @@
       <c r="W593" s="8" t="inlineStr"/>
       <c r="X593" s="8" t="inlineStr"/>
       <c r="Y593" s="9" t="n">
-        <v>46186.27264124234</v>
+        <v>46186.27342851451</v>
       </c>
       <c r="Z593" s="8" t="inlineStr"/>
     </row>
@@ -38591,7 +38591,7 @@
       <c r="W594" s="8" t="inlineStr"/>
       <c r="X594" s="8" t="inlineStr"/>
       <c r="Y594" s="9" t="n">
-        <v>46186.27264124253</v>
+        <v>46186.27342851471</v>
       </c>
       <c r="Z594" s="8" t="inlineStr"/>
     </row>
@@ -38659,7 +38659,7 @@
       <c r="W595" s="8" t="inlineStr"/>
       <c r="X595" s="8" t="inlineStr"/>
       <c r="Y595" s="9" t="n">
-        <v>46186.27264124272</v>
+        <v>46186.27342851491</v>
       </c>
       <c r="Z595" s="8" t="inlineStr"/>
     </row>
@@ -38727,7 +38727,7 @@
       <c r="W596" s="8" t="inlineStr"/>
       <c r="X596" s="8" t="inlineStr"/>
       <c r="Y596" s="9" t="n">
-        <v>46186.2726412429</v>
+        <v>46186.2734285151</v>
       </c>
       <c r="Z596" s="8" t="inlineStr"/>
     </row>
@@ -38795,7 +38795,7 @@
       <c r="W597" s="8" t="inlineStr"/>
       <c r="X597" s="8" t="inlineStr"/>
       <c r="Y597" s="9" t="n">
-        <v>46186.27264124314</v>
+        <v>46186.27342851533</v>
       </c>
       <c r="Z597" s="8" t="inlineStr"/>
     </row>
@@ -38863,7 +38863,7 @@
       <c r="W598" s="8" t="inlineStr"/>
       <c r="X598" s="8" t="inlineStr"/>
       <c r="Y598" s="9" t="n">
-        <v>46186.27264124335</v>
+        <v>46186.27342851557</v>
       </c>
       <c r="Z598" s="8" t="inlineStr"/>
     </row>
@@ -38931,7 +38931,7 @@
       <c r="W599" s="8" t="inlineStr"/>
       <c r="X599" s="8" t="inlineStr"/>
       <c r="Y599" s="9" t="n">
-        <v>46186.27264124353</v>
+        <v>46186.27342851617</v>
       </c>
       <c r="Z599" s="8" t="inlineStr"/>
     </row>
@@ -38995,7 +38995,7 @@
       <c r="W600" s="8" t="inlineStr"/>
       <c r="X600" s="8" t="inlineStr"/>
       <c r="Y600" s="9" t="n">
-        <v>46186.27264124373</v>
+        <v>46186.27342851649</v>
       </c>
       <c r="Z600" s="8" t="inlineStr"/>
     </row>
@@ -39063,7 +39063,7 @@
       <c r="W601" s="8" t="inlineStr"/>
       <c r="X601" s="8" t="inlineStr"/>
       <c r="Y601" s="9" t="n">
-        <v>46186.27264124394</v>
+        <v>46186.27342851682</v>
       </c>
       <c r="Z601" s="8" t="inlineStr"/>
     </row>
@@ -39127,7 +39127,7 @@
       <c r="W602" s="8" t="inlineStr"/>
       <c r="X602" s="8" t="inlineStr"/>
       <c r="Y602" s="9" t="n">
-        <v>46186.27264124414</v>
+        <v>46186.27342851705</v>
       </c>
       <c r="Z602" s="8" t="inlineStr"/>
     </row>
@@ -39183,7 +39183,7 @@
       <c r="W603" s="8" t="inlineStr"/>
       <c r="X603" s="8" t="inlineStr"/>
       <c r="Y603" s="9" t="n">
-        <v>46186.27264124435</v>
+        <v>46186.27342851727</v>
       </c>
       <c r="Z603" s="8" t="inlineStr"/>
     </row>
@@ -39251,7 +39251,7 @@
       <c r="W604" s="8" t="inlineStr"/>
       <c r="X604" s="8" t="inlineStr"/>
       <c r="Y604" s="9" t="n">
-        <v>46186.27264124457</v>
+        <v>46186.2734285175</v>
       </c>
       <c r="Z604" s="8" t="inlineStr"/>
     </row>
@@ -39319,7 +39319,7 @@
       <c r="W605" s="8" t="inlineStr"/>
       <c r="X605" s="8" t="inlineStr"/>
       <c r="Y605" s="9" t="n">
-        <v>46186.27264124477</v>
+        <v>46186.27342851771</v>
       </c>
       <c r="Z605" s="8" t="inlineStr"/>
     </row>
@@ -39391,7 +39391,7 @@
       <c r="W606" s="8" t="inlineStr"/>
       <c r="X606" s="8" t="inlineStr"/>
       <c r="Y606" s="9" t="n">
-        <v>46186.27264124499</v>
+        <v>46186.27342851794</v>
       </c>
       <c r="Z606" s="8" t="inlineStr"/>
     </row>
@@ -39459,7 +39459,7 @@
       <c r="W607" s="8" t="inlineStr"/>
       <c r="X607" s="8" t="inlineStr"/>
       <c r="Y607" s="9" t="n">
-        <v>46186.27264124547</v>
+        <v>46186.27342851815</v>
       </c>
       <c r="Z607" s="8" t="inlineStr"/>
     </row>
@@ -39515,7 +39515,7 @@
       <c r="W608" s="8" t="inlineStr"/>
       <c r="X608" s="8" t="inlineStr"/>
       <c r="Y608" s="9" t="n">
-        <v>46186.27264124579</v>
+        <v>46186.27342851835</v>
       </c>
       <c r="Z608" s="8" t="inlineStr"/>
     </row>
@@ -39583,7 +39583,7 @@
       <c r="W609" s="4" t="inlineStr"/>
       <c r="X609" s="4" t="inlineStr"/>
       <c r="Y609" s="5" t="n">
-        <v>46186.27264124602</v>
+        <v>46186.27342851858</v>
       </c>
       <c r="Z609" s="4" t="inlineStr"/>
     </row>
@@ -39639,7 +39639,7 @@
       <c r="W610" s="8" t="inlineStr"/>
       <c r="X610" s="8" t="inlineStr"/>
       <c r="Y610" s="9" t="n">
-        <v>46186.27264124624</v>
+        <v>46186.27342851915</v>
       </c>
       <c r="Z610" s="8" t="inlineStr"/>
     </row>
@@ -39695,7 +39695,7 @@
       <c r="W611" s="8" t="inlineStr"/>
       <c r="X611" s="8" t="inlineStr"/>
       <c r="Y611" s="9" t="n">
-        <v>46186.27264124688</v>
+        <v>46186.27342851948</v>
       </c>
       <c r="Z611" s="8" t="inlineStr"/>
     </row>
@@ -39751,7 +39751,7 @@
       <c r="W612" s="8" t="inlineStr"/>
       <c r="X612" s="8" t="inlineStr"/>
       <c r="Y612" s="9" t="n">
-        <v>46186.27264124715</v>
+        <v>46186.2734285197</v>
       </c>
       <c r="Z612" s="8" t="inlineStr"/>
     </row>
@@ -39803,7 +39803,7 @@
       <c r="W613" s="8" t="inlineStr"/>
       <c r="X613" s="8" t="inlineStr"/>
       <c r="Y613" s="9" t="n">
-        <v>46186.27264124891</v>
+        <v>46186.2734285199</v>
       </c>
       <c r="Z613" s="8" t="inlineStr"/>
     </row>
@@ -39867,7 +39867,7 @@
       <c r="W614" s="8" t="inlineStr"/>
       <c r="X614" s="8" t="inlineStr"/>
       <c r="Y614" s="9" t="n">
-        <v>46186.27264124991</v>
+        <v>46186.27342852014</v>
       </c>
       <c r="Z614" s="8" t="inlineStr"/>
     </row>
@@ -39919,7 +39919,7 @@
       <c r="W615" s="8" t="inlineStr"/>
       <c r="X615" s="8" t="inlineStr"/>
       <c r="Y615" s="9" t="n">
-        <v>46186.27264125019</v>
+        <v>46186.27342852036</v>
       </c>
       <c r="Z615" s="8" t="inlineStr"/>
     </row>
@@ -39983,7 +39983,7 @@
       <c r="W616" s="8" t="inlineStr"/>
       <c r="X616" s="8" t="inlineStr"/>
       <c r="Y616" s="9" t="n">
-        <v>46186.27264125043</v>
+        <v>46186.27342852056</v>
       </c>
       <c r="Z616" s="8" t="inlineStr"/>
     </row>
@@ -40039,7 +40039,7 @@
       <c r="W617" s="8" t="inlineStr"/>
       <c r="X617" s="8" t="inlineStr"/>
       <c r="Y617" s="9" t="n">
-        <v>46186.27264125066</v>
+        <v>46186.27342852078</v>
       </c>
       <c r="Z617" s="8" t="inlineStr"/>
     </row>
@@ -40103,7 +40103,7 @@
       <c r="W618" s="8" t="inlineStr"/>
       <c r="X618" s="8" t="inlineStr"/>
       <c r="Y618" s="9" t="n">
-        <v>46186.27264125091</v>
+        <v>46186.27342852102</v>
       </c>
       <c r="Z618" s="8" t="inlineStr"/>
     </row>
@@ -40159,7 +40159,7 @@
       <c r="W619" s="8" t="inlineStr"/>
       <c r="X619" s="8" t="inlineStr"/>
       <c r="Y619" s="9" t="n">
-        <v>46186.27264125113</v>
+        <v>46186.27342852121</v>
       </c>
       <c r="Z619" s="8" t="inlineStr"/>
     </row>
@@ -40227,7 +40227,7 @@
       <c r="W620" s="8" t="inlineStr"/>
       <c r="X620" s="8" t="inlineStr"/>
       <c r="Y620" s="9" t="n">
-        <v>46186.27264125133</v>
+        <v>46186.27342852147</v>
       </c>
       <c r="Z620" s="8" t="inlineStr"/>
     </row>
@@ -40291,7 +40291,7 @@
       <c r="W621" s="8" t="inlineStr"/>
       <c r="X621" s="8" t="inlineStr"/>
       <c r="Y621" s="9" t="n">
-        <v>46186.27264125154</v>
+        <v>46186.27342852168</v>
       </c>
       <c r="Z621" s="8" t="inlineStr"/>
     </row>
@@ -40355,7 +40355,7 @@
       <c r="W622" s="8" t="inlineStr"/>
       <c r="X622" s="8" t="inlineStr"/>
       <c r="Y622" s="9" t="n">
-        <v>46186.27264125178</v>
+        <v>46186.27342852193</v>
       </c>
       <c r="Z622" s="8" t="inlineStr"/>
     </row>
@@ -40419,7 +40419,7 @@
       <c r="W623" s="8" t="inlineStr"/>
       <c r="X623" s="8" t="inlineStr"/>
       <c r="Y623" s="9" t="n">
-        <v>46186.27264125198</v>
+        <v>46186.27342852213</v>
       </c>
       <c r="Z623" s="8" t="inlineStr"/>
     </row>
@@ -40475,7 +40475,7 @@
       <c r="W624" s="4" t="inlineStr"/>
       <c r="X624" s="4" t="inlineStr"/>
       <c r="Y624" s="5" t="n">
-        <v>46186.27264125219</v>
+        <v>46186.27342852234</v>
       </c>
       <c r="Z624" s="4" t="inlineStr"/>
     </row>
@@ -40535,7 +40535,7 @@
       <c r="W625" s="4" t="inlineStr"/>
       <c r="X625" s="4" t="inlineStr"/>
       <c r="Y625" s="5" t="n">
-        <v>46186.27264125238</v>
+        <v>46186.27342852256</v>
       </c>
       <c r="Z625" s="4" t="inlineStr"/>
     </row>
@@ -40603,7 +40603,7 @@
       <c r="W626" s="4" t="inlineStr"/>
       <c r="X626" s="4" t="inlineStr"/>
       <c r="Y626" s="5" t="n">
-        <v>46186.27264125266</v>
+        <v>46186.27342852308</v>
       </c>
       <c r="Z626" s="4" t="inlineStr"/>
     </row>
@@ -40671,7 +40671,7 @@
       <c r="W627" s="4" t="inlineStr"/>
       <c r="X627" s="4" t="inlineStr"/>
       <c r="Y627" s="5" t="n">
-        <v>46186.27264125287</v>
+        <v>46186.27342852341</v>
       </c>
       <c r="Z627" s="4" t="inlineStr"/>
     </row>
@@ -40743,7 +40743,7 @@
       <c r="W628" s="4" t="inlineStr"/>
       <c r="X628" s="4" t="inlineStr"/>
       <c r="Y628" s="5" t="n">
-        <v>46186.27264125307</v>
+        <v>46186.27342852409</v>
       </c>
       <c r="Z628" s="4" t="inlineStr"/>
     </row>
@@ -40803,7 +40803,7 @@
       <c r="W629" s="4" t="inlineStr"/>
       <c r="X629" s="4" t="inlineStr"/>
       <c r="Y629" s="5" t="n">
-        <v>46186.27264125326</v>
+        <v>46186.27342852435</v>
       </c>
       <c r="Z629" s="4" t="inlineStr"/>
     </row>
@@ -40884,7 +40884,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13/06/2026 06:32</t>
+          <t>13/06/2026 06:33</t>
         </is>
       </c>
     </row>

--- a/output_transmittal_register.xlsx
+++ b/output_transmittal_register.xlsx
@@ -563,7 +563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 17/06/2026 08:08</t>
+          <t>Generated: 17/06/2026 08:41</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>Yazan Safieh</t>
+          <t>YS</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>Ismaiel Salama</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>Rohit Tharakan</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>Stephen Beadle</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr"/>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>Stephen Beadle</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr"/>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>Stephen Beadle</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr"/>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>Stephen Beadle</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>Rohit Tharakan</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr"/>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>Rohit Tharakan</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>Stephen Beadle</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr"/>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>Ismaiel Salama</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr"/>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>Amit Kumar</t>
+          <t>AK</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr"/>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>Amit Kumar</t>
+          <t>AK</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr"/>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>Ashok Kumar</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr"/>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>Ashok Kumar</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr"/>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr"/>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr"/>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>Ashok Kumar</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr"/>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>Ahmad Chikh bakri</t>
+          <t>ACB</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr"/>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>Ashok Kumar</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr"/>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr"/>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>Ashok Kumar</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>Mohamed Yahia</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr"/>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr"/>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>Ahmad Chikh bakri</t>
+          <t>ACB</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr"/>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>Ahmad Chikh bakri</t>
+          <t>ACB</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr"/>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr"/>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>Loren Leiski</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr"/>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>Ismaiel Salama</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="M84" s="4" t="inlineStr"/>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr"/>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>Mazar Syed</t>
+          <t>MSD</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr"/>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr"/>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr"/>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr"/>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr"/>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>Ashok Kumar</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr"/>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M96" s="4" t="inlineStr"/>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Ibrahim</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr"/>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>Ismaiel Salama</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="M98" s="4" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>Ismaiel Salama</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>Ismaiel Salama</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>John Prabhu</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>John Prabhu</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="M105" s="4" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr"/>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>Rohit Tharakan</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="M113" s="4" t="inlineStr"/>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M117" s="4" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>Mike Lewey</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr"/>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M120" s="4" t="inlineStr"/>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M122" s="4" t="inlineStr"/>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr"/>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>Ashok Kumar</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="M124" s="4" t="inlineStr"/>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>Sherif Zayed</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="M125" s="4" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>Sherif Zayed</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="M126" s="4" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>Sherif Zayed</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>Sherif Zayed</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr"/>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr"/>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M131" s="4" t="inlineStr"/>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M132" s="4" t="inlineStr"/>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M133" s="4" t="inlineStr"/>
@@ -8393,7 +8393,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr"/>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M135" s="4" t="inlineStr"/>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr"/>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr"/>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>Ashok Kumar</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr"/>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>Loren Leiski</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr"/>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>Rohit Tharakan</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>Evripidis Zampiras</t>
+          <t>EZ</t>
         </is>
       </c>
       <c r="M141" s="4" t="inlineStr"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M142" s="4" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M143" s="4" t="inlineStr"/>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>Mohsin Patel</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr"/>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M145" s="4" t="inlineStr"/>
@@ -9145,7 +9145,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M146" s="4" t="inlineStr"/>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M147" s="4" t="inlineStr"/>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M148" s="4" t="inlineStr"/>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M149" s="4" t="inlineStr"/>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr"/>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>Stephen Beadle</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr"/>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Ibrahim</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr"/>
@@ -9593,7 +9593,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>Mohsin Patel</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr"/>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>Mohsin Patel</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr"/>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr"/>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr"/>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M158" s="4" t="inlineStr"/>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M159" s="4" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>Vinod Kalwaghe</t>
+          <t>VAK</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
-          <t>Loren Leiski</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr"/>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M162" s="4" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr"/>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>Siddarth Jayaraman</t>
+          <t>SRJ</t>
         </is>
       </c>
       <c r="M164" s="4" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>Stephen Beadle</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="M165" s="4" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M166" s="4" t="inlineStr"/>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M168" s="4" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M169" s="4" t="inlineStr"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr"/>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
-          <t>Rohit Tharakan</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="M171" s="4" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M173" s="4" t="inlineStr"/>
@@ -10937,7 +10937,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M174" s="4" t="inlineStr"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
-          <t>Mohsin Patel</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="M175" s="4" t="inlineStr"/>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="L177" s="8" t="inlineStr">
         <is>
-          <t>Oladele Kupolati</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M177" s="8" t="inlineStr"/>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M179" s="4" t="inlineStr"/>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>Rohit Tharakan</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>Rohit Tharakan</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="M181" s="4" t="inlineStr"/>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>Rohit Tharakan</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="M182" s="4" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
-          <t>Rohit Tharakan</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="M183" s="4" t="inlineStr"/>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>Rohit Tharakan</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="M184" s="4" t="inlineStr"/>
@@ -11651,7 +11651,7 @@
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M185" s="4" t="inlineStr"/>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M186" s="4" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>Lynneth Santos</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="M187" s="4" t="inlineStr"/>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>Ismaiel Salama</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="M188" s="4" t="inlineStr"/>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M189" s="4" t="inlineStr"/>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>Ashok Kumar</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="M190" s="4" t="inlineStr"/>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M191" s="4" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>Ismaiel Salama</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="M192" s="4" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M193" s="4" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>Mazar Syed</t>
+          <t>MSD</t>
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
-          <t>Evripidis Zampiras</t>
+          <t>EZ</t>
         </is>
       </c>
       <c r="M195" s="4" t="inlineStr"/>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M196" s="4" t="inlineStr"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="L197" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M197" s="4" t="inlineStr">
@@ -12459,7 +12459,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M198" s="4" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="L199" s="4" t="inlineStr">
         <is>
-          <t>Lynneth Santos</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="M199" s="4" t="inlineStr"/>
@@ -12575,7 +12575,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>Yazan Safieh</t>
+          <t>YS</t>
         </is>
       </c>
       <c r="M200" s="4" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M201" s="4" t="inlineStr"/>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M202" s="4" t="inlineStr"/>
@@ -12771,7 +12771,7 @@
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M203" s="4" t="inlineStr"/>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M204" s="4" t="inlineStr"/>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Ibrahim</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr"/>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Ibrahim</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="M206" s="4" t="inlineStr"/>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="L207" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M207" s="4" t="inlineStr"/>
@@ -13097,7 +13097,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M208" s="4" t="inlineStr"/>
@@ -13167,7 +13167,7 @@
       </c>
       <c r="L209" s="4" t="inlineStr">
         <is>
-          <t>Vinod Kalwaghe</t>
+          <t>VAK</t>
         </is>
       </c>
       <c r="M209" s="4" t="inlineStr"/>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>Lynneth Santos</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="M210" s="4" t="inlineStr"/>
@@ -13295,7 +13295,7 @@
       </c>
       <c r="L211" s="4" t="inlineStr">
         <is>
-          <t>Vinod Kalwaghe</t>
+          <t>VAK</t>
         </is>
       </c>
       <c r="M211" s="4" t="inlineStr"/>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>Stephen Beadle</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="M212" s="4" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="L213" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M213" s="4" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>Kaddour Lardjani</t>
+          <t>KLI</t>
         </is>
       </c>
       <c r="M214" s="4" t="inlineStr"/>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
-          <t>Daniel Maddy</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="M215" s="4" t="inlineStr">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>Sandeep Jha</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="M216" s="4" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="L217" s="4" t="inlineStr">
         <is>
-          <t>Sandeep Jha</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="M217" s="4" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M226" s="4" t="inlineStr"/>
@@ -14295,7 +14295,7 @@
       </c>
       <c r="L227" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M227" s="4" t="inlineStr"/>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>Lynneth Santos</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="M228" s="4" t="inlineStr"/>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="L229" s="4" t="inlineStr">
         <is>
-          <t>Ahmad Chikh bakri</t>
+          <t>ACB</t>
         </is>
       </c>
       <c r="M229" s="4" t="inlineStr"/>
@@ -14487,7 +14487,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>Allan Halferty</t>
+          <t>AH</t>
         </is>
       </c>
       <c r="M230" s="4" t="inlineStr"/>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="L231" s="4" t="inlineStr">
         <is>
-          <t>Nageswara Ampolu</t>
+          <t>NRA</t>
         </is>
       </c>
       <c r="M231" s="4" t="inlineStr"/>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>John Prabhu</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="M232" s="4" t="inlineStr"/>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="L233" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Ibrahim</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="M233" s="4" t="inlineStr"/>
@@ -14731,7 +14731,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M234" s="4" t="inlineStr">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="L235" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M235" s="4" t="inlineStr"/>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M236" s="4" t="inlineStr"/>
@@ -14915,7 +14915,7 @@
       </c>
       <c r="L237" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M237" s="4" t="inlineStr"/>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M238" s="4" t="inlineStr"/>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="L239" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M239" s="4" t="inlineStr"/>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M240" s="4" t="inlineStr"/>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="L241" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M241" s="4" t="inlineStr"/>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M242" s="4" t="inlineStr"/>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="L243" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M243" s="4" t="inlineStr"/>
@@ -15363,7 +15363,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M244" s="4" t="inlineStr"/>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="L245" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M245" s="4" t="inlineStr"/>
@@ -15491,7 +15491,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M246" s="4" t="inlineStr"/>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="L247" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M247" s="4" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M248" s="4" t="inlineStr"/>
@@ -15681,7 +15681,7 @@
       </c>
       <c r="L249" s="4" t="inlineStr">
         <is>
-          <t>Vinod Kalwaghe</t>
+          <t>VAK</t>
         </is>
       </c>
       <c r="M249" s="4" t="inlineStr"/>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="L251" s="4" t="inlineStr">
         <is>
-          <t>Ashok Kumar</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="M251" s="4" t="inlineStr"/>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>Lynneth Santos</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="M252" s="4" t="inlineStr"/>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="L253" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M253" s="4" t="inlineStr"/>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>Ismaiel Salama</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="M254" s="4" t="inlineStr"/>
@@ -16055,7 +16055,7 @@
       </c>
       <c r="L255" s="4" t="inlineStr">
         <is>
-          <t>Yazan Safieh</t>
+          <t>YS</t>
         </is>
       </c>
       <c r="M255" s="4" t="inlineStr">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>Yazan Safieh</t>
+          <t>YS</t>
         </is>
       </c>
       <c r="M256" s="4" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="L257" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M257" s="4" t="inlineStr">
@@ -16231,7 +16231,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M258" s="4" t="inlineStr"/>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="L259" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M259" s="4" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M260" s="4" t="inlineStr"/>
@@ -16415,7 +16415,7 @@
       </c>
       <c r="L261" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Ibrahim</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="M261" s="4" t="inlineStr"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>Ashok Kumar</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="M262" s="4" t="inlineStr"/>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="L263" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M263" s="4" t="inlineStr">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M264" s="4" t="inlineStr"/>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="L265" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M265" s="4" t="inlineStr"/>
@@ -16733,7 +16733,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M266" s="4" t="inlineStr"/>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="L267" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M267" s="4" t="inlineStr"/>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M268" s="4" t="inlineStr"/>
@@ -16925,7 +16925,7 @@
       </c>
       <c r="L269" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M269" s="4" t="inlineStr">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M270" s="4" t="inlineStr">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>Stephen Beadle</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>Stephen Beadle</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="M272" s="4" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="L273" s="4" t="inlineStr">
         <is>
-          <t>Stephen Beadle</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="M273" s="4" t="inlineStr">
@@ -17265,7 +17265,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M274" s="4" t="inlineStr"/>
@@ -17317,7 +17317,7 @@
       </c>
       <c r="L275" s="4" t="inlineStr">
         <is>
-          <t>Mike Lewey</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="M275" s="4" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M276" s="4" t="inlineStr"/>
@@ -17437,7 +17437,7 @@
       </c>
       <c r="L277" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M277" s="4" t="inlineStr">
@@ -17505,7 +17505,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M278" s="4" t="inlineStr"/>
@@ -17569,7 +17569,7 @@
       </c>
       <c r="L279" s="4" t="inlineStr">
         <is>
-          <t>Mohamed Yahia</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="M279" s="4" t="inlineStr"/>
@@ -17633,7 +17633,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>Stephen Beadle</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="M280" s="4" t="inlineStr"/>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="L281" s="4" t="inlineStr">
         <is>
-          <t>Nageswara Ampolu</t>
+          <t>NRA</t>
         </is>
       </c>
       <c r="M281" s="4" t="inlineStr"/>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>Ismaiel Salama</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="M282" s="4" t="inlineStr"/>
@@ -17825,7 +17825,7 @@
       </c>
       <c r="L283" s="4" t="inlineStr">
         <is>
-          <t>Lynneth Santos</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="M283" s="4" t="inlineStr"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>Amit Kumar</t>
+          <t>AK</t>
         </is>
       </c>
       <c r="M284" s="4" t="inlineStr"/>
@@ -17947,7 +17947,7 @@
       </c>
       <c r="L285" s="4" t="inlineStr">
         <is>
-          <t>Amit Kumar</t>
+          <t>AK</t>
         </is>
       </c>
       <c r="M285" s="4" t="inlineStr"/>
@@ -18011,7 +18011,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>Alister White</t>
+          <t>AW</t>
         </is>
       </c>
       <c r="M286" s="4" t="inlineStr"/>
@@ -18075,7 +18075,7 @@
       </c>
       <c r="L287" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M287" s="4" t="inlineStr"/>
@@ -18139,7 +18139,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>Loren Leiski</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="M288" s="4" t="inlineStr"/>
@@ -18203,7 +18203,7 @@
       </c>
       <c r="L289" s="4" t="inlineStr">
         <is>
-          <t>Loren Leiski</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="M289" s="4" t="inlineStr"/>
@@ -18251,7 +18251,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M290" s="4" t="inlineStr"/>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="L291" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M291" s="4" t="inlineStr"/>
@@ -18379,7 +18379,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>Ahmad Chikh bakri</t>
+          <t>ACB</t>
         </is>
       </c>
       <c r="M292" s="4" t="inlineStr"/>
@@ -18443,7 +18443,7 @@
       </c>
       <c r="L293" s="4" t="inlineStr">
         <is>
-          <t>Mazar Syed</t>
+          <t>MSD</t>
         </is>
       </c>
       <c r="M293" s="4" t="inlineStr"/>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M294" s="4" t="inlineStr"/>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="L295" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M295" s="4" t="inlineStr"/>
@@ -18637,7 +18637,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M296" s="4" t="inlineStr"/>
@@ -18701,7 +18701,7 @@
       </c>
       <c r="L297" s="4" t="inlineStr">
         <is>
-          <t>Lynneth Santos</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="M297" s="4" t="inlineStr"/>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Ibrahim</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="M298" s="4" t="inlineStr"/>
@@ -18829,7 +18829,7 @@
       </c>
       <c r="L299" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M299" s="4" t="inlineStr"/>
@@ -18893,7 +18893,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>Sherif Zayed</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="M300" s="4" t="inlineStr">
@@ -18967,7 +18967,7 @@
       </c>
       <c r="L301" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M301" s="4" t="inlineStr"/>
@@ -19037,7 +19037,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>Arunkumar Ramakrishnan</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="M302" s="4" t="inlineStr"/>
@@ -19101,7 +19101,7 @@
       </c>
       <c r="L303" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M303" s="4" t="inlineStr"/>
@@ -19153,7 +19153,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M304" s="4" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="L305" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M305" s="4" t="inlineStr"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>Rohit Tharakan</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="M306" s="4" t="inlineStr">
@@ -19359,7 +19359,7 @@
       </c>
       <c r="L307" s="4" t="inlineStr">
         <is>
-          <t>Vinod Kalwaghe</t>
+          <t>VAK</t>
         </is>
       </c>
       <c r="M307" s="4" t="inlineStr"/>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M308" s="4" t="inlineStr">
@@ -19601,7 +19601,7 @@
       </c>
       <c r="L311" s="4" t="inlineStr">
         <is>
-          <t>Vinod Kalwaghe</t>
+          <t>VAK</t>
         </is>
       </c>
       <c r="M311" s="4" t="inlineStr"/>
@@ -19801,7 +19801,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>Mohsin Patel</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="M314" s="4" t="inlineStr"/>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="L315" s="4" t="inlineStr">
         <is>
-          <t>Mike Lewey</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="M315" s="4" t="inlineStr">
@@ -19927,7 +19927,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>Mazar Syed</t>
+          <t>MSD</t>
         </is>
       </c>
       <c r="M316" s="4" t="inlineStr"/>
@@ -19991,7 +19991,7 @@
       </c>
       <c r="L317" s="4" t="inlineStr">
         <is>
-          <t>Mazar Syed</t>
+          <t>MSD</t>
         </is>
       </c>
       <c r="M317" s="4" t="inlineStr"/>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>Mazar Syed</t>
+          <t>MSD</t>
         </is>
       </c>
       <c r="M318" s="4" t="inlineStr"/>
@@ -20107,7 +20107,7 @@
       </c>
       <c r="L319" s="4" t="inlineStr">
         <is>
-          <t>Yazan Safieh</t>
+          <t>YS</t>
         </is>
       </c>
       <c r="M319" s="4" t="inlineStr">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>Ismaiel Salama</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="M320" s="4" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="L321" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M321" s="4" t="inlineStr">
@@ -20275,7 +20275,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>Sherif Zayed</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="M322" s="4" t="inlineStr">
@@ -20327,7 +20327,7 @@
       </c>
       <c r="L323" s="4" t="inlineStr">
         <is>
-          <t>Sherif Zayed</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="M323" s="4" t="inlineStr">
@@ -20465,7 +20465,7 @@
       </c>
       <c r="L325" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M325" s="4" t="inlineStr"/>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>Alister White</t>
+          <t>AW</t>
         </is>
       </c>
       <c r="M326" s="4" t="inlineStr"/>
@@ -20593,7 +20593,7 @@
       </c>
       <c r="L327" s="4" t="inlineStr">
         <is>
-          <t>Ismaiel Salama</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="M327" s="4" t="inlineStr">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M328" s="4" t="inlineStr"/>
@@ -20725,7 +20725,7 @@
       </c>
       <c r="L329" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M329" s="4" t="inlineStr"/>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M330" s="4" t="inlineStr"/>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="L331" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M331" s="4" t="inlineStr"/>
@@ -20917,7 +20917,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M332" s="4" t="inlineStr"/>
@@ -20981,7 +20981,7 @@
       </c>
       <c r="L333" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M333" s="4" t="inlineStr"/>
@@ -21045,7 +21045,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Ibrahim</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="M334" s="4" t="inlineStr"/>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="L335" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M335" s="4" t="inlineStr"/>
@@ -21173,7 +21173,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>Ismaiel Salama</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="M336" s="4" t="inlineStr"/>
@@ -21237,7 +21237,7 @@
       </c>
       <c r="L337" s="4" t="inlineStr">
         <is>
-          <t>Suresh Shetty</t>
+          <t>SSY</t>
         </is>
       </c>
       <c r="M337" s="4" t="inlineStr"/>
@@ -21347,7 +21347,7 @@
       </c>
       <c r="L339" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M339" s="4" t="inlineStr">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M340" s="4" t="inlineStr"/>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="L341" s="4" t="inlineStr">
         <is>
-          <t>Shahab Ahmad Khan</t>
+          <t>SAK</t>
         </is>
       </c>
       <c r="M341" s="4" t="inlineStr"/>
@@ -21543,7 +21543,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M342" s="4" t="inlineStr">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="L343" s="4" t="inlineStr">
         <is>
-          <t>Mahmoud Saad</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="M343" s="4" t="inlineStr">
@@ -46607,7 +46607,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17/06/2026 08:08</t>
+          <t>17/06/2026 08:41</t>
         </is>
       </c>
     </row>
